--- a/data/output/topik_per_lokasi.xlsx
+++ b/data/output/topik_per_lokasi.xlsx
@@ -17,16 +17,13 @@
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <numFmts count="0"/>
-  <fonts count="2">
+  <fonts count="1">
     <font>
       <name val="Calibri"/>
       <family val="2"/>
       <color theme="1"/>
       <sz val="11"/>
       <scheme val="minor"/>
-    </font>
-    <font>
-      <b val="1"/>
     </font>
   </fonts>
   <fills count="2">
@@ -37,7 +34,7 @@
       <patternFill patternType="gray125"/>
     </fill>
   </fills>
-  <borders count="2">
+  <borders count="1">
     <border>
       <left/>
       <right/>
@@ -45,21 +42,12 @@
       <bottom/>
       <diagonal/>
     </border>
-    <border>
-      <left style="thin"/>
-      <right style="thin"/>
-      <top style="thin"/>
-      <bottom style="thin"/>
-    </border>
   </borders>
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="2">
+  <cellXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
-    <xf numFmtId="0" fontId="1" fillId="0" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment horizontal="center" vertical="top"/>
-    </xf>
   </cellXfs>
   <cellStyles count="1">
     <cellStyle name="Normal" xfId="0" builtinId="0" hidden="0"/>
@@ -429,39 +417,39 @@
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
-      <c r="A1" s="1" t="inlineStr">
+      <c r="A1" t="inlineStr">
         <is>
           <t>nama_tempat</t>
         </is>
       </c>
-      <c r="B1" s="1" t="inlineStr">
+      <c r="B1" t="inlineStr">
         <is>
           <t>Topik 0 - Tempat Ibadah</t>
         </is>
       </c>
-      <c r="C1" s="1" t="inlineStr">
+      <c r="C1" t="inlineStr">
         <is>
           <t>Topik 1 - Wisata Keluarga</t>
         </is>
       </c>
-      <c r="D1" s="1" t="inlineStr">
+      <c r="D1" t="inlineStr">
         <is>
           <t>Topik 2 - Lokasi Wisata</t>
         </is>
       </c>
-      <c r="E1" s="1" t="inlineStr">
+      <c r="E1" t="inlineStr">
         <is>
           <t>Topik 3 - Kualitas Lingkungan</t>
         </is>
       </c>
-      <c r="F1" s="1" t="inlineStr">
+      <c r="F1" t="inlineStr">
         <is>
           <t>Topik 4 - Aktivitas Ekonomi</t>
         </is>
       </c>
     </row>
     <row r="2">
-      <c r="A2" s="1" t="inlineStr">
+      <c r="A2" t="inlineStr">
         <is>
           <t>ALUN ALUN GADOBANGKONG</t>
         </is>
@@ -483,7 +471,7 @@
       </c>
     </row>
     <row r="3">
-      <c r="A3" s="1" t="inlineStr">
+      <c r="A3" t="inlineStr">
         <is>
           <t>Alun - Alun Palabuhanratu</t>
         </is>
@@ -505,7 +493,7 @@
       </c>
     </row>
     <row r="4">
-      <c r="A4" s="1" t="inlineStr">
+      <c r="A4" t="inlineStr">
         <is>
           <t>Dermaga Karang Sari Pelabuhanratu</t>
         </is>
@@ -527,7 +515,7 @@
       </c>
     </row>
     <row r="5">
-      <c r="A5" s="1" t="inlineStr">
+      <c r="A5" t="inlineStr">
         <is>
           <t>Goa Karang Pamulang</t>
         </is>
@@ -549,7 +537,7 @@
       </c>
     </row>
     <row r="6">
-      <c r="A6" s="1" t="inlineStr">
+      <c r="A6" t="inlineStr">
         <is>
           <t>Hidden Gems Pelabuhanratu</t>
         </is>
@@ -571,7 +559,7 @@
       </c>
     </row>
     <row r="7">
-      <c r="A7" s="1" t="inlineStr">
+      <c r="A7" t="inlineStr">
         <is>
           <t>Ilove Palabuhanratu</t>
         </is>
@@ -593,7 +581,7 @@
       </c>
     </row>
     <row r="8">
-      <c r="A8" s="1" t="inlineStr">
+      <c r="A8" t="inlineStr">
         <is>
           <t>Jangilus Monument</t>
         </is>
@@ -615,7 +603,7 @@
       </c>
     </row>
     <row r="9">
-      <c r="A9" s="1" t="inlineStr">
+      <c r="A9" t="inlineStr">
         <is>
           <t>Lapang Cangehgar Pelabuhanratu</t>
         </is>
@@ -637,7 +625,7 @@
       </c>
     </row>
     <row r="10">
-      <c r="A10" s="1" t="inlineStr">
+      <c r="A10" t="inlineStr">
         <is>
           <t>Muara Citepus Palabuhanratu</t>
         </is>
@@ -659,7 +647,7 @@
       </c>
     </row>
     <row r="11">
-      <c r="A11" s="1" t="inlineStr">
+      <c r="A11" t="inlineStr">
         <is>
           <t>PANTAI CIBANGBAN</t>
         </is>
@@ -681,7 +669,7 @@
       </c>
     </row>
     <row r="12">
-      <c r="A12" s="1" t="inlineStr">
+      <c r="A12" t="inlineStr">
         <is>
           <t>Pantai Batu Bintang</t>
         </is>
@@ -703,7 +691,7 @@
       </c>
     </row>
     <row r="13">
-      <c r="A13" s="1" t="inlineStr">
+      <c r="A13" t="inlineStr">
         <is>
           <t>Pantai Citepus</t>
         </is>
@@ -725,7 +713,7 @@
       </c>
     </row>
     <row r="14">
-      <c r="A14" s="1" t="inlineStr">
+      <c r="A14" t="inlineStr">
         <is>
           <t>Pantai Citepus Sukabumi</t>
         </is>
@@ -747,7 +735,7 @@
       </c>
     </row>
     <row r="15">
-      <c r="A15" s="1" t="inlineStr">
+      <c r="A15" t="inlineStr">
         <is>
           <t>Pantai Gopalo</t>
         </is>
@@ -769,7 +757,7 @@
       </c>
     </row>
     <row r="16">
-      <c r="A16" s="1" t="inlineStr">
+      <c r="A16" t="inlineStr">
         <is>
           <t>Pantai Istana Presiden Pelabuhanratu</t>
         </is>
@@ -791,7 +779,7 @@
       </c>
     </row>
     <row r="17">
-      <c r="A17" s="1" t="inlineStr">
+      <c r="A17" t="inlineStr">
         <is>
           <t>Pantai Kandita</t>
         </is>
@@ -813,7 +801,7 @@
       </c>
     </row>
     <row r="18">
-      <c r="A18" s="1" t="inlineStr">
+      <c r="A18" t="inlineStr">
         <is>
           <t>Pantai Karang Sari</t>
         </is>
@@ -835,7 +823,7 @@
       </c>
     </row>
     <row r="19">
-      <c r="A19" s="1" t="inlineStr">
+      <c r="A19" t="inlineStr">
         <is>
           <t>Pantai Pelabuhan Ratu</t>
         </is>
@@ -857,7 +845,7 @@
       </c>
     </row>
     <row r="20">
-      <c r="A20" s="1" t="inlineStr">
+      <c r="A20" t="inlineStr">
         <is>
           <t>Pantai Twenty Cipatuguran</t>
         </is>
@@ -879,7 +867,7 @@
       </c>
     </row>
     <row r="21">
-      <c r="A21" s="1" t="inlineStr">
+      <c r="A21" t="inlineStr">
         <is>
           <t>Pantai buffalo</t>
         </is>
@@ -901,7 +889,7 @@
       </c>
     </row>
     <row r="22">
-      <c r="A22" s="1" t="inlineStr">
+      <c r="A22" t="inlineStr">
         <is>
           <t>Pesanggrahan Tenjo Resmi Pelabuhan Ratu</t>
         </is>
@@ -923,7 +911,7 @@
       </c>
     </row>
     <row r="23">
-      <c r="A23" s="1" t="inlineStr">
+      <c r="A23" t="inlineStr">
         <is>
           <t>Saung Bintang Katineung, wisata pantai, air dan kuliner</t>
         </is>
@@ -945,7 +933,7 @@
       </c>
     </row>
     <row r="24">
-      <c r="A24" s="1" t="inlineStr">
+      <c r="A24" t="inlineStr">
         <is>
           <t>Situ Rawa Kalong</t>
         </is>
@@ -967,7 +955,7 @@
       </c>
     </row>
     <row r="25">
-      <c r="A25" s="1" t="inlineStr">
+      <c r="A25" t="inlineStr">
         <is>
           <t>Smile hill Pelabuhan Ratu</t>
         </is>
@@ -989,7 +977,7 @@
       </c>
     </row>
     <row r="26">
-      <c r="A26" s="1" t="inlineStr">
+      <c r="A26" t="inlineStr">
         <is>
           <t>Taman Bappeda</t>
         </is>
@@ -1011,7 +999,7 @@
       </c>
     </row>
     <row r="27">
-      <c r="A27" s="1" t="inlineStr">
+      <c r="A27" t="inlineStr">
         <is>
           <t>Taman Bunga Gunung Sumping</t>
         </is>
@@ -1033,7 +1021,7 @@
       </c>
     </row>
     <row r="28">
-      <c r="A28" s="1" t="inlineStr">
+      <c r="A28" t="inlineStr">
         <is>
           <t>Taman Bunga Pelabuhan Ratu</t>
         </is>
@@ -1055,7 +1043,7 @@
       </c>
     </row>
     <row r="29">
-      <c r="A29" s="1" t="inlineStr">
+      <c r="A29" t="inlineStr">
         <is>
           <t>Taman Citepus (Ruang Terbuka Hijau) RTH</t>
         </is>
@@ -1077,7 +1065,7 @@
       </c>
     </row>
     <row r="30">
-      <c r="A30" s="1" t="inlineStr">
+      <c r="A30" t="inlineStr">
         <is>
           <t>Taman Kota Cangehgar Palabuhanratu</t>
         </is>
@@ -1099,7 +1087,7 @@
       </c>
     </row>
     <row r="31">
-      <c r="A31" s="1" t="inlineStr">
+      <c r="A31" t="inlineStr">
         <is>
           <t>Waterpark Citepus Pelabuhanratu</t>
         </is>
@@ -1121,7 +1109,7 @@
       </c>
     </row>
     <row r="32">
-      <c r="A32" s="1" t="inlineStr">
+      <c r="A32" t="inlineStr">
         <is>
           <t>Wisata Alam Pantai Sukawayana</t>
         </is>
@@ -1143,7 +1131,7 @@
       </c>
     </row>
     <row r="33">
-      <c r="A33" s="1" t="inlineStr">
+      <c r="A33" t="inlineStr">
         <is>
           <t>i-Pe Beach Pelabuhanratu</t>
         </is>

--- a/data/output/topik_per_lokasi.xlsx
+++ b/data/output/topik_per_lokasi.xlsx
@@ -455,19 +455,19 @@
         </is>
       </c>
       <c r="B2" t="n">
-        <v>5</v>
+        <v>3</v>
       </c>
       <c r="C2" t="n">
+        <v>20</v>
+      </c>
+      <c r="D2" t="n">
+        <v>13</v>
+      </c>
+      <c r="E2" t="n">
+        <v>7</v>
+      </c>
+      <c r="F2" t="n">
         <v>4</v>
-      </c>
-      <c r="D2" t="n">
-        <v>11</v>
-      </c>
-      <c r="E2" t="n">
-        <v>17</v>
-      </c>
-      <c r="F2" t="n">
-        <v>10</v>
       </c>
     </row>
     <row r="3">
@@ -477,19 +477,19 @@
         </is>
       </c>
       <c r="B3" t="n">
-        <v>41</v>
+        <v>189</v>
       </c>
       <c r="C3" t="n">
-        <v>30</v>
+        <v>95</v>
       </c>
       <c r="D3" t="n">
-        <v>87</v>
+        <v>76</v>
       </c>
       <c r="E3" t="n">
-        <v>51</v>
+        <v>93</v>
       </c>
       <c r="F3" t="n">
-        <v>70</v>
+        <v>44</v>
       </c>
     </row>
     <row r="4">
@@ -502,13 +502,13 @@
         <v>0</v>
       </c>
       <c r="C4" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="D4" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="E4" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="F4" t="n">
         <v>0</v>
@@ -521,19 +521,19 @@
         </is>
       </c>
       <c r="B5" t="n">
-        <v>8</v>
+        <v>1</v>
       </c>
       <c r="C5" t="n">
+        <v>6</v>
+      </c>
+      <c r="D5" t="n">
+        <v>6</v>
+      </c>
+      <c r="E5" t="n">
         <v>4</v>
       </c>
-      <c r="D5" t="n">
-        <v>1</v>
-      </c>
-      <c r="E5" t="n">
-        <v>5</v>
-      </c>
       <c r="F5" t="n">
-        <v>3</v>
+        <v>4</v>
       </c>
     </row>
     <row r="6">
@@ -546,13 +546,13 @@
         <v>0</v>
       </c>
       <c r="C6" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="D6" t="n">
         <v>0</v>
       </c>
       <c r="E6" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="F6" t="n">
         <v>0</v>
@@ -565,16 +565,16 @@
         </is>
       </c>
       <c r="B7" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="C7" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="D7" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="E7" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="F7" t="n">
         <v>1</v>
@@ -587,19 +587,19 @@
         </is>
       </c>
       <c r="B8" t="n">
-        <v>22</v>
+        <v>5</v>
       </c>
       <c r="C8" t="n">
-        <v>37</v>
+        <v>49</v>
       </c>
       <c r="D8" t="n">
-        <v>79</v>
+        <v>73</v>
       </c>
       <c r="E8" t="n">
-        <v>36</v>
+        <v>41</v>
       </c>
       <c r="F8" t="n">
-        <v>23</v>
+        <v>29</v>
       </c>
     </row>
     <row r="9">
@@ -609,19 +609,19 @@
         </is>
       </c>
       <c r="B9" t="n">
-        <v>32</v>
+        <v>6</v>
       </c>
       <c r="C9" t="n">
-        <v>75</v>
+        <v>106</v>
       </c>
       <c r="D9" t="n">
-        <v>43</v>
+        <v>52</v>
       </c>
       <c r="E9" t="n">
-        <v>67</v>
+        <v>44</v>
       </c>
       <c r="F9" t="n">
-        <v>61</v>
+        <v>70</v>
       </c>
     </row>
     <row r="10">
@@ -631,19 +631,19 @@
         </is>
       </c>
       <c r="B10" t="n">
+        <v>0</v>
+      </c>
+      <c r="C10" t="n">
+        <v>6</v>
+      </c>
+      <c r="D10" t="n">
+        <v>12</v>
+      </c>
+      <c r="E10" t="n">
         <v>11</v>
       </c>
-      <c r="C10" t="n">
-        <v>5</v>
-      </c>
-      <c r="D10" t="n">
-        <v>2</v>
-      </c>
-      <c r="E10" t="n">
-        <v>13</v>
-      </c>
       <c r="F10" t="n">
-        <v>8</v>
+        <v>10</v>
       </c>
     </row>
     <row r="11">
@@ -653,19 +653,19 @@
         </is>
       </c>
       <c r="B11" t="n">
-        <v>40</v>
+        <v>5</v>
       </c>
       <c r="C11" t="n">
-        <v>35</v>
+        <v>53</v>
       </c>
       <c r="D11" t="n">
-        <v>26</v>
+        <v>46</v>
       </c>
       <c r="E11" t="n">
-        <v>88</v>
+        <v>89</v>
       </c>
       <c r="F11" t="n">
-        <v>46</v>
+        <v>42</v>
       </c>
     </row>
     <row r="12">
@@ -675,19 +675,19 @@
         </is>
       </c>
       <c r="B12" t="n">
-        <v>31</v>
+        <v>1</v>
       </c>
       <c r="C12" t="n">
-        <v>9</v>
+        <v>34</v>
       </c>
       <c r="D12" t="n">
-        <v>28</v>
+        <v>54</v>
       </c>
       <c r="E12" t="n">
-        <v>56</v>
+        <v>71</v>
       </c>
       <c r="F12" t="n">
-        <v>56</v>
+        <v>20</v>
       </c>
     </row>
     <row r="13">
@@ -697,19 +697,19 @@
         </is>
       </c>
       <c r="B13" t="n">
-        <v>17</v>
+        <v>1</v>
       </c>
       <c r="C13" t="n">
-        <v>8</v>
+        <v>26</v>
       </c>
       <c r="D13" t="n">
-        <v>29</v>
+        <v>35</v>
       </c>
       <c r="E13" t="n">
-        <v>40</v>
+        <v>83</v>
       </c>
       <c r="F13" t="n">
-        <v>66</v>
+        <v>15</v>
       </c>
     </row>
     <row r="14">
@@ -719,19 +719,19 @@
         </is>
       </c>
       <c r="B14" t="n">
-        <v>37</v>
+        <v>5</v>
       </c>
       <c r="C14" t="n">
-        <v>24</v>
+        <v>51</v>
       </c>
       <c r="D14" t="n">
-        <v>39</v>
+        <v>41</v>
       </c>
       <c r="E14" t="n">
-        <v>57</v>
+        <v>77</v>
       </c>
       <c r="F14" t="n">
-        <v>45</v>
+        <v>28</v>
       </c>
     </row>
     <row r="15">
@@ -741,19 +741,19 @@
         </is>
       </c>
       <c r="B15" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="C15" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="D15" t="n">
         <v>0</v>
       </c>
       <c r="E15" t="n">
+        <v>0</v>
+      </c>
+      <c r="F15" t="n">
         <v>2</v>
-      </c>
-      <c r="F15" t="n">
-        <v>1</v>
       </c>
     </row>
     <row r="16">
@@ -763,19 +763,19 @@
         </is>
       </c>
       <c r="B16" t="n">
-        <v>39</v>
+        <v>3</v>
       </c>
       <c r="C16" t="n">
-        <v>10</v>
+        <v>58</v>
       </c>
       <c r="D16" t="n">
-        <v>37</v>
+        <v>47</v>
       </c>
       <c r="E16" t="n">
-        <v>66</v>
+        <v>85</v>
       </c>
       <c r="F16" t="n">
-        <v>58</v>
+        <v>17</v>
       </c>
     </row>
     <row r="17">
@@ -785,7 +785,7 @@
         </is>
       </c>
       <c r="B17" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="C17" t="n">
         <v>0</v>
@@ -794,7 +794,7 @@
         <v>0</v>
       </c>
       <c r="E17" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="F17" t="n">
         <v>1</v>
@@ -807,19 +807,19 @@
         </is>
       </c>
       <c r="B18" t="n">
-        <v>33</v>
+        <v>1</v>
       </c>
       <c r="C18" t="n">
-        <v>20</v>
+        <v>25</v>
       </c>
       <c r="D18" t="n">
-        <v>21</v>
+        <v>37</v>
       </c>
       <c r="E18" t="n">
         <v>43</v>
       </c>
       <c r="F18" t="n">
-        <v>13</v>
+        <v>24</v>
       </c>
     </row>
     <row r="19">
@@ -829,19 +829,19 @@
         </is>
       </c>
       <c r="B19" t="n">
-        <v>46</v>
+        <v>3</v>
       </c>
       <c r="C19" t="n">
-        <v>25</v>
+        <v>47</v>
       </c>
       <c r="D19" t="n">
-        <v>49</v>
+        <v>70</v>
       </c>
       <c r="E19" t="n">
-        <v>67</v>
+        <v>91</v>
       </c>
       <c r="F19" t="n">
-        <v>60</v>
+        <v>36</v>
       </c>
     </row>
     <row r="20">
@@ -851,16 +851,16 @@
         </is>
       </c>
       <c r="B20" t="n">
-        <v>6</v>
+        <v>0</v>
       </c>
       <c r="C20" t="n">
+        <v>12</v>
+      </c>
+      <c r="D20" t="n">
         <v>7</v>
       </c>
-      <c r="D20" t="n">
-        <v>5</v>
-      </c>
       <c r="E20" t="n">
-        <v>8</v>
+        <v>7</v>
       </c>
       <c r="F20" t="n">
         <v>5</v>
@@ -876,16 +876,16 @@
         <v>2</v>
       </c>
       <c r="C21" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="D21" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="E21" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="F21" t="n">
-        <v>5</v>
+        <v>1</v>
       </c>
     </row>
     <row r="22">
@@ -895,19 +895,19 @@
         </is>
       </c>
       <c r="B22" t="n">
+        <v>4</v>
+      </c>
+      <c r="C22" t="n">
+        <v>51</v>
+      </c>
+      <c r="D22" t="n">
+        <v>46</v>
+      </c>
+      <c r="E22" t="n">
         <v>35</v>
       </c>
-      <c r="C22" t="n">
+      <c r="F22" t="n">
         <v>32</v>
-      </c>
-      <c r="D22" t="n">
-        <v>26</v>
-      </c>
-      <c r="E22" t="n">
-        <v>50</v>
-      </c>
-      <c r="F22" t="n">
-        <v>25</v>
       </c>
     </row>
     <row r="23">
@@ -920,16 +920,16 @@
         <v>0</v>
       </c>
       <c r="C23" t="n">
+        <v>1</v>
+      </c>
+      <c r="D23" t="n">
         <v>2</v>
       </c>
-      <c r="D23" t="n">
-        <v>1</v>
-      </c>
       <c r="E23" t="n">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="F23" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
     </row>
     <row r="24">
@@ -942,13 +942,13 @@
         <v>0</v>
       </c>
       <c r="C24" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="D24" t="n">
         <v>0</v>
       </c>
       <c r="E24" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="F24" t="n">
         <v>0</v>
@@ -961,19 +961,19 @@
         </is>
       </c>
       <c r="B25" t="n">
-        <v>11</v>
+        <v>1</v>
       </c>
       <c r="C25" t="n">
-        <v>6</v>
+        <v>16</v>
       </c>
       <c r="D25" t="n">
+        <v>15</v>
+      </c>
+      <c r="E25" t="n">
+        <v>8</v>
+      </c>
+      <c r="F25" t="n">
         <v>12</v>
-      </c>
-      <c r="E25" t="n">
-        <v>14</v>
-      </c>
-      <c r="F25" t="n">
-        <v>9</v>
       </c>
     </row>
     <row r="26">
@@ -983,19 +983,19 @@
         </is>
       </c>
       <c r="B26" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="C26" t="n">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="D26" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="E26" t="n">
-        <v>4</v>
+        <v>1</v>
       </c>
       <c r="F26" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
     </row>
     <row r="27">
@@ -1005,19 +1005,19 @@
         </is>
       </c>
       <c r="B27" t="n">
+        <v>3</v>
+      </c>
+      <c r="C27" t="n">
+        <v>35</v>
+      </c>
+      <c r="D27" t="n">
+        <v>27</v>
+      </c>
+      <c r="E27" t="n">
         <v>15</v>
       </c>
-      <c r="C27" t="n">
-        <v>23</v>
-      </c>
-      <c r="D27" t="n">
-        <v>16</v>
-      </c>
-      <c r="E27" t="n">
-        <v>33</v>
-      </c>
       <c r="F27" t="n">
-        <v>18</v>
+        <v>25</v>
       </c>
     </row>
     <row r="28">
@@ -1027,19 +1027,19 @@
         </is>
       </c>
       <c r="B28" t="n">
+        <v>0</v>
+      </c>
+      <c r="C28" t="n">
+        <v>4</v>
+      </c>
+      <c r="D28" t="n">
+        <v>4</v>
+      </c>
+      <c r="E28" t="n">
         <v>2</v>
       </c>
-      <c r="C28" t="n">
-        <v>1</v>
-      </c>
-      <c r="D28" t="n">
-        <v>1</v>
-      </c>
-      <c r="E28" t="n">
-        <v>4</v>
-      </c>
       <c r="F28" t="n">
-        <v>3</v>
+        <v>1</v>
       </c>
     </row>
     <row r="29">
@@ -1049,16 +1049,16 @@
         </is>
       </c>
       <c r="B29" t="n">
+        <v>0</v>
+      </c>
+      <c r="C29" t="n">
+        <v>5</v>
+      </c>
+      <c r="D29" t="n">
+        <v>10</v>
+      </c>
+      <c r="E29" t="n">
         <v>4</v>
-      </c>
-      <c r="C29" t="n">
-        <v>6</v>
-      </c>
-      <c r="D29" t="n">
-        <v>2</v>
-      </c>
-      <c r="E29" t="n">
-        <v>7</v>
       </c>
       <c r="F29" t="n">
         <v>3</v>
@@ -1074,7 +1074,7 @@
         <v>1</v>
       </c>
       <c r="C30" t="n">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="D30" t="n">
         <v>2</v>
@@ -1083,7 +1083,7 @@
         <v>1</v>
       </c>
       <c r="F30" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
     </row>
     <row r="31">
@@ -1093,19 +1093,19 @@
         </is>
       </c>
       <c r="B31" t="n">
-        <v>8</v>
+        <v>4</v>
       </c>
       <c r="C31" t="n">
-        <v>14</v>
+        <v>15</v>
       </c>
       <c r="D31" t="n">
-        <v>10</v>
+        <v>19</v>
       </c>
       <c r="E31" t="n">
-        <v>21</v>
+        <v>23</v>
       </c>
       <c r="F31" t="n">
-        <v>11</v>
+        <v>3</v>
       </c>
     </row>
     <row r="32">
@@ -1115,19 +1115,19 @@
         </is>
       </c>
       <c r="B32" t="n">
-        <v>25</v>
+        <v>4</v>
       </c>
       <c r="C32" t="n">
-        <v>16</v>
+        <v>47</v>
       </c>
       <c r="D32" t="n">
-        <v>11</v>
+        <v>23</v>
       </c>
       <c r="E32" t="n">
-        <v>48</v>
+        <v>37</v>
       </c>
       <c r="F32" t="n">
-        <v>30</v>
+        <v>19</v>
       </c>
     </row>
     <row r="33">
@@ -1137,19 +1137,19 @@
         </is>
       </c>
       <c r="B33" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="C33" t="n">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="D33" t="n">
-        <v>2</v>
+        <v>5</v>
       </c>
       <c r="E33" t="n">
-        <v>8</v>
+        <v>7</v>
       </c>
       <c r="F33" t="n">
-        <v>3</v>
+        <v>1</v>
       </c>
     </row>
   </sheetData>

--- a/data/output/topik_per_lokasi.xlsx
+++ b/data/output/topik_per_lokasi.xlsx
@@ -455,19 +455,19 @@
         </is>
       </c>
       <c r="B2" t="n">
-        <v>3</v>
+        <v>49</v>
       </c>
       <c r="C2" t="n">
-        <v>20</v>
+        <v>8</v>
       </c>
       <c r="D2" t="n">
-        <v>13</v>
+        <v>21</v>
       </c>
       <c r="E2" t="n">
+        <v>9</v>
+      </c>
+      <c r="F2" t="n">
         <v>7</v>
-      </c>
-      <c r="F2" t="n">
-        <v>4</v>
       </c>
     </row>
     <row r="3">
@@ -477,19 +477,19 @@
         </is>
       </c>
       <c r="B3" t="n">
-        <v>189</v>
+        <v>210</v>
       </c>
       <c r="C3" t="n">
-        <v>95</v>
+        <v>33</v>
       </c>
       <c r="D3" t="n">
-        <v>76</v>
+        <v>50</v>
       </c>
       <c r="E3" t="n">
-        <v>93</v>
+        <v>58</v>
       </c>
       <c r="F3" t="n">
-        <v>44</v>
+        <v>146</v>
       </c>
     </row>
     <row r="4">
@@ -505,13 +505,13 @@
         <v>0</v>
       </c>
       <c r="D4" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="E4" t="n">
         <v>1</v>
       </c>
       <c r="F4" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
     </row>
     <row r="5">
@@ -524,16 +524,16 @@
         <v>1</v>
       </c>
       <c r="C5" t="n">
-        <v>6</v>
+        <v>3</v>
       </c>
       <c r="D5" t="n">
-        <v>6</v>
+        <v>4</v>
       </c>
       <c r="E5" t="n">
-        <v>4</v>
+        <v>8</v>
       </c>
       <c r="F5" t="n">
-        <v>4</v>
+        <v>5</v>
       </c>
     </row>
     <row r="6">
@@ -568,10 +568,10 @@
         <v>0</v>
       </c>
       <c r="C7" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="D7" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="E7" t="n">
         <v>1</v>
@@ -590,16 +590,16 @@
         <v>5</v>
       </c>
       <c r="C8" t="n">
-        <v>49</v>
+        <v>42</v>
       </c>
       <c r="D8" t="n">
-        <v>73</v>
+        <v>37</v>
       </c>
       <c r="E8" t="n">
-        <v>41</v>
+        <v>39</v>
       </c>
       <c r="F8" t="n">
-        <v>29</v>
+        <v>74</v>
       </c>
     </row>
     <row r="9">
@@ -612,16 +612,16 @@
         <v>6</v>
       </c>
       <c r="C9" t="n">
-        <v>106</v>
+        <v>34</v>
       </c>
       <c r="D9" t="n">
-        <v>52</v>
+        <v>51</v>
       </c>
       <c r="E9" t="n">
-        <v>44</v>
+        <v>98</v>
       </c>
       <c r="F9" t="n">
-        <v>70</v>
+        <v>89</v>
       </c>
     </row>
     <row r="10">
@@ -637,13 +637,13 @@
         <v>6</v>
       </c>
       <c r="D10" t="n">
-        <v>12</v>
+        <v>16</v>
       </c>
       <c r="E10" t="n">
-        <v>11</v>
+        <v>16</v>
       </c>
       <c r="F10" t="n">
-        <v>10</v>
+        <v>1</v>
       </c>
     </row>
     <row r="11">
@@ -653,19 +653,19 @@
         </is>
       </c>
       <c r="B11" t="n">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="C11" t="n">
-        <v>53</v>
+        <v>28</v>
       </c>
       <c r="D11" t="n">
-        <v>46</v>
+        <v>98</v>
       </c>
       <c r="E11" t="n">
-        <v>89</v>
+        <v>85</v>
       </c>
       <c r="F11" t="n">
-        <v>42</v>
+        <v>18</v>
       </c>
     </row>
     <row r="12">
@@ -675,19 +675,19 @@
         </is>
       </c>
       <c r="B12" t="n">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="C12" t="n">
-        <v>34</v>
+        <v>42</v>
       </c>
       <c r="D12" t="n">
-        <v>54</v>
+        <v>73</v>
       </c>
       <c r="E12" t="n">
-        <v>71</v>
+        <v>47</v>
       </c>
       <c r="F12" t="n">
-        <v>20</v>
+        <v>15</v>
       </c>
     </row>
     <row r="13">
@@ -697,19 +697,19 @@
         </is>
       </c>
       <c r="B13" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="C13" t="n">
-        <v>26</v>
+        <v>27</v>
       </c>
       <c r="D13" t="n">
+        <v>90</v>
+      </c>
+      <c r="E13" t="n">
         <v>35</v>
       </c>
-      <c r="E13" t="n">
-        <v>83</v>
-      </c>
       <c r="F13" t="n">
-        <v>15</v>
+        <v>6</v>
       </c>
     </row>
     <row r="14">
@@ -719,19 +719,19 @@
         </is>
       </c>
       <c r="B14" t="n">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="C14" t="n">
-        <v>51</v>
+        <v>37</v>
       </c>
       <c r="D14" t="n">
-        <v>41</v>
+        <v>66</v>
       </c>
       <c r="E14" t="n">
-        <v>77</v>
+        <v>72</v>
       </c>
       <c r="F14" t="n">
-        <v>28</v>
+        <v>21</v>
       </c>
     </row>
     <row r="15">
@@ -744,16 +744,16 @@
         <v>0</v>
       </c>
       <c r="C15" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="D15" t="n">
-        <v>0</v>
+        <v>3</v>
       </c>
       <c r="E15" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="F15" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
     </row>
     <row r="16">
@@ -763,19 +763,19 @@
         </is>
       </c>
       <c r="B16" t="n">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="C16" t="n">
-        <v>58</v>
+        <v>37</v>
       </c>
       <c r="D16" t="n">
-        <v>47</v>
+        <v>118</v>
       </c>
       <c r="E16" t="n">
-        <v>85</v>
+        <v>37</v>
       </c>
       <c r="F16" t="n">
-        <v>17</v>
+        <v>14</v>
       </c>
     </row>
     <row r="17">
@@ -791,13 +791,13 @@
         <v>0</v>
       </c>
       <c r="D17" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="E17" t="n">
         <v>1</v>
       </c>
       <c r="F17" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
     </row>
     <row r="18">
@@ -807,19 +807,19 @@
         </is>
       </c>
       <c r="B18" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="C18" t="n">
-        <v>25</v>
+        <v>18</v>
       </c>
       <c r="D18" t="n">
-        <v>37</v>
+        <v>43</v>
       </c>
       <c r="E18" t="n">
-        <v>43</v>
+        <v>57</v>
       </c>
       <c r="F18" t="n">
-        <v>24</v>
+        <v>10</v>
       </c>
     </row>
     <row r="19">
@@ -829,19 +829,19 @@
         </is>
       </c>
       <c r="B19" t="n">
-        <v>3</v>
+        <v>5</v>
       </c>
       <c r="C19" t="n">
-        <v>47</v>
+        <v>35</v>
       </c>
       <c r="D19" t="n">
-        <v>70</v>
+        <v>89</v>
       </c>
       <c r="E19" t="n">
-        <v>91</v>
+        <v>101</v>
       </c>
       <c r="F19" t="n">
-        <v>36</v>
+        <v>17</v>
       </c>
     </row>
     <row r="20">
@@ -851,16 +851,16 @@
         </is>
       </c>
       <c r="B20" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="C20" t="n">
-        <v>12</v>
+        <v>3</v>
       </c>
       <c r="D20" t="n">
-        <v>7</v>
+        <v>11</v>
       </c>
       <c r="E20" t="n">
-        <v>7</v>
+        <v>11</v>
       </c>
       <c r="F20" t="n">
         <v>5</v>
@@ -873,7 +873,7 @@
         </is>
       </c>
       <c r="B21" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="C21" t="n">
         <v>1</v>
@@ -882,7 +882,7 @@
         <v>2</v>
       </c>
       <c r="E21" t="n">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="F21" t="n">
         <v>1</v>
@@ -895,19 +895,19 @@
         </is>
       </c>
       <c r="B22" t="n">
-        <v>4</v>
+        <v>7</v>
       </c>
       <c r="C22" t="n">
-        <v>51</v>
+        <v>29</v>
       </c>
       <c r="D22" t="n">
-        <v>46</v>
+        <v>54</v>
       </c>
       <c r="E22" t="n">
-        <v>35</v>
+        <v>60</v>
       </c>
       <c r="F22" t="n">
-        <v>32</v>
+        <v>18</v>
       </c>
     </row>
     <row r="23">
@@ -920,16 +920,16 @@
         <v>0</v>
       </c>
       <c r="C23" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="D23" t="n">
         <v>2</v>
       </c>
       <c r="E23" t="n">
+        <v>1</v>
+      </c>
+      <c r="F23" t="n">
         <v>3</v>
-      </c>
-      <c r="F23" t="n">
-        <v>0</v>
       </c>
     </row>
     <row r="24">
@@ -964,16 +964,16 @@
         <v>1</v>
       </c>
       <c r="C25" t="n">
-        <v>16</v>
+        <v>13</v>
       </c>
       <c r="D25" t="n">
-        <v>15</v>
+        <v>18</v>
       </c>
       <c r="E25" t="n">
-        <v>8</v>
+        <v>14</v>
       </c>
       <c r="F25" t="n">
-        <v>12</v>
+        <v>6</v>
       </c>
     </row>
     <row r="26">
@@ -986,16 +986,16 @@
         <v>0</v>
       </c>
       <c r="C26" t="n">
+        <v>0</v>
+      </c>
+      <c r="D26" t="n">
+        <v>1</v>
+      </c>
+      <c r="E26" t="n">
+        <v>4</v>
+      </c>
+      <c r="F26" t="n">
         <v>3</v>
-      </c>
-      <c r="D26" t="n">
-        <v>2</v>
-      </c>
-      <c r="E26" t="n">
-        <v>1</v>
-      </c>
-      <c r="F26" t="n">
-        <v>2</v>
       </c>
     </row>
     <row r="27">
@@ -1005,19 +1005,19 @@
         </is>
       </c>
       <c r="B27" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="C27" t="n">
-        <v>35</v>
+        <v>11</v>
       </c>
       <c r="D27" t="n">
-        <v>27</v>
+        <v>24</v>
       </c>
       <c r="E27" t="n">
-        <v>15</v>
+        <v>51</v>
       </c>
       <c r="F27" t="n">
-        <v>25</v>
+        <v>17</v>
       </c>
     </row>
     <row r="28">
@@ -1030,16 +1030,16 @@
         <v>0</v>
       </c>
       <c r="C28" t="n">
+        <v>1</v>
+      </c>
+      <c r="D28" t="n">
+        <v>3</v>
+      </c>
+      <c r="E28" t="n">
+        <v>3</v>
+      </c>
+      <c r="F28" t="n">
         <v>4</v>
-      </c>
-      <c r="D28" t="n">
-        <v>4</v>
-      </c>
-      <c r="E28" t="n">
-        <v>2</v>
-      </c>
-      <c r="F28" t="n">
-        <v>1</v>
       </c>
     </row>
     <row r="29">
@@ -1052,16 +1052,16 @@
         <v>0</v>
       </c>
       <c r="C29" t="n">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="D29" t="n">
-        <v>10</v>
+        <v>9</v>
       </c>
       <c r="E29" t="n">
-        <v>4</v>
+        <v>7</v>
       </c>
       <c r="F29" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
     </row>
     <row r="30">
@@ -1074,16 +1074,16 @@
         <v>1</v>
       </c>
       <c r="C30" t="n">
+        <v>1</v>
+      </c>
+      <c r="D30" t="n">
+        <v>0</v>
+      </c>
+      <c r="E30" t="n">
+        <v>2</v>
+      </c>
+      <c r="F30" t="n">
         <v>3</v>
-      </c>
-      <c r="D30" t="n">
-        <v>2</v>
-      </c>
-      <c r="E30" t="n">
-        <v>1</v>
-      </c>
-      <c r="F30" t="n">
-        <v>0</v>
       </c>
     </row>
     <row r="31">
@@ -1093,19 +1093,19 @@
         </is>
       </c>
       <c r="B31" t="n">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="C31" t="n">
-        <v>15</v>
+        <v>13</v>
       </c>
       <c r="D31" t="n">
-        <v>19</v>
+        <v>20</v>
       </c>
       <c r="E31" t="n">
-        <v>23</v>
+        <v>21</v>
       </c>
       <c r="F31" t="n">
-        <v>3</v>
+        <v>5</v>
       </c>
     </row>
     <row r="32">
@@ -1115,19 +1115,19 @@
         </is>
       </c>
       <c r="B32" t="n">
-        <v>4</v>
+        <v>7</v>
       </c>
       <c r="C32" t="n">
-        <v>47</v>
+        <v>17</v>
       </c>
       <c r="D32" t="n">
-        <v>23</v>
+        <v>56</v>
       </c>
       <c r="E32" t="n">
-        <v>37</v>
+        <v>42</v>
       </c>
       <c r="F32" t="n">
-        <v>19</v>
+        <v>8</v>
       </c>
     </row>
     <row r="33">
@@ -1143,10 +1143,10 @@
         <v>3</v>
       </c>
       <c r="D33" t="n">
-        <v>5</v>
+        <v>9</v>
       </c>
       <c r="E33" t="n">
-        <v>7</v>
+        <v>3</v>
       </c>
       <c r="F33" t="n">
         <v>1</v>

--- a/data/output/topik_per_lokasi.xlsx
+++ b/data/output/topik_per_lokasi.xlsx
@@ -455,19 +455,19 @@
         </is>
       </c>
       <c r="B2" t="n">
-        <v>49</v>
+        <v>48</v>
       </c>
       <c r="C2" t="n">
-        <v>8</v>
+        <v>14</v>
       </c>
       <c r="D2" t="n">
-        <v>21</v>
+        <v>15</v>
       </c>
       <c r="E2" t="n">
-        <v>9</v>
+        <v>6</v>
       </c>
       <c r="F2" t="n">
-        <v>7</v>
+        <v>11</v>
       </c>
     </row>
     <row r="3">
@@ -477,19 +477,19 @@
         </is>
       </c>
       <c r="B3" t="n">
-        <v>210</v>
+        <v>203</v>
       </c>
       <c r="C3" t="n">
-        <v>33</v>
+        <v>89</v>
       </c>
       <c r="D3" t="n">
-        <v>50</v>
+        <v>118</v>
       </c>
       <c r="E3" t="n">
-        <v>58</v>
+        <v>28</v>
       </c>
       <c r="F3" t="n">
-        <v>146</v>
+        <v>59</v>
       </c>
     </row>
     <row r="4">
@@ -508,10 +508,10 @@
         <v>0</v>
       </c>
       <c r="E4" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="F4" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
     </row>
     <row r="5">
@@ -524,16 +524,16 @@
         <v>1</v>
       </c>
       <c r="C5" t="n">
-        <v>3</v>
+        <v>9</v>
       </c>
       <c r="D5" t="n">
         <v>4</v>
       </c>
       <c r="E5" t="n">
-        <v>8</v>
+        <v>5</v>
       </c>
       <c r="F5" t="n">
-        <v>5</v>
+        <v>2</v>
       </c>
     </row>
     <row r="6">
@@ -552,10 +552,10 @@
         <v>0</v>
       </c>
       <c r="E6" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="F6" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
     </row>
     <row r="7">
@@ -568,13 +568,13 @@
         <v>0</v>
       </c>
       <c r="C7" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="D7" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="E7" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="F7" t="n">
         <v>1</v>
@@ -587,19 +587,19 @@
         </is>
       </c>
       <c r="B8" t="n">
-        <v>5</v>
+        <v>7</v>
       </c>
       <c r="C8" t="n">
+        <v>96</v>
+      </c>
+      <c r="D8" t="n">
+        <v>29</v>
+      </c>
+      <c r="E8" t="n">
+        <v>23</v>
+      </c>
+      <c r="F8" t="n">
         <v>42</v>
-      </c>
-      <c r="D8" t="n">
-        <v>37</v>
-      </c>
-      <c r="E8" t="n">
-        <v>39</v>
-      </c>
-      <c r="F8" t="n">
-        <v>74</v>
       </c>
     </row>
     <row r="9">
@@ -609,19 +609,19 @@
         </is>
       </c>
       <c r="B9" t="n">
-        <v>6</v>
+        <v>245</v>
       </c>
       <c r="C9" t="n">
-        <v>34</v>
+        <v>76</v>
       </c>
       <c r="D9" t="n">
-        <v>51</v>
+        <v>105</v>
       </c>
       <c r="E9" t="n">
-        <v>98</v>
+        <v>49</v>
       </c>
       <c r="F9" t="n">
-        <v>89</v>
+        <v>45</v>
       </c>
     </row>
     <row r="10">
@@ -631,19 +631,19 @@
         </is>
       </c>
       <c r="B10" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="C10" t="n">
+        <v>10</v>
+      </c>
+      <c r="D10" t="n">
+        <v>15</v>
+      </c>
+      <c r="E10" t="n">
+        <v>7</v>
+      </c>
+      <c r="F10" t="n">
         <v>6</v>
-      </c>
-      <c r="D10" t="n">
-        <v>16</v>
-      </c>
-      <c r="E10" t="n">
-        <v>16</v>
-      </c>
-      <c r="F10" t="n">
-        <v>1</v>
       </c>
     </row>
     <row r="11">
@@ -653,19 +653,19 @@
         </is>
       </c>
       <c r="B11" t="n">
-        <v>6</v>
+        <v>8</v>
       </c>
       <c r="C11" t="n">
-        <v>28</v>
+        <v>89</v>
       </c>
       <c r="D11" t="n">
         <v>98</v>
       </c>
       <c r="E11" t="n">
-        <v>85</v>
+        <v>17</v>
       </c>
       <c r="F11" t="n">
-        <v>18</v>
+        <v>23</v>
       </c>
     </row>
     <row r="12">
@@ -675,19 +675,19 @@
         </is>
       </c>
       <c r="B12" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="C12" t="n">
-        <v>42</v>
+        <v>61</v>
       </c>
       <c r="D12" t="n">
-        <v>73</v>
+        <v>90</v>
       </c>
       <c r="E12" t="n">
-        <v>47</v>
+        <v>9</v>
       </c>
       <c r="F12" t="n">
-        <v>15</v>
+        <v>18</v>
       </c>
     </row>
     <row r="13">
@@ -697,19 +697,19 @@
         </is>
       </c>
       <c r="B13" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="C13" t="n">
-        <v>27</v>
+        <v>49</v>
       </c>
       <c r="D13" t="n">
-        <v>90</v>
+        <v>100</v>
       </c>
       <c r="E13" t="n">
-        <v>35</v>
+        <v>6</v>
       </c>
       <c r="F13" t="n">
-        <v>6</v>
+        <v>5</v>
       </c>
     </row>
     <row r="14">
@@ -719,19 +719,19 @@
         </is>
       </c>
       <c r="B14" t="n">
-        <v>6</v>
+        <v>1</v>
       </c>
       <c r="C14" t="n">
-        <v>37</v>
+        <v>77</v>
       </c>
       <c r="D14" t="n">
-        <v>66</v>
+        <v>81</v>
       </c>
       <c r="E14" t="n">
-        <v>72</v>
+        <v>18</v>
       </c>
       <c r="F14" t="n">
-        <v>21</v>
+        <v>25</v>
       </c>
     </row>
     <row r="15">
@@ -744,10 +744,10 @@
         <v>0</v>
       </c>
       <c r="C15" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="D15" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="E15" t="n">
         <v>1</v>
@@ -763,19 +763,19 @@
         </is>
       </c>
       <c r="B16" t="n">
-        <v>4</v>
+        <v>2</v>
       </c>
       <c r="C16" t="n">
-        <v>37</v>
+        <v>61</v>
       </c>
       <c r="D16" t="n">
-        <v>118</v>
+        <v>110</v>
       </c>
       <c r="E16" t="n">
-        <v>37</v>
+        <v>19</v>
       </c>
       <c r="F16" t="n">
-        <v>14</v>
+        <v>18</v>
       </c>
     </row>
     <row r="17">
@@ -788,13 +788,13 @@
         <v>0</v>
       </c>
       <c r="C17" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="D17" t="n">
         <v>1</v>
       </c>
       <c r="E17" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="F17" t="n">
         <v>0</v>
@@ -807,19 +807,19 @@
         </is>
       </c>
       <c r="B18" t="n">
-        <v>2</v>
+        <v>119</v>
       </c>
       <c r="C18" t="n">
-        <v>18</v>
+        <v>52</v>
       </c>
       <c r="D18" t="n">
-        <v>43</v>
+        <v>36</v>
       </c>
       <c r="E18" t="n">
-        <v>57</v>
+        <v>17</v>
       </c>
       <c r="F18" t="n">
-        <v>10</v>
+        <v>29</v>
       </c>
     </row>
     <row r="19">
@@ -829,19 +829,19 @@
         </is>
       </c>
       <c r="B19" t="n">
-        <v>5</v>
+        <v>206</v>
       </c>
       <c r="C19" t="n">
-        <v>35</v>
+        <v>101</v>
       </c>
       <c r="D19" t="n">
-        <v>89</v>
+        <v>98</v>
       </c>
       <c r="E19" t="n">
-        <v>101</v>
+        <v>26</v>
       </c>
       <c r="F19" t="n">
-        <v>17</v>
+        <v>26</v>
       </c>
     </row>
     <row r="20">
@@ -851,16 +851,16 @@
         </is>
       </c>
       <c r="B20" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="C20" t="n">
+        <v>10</v>
+      </c>
+      <c r="D20" t="n">
+        <v>13</v>
+      </c>
+      <c r="E20" t="n">
         <v>3</v>
-      </c>
-      <c r="D20" t="n">
-        <v>11</v>
-      </c>
-      <c r="E20" t="n">
-        <v>11</v>
       </c>
       <c r="F20" t="n">
         <v>5</v>
@@ -876,16 +876,16 @@
         <v>0</v>
       </c>
       <c r="C21" t="n">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="D21" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="E21" t="n">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="F21" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
     </row>
     <row r="22">
@@ -895,19 +895,19 @@
         </is>
       </c>
       <c r="B22" t="n">
-        <v>7</v>
+        <v>5</v>
       </c>
       <c r="C22" t="n">
-        <v>29</v>
+        <v>90</v>
       </c>
       <c r="D22" t="n">
-        <v>54</v>
+        <v>24</v>
       </c>
       <c r="E22" t="n">
-        <v>60</v>
+        <v>13</v>
       </c>
       <c r="F22" t="n">
-        <v>18</v>
+        <v>36</v>
       </c>
     </row>
     <row r="23">
@@ -920,7 +920,7 @@
         <v>0</v>
       </c>
       <c r="C23" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="D23" t="n">
         <v>2</v>
@@ -929,7 +929,7 @@
         <v>1</v>
       </c>
       <c r="F23" t="n">
-        <v>3</v>
+        <v>1</v>
       </c>
     </row>
     <row r="24">
@@ -939,19 +939,19 @@
         </is>
       </c>
       <c r="B24" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="C24" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="D24" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="E24" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="F24" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
     </row>
     <row r="25">
@@ -961,19 +961,19 @@
         </is>
       </c>
       <c r="B25" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="C25" t="n">
-        <v>13</v>
+        <v>31</v>
       </c>
       <c r="D25" t="n">
-        <v>18</v>
+        <v>6</v>
       </c>
       <c r="E25" t="n">
-        <v>14</v>
+        <v>6</v>
       </c>
       <c r="F25" t="n">
-        <v>6</v>
+        <v>9</v>
       </c>
     </row>
     <row r="26">
@@ -986,16 +986,16 @@
         <v>0</v>
       </c>
       <c r="C26" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="D26" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="E26" t="n">
+        <v>0</v>
+      </c>
+      <c r="F26" t="n">
         <v>4</v>
-      </c>
-      <c r="F26" t="n">
-        <v>3</v>
       </c>
     </row>
     <row r="27">
@@ -1005,19 +1005,19 @@
         </is>
       </c>
       <c r="B27" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="C27" t="n">
+        <v>49</v>
+      </c>
+      <c r="D27" t="n">
+        <v>23</v>
+      </c>
+      <c r="E27" t="n">
         <v>11</v>
       </c>
-      <c r="D27" t="n">
-        <v>24</v>
-      </c>
-      <c r="E27" t="n">
-        <v>51</v>
-      </c>
       <c r="F27" t="n">
-        <v>17</v>
+        <v>21</v>
       </c>
     </row>
     <row r="28">
@@ -1030,13 +1030,13 @@
         <v>0</v>
       </c>
       <c r="C28" t="n">
-        <v>1</v>
+        <v>4</v>
       </c>
       <c r="D28" t="n">
         <v>3</v>
       </c>
       <c r="E28" t="n">
-        <v>3</v>
+        <v>0</v>
       </c>
       <c r="F28" t="n">
         <v>4</v>
@@ -1049,19 +1049,19 @@
         </is>
       </c>
       <c r="B29" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="C29" t="n">
-        <v>4</v>
+        <v>8</v>
       </c>
       <c r="D29" t="n">
-        <v>9</v>
+        <v>12</v>
       </c>
       <c r="E29" t="n">
-        <v>7</v>
+        <v>1</v>
       </c>
       <c r="F29" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
     </row>
     <row r="30">
@@ -1077,10 +1077,10 @@
         <v>1</v>
       </c>
       <c r="D30" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="E30" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="F30" t="n">
         <v>3</v>
@@ -1093,19 +1093,19 @@
         </is>
       </c>
       <c r="B31" t="n">
-        <v>5</v>
+        <v>2</v>
       </c>
       <c r="C31" t="n">
-        <v>13</v>
+        <v>15</v>
       </c>
       <c r="D31" t="n">
-        <v>20</v>
+        <v>28</v>
       </c>
       <c r="E31" t="n">
-        <v>21</v>
+        <v>9</v>
       </c>
       <c r="F31" t="n">
-        <v>5</v>
+        <v>10</v>
       </c>
     </row>
     <row r="32">
@@ -1115,19 +1115,19 @@
         </is>
       </c>
       <c r="B32" t="n">
-        <v>7</v>
+        <v>1</v>
       </c>
       <c r="C32" t="n">
-        <v>17</v>
+        <v>53</v>
       </c>
       <c r="D32" t="n">
-        <v>56</v>
+        <v>50</v>
       </c>
       <c r="E32" t="n">
-        <v>42</v>
+        <v>14</v>
       </c>
       <c r="F32" t="n">
-        <v>8</v>
+        <v>12</v>
       </c>
     </row>
     <row r="33">
@@ -1137,19 +1137,19 @@
         </is>
       </c>
       <c r="B33" t="n">
-        <v>0</v>
+        <v>15</v>
       </c>
       <c r="C33" t="n">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="D33" t="n">
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="E33" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="F33" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
     </row>
   </sheetData>

--- a/data/output/topik_per_lokasi.xlsx
+++ b/data/output/topik_per_lokasi.xlsx
@@ -455,19 +455,19 @@
         </is>
       </c>
       <c r="B2" t="n">
-        <v>48</v>
+        <v>49</v>
       </c>
       <c r="C2" t="n">
-        <v>14</v>
+        <v>11</v>
       </c>
       <c r="D2" t="n">
-        <v>15</v>
+        <v>17</v>
       </c>
       <c r="E2" t="n">
-        <v>6</v>
+        <v>9</v>
       </c>
       <c r="F2" t="n">
-        <v>11</v>
+        <v>8</v>
       </c>
     </row>
     <row r="3">
@@ -477,19 +477,19 @@
         </is>
       </c>
       <c r="B3" t="n">
-        <v>203</v>
+        <v>208</v>
       </c>
       <c r="C3" t="n">
-        <v>89</v>
+        <v>38</v>
       </c>
       <c r="D3" t="n">
-        <v>118</v>
+        <v>62</v>
       </c>
       <c r="E3" t="n">
-        <v>28</v>
+        <v>70</v>
       </c>
       <c r="F3" t="n">
-        <v>59</v>
+        <v>119</v>
       </c>
     </row>
     <row r="4">
@@ -505,13 +505,13 @@
         <v>0</v>
       </c>
       <c r="D4" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="E4" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="F4" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
     </row>
     <row r="5">
@@ -521,19 +521,19 @@
         </is>
       </c>
       <c r="B5" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="C5" t="n">
-        <v>9</v>
+        <v>8</v>
       </c>
       <c r="D5" t="n">
-        <v>4</v>
+        <v>2</v>
       </c>
       <c r="E5" t="n">
-        <v>5</v>
+        <v>1</v>
       </c>
       <c r="F5" t="n">
-        <v>2</v>
+        <v>8</v>
       </c>
     </row>
     <row r="6">
@@ -549,13 +549,13 @@
         <v>0</v>
       </c>
       <c r="D6" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="E6" t="n">
         <v>0</v>
       </c>
       <c r="F6" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
     </row>
     <row r="7">
@@ -568,16 +568,16 @@
         <v>0</v>
       </c>
       <c r="C7" t="n">
+        <v>1</v>
+      </c>
+      <c r="D7" t="n">
+        <v>0</v>
+      </c>
+      <c r="E7" t="n">
+        <v>0</v>
+      </c>
+      <c r="F7" t="n">
         <v>2</v>
-      </c>
-      <c r="D7" t="n">
-        <v>0</v>
-      </c>
-      <c r="E7" t="n">
-        <v>0</v>
-      </c>
-      <c r="F7" t="n">
-        <v>1</v>
       </c>
     </row>
     <row r="8">
@@ -587,19 +587,19 @@
         </is>
       </c>
       <c r="B8" t="n">
-        <v>7</v>
+        <v>1</v>
       </c>
       <c r="C8" t="n">
-        <v>96</v>
+        <v>59</v>
       </c>
       <c r="D8" t="n">
-        <v>29</v>
+        <v>39</v>
       </c>
       <c r="E8" t="n">
-        <v>23</v>
+        <v>31</v>
       </c>
       <c r="F8" t="n">
-        <v>42</v>
+        <v>67</v>
       </c>
     </row>
     <row r="9">
@@ -609,19 +609,19 @@
         </is>
       </c>
       <c r="B9" t="n">
-        <v>245</v>
+        <v>246</v>
       </c>
       <c r="C9" t="n">
-        <v>76</v>
+        <v>51</v>
       </c>
       <c r="D9" t="n">
+        <v>57</v>
+      </c>
+      <c r="E9" t="n">
         <v>105</v>
       </c>
-      <c r="E9" t="n">
-        <v>49</v>
-      </c>
       <c r="F9" t="n">
-        <v>45</v>
+        <v>61</v>
       </c>
     </row>
     <row r="10">
@@ -631,19 +631,19 @@
         </is>
       </c>
       <c r="B10" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="C10" t="n">
+        <v>15</v>
+      </c>
+      <c r="D10" t="n">
         <v>10</v>
       </c>
-      <c r="D10" t="n">
-        <v>15</v>
-      </c>
       <c r="E10" t="n">
-        <v>7</v>
+        <v>3</v>
       </c>
       <c r="F10" t="n">
-        <v>6</v>
+        <v>11</v>
       </c>
     </row>
     <row r="11">
@@ -653,19 +653,19 @@
         </is>
       </c>
       <c r="B11" t="n">
-        <v>8</v>
+        <v>6</v>
       </c>
       <c r="C11" t="n">
-        <v>89</v>
+        <v>42</v>
       </c>
       <c r="D11" t="n">
-        <v>98</v>
+        <v>103</v>
       </c>
       <c r="E11" t="n">
-        <v>17</v>
+        <v>34</v>
       </c>
       <c r="F11" t="n">
-        <v>23</v>
+        <v>50</v>
       </c>
     </row>
     <row r="12">
@@ -678,16 +678,16 @@
         <v>2</v>
       </c>
       <c r="C12" t="n">
-        <v>61</v>
+        <v>23</v>
       </c>
       <c r="D12" t="n">
-        <v>90</v>
+        <v>94</v>
       </c>
       <c r="E12" t="n">
-        <v>9</v>
+        <v>20</v>
       </c>
       <c r="F12" t="n">
-        <v>18</v>
+        <v>41</v>
       </c>
     </row>
     <row r="13">
@@ -697,19 +697,19 @@
         </is>
       </c>
       <c r="B13" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="C13" t="n">
-        <v>49</v>
+        <v>18</v>
       </c>
       <c r="D13" t="n">
-        <v>100</v>
+        <v>87</v>
       </c>
       <c r="E13" t="n">
-        <v>6</v>
+        <v>16</v>
       </c>
       <c r="F13" t="n">
-        <v>5</v>
+        <v>38</v>
       </c>
     </row>
     <row r="14">
@@ -719,19 +719,19 @@
         </is>
       </c>
       <c r="B14" t="n">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="C14" t="n">
-        <v>77</v>
+        <v>50</v>
       </c>
       <c r="D14" t="n">
-        <v>81</v>
+        <v>70</v>
       </c>
       <c r="E14" t="n">
-        <v>18</v>
+        <v>32</v>
       </c>
       <c r="F14" t="n">
-        <v>25</v>
+        <v>47</v>
       </c>
     </row>
     <row r="15">
@@ -750,10 +750,10 @@
         <v>2</v>
       </c>
       <c r="E15" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="F15" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
     </row>
     <row r="16">
@@ -763,19 +763,19 @@
         </is>
       </c>
       <c r="B16" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="C16" t="n">
-        <v>61</v>
+        <v>37</v>
       </c>
       <c r="D16" t="n">
-        <v>110</v>
+        <v>109</v>
       </c>
       <c r="E16" t="n">
-        <v>19</v>
+        <v>29</v>
       </c>
       <c r="F16" t="n">
-        <v>18</v>
+        <v>35</v>
       </c>
     </row>
     <row r="17">
@@ -807,19 +807,19 @@
         </is>
       </c>
       <c r="B18" t="n">
-        <v>119</v>
+        <v>120</v>
       </c>
       <c r="C18" t="n">
-        <v>52</v>
+        <v>38</v>
       </c>
       <c r="D18" t="n">
-        <v>36</v>
+        <v>42</v>
       </c>
       <c r="E18" t="n">
-        <v>17</v>
+        <v>14</v>
       </c>
       <c r="F18" t="n">
-        <v>29</v>
+        <v>39</v>
       </c>
     </row>
     <row r="19">
@@ -829,19 +829,19 @@
         </is>
       </c>
       <c r="B19" t="n">
-        <v>206</v>
+        <v>215</v>
       </c>
       <c r="C19" t="n">
-        <v>101</v>
+        <v>60</v>
       </c>
       <c r="D19" t="n">
-        <v>98</v>
+        <v>84</v>
       </c>
       <c r="E19" t="n">
-        <v>26</v>
+        <v>39</v>
       </c>
       <c r="F19" t="n">
-        <v>26</v>
+        <v>70</v>
       </c>
     </row>
     <row r="20">
@@ -854,16 +854,16 @@
         <v>0</v>
       </c>
       <c r="C20" t="n">
-        <v>10</v>
+        <v>8</v>
       </c>
       <c r="D20" t="n">
-        <v>13</v>
+        <v>9</v>
       </c>
       <c r="E20" t="n">
-        <v>3</v>
+        <v>8</v>
       </c>
       <c r="F20" t="n">
-        <v>5</v>
+        <v>6</v>
       </c>
     </row>
     <row r="21">
@@ -873,19 +873,19 @@
         </is>
       </c>
       <c r="B21" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="C21" t="n">
-        <v>3</v>
+        <v>0</v>
       </c>
       <c r="D21" t="n">
         <v>3</v>
       </c>
       <c r="E21" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="F21" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
     </row>
     <row r="22">
@@ -898,16 +898,16 @@
         <v>5</v>
       </c>
       <c r="C22" t="n">
-        <v>90</v>
+        <v>45</v>
       </c>
       <c r="D22" t="n">
-        <v>24</v>
+        <v>36</v>
       </c>
       <c r="E22" t="n">
-        <v>13</v>
+        <v>37</v>
       </c>
       <c r="F22" t="n">
-        <v>36</v>
+        <v>45</v>
       </c>
     </row>
     <row r="23">
@@ -920,13 +920,13 @@
         <v>0</v>
       </c>
       <c r="C23" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="D23" t="n">
-        <v>2</v>
+        <v>5</v>
       </c>
       <c r="E23" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="F23" t="n">
         <v>1</v>
@@ -948,10 +948,10 @@
         <v>1</v>
       </c>
       <c r="E24" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="F24" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
     </row>
     <row r="25">
@@ -964,16 +964,16 @@
         <v>0</v>
       </c>
       <c r="C25" t="n">
-        <v>31</v>
+        <v>20</v>
       </c>
       <c r="D25" t="n">
-        <v>6</v>
+        <v>10</v>
       </c>
       <c r="E25" t="n">
-        <v>6</v>
+        <v>9</v>
       </c>
       <c r="F25" t="n">
-        <v>9</v>
+        <v>13</v>
       </c>
     </row>
     <row r="26">
@@ -986,16 +986,16 @@
         <v>0</v>
       </c>
       <c r="C26" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="D26" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="E26" t="n">
-        <v>0</v>
+        <v>4</v>
       </c>
       <c r="F26" t="n">
-        <v>4</v>
+        <v>1</v>
       </c>
     </row>
     <row r="27">
@@ -1005,19 +1005,19 @@
         </is>
       </c>
       <c r="B27" t="n">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="C27" t="n">
-        <v>49</v>
+        <v>37</v>
       </c>
       <c r="D27" t="n">
-        <v>23</v>
+        <v>19</v>
       </c>
       <c r="E27" t="n">
-        <v>11</v>
+        <v>16</v>
       </c>
       <c r="F27" t="n">
-        <v>21</v>
+        <v>30</v>
       </c>
     </row>
     <row r="28">
@@ -1033,10 +1033,10 @@
         <v>4</v>
       </c>
       <c r="D28" t="n">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="E28" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="F28" t="n">
         <v>4</v>
@@ -1052,16 +1052,16 @@
         <v>1</v>
       </c>
       <c r="C29" t="n">
-        <v>8</v>
+        <v>6</v>
       </c>
       <c r="D29" t="n">
+        <v>3</v>
+      </c>
+      <c r="E29" t="n">
+        <v>0</v>
+      </c>
+      <c r="F29" t="n">
         <v>12</v>
-      </c>
-      <c r="E29" t="n">
-        <v>1</v>
-      </c>
-      <c r="F29" t="n">
-        <v>0</v>
       </c>
     </row>
     <row r="30">
@@ -1074,16 +1074,16 @@
         <v>1</v>
       </c>
       <c r="C30" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="D30" t="n">
         <v>2</v>
       </c>
       <c r="E30" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="F30" t="n">
-        <v>3</v>
+        <v>1</v>
       </c>
     </row>
     <row r="31">
@@ -1093,19 +1093,19 @@
         </is>
       </c>
       <c r="B31" t="n">
-        <v>2</v>
+        <v>4</v>
       </c>
       <c r="C31" t="n">
-        <v>15</v>
+        <v>12</v>
       </c>
       <c r="D31" t="n">
-        <v>28</v>
+        <v>25</v>
       </c>
       <c r="E31" t="n">
-        <v>9</v>
+        <v>16</v>
       </c>
       <c r="F31" t="n">
-        <v>10</v>
+        <v>7</v>
       </c>
     </row>
     <row r="32">
@@ -1118,16 +1118,16 @@
         <v>1</v>
       </c>
       <c r="C32" t="n">
-        <v>53</v>
+        <v>39</v>
       </c>
       <c r="D32" t="n">
-        <v>50</v>
+        <v>51</v>
       </c>
       <c r="E32" t="n">
         <v>14</v>
       </c>
       <c r="F32" t="n">
-        <v>12</v>
+        <v>25</v>
       </c>
     </row>
     <row r="33">
@@ -1140,16 +1140,16 @@
         <v>15</v>
       </c>
       <c r="C33" t="n">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="D33" t="n">
-        <v>10</v>
+        <v>9</v>
       </c>
       <c r="E33" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="F33" t="n">
-        <v>0</v>
+        <v>3</v>
       </c>
     </row>
   </sheetData>

--- a/data/output/topik_per_lokasi.xlsx
+++ b/data/output/topik_per_lokasi.xlsx
@@ -455,16 +455,16 @@
         </is>
       </c>
       <c r="B2" t="n">
-        <v>49</v>
+        <v>45</v>
       </c>
       <c r="C2" t="n">
         <v>11</v>
       </c>
       <c r="D2" t="n">
-        <v>17</v>
+        <v>12</v>
       </c>
       <c r="E2" t="n">
-        <v>9</v>
+        <v>18</v>
       </c>
       <c r="F2" t="n">
         <v>8</v>
@@ -477,19 +477,19 @@
         </is>
       </c>
       <c r="B3" t="n">
-        <v>208</v>
+        <v>202</v>
       </c>
       <c r="C3" t="n">
-        <v>38</v>
+        <v>48</v>
       </c>
       <c r="D3" t="n">
-        <v>62</v>
+        <v>141</v>
       </c>
       <c r="E3" t="n">
-        <v>70</v>
+        <v>82</v>
       </c>
       <c r="F3" t="n">
-        <v>119</v>
+        <v>24</v>
       </c>
     </row>
     <row r="4">
@@ -508,10 +508,10 @@
         <v>1</v>
       </c>
       <c r="E4" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="F4" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
     </row>
     <row r="5">
@@ -521,19 +521,19 @@
         </is>
       </c>
       <c r="B5" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="C5" t="n">
-        <v>8</v>
+        <v>7</v>
       </c>
       <c r="D5" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="E5" t="n">
-        <v>1</v>
+        <v>7</v>
       </c>
       <c r="F5" t="n">
-        <v>8</v>
+        <v>6</v>
       </c>
     </row>
     <row r="6">
@@ -571,13 +571,13 @@
         <v>1</v>
       </c>
       <c r="D7" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="E7" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="F7" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
     </row>
     <row r="8">
@@ -587,19 +587,19 @@
         </is>
       </c>
       <c r="B8" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="C8" t="n">
-        <v>59</v>
+        <v>29</v>
       </c>
       <c r="D8" t="n">
-        <v>39</v>
+        <v>84</v>
       </c>
       <c r="E8" t="n">
+        <v>51</v>
+      </c>
+      <c r="F8" t="n">
         <v>31</v>
-      </c>
-      <c r="F8" t="n">
-        <v>67</v>
       </c>
     </row>
     <row r="9">
@@ -609,19 +609,19 @@
         </is>
       </c>
       <c r="B9" t="n">
-        <v>246</v>
+        <v>237</v>
       </c>
       <c r="C9" t="n">
-        <v>51</v>
+        <v>55</v>
       </c>
       <c r="D9" t="n">
-        <v>57</v>
+        <v>59</v>
       </c>
       <c r="E9" t="n">
-        <v>105</v>
+        <v>121</v>
       </c>
       <c r="F9" t="n">
-        <v>61</v>
+        <v>48</v>
       </c>
     </row>
     <row r="10">
@@ -634,16 +634,16 @@
         <v>0</v>
       </c>
       <c r="C10" t="n">
-        <v>15</v>
+        <v>8</v>
       </c>
       <c r="D10" t="n">
-        <v>10</v>
+        <v>5</v>
       </c>
       <c r="E10" t="n">
-        <v>3</v>
+        <v>25</v>
       </c>
       <c r="F10" t="n">
-        <v>11</v>
+        <v>1</v>
       </c>
     </row>
     <row r="11">
@@ -653,19 +653,19 @@
         </is>
       </c>
       <c r="B11" t="n">
-        <v>6</v>
+        <v>3</v>
       </c>
       <c r="C11" t="n">
-        <v>42</v>
+        <v>52</v>
       </c>
       <c r="D11" t="n">
-        <v>103</v>
+        <v>39</v>
       </c>
       <c r="E11" t="n">
-        <v>34</v>
+        <v>126</v>
       </c>
       <c r="F11" t="n">
-        <v>50</v>
+        <v>15</v>
       </c>
     </row>
     <row r="12">
@@ -678,16 +678,16 @@
         <v>2</v>
       </c>
       <c r="C12" t="n">
+        <v>52</v>
+      </c>
+      <c r="D12" t="n">
         <v>23</v>
       </c>
-      <c r="D12" t="n">
-        <v>94</v>
-      </c>
       <c r="E12" t="n">
-        <v>20</v>
+        <v>101</v>
       </c>
       <c r="F12" t="n">
-        <v>41</v>
+        <v>2</v>
       </c>
     </row>
     <row r="13">
@@ -697,19 +697,19 @@
         </is>
       </c>
       <c r="B13" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="C13" t="n">
+        <v>52</v>
+      </c>
+      <c r="D13" t="n">
         <v>18</v>
       </c>
-      <c r="D13" t="n">
-        <v>87</v>
-      </c>
       <c r="E13" t="n">
-        <v>16</v>
+        <v>88</v>
       </c>
       <c r="F13" t="n">
-        <v>38</v>
+        <v>2</v>
       </c>
     </row>
     <row r="14">
@@ -722,16 +722,16 @@
         <v>3</v>
       </c>
       <c r="C14" t="n">
-        <v>50</v>
+        <v>55</v>
       </c>
       <c r="D14" t="n">
-        <v>70</v>
+        <v>31</v>
       </c>
       <c r="E14" t="n">
-        <v>32</v>
+        <v>106</v>
       </c>
       <c r="F14" t="n">
-        <v>47</v>
+        <v>7</v>
       </c>
     </row>
     <row r="15">
@@ -744,16 +744,16 @@
         <v>0</v>
       </c>
       <c r="C15" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="D15" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="E15" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="F15" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
     </row>
     <row r="16">
@@ -763,19 +763,19 @@
         </is>
       </c>
       <c r="B16" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="C16" t="n">
-        <v>37</v>
+        <v>60</v>
       </c>
       <c r="D16" t="n">
-        <v>109</v>
+        <v>33</v>
       </c>
       <c r="E16" t="n">
-        <v>29</v>
+        <v>112</v>
       </c>
       <c r="F16" t="n">
-        <v>35</v>
+        <v>3</v>
       </c>
     </row>
     <row r="17">
@@ -791,10 +791,10 @@
         <v>1</v>
       </c>
       <c r="D17" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="E17" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="F17" t="n">
         <v>0</v>
@@ -810,16 +810,16 @@
         <v>120</v>
       </c>
       <c r="C18" t="n">
-        <v>38</v>
+        <v>19</v>
       </c>
       <c r="D18" t="n">
-        <v>42</v>
+        <v>18</v>
       </c>
       <c r="E18" t="n">
-        <v>14</v>
+        <v>81</v>
       </c>
       <c r="F18" t="n">
-        <v>39</v>
+        <v>15</v>
       </c>
     </row>
     <row r="19">
@@ -829,19 +829,19 @@
         </is>
       </c>
       <c r="B19" t="n">
-        <v>215</v>
+        <v>210</v>
       </c>
       <c r="C19" t="n">
-        <v>60</v>
+        <v>39</v>
       </c>
       <c r="D19" t="n">
-        <v>84</v>
+        <v>39</v>
       </c>
       <c r="E19" t="n">
-        <v>39</v>
+        <v>158</v>
       </c>
       <c r="F19" t="n">
-        <v>70</v>
+        <v>22</v>
       </c>
     </row>
     <row r="20">
@@ -854,16 +854,16 @@
         <v>0</v>
       </c>
       <c r="C20" t="n">
-        <v>8</v>
+        <v>5</v>
       </c>
       <c r="D20" t="n">
-        <v>9</v>
+        <v>6</v>
       </c>
       <c r="E20" t="n">
-        <v>8</v>
+        <v>19</v>
       </c>
       <c r="F20" t="n">
-        <v>6</v>
+        <v>1</v>
       </c>
     </row>
     <row r="21">
@@ -876,13 +876,13 @@
         <v>1</v>
       </c>
       <c r="C21" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="D21" t="n">
-        <v>3</v>
+        <v>0</v>
       </c>
       <c r="E21" t="n">
-        <v>2</v>
+        <v>4</v>
       </c>
       <c r="F21" t="n">
         <v>1</v>
@@ -895,19 +895,19 @@
         </is>
       </c>
       <c r="B22" t="n">
-        <v>5</v>
+        <v>7</v>
       </c>
       <c r="C22" t="n">
-        <v>45</v>
+        <v>30</v>
       </c>
       <c r="D22" t="n">
-        <v>36</v>
+        <v>35</v>
       </c>
       <c r="E22" t="n">
-        <v>37</v>
+        <v>84</v>
       </c>
       <c r="F22" t="n">
-        <v>45</v>
+        <v>12</v>
       </c>
     </row>
     <row r="23">
@@ -920,16 +920,16 @@
         <v>0</v>
       </c>
       <c r="C23" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="D23" t="n">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="E23" t="n">
         <v>0</v>
       </c>
       <c r="F23" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
     </row>
     <row r="24">
@@ -939,16 +939,16 @@
         </is>
       </c>
       <c r="B24" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="C24" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="D24" t="n">
         <v>1</v>
       </c>
       <c r="E24" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="F24" t="n">
         <v>0</v>
@@ -964,16 +964,16 @@
         <v>0</v>
       </c>
       <c r="C25" t="n">
-        <v>20</v>
+        <v>5</v>
       </c>
       <c r="D25" t="n">
-        <v>10</v>
+        <v>13</v>
       </c>
       <c r="E25" t="n">
-        <v>9</v>
+        <v>31</v>
       </c>
       <c r="F25" t="n">
-        <v>13</v>
+        <v>3</v>
       </c>
     </row>
     <row r="26">
@@ -989,13 +989,13 @@
         <v>3</v>
       </c>
       <c r="D26" t="n">
-        <v>0</v>
+        <v>3</v>
       </c>
       <c r="E26" t="n">
-        <v>4</v>
+        <v>2</v>
       </c>
       <c r="F26" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
     </row>
     <row r="27">
@@ -1005,19 +1005,19 @@
         </is>
       </c>
       <c r="B27" t="n">
-        <v>3</v>
+        <v>88</v>
       </c>
       <c r="C27" t="n">
-        <v>37</v>
+        <v>14</v>
       </c>
       <c r="D27" t="n">
-        <v>19</v>
+        <v>26</v>
       </c>
       <c r="E27" t="n">
-        <v>16</v>
+        <v>57</v>
       </c>
       <c r="F27" t="n">
-        <v>30</v>
+        <v>15</v>
       </c>
     </row>
     <row r="28">
@@ -1030,16 +1030,16 @@
         <v>0</v>
       </c>
       <c r="C28" t="n">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="D28" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="E28" t="n">
-        <v>2</v>
+        <v>6</v>
       </c>
       <c r="F28" t="n">
-        <v>4</v>
+        <v>0</v>
       </c>
     </row>
     <row r="29">
@@ -1052,16 +1052,16 @@
         <v>1</v>
       </c>
       <c r="C29" t="n">
-        <v>6</v>
+        <v>4</v>
       </c>
       <c r="D29" t="n">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="E29" t="n">
-        <v>0</v>
+        <v>14</v>
       </c>
       <c r="F29" t="n">
-        <v>12</v>
+        <v>2</v>
       </c>
     </row>
     <row r="30">
@@ -1074,10 +1074,10 @@
         <v>1</v>
       </c>
       <c r="C30" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="D30" t="n">
-        <v>2</v>
+        <v>4</v>
       </c>
       <c r="E30" t="n">
         <v>1</v>
@@ -1093,19 +1093,19 @@
         </is>
       </c>
       <c r="B31" t="n">
-        <v>4</v>
+        <v>1</v>
       </c>
       <c r="C31" t="n">
-        <v>12</v>
+        <v>19</v>
       </c>
       <c r="D31" t="n">
-        <v>25</v>
+        <v>13</v>
       </c>
       <c r="E31" t="n">
-        <v>16</v>
+        <v>18</v>
       </c>
       <c r="F31" t="n">
-        <v>7</v>
+        <v>13</v>
       </c>
     </row>
     <row r="32">
@@ -1115,19 +1115,19 @@
         </is>
       </c>
       <c r="B32" t="n">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="C32" t="n">
-        <v>39</v>
+        <v>19</v>
       </c>
       <c r="D32" t="n">
-        <v>51</v>
+        <v>27</v>
       </c>
       <c r="E32" t="n">
-        <v>14</v>
+        <v>73</v>
       </c>
       <c r="F32" t="n">
-        <v>25</v>
+        <v>8</v>
       </c>
     </row>
     <row r="33">
@@ -1140,16 +1140,16 @@
         <v>15</v>
       </c>
       <c r="C33" t="n">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="D33" t="n">
-        <v>9</v>
+        <v>2</v>
       </c>
       <c r="E33" t="n">
-        <v>1</v>
+        <v>10</v>
       </c>
       <c r="F33" t="n">
-        <v>3</v>
+        <v>0</v>
       </c>
     </row>
   </sheetData>

--- a/data/output/topik_per_lokasi.xlsx
+++ b/data/output/topik_per_lokasi.xlsx
@@ -458,16 +458,16 @@
         <v>45</v>
       </c>
       <c r="C2" t="n">
-        <v>11</v>
+        <v>15</v>
       </c>
       <c r="D2" t="n">
-        <v>12</v>
+        <v>9</v>
       </c>
       <c r="E2" t="n">
-        <v>18</v>
+        <v>15</v>
       </c>
       <c r="F2" t="n">
-        <v>8</v>
+        <v>10</v>
       </c>
     </row>
     <row r="3">
@@ -477,19 +477,19 @@
         </is>
       </c>
       <c r="B3" t="n">
-        <v>202</v>
+        <v>197</v>
       </c>
       <c r="C3" t="n">
-        <v>48</v>
+        <v>122</v>
       </c>
       <c r="D3" t="n">
-        <v>141</v>
+        <v>19</v>
       </c>
       <c r="E3" t="n">
-        <v>82</v>
+        <v>86</v>
       </c>
       <c r="F3" t="n">
-        <v>24</v>
+        <v>73</v>
       </c>
     </row>
     <row r="4">
@@ -505,13 +505,13 @@
         <v>0</v>
       </c>
       <c r="D4" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="E4" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="F4" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
     </row>
     <row r="5">
@@ -521,19 +521,19 @@
         </is>
       </c>
       <c r="B5" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="C5" t="n">
-        <v>7</v>
+        <v>9</v>
       </c>
       <c r="D5" t="n">
-        <v>1</v>
+        <v>4</v>
       </c>
       <c r="E5" t="n">
         <v>7</v>
       </c>
       <c r="F5" t="n">
-        <v>6</v>
+        <v>0</v>
       </c>
     </row>
     <row r="6">
@@ -549,10 +549,10 @@
         <v>0</v>
       </c>
       <c r="D6" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="E6" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="F6" t="n">
         <v>0</v>
@@ -587,19 +587,19 @@
         </is>
       </c>
       <c r="B8" t="n">
-        <v>2</v>
+        <v>5</v>
       </c>
       <c r="C8" t="n">
-        <v>29</v>
+        <v>59</v>
       </c>
       <c r="D8" t="n">
-        <v>84</v>
+        <v>55</v>
       </c>
       <c r="E8" t="n">
-        <v>51</v>
+        <v>28</v>
       </c>
       <c r="F8" t="n">
-        <v>31</v>
+        <v>50</v>
       </c>
     </row>
     <row r="9">
@@ -609,19 +609,19 @@
         </is>
       </c>
       <c r="B9" t="n">
-        <v>237</v>
+        <v>239</v>
       </c>
       <c r="C9" t="n">
-        <v>55</v>
+        <v>123</v>
       </c>
       <c r="D9" t="n">
-        <v>59</v>
+        <v>36</v>
       </c>
       <c r="E9" t="n">
-        <v>121</v>
+        <v>80</v>
       </c>
       <c r="F9" t="n">
-        <v>48</v>
+        <v>42</v>
       </c>
     </row>
     <row r="10">
@@ -634,16 +634,16 @@
         <v>0</v>
       </c>
       <c r="C10" t="n">
+        <v>13</v>
+      </c>
+      <c r="D10" t="n">
         <v>8</v>
       </c>
-      <c r="D10" t="n">
-        <v>5</v>
-      </c>
       <c r="E10" t="n">
-        <v>25</v>
+        <v>15</v>
       </c>
       <c r="F10" t="n">
-        <v>1</v>
+        <v>3</v>
       </c>
     </row>
     <row r="11">
@@ -656,16 +656,16 @@
         <v>3</v>
       </c>
       <c r="C11" t="n">
-        <v>52</v>
+        <v>61</v>
       </c>
       <c r="D11" t="n">
-        <v>39</v>
+        <v>24</v>
       </c>
       <c r="E11" t="n">
-        <v>126</v>
+        <v>128</v>
       </c>
       <c r="F11" t="n">
-        <v>15</v>
+        <v>19</v>
       </c>
     </row>
     <row r="12">
@@ -675,19 +675,19 @@
         </is>
       </c>
       <c r="B12" t="n">
-        <v>2</v>
+        <v>4</v>
       </c>
       <c r="C12" t="n">
-        <v>52</v>
+        <v>57</v>
       </c>
       <c r="D12" t="n">
-        <v>23</v>
+        <v>20</v>
       </c>
       <c r="E12" t="n">
-        <v>101</v>
+        <v>88</v>
       </c>
       <c r="F12" t="n">
-        <v>2</v>
+        <v>11</v>
       </c>
     </row>
     <row r="13">
@@ -697,19 +697,19 @@
         </is>
       </c>
       <c r="B13" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="C13" t="n">
-        <v>52</v>
+        <v>22</v>
       </c>
       <c r="D13" t="n">
-        <v>18</v>
+        <v>16</v>
       </c>
       <c r="E13" t="n">
-        <v>88</v>
+        <v>115</v>
       </c>
       <c r="F13" t="n">
-        <v>2</v>
+        <v>6</v>
       </c>
     </row>
     <row r="14">
@@ -719,19 +719,19 @@
         </is>
       </c>
       <c r="B14" t="n">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="C14" t="n">
-        <v>55</v>
+        <v>46</v>
       </c>
       <c r="D14" t="n">
-        <v>31</v>
+        <v>32</v>
       </c>
       <c r="E14" t="n">
-        <v>106</v>
+        <v>103</v>
       </c>
       <c r="F14" t="n">
-        <v>7</v>
+        <v>17</v>
       </c>
     </row>
     <row r="15">
@@ -744,16 +744,16 @@
         <v>0</v>
       </c>
       <c r="C15" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="D15" t="n">
         <v>0</v>
       </c>
       <c r="E15" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="F15" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
     </row>
     <row r="16">
@@ -763,19 +763,19 @@
         </is>
       </c>
       <c r="B16" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="C16" t="n">
-        <v>60</v>
+        <v>53</v>
       </c>
       <c r="D16" t="n">
-        <v>33</v>
+        <v>20</v>
       </c>
       <c r="E16" t="n">
-        <v>112</v>
+        <v>131</v>
       </c>
       <c r="F16" t="n">
-        <v>3</v>
+        <v>5</v>
       </c>
     </row>
     <row r="17">
@@ -788,10 +788,10 @@
         <v>0</v>
       </c>
       <c r="C17" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="D17" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="E17" t="n">
         <v>1</v>
@@ -807,19 +807,19 @@
         </is>
       </c>
       <c r="B18" t="n">
-        <v>120</v>
+        <v>121</v>
       </c>
       <c r="C18" t="n">
-        <v>19</v>
+        <v>37</v>
       </c>
       <c r="D18" t="n">
-        <v>18</v>
+        <v>27</v>
       </c>
       <c r="E18" t="n">
-        <v>81</v>
+        <v>54</v>
       </c>
       <c r="F18" t="n">
-        <v>15</v>
+        <v>14</v>
       </c>
     </row>
     <row r="19">
@@ -829,19 +829,19 @@
         </is>
       </c>
       <c r="B19" t="n">
-        <v>210</v>
+        <v>211</v>
       </c>
       <c r="C19" t="n">
-        <v>39</v>
+        <v>63</v>
       </c>
       <c r="D19" t="n">
-        <v>39</v>
+        <v>41</v>
       </c>
       <c r="E19" t="n">
-        <v>158</v>
+        <v>127</v>
       </c>
       <c r="F19" t="n">
-        <v>22</v>
+        <v>26</v>
       </c>
     </row>
     <row r="20">
@@ -854,16 +854,16 @@
         <v>0</v>
       </c>
       <c r="C20" t="n">
+        <v>7</v>
+      </c>
+      <c r="D20" t="n">
         <v>5</v>
-      </c>
-      <c r="D20" t="n">
-        <v>6</v>
       </c>
       <c r="E20" t="n">
         <v>19</v>
       </c>
       <c r="F20" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
     </row>
     <row r="21">
@@ -879,13 +879,13 @@
         <v>1</v>
       </c>
       <c r="D21" t="n">
-        <v>0</v>
+        <v>3</v>
       </c>
       <c r="E21" t="n">
-        <v>4</v>
+        <v>2</v>
       </c>
       <c r="F21" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
     </row>
     <row r="22">
@@ -895,19 +895,19 @@
         </is>
       </c>
       <c r="B22" t="n">
-        <v>7</v>
+        <v>4</v>
       </c>
       <c r="C22" t="n">
-        <v>30</v>
+        <v>66</v>
       </c>
       <c r="D22" t="n">
-        <v>35</v>
+        <v>27</v>
       </c>
       <c r="E22" t="n">
-        <v>84</v>
+        <v>48</v>
       </c>
       <c r="F22" t="n">
-        <v>12</v>
+        <v>23</v>
       </c>
     </row>
     <row r="23">
@@ -923,10 +923,10 @@
         <v>2</v>
       </c>
       <c r="D23" t="n">
+        <v>0</v>
+      </c>
+      <c r="E23" t="n">
         <v>4</v>
-      </c>
-      <c r="E23" t="n">
-        <v>0</v>
       </c>
       <c r="F23" t="n">
         <v>0</v>
@@ -942,16 +942,16 @@
         <v>0</v>
       </c>
       <c r="C24" t="n">
+        <v>0</v>
+      </c>
+      <c r="D24" t="n">
+        <v>0</v>
+      </c>
+      <c r="E24" t="n">
         <v>2</v>
       </c>
-      <c r="D24" t="n">
-        <v>1</v>
-      </c>
-      <c r="E24" t="n">
-        <v>0</v>
-      </c>
       <c r="F24" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
     </row>
     <row r="25">
@@ -961,19 +961,19 @@
         </is>
       </c>
       <c r="B25" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="C25" t="n">
+        <v>29</v>
+      </c>
+      <c r="D25" t="n">
+        <v>9</v>
+      </c>
+      <c r="E25" t="n">
+        <v>8</v>
+      </c>
+      <c r="F25" t="n">
         <v>5</v>
-      </c>
-      <c r="D25" t="n">
-        <v>13</v>
-      </c>
-      <c r="E25" t="n">
-        <v>31</v>
-      </c>
-      <c r="F25" t="n">
-        <v>3</v>
       </c>
     </row>
     <row r="26">
@@ -986,13 +986,13 @@
         <v>0</v>
       </c>
       <c r="C26" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="D26" t="n">
         <v>3</v>
       </c>
       <c r="E26" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="F26" t="n">
         <v>0</v>
@@ -1005,19 +1005,19 @@
         </is>
       </c>
       <c r="B27" t="n">
-        <v>88</v>
+        <v>90</v>
       </c>
       <c r="C27" t="n">
-        <v>14</v>
+        <v>39</v>
       </c>
       <c r="D27" t="n">
         <v>26</v>
       </c>
       <c r="E27" t="n">
-        <v>57</v>
+        <v>29</v>
       </c>
       <c r="F27" t="n">
-        <v>15</v>
+        <v>16</v>
       </c>
     </row>
     <row r="28">
@@ -1030,10 +1030,10 @@
         <v>0</v>
       </c>
       <c r="C28" t="n">
-        <v>3</v>
+        <v>5</v>
       </c>
       <c r="D28" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="E28" t="n">
         <v>6</v>
@@ -1049,19 +1049,19 @@
         </is>
       </c>
       <c r="B29" t="n">
-        <v>1</v>
+        <v>21</v>
       </c>
       <c r="C29" t="n">
+        <v>7</v>
+      </c>
+      <c r="D29" t="n">
+        <v>1</v>
+      </c>
+      <c r="E29" t="n">
+        <v>10</v>
+      </c>
+      <c r="F29" t="n">
         <v>4</v>
-      </c>
-      <c r="D29" t="n">
-        <v>1</v>
-      </c>
-      <c r="E29" t="n">
-        <v>14</v>
-      </c>
-      <c r="F29" t="n">
-        <v>2</v>
       </c>
     </row>
     <row r="30">
@@ -1074,16 +1074,16 @@
         <v>1</v>
       </c>
       <c r="C30" t="n">
-        <v>0</v>
+        <v>3</v>
       </c>
       <c r="D30" t="n">
-        <v>4</v>
+        <v>0</v>
       </c>
       <c r="E30" t="n">
         <v>1</v>
       </c>
       <c r="F30" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
     </row>
     <row r="31">
@@ -1093,19 +1093,19 @@
         </is>
       </c>
       <c r="B31" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="C31" t="n">
-        <v>19</v>
+        <v>10</v>
       </c>
       <c r="D31" t="n">
-        <v>13</v>
+        <v>17</v>
       </c>
       <c r="E31" t="n">
-        <v>18</v>
+        <v>27</v>
       </c>
       <c r="F31" t="n">
-        <v>13</v>
+        <v>8</v>
       </c>
     </row>
     <row r="32">
@@ -1115,19 +1115,19 @@
         </is>
       </c>
       <c r="B32" t="n">
-        <v>3</v>
+        <v>0</v>
       </c>
       <c r="C32" t="n">
-        <v>19</v>
+        <v>43</v>
       </c>
       <c r="D32" t="n">
-        <v>27</v>
+        <v>11</v>
       </c>
       <c r="E32" t="n">
-        <v>73</v>
+        <v>70</v>
       </c>
       <c r="F32" t="n">
-        <v>8</v>
+        <v>6</v>
       </c>
     </row>
     <row r="33">
@@ -1140,16 +1140,16 @@
         <v>15</v>
       </c>
       <c r="C33" t="n">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="D33" t="n">
         <v>2</v>
       </c>
       <c r="E33" t="n">
-        <v>10</v>
+        <v>8</v>
       </c>
       <c r="F33" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
     </row>
   </sheetData>

--- a/data/output/topik_per_lokasi.xlsx
+++ b/data/output/topik_per_lokasi.xlsx
@@ -455,19 +455,19 @@
         </is>
       </c>
       <c r="B2" t="n">
-        <v>45</v>
+        <v>46</v>
       </c>
       <c r="C2" t="n">
-        <v>15</v>
+        <v>8</v>
       </c>
       <c r="D2" t="n">
-        <v>9</v>
+        <v>8</v>
       </c>
       <c r="E2" t="n">
-        <v>15</v>
+        <v>18</v>
       </c>
       <c r="F2" t="n">
-        <v>10</v>
+        <v>14</v>
       </c>
     </row>
     <row r="3">
@@ -477,19 +477,19 @@
         </is>
       </c>
       <c r="B3" t="n">
-        <v>197</v>
+        <v>193</v>
       </c>
       <c r="C3" t="n">
-        <v>122</v>
+        <v>46</v>
       </c>
       <c r="D3" t="n">
-        <v>19</v>
+        <v>103</v>
       </c>
       <c r="E3" t="n">
-        <v>86</v>
+        <v>72</v>
       </c>
       <c r="F3" t="n">
-        <v>73</v>
+        <v>83</v>
       </c>
     </row>
     <row r="4">
@@ -502,16 +502,16 @@
         <v>0</v>
       </c>
       <c r="C4" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="D4" t="n">
         <v>0</v>
       </c>
       <c r="E4" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="F4" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
     </row>
     <row r="5">
@@ -521,19 +521,19 @@
         </is>
       </c>
       <c r="B5" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="C5" t="n">
+        <v>7</v>
+      </c>
+      <c r="D5" t="n">
+        <v>1</v>
+      </c>
+      <c r="E5" t="n">
         <v>9</v>
       </c>
-      <c r="D5" t="n">
+      <c r="F5" t="n">
         <v>4</v>
-      </c>
-      <c r="E5" t="n">
-        <v>7</v>
-      </c>
-      <c r="F5" t="n">
-        <v>0</v>
       </c>
     </row>
     <row r="6">
@@ -552,10 +552,10 @@
         <v>0</v>
       </c>
       <c r="E6" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="F6" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
     </row>
     <row r="7">
@@ -568,7 +568,7 @@
         <v>0</v>
       </c>
       <c r="C7" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="D7" t="n">
         <v>1</v>
@@ -577,7 +577,7 @@
         <v>1</v>
       </c>
       <c r="F7" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
     </row>
     <row r="8">
@@ -587,19 +587,19 @@
         </is>
       </c>
       <c r="B8" t="n">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="C8" t="n">
-        <v>59</v>
+        <v>24</v>
       </c>
       <c r="D8" t="n">
-        <v>55</v>
+        <v>54</v>
       </c>
       <c r="E8" t="n">
-        <v>28</v>
+        <v>74</v>
       </c>
       <c r="F8" t="n">
-        <v>50</v>
+        <v>41</v>
       </c>
     </row>
     <row r="9">
@@ -609,19 +609,19 @@
         </is>
       </c>
       <c r="B9" t="n">
-        <v>239</v>
+        <v>244</v>
       </c>
       <c r="C9" t="n">
-        <v>123</v>
+        <v>33</v>
       </c>
       <c r="D9" t="n">
-        <v>36</v>
+        <v>54</v>
       </c>
       <c r="E9" t="n">
-        <v>80</v>
+        <v>83</v>
       </c>
       <c r="F9" t="n">
-        <v>42</v>
+        <v>106</v>
       </c>
     </row>
     <row r="10">
@@ -634,16 +634,16 @@
         <v>0</v>
       </c>
       <c r="C10" t="n">
-        <v>13</v>
+        <v>11</v>
       </c>
       <c r="D10" t="n">
-        <v>8</v>
+        <v>1</v>
       </c>
       <c r="E10" t="n">
-        <v>15</v>
+        <v>18</v>
       </c>
       <c r="F10" t="n">
-        <v>3</v>
+        <v>9</v>
       </c>
     </row>
     <row r="11">
@@ -653,19 +653,19 @@
         </is>
       </c>
       <c r="B11" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="C11" t="n">
-        <v>61</v>
+        <v>47</v>
       </c>
       <c r="D11" t="n">
-        <v>24</v>
+        <v>13</v>
       </c>
       <c r="E11" t="n">
-        <v>128</v>
+        <v>122</v>
       </c>
       <c r="F11" t="n">
-        <v>19</v>
+        <v>51</v>
       </c>
     </row>
     <row r="12">
@@ -675,19 +675,19 @@
         </is>
       </c>
       <c r="B12" t="n">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="C12" t="n">
-        <v>57</v>
+        <v>41</v>
       </c>
       <c r="D12" t="n">
-        <v>20</v>
+        <v>11</v>
       </c>
       <c r="E12" t="n">
-        <v>88</v>
+        <v>105</v>
       </c>
       <c r="F12" t="n">
-        <v>11</v>
+        <v>18</v>
       </c>
     </row>
     <row r="13">
@@ -700,16 +700,16 @@
         <v>1</v>
       </c>
       <c r="C13" t="n">
-        <v>22</v>
+        <v>36</v>
       </c>
       <c r="D13" t="n">
-        <v>16</v>
+        <v>10</v>
       </c>
       <c r="E13" t="n">
-        <v>115</v>
+        <v>100</v>
       </c>
       <c r="F13" t="n">
-        <v>6</v>
+        <v>13</v>
       </c>
     </row>
     <row r="14">
@@ -719,19 +719,19 @@
         </is>
       </c>
       <c r="B14" t="n">
-        <v>4</v>
+        <v>2</v>
       </c>
       <c r="C14" t="n">
         <v>46</v>
       </c>
       <c r="D14" t="n">
-        <v>32</v>
+        <v>18</v>
       </c>
       <c r="E14" t="n">
-        <v>103</v>
+        <v>94</v>
       </c>
       <c r="F14" t="n">
-        <v>17</v>
+        <v>42</v>
       </c>
     </row>
     <row r="15">
@@ -744,16 +744,16 @@
         <v>0</v>
       </c>
       <c r="C15" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="D15" t="n">
         <v>0</v>
       </c>
       <c r="E15" t="n">
+        <v>0</v>
+      </c>
+      <c r="F15" t="n">
         <v>3</v>
-      </c>
-      <c r="F15" t="n">
-        <v>1</v>
       </c>
     </row>
     <row r="16">
@@ -763,19 +763,19 @@
         </is>
       </c>
       <c r="B16" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="C16" t="n">
-        <v>53</v>
+        <v>42</v>
       </c>
       <c r="D16" t="n">
-        <v>20</v>
+        <v>19</v>
       </c>
       <c r="E16" t="n">
-        <v>131</v>
+        <v>121</v>
       </c>
       <c r="F16" t="n">
-        <v>5</v>
+        <v>26</v>
       </c>
     </row>
     <row r="17">
@@ -791,10 +791,10 @@
         <v>0</v>
       </c>
       <c r="D17" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="E17" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="F17" t="n">
         <v>0</v>
@@ -807,19 +807,19 @@
         </is>
       </c>
       <c r="B18" t="n">
-        <v>121</v>
+        <v>119</v>
       </c>
       <c r="C18" t="n">
-        <v>37</v>
+        <v>29</v>
       </c>
       <c r="D18" t="n">
-        <v>27</v>
+        <v>12</v>
       </c>
       <c r="E18" t="n">
-        <v>54</v>
+        <v>63</v>
       </c>
       <c r="F18" t="n">
-        <v>14</v>
+        <v>30</v>
       </c>
     </row>
     <row r="19">
@@ -829,19 +829,19 @@
         </is>
       </c>
       <c r="B19" t="n">
-        <v>211</v>
+        <v>212</v>
       </c>
       <c r="C19" t="n">
-        <v>63</v>
+        <v>54</v>
       </c>
       <c r="D19" t="n">
-        <v>41</v>
+        <v>34</v>
       </c>
       <c r="E19" t="n">
-        <v>127</v>
+        <v>123</v>
       </c>
       <c r="F19" t="n">
-        <v>26</v>
+        <v>45</v>
       </c>
     </row>
     <row r="20">
@@ -854,16 +854,16 @@
         <v>0</v>
       </c>
       <c r="C20" t="n">
-        <v>7</v>
+        <v>6</v>
       </c>
       <c r="D20" t="n">
-        <v>5</v>
+        <v>2</v>
       </c>
       <c r="E20" t="n">
-        <v>19</v>
+        <v>17</v>
       </c>
       <c r="F20" t="n">
-        <v>0</v>
+        <v>6</v>
       </c>
     </row>
     <row r="21">
@@ -873,19 +873,19 @@
         </is>
       </c>
       <c r="B21" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="C21" t="n">
         <v>1</v>
       </c>
       <c r="D21" t="n">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="E21" t="n">
         <v>2</v>
       </c>
       <c r="F21" t="n">
-        <v>0</v>
+        <v>3</v>
       </c>
     </row>
     <row r="22">
@@ -895,19 +895,19 @@
         </is>
       </c>
       <c r="B22" t="n">
-        <v>4</v>
+        <v>6</v>
       </c>
       <c r="C22" t="n">
-        <v>66</v>
+        <v>40</v>
       </c>
       <c r="D22" t="n">
-        <v>27</v>
+        <v>18</v>
       </c>
       <c r="E22" t="n">
-        <v>48</v>
+        <v>65</v>
       </c>
       <c r="F22" t="n">
-        <v>23</v>
+        <v>39</v>
       </c>
     </row>
     <row r="23">
@@ -920,16 +920,16 @@
         <v>0</v>
       </c>
       <c r="C23" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="D23" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="E23" t="n">
         <v>4</v>
       </c>
       <c r="F23" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
     </row>
     <row r="24">
@@ -945,10 +945,10 @@
         <v>0</v>
       </c>
       <c r="D24" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="E24" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="F24" t="n">
         <v>1</v>
@@ -961,19 +961,19 @@
         </is>
       </c>
       <c r="B25" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="C25" t="n">
-        <v>29</v>
+        <v>12</v>
       </c>
       <c r="D25" t="n">
-        <v>9</v>
+        <v>6</v>
       </c>
       <c r="E25" t="n">
-        <v>8</v>
+        <v>22</v>
       </c>
       <c r="F25" t="n">
-        <v>5</v>
+        <v>12</v>
       </c>
     </row>
     <row r="26">
@@ -986,16 +986,16 @@
         <v>0</v>
       </c>
       <c r="C26" t="n">
+        <v>1</v>
+      </c>
+      <c r="D26" t="n">
         <v>2</v>
       </c>
-      <c r="D26" t="n">
-        <v>3</v>
-      </c>
       <c r="E26" t="n">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="F26" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
     </row>
     <row r="27">
@@ -1005,19 +1005,19 @@
         </is>
       </c>
       <c r="B27" t="n">
-        <v>90</v>
+        <v>94</v>
       </c>
       <c r="C27" t="n">
-        <v>39</v>
+        <v>24</v>
       </c>
       <c r="D27" t="n">
-        <v>26</v>
+        <v>12</v>
       </c>
       <c r="E27" t="n">
-        <v>29</v>
+        <v>38</v>
       </c>
       <c r="F27" t="n">
-        <v>16</v>
+        <v>32</v>
       </c>
     </row>
     <row r="28">
@@ -1030,16 +1030,16 @@
         <v>0</v>
       </c>
       <c r="C28" t="n">
+        <v>3</v>
+      </c>
+      <c r="D28" t="n">
+        <v>1</v>
+      </c>
+      <c r="E28" t="n">
         <v>5</v>
       </c>
-      <c r="D28" t="n">
-        <v>0</v>
-      </c>
-      <c r="E28" t="n">
-        <v>6</v>
-      </c>
       <c r="F28" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
     </row>
     <row r="29">
@@ -1049,16 +1049,16 @@
         </is>
       </c>
       <c r="B29" t="n">
-        <v>21</v>
+        <v>23</v>
       </c>
       <c r="C29" t="n">
-        <v>7</v>
+        <v>3</v>
       </c>
       <c r="D29" t="n">
         <v>1</v>
       </c>
       <c r="E29" t="n">
-        <v>10</v>
+        <v>12</v>
       </c>
       <c r="F29" t="n">
         <v>4</v>
@@ -1074,16 +1074,16 @@
         <v>1</v>
       </c>
       <c r="C30" t="n">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="D30" t="n">
-        <v>0</v>
+        <v>4</v>
       </c>
       <c r="E30" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="F30" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
     </row>
     <row r="31">
@@ -1096,13 +1096,13 @@
         <v>2</v>
       </c>
       <c r="C31" t="n">
-        <v>10</v>
+        <v>12</v>
       </c>
       <c r="D31" t="n">
-        <v>17</v>
+        <v>11</v>
       </c>
       <c r="E31" t="n">
-        <v>27</v>
+        <v>31</v>
       </c>
       <c r="F31" t="n">
         <v>8</v>
@@ -1115,19 +1115,19 @@
         </is>
       </c>
       <c r="B32" t="n">
-        <v>0</v>
+        <v>103</v>
       </c>
       <c r="C32" t="n">
-        <v>43</v>
+        <v>21</v>
       </c>
       <c r="D32" t="n">
-        <v>11</v>
+        <v>8</v>
       </c>
       <c r="E32" t="n">
-        <v>70</v>
+        <v>68</v>
       </c>
       <c r="F32" t="n">
-        <v>6</v>
+        <v>39</v>
       </c>
     </row>
     <row r="33">
@@ -1140,16 +1140,16 @@
         <v>15</v>
       </c>
       <c r="C33" t="n">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="D33" t="n">
+        <v>1</v>
+      </c>
+      <c r="E33" t="n">
+        <v>9</v>
+      </c>
+      <c r="F33" t="n">
         <v>2</v>
-      </c>
-      <c r="E33" t="n">
-        <v>8</v>
-      </c>
-      <c r="F33" t="n">
-        <v>1</v>
       </c>
     </row>
   </sheetData>

--- a/data/output/topik_per_lokasi.xlsx
+++ b/data/output/topik_per_lokasi.xlsx
@@ -455,19 +455,19 @@
         </is>
       </c>
       <c r="B2" t="n">
-        <v>46</v>
+        <v>47</v>
       </c>
       <c r="C2" t="n">
-        <v>8</v>
+        <v>7</v>
       </c>
       <c r="D2" t="n">
         <v>8</v>
       </c>
       <c r="E2" t="n">
-        <v>18</v>
+        <v>19</v>
       </c>
       <c r="F2" t="n">
-        <v>14</v>
+        <v>13</v>
       </c>
     </row>
     <row r="3">
@@ -477,19 +477,19 @@
         </is>
       </c>
       <c r="B3" t="n">
-        <v>193</v>
+        <v>191</v>
       </c>
       <c r="C3" t="n">
-        <v>46</v>
+        <v>50</v>
       </c>
       <c r="D3" t="n">
-        <v>103</v>
+        <v>91</v>
       </c>
       <c r="E3" t="n">
-        <v>72</v>
+        <v>75</v>
       </c>
       <c r="F3" t="n">
-        <v>83</v>
+        <v>90</v>
       </c>
     </row>
     <row r="4">
@@ -499,7 +499,7 @@
         </is>
       </c>
       <c r="B4" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="C4" t="n">
         <v>1</v>
@@ -524,10 +524,10 @@
         <v>0</v>
       </c>
       <c r="C5" t="n">
-        <v>7</v>
+        <v>6</v>
       </c>
       <c r="D5" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="E5" t="n">
         <v>9</v>
@@ -574,10 +574,10 @@
         <v>1</v>
       </c>
       <c r="E7" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="F7" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
     </row>
     <row r="8">
@@ -590,16 +590,16 @@
         <v>4</v>
       </c>
       <c r="C8" t="n">
-        <v>24</v>
+        <v>26</v>
       </c>
       <c r="D8" t="n">
-        <v>54</v>
+        <v>57</v>
       </c>
       <c r="E8" t="n">
-        <v>74</v>
+        <v>72</v>
       </c>
       <c r="F8" t="n">
-        <v>41</v>
+        <v>38</v>
       </c>
     </row>
     <row r="9">
@@ -609,19 +609,19 @@
         </is>
       </c>
       <c r="B9" t="n">
-        <v>244</v>
+        <v>243</v>
       </c>
       <c r="C9" t="n">
         <v>33</v>
       </c>
       <c r="D9" t="n">
-        <v>54</v>
+        <v>57</v>
       </c>
       <c r="E9" t="n">
         <v>83</v>
       </c>
       <c r="F9" t="n">
-        <v>106</v>
+        <v>104</v>
       </c>
     </row>
     <row r="10">
@@ -634,16 +634,16 @@
         <v>0</v>
       </c>
       <c r="C10" t="n">
-        <v>11</v>
+        <v>12</v>
       </c>
       <c r="D10" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="E10" t="n">
         <v>18</v>
       </c>
       <c r="F10" t="n">
-        <v>9</v>
+        <v>7</v>
       </c>
     </row>
     <row r="11">
@@ -656,16 +656,16 @@
         <v>2</v>
       </c>
       <c r="C11" t="n">
-        <v>47</v>
+        <v>48</v>
       </c>
       <c r="D11" t="n">
         <v>13</v>
       </c>
       <c r="E11" t="n">
-        <v>122</v>
+        <v>125</v>
       </c>
       <c r="F11" t="n">
-        <v>51</v>
+        <v>47</v>
       </c>
     </row>
     <row r="12">
@@ -675,19 +675,19 @@
         </is>
       </c>
       <c r="B12" t="n">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="C12" t="n">
-        <v>41</v>
+        <v>40</v>
       </c>
       <c r="D12" t="n">
-        <v>11</v>
+        <v>12</v>
       </c>
       <c r="E12" t="n">
-        <v>105</v>
+        <v>107</v>
       </c>
       <c r="F12" t="n">
-        <v>18</v>
+        <v>17</v>
       </c>
     </row>
     <row r="13">
@@ -700,13 +700,13 @@
         <v>1</v>
       </c>
       <c r="C13" t="n">
-        <v>36</v>
+        <v>35</v>
       </c>
       <c r="D13" t="n">
         <v>10</v>
       </c>
       <c r="E13" t="n">
-        <v>100</v>
+        <v>101</v>
       </c>
       <c r="F13" t="n">
         <v>13</v>
@@ -728,10 +728,10 @@
         <v>18</v>
       </c>
       <c r="E14" t="n">
-        <v>94</v>
+        <v>97</v>
       </c>
       <c r="F14" t="n">
-        <v>42</v>
+        <v>39</v>
       </c>
     </row>
     <row r="15">
@@ -744,7 +744,7 @@
         <v>0</v>
       </c>
       <c r="C15" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="D15" t="n">
         <v>0</v>
@@ -753,7 +753,7 @@
         <v>0</v>
       </c>
       <c r="F15" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
     </row>
     <row r="16">
@@ -772,10 +772,10 @@
         <v>19</v>
       </c>
       <c r="E16" t="n">
-        <v>121</v>
+        <v>122</v>
       </c>
       <c r="F16" t="n">
-        <v>26</v>
+        <v>25</v>
       </c>
     </row>
     <row r="17">
@@ -813,13 +813,13 @@
         <v>29</v>
       </c>
       <c r="D18" t="n">
-        <v>12</v>
+        <v>14</v>
       </c>
       <c r="E18" t="n">
         <v>63</v>
       </c>
       <c r="F18" t="n">
-        <v>30</v>
+        <v>28</v>
       </c>
     </row>
     <row r="19">
@@ -829,19 +829,19 @@
         </is>
       </c>
       <c r="B19" t="n">
-        <v>212</v>
+        <v>213</v>
       </c>
       <c r="C19" t="n">
-        <v>54</v>
+        <v>60</v>
       </c>
       <c r="D19" t="n">
-        <v>34</v>
+        <v>35</v>
       </c>
       <c r="E19" t="n">
-        <v>123</v>
+        <v>120</v>
       </c>
       <c r="F19" t="n">
-        <v>45</v>
+        <v>40</v>
       </c>
     </row>
     <row r="20">
@@ -882,10 +882,10 @@
         <v>1</v>
       </c>
       <c r="E21" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="F21" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
     </row>
     <row r="22">
@@ -898,16 +898,16 @@
         <v>6</v>
       </c>
       <c r="C22" t="n">
-        <v>40</v>
+        <v>39</v>
       </c>
       <c r="D22" t="n">
         <v>18</v>
       </c>
       <c r="E22" t="n">
-        <v>65</v>
+        <v>67</v>
       </c>
       <c r="F22" t="n">
-        <v>39</v>
+        <v>38</v>
       </c>
     </row>
     <row r="23">
@@ -970,10 +970,10 @@
         <v>6</v>
       </c>
       <c r="E25" t="n">
-        <v>22</v>
+        <v>23</v>
       </c>
       <c r="F25" t="n">
-        <v>12</v>
+        <v>11</v>
       </c>
     </row>
     <row r="26">
@@ -992,10 +992,10 @@
         <v>2</v>
       </c>
       <c r="E26" t="n">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="F26" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
     </row>
     <row r="27">
@@ -1005,19 +1005,19 @@
         </is>
       </c>
       <c r="B27" t="n">
-        <v>94</v>
+        <v>96</v>
       </c>
       <c r="C27" t="n">
         <v>24</v>
       </c>
       <c r="D27" t="n">
-        <v>12</v>
+        <v>14</v>
       </c>
       <c r="E27" t="n">
-        <v>38</v>
+        <v>39</v>
       </c>
       <c r="F27" t="n">
-        <v>32</v>
+        <v>27</v>
       </c>
     </row>
     <row r="28">
@@ -1030,7 +1030,7 @@
         <v>0</v>
       </c>
       <c r="C28" t="n">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="D28" t="n">
         <v>1</v>
@@ -1039,7 +1039,7 @@
         <v>5</v>
       </c>
       <c r="F28" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
     </row>
     <row r="29">
@@ -1058,10 +1058,10 @@
         <v>1</v>
       </c>
       <c r="E29" t="n">
-        <v>12</v>
+        <v>11</v>
       </c>
       <c r="F29" t="n">
-        <v>4</v>
+        <v>5</v>
       </c>
     </row>
     <row r="30">
@@ -1093,16 +1093,16 @@
         </is>
       </c>
       <c r="B31" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="C31" t="n">
-        <v>12</v>
+        <v>11</v>
       </c>
       <c r="D31" t="n">
-        <v>11</v>
+        <v>9</v>
       </c>
       <c r="E31" t="n">
-        <v>31</v>
+        <v>33</v>
       </c>
       <c r="F31" t="n">
         <v>8</v>
@@ -1115,19 +1115,19 @@
         </is>
       </c>
       <c r="B32" t="n">
-        <v>103</v>
+        <v>101</v>
       </c>
       <c r="C32" t="n">
-        <v>21</v>
+        <v>24</v>
       </c>
       <c r="D32" t="n">
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="E32" t="n">
-        <v>68</v>
+        <v>67</v>
       </c>
       <c r="F32" t="n">
-        <v>39</v>
+        <v>38</v>
       </c>
     </row>
     <row r="33">

--- a/data/output/topik_per_lokasi.xlsx
+++ b/data/output/topik_per_lokasi.xlsx
@@ -455,19 +455,19 @@
         </is>
       </c>
       <c r="B2" t="n">
-        <v>47</v>
+        <v>46</v>
       </c>
       <c r="C2" t="n">
+        <v>8</v>
+      </c>
+      <c r="D2" t="n">
+        <v>15</v>
+      </c>
+      <c r="E2" t="n">
+        <v>18</v>
+      </c>
+      <c r="F2" t="n">
         <v>7</v>
-      </c>
-      <c r="D2" t="n">
-        <v>8</v>
-      </c>
-      <c r="E2" t="n">
-        <v>19</v>
-      </c>
-      <c r="F2" t="n">
-        <v>13</v>
       </c>
     </row>
     <row r="3">
@@ -477,19 +477,19 @@
         </is>
       </c>
       <c r="B3" t="n">
-        <v>191</v>
+        <v>205</v>
       </c>
       <c r="C3" t="n">
-        <v>50</v>
+        <v>41</v>
       </c>
       <c r="D3" t="n">
-        <v>91</v>
+        <v>151</v>
       </c>
       <c r="E3" t="n">
-        <v>75</v>
+        <v>29</v>
       </c>
       <c r="F3" t="n">
-        <v>90</v>
+        <v>71</v>
       </c>
     </row>
     <row r="4">
@@ -502,13 +502,13 @@
         <v>1</v>
       </c>
       <c r="C4" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="D4" t="n">
         <v>0</v>
       </c>
       <c r="E4" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="F4" t="n">
         <v>1</v>
@@ -521,19 +521,19 @@
         </is>
       </c>
       <c r="B5" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="C5" t="n">
-        <v>6</v>
+        <v>5</v>
       </c>
       <c r="D5" t="n">
-        <v>2</v>
+        <v>8</v>
       </c>
       <c r="E5" t="n">
-        <v>9</v>
+        <v>4</v>
       </c>
       <c r="F5" t="n">
-        <v>4</v>
+        <v>3</v>
       </c>
     </row>
     <row r="6">
@@ -552,10 +552,10 @@
         <v>0</v>
       </c>
       <c r="E6" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="F6" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
     </row>
     <row r="7">
@@ -568,16 +568,16 @@
         <v>0</v>
       </c>
       <c r="C7" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="D7" t="n">
         <v>1</v>
       </c>
       <c r="E7" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="F7" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
     </row>
     <row r="8">
@@ -587,19 +587,19 @@
         </is>
       </c>
       <c r="B8" t="n">
-        <v>4</v>
+        <v>7</v>
       </c>
       <c r="C8" t="n">
-        <v>26</v>
+        <v>37</v>
       </c>
       <c r="D8" t="n">
-        <v>57</v>
+        <v>45</v>
       </c>
       <c r="E8" t="n">
-        <v>72</v>
+        <v>32</v>
       </c>
       <c r="F8" t="n">
-        <v>38</v>
+        <v>76</v>
       </c>
     </row>
     <row r="9">
@@ -609,19 +609,19 @@
         </is>
       </c>
       <c r="B9" t="n">
-        <v>243</v>
+        <v>235</v>
       </c>
       <c r="C9" t="n">
-        <v>33</v>
+        <v>41</v>
       </c>
       <c r="D9" t="n">
-        <v>57</v>
+        <v>151</v>
       </c>
       <c r="E9" t="n">
-        <v>83</v>
+        <v>55</v>
       </c>
       <c r="F9" t="n">
-        <v>104</v>
+        <v>38</v>
       </c>
     </row>
     <row r="10">
@@ -634,16 +634,16 @@
         <v>0</v>
       </c>
       <c r="C10" t="n">
-        <v>12</v>
+        <v>9</v>
       </c>
       <c r="D10" t="n">
+        <v>18</v>
+      </c>
+      <c r="E10" t="n">
+        <v>10</v>
+      </c>
+      <c r="F10" t="n">
         <v>2</v>
-      </c>
-      <c r="E10" t="n">
-        <v>18</v>
-      </c>
-      <c r="F10" t="n">
-        <v>7</v>
       </c>
     </row>
     <row r="11">
@@ -656,16 +656,16 @@
         <v>2</v>
       </c>
       <c r="C11" t="n">
-        <v>48</v>
+        <v>64</v>
       </c>
       <c r="D11" t="n">
-        <v>13</v>
+        <v>96</v>
       </c>
       <c r="E11" t="n">
-        <v>125</v>
+        <v>49</v>
       </c>
       <c r="F11" t="n">
-        <v>47</v>
+        <v>24</v>
       </c>
     </row>
     <row r="12">
@@ -675,19 +675,19 @@
         </is>
       </c>
       <c r="B12" t="n">
-        <v>4</v>
+        <v>1</v>
       </c>
       <c r="C12" t="n">
-        <v>40</v>
+        <v>26</v>
       </c>
       <c r="D12" t="n">
+        <v>82</v>
+      </c>
+      <c r="E12" t="n">
+        <v>59</v>
+      </c>
+      <c r="F12" t="n">
         <v>12</v>
-      </c>
-      <c r="E12" t="n">
-        <v>107</v>
-      </c>
-      <c r="F12" t="n">
-        <v>17</v>
       </c>
     </row>
     <row r="13">
@@ -697,19 +697,19 @@
         </is>
       </c>
       <c r="B13" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="C13" t="n">
-        <v>35</v>
+        <v>27</v>
       </c>
       <c r="D13" t="n">
-        <v>10</v>
+        <v>101</v>
       </c>
       <c r="E13" t="n">
-        <v>101</v>
+        <v>27</v>
       </c>
       <c r="F13" t="n">
-        <v>13</v>
+        <v>5</v>
       </c>
     </row>
     <row r="14">
@@ -719,19 +719,19 @@
         </is>
       </c>
       <c r="B14" t="n">
-        <v>2</v>
+        <v>4</v>
       </c>
       <c r="C14" t="n">
-        <v>46</v>
+        <v>50</v>
       </c>
       <c r="D14" t="n">
-        <v>18</v>
+        <v>89</v>
       </c>
       <c r="E14" t="n">
-        <v>97</v>
+        <v>42</v>
       </c>
       <c r="F14" t="n">
-        <v>39</v>
+        <v>17</v>
       </c>
     </row>
     <row r="15">
@@ -747,13 +747,13 @@
         <v>2</v>
       </c>
       <c r="D15" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="E15" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="F15" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
     </row>
     <row r="16">
@@ -763,19 +763,19 @@
         </is>
       </c>
       <c r="B16" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="C16" t="n">
-        <v>42</v>
+        <v>35</v>
       </c>
       <c r="D16" t="n">
-        <v>19</v>
+        <v>111</v>
       </c>
       <c r="E16" t="n">
-        <v>122</v>
+        <v>53</v>
       </c>
       <c r="F16" t="n">
-        <v>25</v>
+        <v>10</v>
       </c>
     </row>
     <row r="17">
@@ -788,13 +788,13 @@
         <v>0</v>
       </c>
       <c r="C17" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="D17" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="E17" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="F17" t="n">
         <v>0</v>
@@ -807,19 +807,19 @@
         </is>
       </c>
       <c r="B18" t="n">
-        <v>119</v>
+        <v>120</v>
       </c>
       <c r="C18" t="n">
-        <v>29</v>
+        <v>39</v>
       </c>
       <c r="D18" t="n">
-        <v>14</v>
+        <v>38</v>
       </c>
       <c r="E18" t="n">
-        <v>63</v>
+        <v>40</v>
       </c>
       <c r="F18" t="n">
-        <v>28</v>
+        <v>16</v>
       </c>
     </row>
     <row r="19">
@@ -829,19 +829,19 @@
         </is>
       </c>
       <c r="B19" t="n">
-        <v>213</v>
+        <v>212</v>
       </c>
       <c r="C19" t="n">
-        <v>60</v>
+        <v>78</v>
       </c>
       <c r="D19" t="n">
-        <v>35</v>
+        <v>109</v>
       </c>
       <c r="E19" t="n">
-        <v>120</v>
+        <v>52</v>
       </c>
       <c r="F19" t="n">
-        <v>40</v>
+        <v>17</v>
       </c>
     </row>
     <row r="20">
@@ -857,13 +857,13 @@
         <v>6</v>
       </c>
       <c r="D20" t="n">
+        <v>19</v>
+      </c>
+      <c r="E20" t="n">
+        <v>4</v>
+      </c>
+      <c r="F20" t="n">
         <v>2</v>
-      </c>
-      <c r="E20" t="n">
-        <v>17</v>
-      </c>
-      <c r="F20" t="n">
-        <v>6</v>
       </c>
     </row>
     <row r="21">
@@ -876,16 +876,16 @@
         <v>0</v>
       </c>
       <c r="C21" t="n">
-        <v>1</v>
+        <v>4</v>
       </c>
       <c r="D21" t="n">
         <v>1</v>
       </c>
       <c r="E21" t="n">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="F21" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
     </row>
     <row r="22">
@@ -895,19 +895,19 @@
         </is>
       </c>
       <c r="B22" t="n">
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="C22" t="n">
-        <v>39</v>
+        <v>38</v>
       </c>
       <c r="D22" t="n">
-        <v>18</v>
+        <v>54</v>
       </c>
       <c r="E22" t="n">
-        <v>67</v>
+        <v>49</v>
       </c>
       <c r="F22" t="n">
-        <v>38</v>
+        <v>20</v>
       </c>
     </row>
     <row r="23">
@@ -920,13 +920,13 @@
         <v>0</v>
       </c>
       <c r="C23" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="D23" t="n">
         <v>1</v>
       </c>
       <c r="E23" t="n">
-        <v>4</v>
+        <v>2</v>
       </c>
       <c r="F23" t="n">
         <v>1</v>
@@ -942,10 +942,10 @@
         <v>0</v>
       </c>
       <c r="C24" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="D24" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="E24" t="n">
         <v>1</v>
@@ -964,16 +964,16 @@
         <v>0</v>
       </c>
       <c r="C25" t="n">
-        <v>12</v>
+        <v>14</v>
       </c>
       <c r="D25" t="n">
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="E25" t="n">
         <v>23</v>
       </c>
       <c r="F25" t="n">
-        <v>11</v>
+        <v>8</v>
       </c>
     </row>
     <row r="26">
@@ -986,16 +986,16 @@
         <v>0</v>
       </c>
       <c r="C26" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="D26" t="n">
-        <v>2</v>
+        <v>4</v>
       </c>
       <c r="E26" t="n">
-        <v>5</v>
+        <v>1</v>
       </c>
       <c r="F26" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
     </row>
     <row r="27">
@@ -1005,19 +1005,19 @@
         </is>
       </c>
       <c r="B27" t="n">
-        <v>96</v>
+        <v>89</v>
       </c>
       <c r="C27" t="n">
-        <v>24</v>
+        <v>33</v>
       </c>
       <c r="D27" t="n">
-        <v>14</v>
+        <v>34</v>
       </c>
       <c r="E27" t="n">
-        <v>39</v>
+        <v>22</v>
       </c>
       <c r="F27" t="n">
-        <v>27</v>
+        <v>22</v>
       </c>
     </row>
     <row r="28">
@@ -1027,19 +1027,19 @@
         </is>
       </c>
       <c r="B28" t="n">
-        <v>0</v>
+        <v>3</v>
       </c>
       <c r="C28" t="n">
-        <v>4</v>
+        <v>2</v>
       </c>
       <c r="D28" t="n">
-        <v>1</v>
+        <v>8</v>
       </c>
       <c r="E28" t="n">
-        <v>5</v>
+        <v>1</v>
       </c>
       <c r="F28" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
     </row>
     <row r="29">
@@ -1049,19 +1049,19 @@
         </is>
       </c>
       <c r="B29" t="n">
-        <v>23</v>
+        <v>21</v>
       </c>
       <c r="C29" t="n">
         <v>3</v>
       </c>
       <c r="D29" t="n">
-        <v>1</v>
+        <v>10</v>
       </c>
       <c r="E29" t="n">
-        <v>11</v>
+        <v>8</v>
       </c>
       <c r="F29" t="n">
-        <v>5</v>
+        <v>1</v>
       </c>
     </row>
     <row r="30">
@@ -1077,10 +1077,10 @@
         <v>1</v>
       </c>
       <c r="D30" t="n">
-        <v>4</v>
+        <v>1</v>
       </c>
       <c r="E30" t="n">
-        <v>0</v>
+        <v>3</v>
       </c>
       <c r="F30" t="n">
         <v>1</v>
@@ -1096,13 +1096,13 @@
         <v>3</v>
       </c>
       <c r="C31" t="n">
-        <v>11</v>
+        <v>12</v>
       </c>
       <c r="D31" t="n">
-        <v>9</v>
+        <v>24</v>
       </c>
       <c r="E31" t="n">
-        <v>33</v>
+        <v>17</v>
       </c>
       <c r="F31" t="n">
         <v>8</v>
@@ -1115,19 +1115,19 @@
         </is>
       </c>
       <c r="B32" t="n">
-        <v>101</v>
+        <v>99</v>
       </c>
       <c r="C32" t="n">
-        <v>24</v>
+        <v>34</v>
       </c>
       <c r="D32" t="n">
-        <v>9</v>
+        <v>52</v>
       </c>
       <c r="E32" t="n">
-        <v>67</v>
+        <v>37</v>
       </c>
       <c r="F32" t="n">
-        <v>38</v>
+        <v>17</v>
       </c>
     </row>
     <row r="33">
@@ -1140,16 +1140,16 @@
         <v>15</v>
       </c>
       <c r="C33" t="n">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="D33" t="n">
-        <v>1</v>
+        <v>7</v>
       </c>
       <c r="E33" t="n">
-        <v>9</v>
+        <v>5</v>
       </c>
       <c r="F33" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
     </row>
   </sheetData>

--- a/data/output/topik_per_lokasi.xlsx
+++ b/data/output/topik_per_lokasi.xlsx
@@ -458,13 +458,13 @@
         <v>46</v>
       </c>
       <c r="C2" t="n">
-        <v>8</v>
+        <v>12</v>
       </c>
       <c r="D2" t="n">
-        <v>15</v>
+        <v>17</v>
       </c>
       <c r="E2" t="n">
-        <v>18</v>
+        <v>12</v>
       </c>
       <c r="F2" t="n">
         <v>7</v>
@@ -480,16 +480,16 @@
         <v>205</v>
       </c>
       <c r="C3" t="n">
-        <v>41</v>
+        <v>112</v>
       </c>
       <c r="D3" t="n">
-        <v>151</v>
+        <v>90</v>
       </c>
       <c r="E3" t="n">
-        <v>29</v>
+        <v>38</v>
       </c>
       <c r="F3" t="n">
-        <v>71</v>
+        <v>52</v>
       </c>
     </row>
     <row r="4">
@@ -502,16 +502,16 @@
         <v>1</v>
       </c>
       <c r="C4" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="D4" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="E4" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="F4" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
     </row>
     <row r="5">
@@ -521,16 +521,16 @@
         </is>
       </c>
       <c r="B5" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="C5" t="n">
-        <v>5</v>
+        <v>3</v>
       </c>
       <c r="D5" t="n">
-        <v>8</v>
+        <v>7</v>
       </c>
       <c r="E5" t="n">
-        <v>4</v>
+        <v>6</v>
       </c>
       <c r="F5" t="n">
         <v>3</v>
@@ -549,10 +549,10 @@
         <v>0</v>
       </c>
       <c r="D6" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="E6" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="F6" t="n">
         <v>0</v>
@@ -568,10 +568,10 @@
         <v>0</v>
       </c>
       <c r="C7" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="D7" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="E7" t="n">
         <v>0</v>
@@ -587,19 +587,19 @@
         </is>
       </c>
       <c r="B8" t="n">
-        <v>7</v>
+        <v>4</v>
       </c>
       <c r="C8" t="n">
-        <v>37</v>
+        <v>59</v>
       </c>
       <c r="D8" t="n">
-        <v>45</v>
+        <v>33</v>
       </c>
       <c r="E8" t="n">
-        <v>32</v>
+        <v>48</v>
       </c>
       <c r="F8" t="n">
-        <v>76</v>
+        <v>53</v>
       </c>
     </row>
     <row r="9">
@@ -609,19 +609,19 @@
         </is>
       </c>
       <c r="B9" t="n">
-        <v>235</v>
+        <v>234</v>
       </c>
       <c r="C9" t="n">
-        <v>41</v>
+        <v>45</v>
       </c>
       <c r="D9" t="n">
-        <v>151</v>
+        <v>127</v>
       </c>
       <c r="E9" t="n">
         <v>55</v>
       </c>
       <c r="F9" t="n">
-        <v>38</v>
+        <v>59</v>
       </c>
     </row>
     <row r="10">
@@ -634,13 +634,13 @@
         <v>0</v>
       </c>
       <c r="C10" t="n">
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="D10" t="n">
-        <v>18</v>
+        <v>24</v>
       </c>
       <c r="E10" t="n">
-        <v>10</v>
+        <v>3</v>
       </c>
       <c r="F10" t="n">
         <v>2</v>
@@ -656,16 +656,16 @@
         <v>2</v>
       </c>
       <c r="C11" t="n">
-        <v>64</v>
+        <v>70</v>
       </c>
       <c r="D11" t="n">
-        <v>96</v>
+        <v>104</v>
       </c>
       <c r="E11" t="n">
-        <v>49</v>
+        <v>29</v>
       </c>
       <c r="F11" t="n">
-        <v>24</v>
+        <v>30</v>
       </c>
     </row>
     <row r="12">
@@ -675,19 +675,19 @@
         </is>
       </c>
       <c r="B12" t="n">
-        <v>1</v>
+        <v>6</v>
       </c>
       <c r="C12" t="n">
-        <v>26</v>
+        <v>68</v>
       </c>
       <c r="D12" t="n">
-        <v>82</v>
+        <v>67</v>
       </c>
       <c r="E12" t="n">
-        <v>59</v>
+        <v>24</v>
       </c>
       <c r="F12" t="n">
-        <v>12</v>
+        <v>18</v>
       </c>
     </row>
     <row r="13">
@@ -700,16 +700,16 @@
         <v>0</v>
       </c>
       <c r="C13" t="n">
-        <v>27</v>
+        <v>49</v>
       </c>
       <c r="D13" t="n">
-        <v>101</v>
+        <v>85</v>
       </c>
       <c r="E13" t="n">
-        <v>27</v>
+        <v>12</v>
       </c>
       <c r="F13" t="n">
-        <v>5</v>
+        <v>14</v>
       </c>
     </row>
     <row r="14">
@@ -722,16 +722,16 @@
         <v>4</v>
       </c>
       <c r="C14" t="n">
-        <v>50</v>
+        <v>47</v>
       </c>
       <c r="D14" t="n">
-        <v>89</v>
+        <v>97</v>
       </c>
       <c r="E14" t="n">
-        <v>42</v>
+        <v>34</v>
       </c>
       <c r="F14" t="n">
-        <v>17</v>
+        <v>20</v>
       </c>
     </row>
     <row r="15">
@@ -744,16 +744,16 @@
         <v>0</v>
       </c>
       <c r="C15" t="n">
+        <v>0</v>
+      </c>
+      <c r="D15" t="n">
         <v>2</v>
       </c>
-      <c r="D15" t="n">
-        <v>1</v>
-      </c>
       <c r="E15" t="n">
         <v>1</v>
       </c>
       <c r="F15" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
     </row>
     <row r="16">
@@ -766,16 +766,16 @@
         <v>1</v>
       </c>
       <c r="C16" t="n">
-        <v>35</v>
+        <v>69</v>
       </c>
       <c r="D16" t="n">
-        <v>111</v>
+        <v>97</v>
       </c>
       <c r="E16" t="n">
-        <v>53</v>
+        <v>34</v>
       </c>
       <c r="F16" t="n">
-        <v>10</v>
+        <v>9</v>
       </c>
     </row>
     <row r="17">
@@ -788,10 +788,10 @@
         <v>0</v>
       </c>
       <c r="C17" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="D17" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="E17" t="n">
         <v>0</v>
@@ -810,16 +810,16 @@
         <v>120</v>
       </c>
       <c r="C18" t="n">
-        <v>39</v>
+        <v>40</v>
       </c>
       <c r="D18" t="n">
-        <v>38</v>
+        <v>58</v>
       </c>
       <c r="E18" t="n">
-        <v>40</v>
+        <v>17</v>
       </c>
       <c r="F18" t="n">
-        <v>16</v>
+        <v>18</v>
       </c>
     </row>
     <row r="19">
@@ -829,19 +829,19 @@
         </is>
       </c>
       <c r="B19" t="n">
-        <v>212</v>
+        <v>214</v>
       </c>
       <c r="C19" t="n">
-        <v>78</v>
+        <v>88</v>
       </c>
       <c r="D19" t="n">
-        <v>109</v>
+        <v>115</v>
       </c>
       <c r="E19" t="n">
-        <v>52</v>
+        <v>23</v>
       </c>
       <c r="F19" t="n">
-        <v>17</v>
+        <v>28</v>
       </c>
     </row>
     <row r="20">
@@ -854,16 +854,16 @@
         <v>0</v>
       </c>
       <c r="C20" t="n">
-        <v>6</v>
+        <v>8</v>
       </c>
       <c r="D20" t="n">
-        <v>19</v>
+        <v>16</v>
       </c>
       <c r="E20" t="n">
         <v>4</v>
       </c>
       <c r="F20" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
     </row>
     <row r="21">
@@ -873,19 +873,19 @@
         </is>
       </c>
       <c r="B21" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="C21" t="n">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="D21" t="n">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="E21" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="F21" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
     </row>
     <row r="22">
@@ -895,19 +895,19 @@
         </is>
       </c>
       <c r="B22" t="n">
-        <v>7</v>
+        <v>5</v>
       </c>
       <c r="C22" t="n">
-        <v>38</v>
+        <v>42</v>
       </c>
       <c r="D22" t="n">
-        <v>54</v>
+        <v>64</v>
       </c>
       <c r="E22" t="n">
-        <v>49</v>
+        <v>32</v>
       </c>
       <c r="F22" t="n">
-        <v>20</v>
+        <v>25</v>
       </c>
     </row>
     <row r="23">
@@ -920,16 +920,16 @@
         <v>0</v>
       </c>
       <c r="C23" t="n">
+        <v>1</v>
+      </c>
+      <c r="D23" t="n">
         <v>2</v>
       </c>
-      <c r="D23" t="n">
-        <v>1</v>
-      </c>
       <c r="E23" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="F23" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
     </row>
     <row r="24">
@@ -939,19 +939,19 @@
         </is>
       </c>
       <c r="B24" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="C24" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="D24" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="E24" t="n">
         <v>1</v>
       </c>
       <c r="F24" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
     </row>
     <row r="25">
@@ -964,16 +964,16 @@
         <v>0</v>
       </c>
       <c r="C25" t="n">
+        <v>18</v>
+      </c>
+      <c r="D25" t="n">
         <v>14</v>
       </c>
-      <c r="D25" t="n">
-        <v>7</v>
-      </c>
       <c r="E25" t="n">
-        <v>23</v>
+        <v>10</v>
       </c>
       <c r="F25" t="n">
-        <v>8</v>
+        <v>10</v>
       </c>
     </row>
     <row r="26">
@@ -986,13 +986,13 @@
         <v>0</v>
       </c>
       <c r="C26" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="D26" t="n">
+        <v>3</v>
+      </c>
+      <c r="E26" t="n">
         <v>4</v>
-      </c>
-      <c r="E26" t="n">
-        <v>1</v>
       </c>
       <c r="F26" t="n">
         <v>1</v>
@@ -1005,19 +1005,19 @@
         </is>
       </c>
       <c r="B27" t="n">
-        <v>89</v>
+        <v>88</v>
       </c>
       <c r="C27" t="n">
-        <v>33</v>
+        <v>35</v>
       </c>
       <c r="D27" t="n">
-        <v>34</v>
+        <v>39</v>
       </c>
       <c r="E27" t="n">
-        <v>22</v>
+        <v>18</v>
       </c>
       <c r="F27" t="n">
-        <v>22</v>
+        <v>20</v>
       </c>
     </row>
     <row r="28">
@@ -1033,10 +1033,10 @@
         <v>2</v>
       </c>
       <c r="D28" t="n">
-        <v>8</v>
+        <v>6</v>
       </c>
       <c r="E28" t="n">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="F28" t="n">
         <v>0</v>
@@ -1052,16 +1052,16 @@
         <v>21</v>
       </c>
       <c r="C29" t="n">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="D29" t="n">
-        <v>10</v>
+        <v>12</v>
       </c>
       <c r="E29" t="n">
-        <v>8</v>
+        <v>2</v>
       </c>
       <c r="F29" t="n">
-        <v>1</v>
+        <v>4</v>
       </c>
     </row>
     <row r="30">
@@ -1074,13 +1074,13 @@
         <v>1</v>
       </c>
       <c r="C30" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="D30" t="n">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="E30" t="n">
-        <v>3</v>
+        <v>0</v>
       </c>
       <c r="F30" t="n">
         <v>1</v>
@@ -1093,19 +1093,19 @@
         </is>
       </c>
       <c r="B31" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="C31" t="n">
+        <v>25</v>
+      </c>
+      <c r="D31" t="n">
+        <v>13</v>
+      </c>
+      <c r="E31" t="n">
         <v>12</v>
       </c>
-      <c r="D31" t="n">
-        <v>24</v>
-      </c>
-      <c r="E31" t="n">
-        <v>17</v>
-      </c>
       <c r="F31" t="n">
-        <v>8</v>
+        <v>12</v>
       </c>
     </row>
     <row r="32">
@@ -1115,19 +1115,19 @@
         </is>
       </c>
       <c r="B32" t="n">
-        <v>99</v>
+        <v>101</v>
       </c>
       <c r="C32" t="n">
-        <v>34</v>
+        <v>33</v>
       </c>
       <c r="D32" t="n">
-        <v>52</v>
+        <v>50</v>
       </c>
       <c r="E32" t="n">
-        <v>37</v>
+        <v>32</v>
       </c>
       <c r="F32" t="n">
-        <v>17</v>
+        <v>23</v>
       </c>
     </row>
     <row r="33">
@@ -1140,16 +1140,16 @@
         <v>15</v>
       </c>
       <c r="C33" t="n">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="D33" t="n">
-        <v>7</v>
+        <v>10</v>
       </c>
       <c r="E33" t="n">
-        <v>5</v>
+        <v>2</v>
       </c>
       <c r="F33" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
     </row>
   </sheetData>

--- a/data/output/topik_per_lokasi.xlsx
+++ b/data/output/topik_per_lokasi.xlsx
@@ -455,19 +455,19 @@
         </is>
       </c>
       <c r="B2" t="n">
-        <v>46</v>
+        <v>39</v>
       </c>
       <c r="C2" t="n">
-        <v>12</v>
+        <v>3</v>
       </c>
       <c r="D2" t="n">
-        <v>17</v>
+        <v>13</v>
       </c>
       <c r="E2" t="n">
-        <v>12</v>
+        <v>28</v>
       </c>
       <c r="F2" t="n">
-        <v>7</v>
+        <v>11</v>
       </c>
     </row>
     <row r="3">
@@ -477,19 +477,19 @@
         </is>
       </c>
       <c r="B3" t="n">
-        <v>205</v>
+        <v>135</v>
       </c>
       <c r="C3" t="n">
-        <v>112</v>
+        <v>32</v>
       </c>
       <c r="D3" t="n">
-        <v>90</v>
+        <v>131</v>
       </c>
       <c r="E3" t="n">
-        <v>38</v>
+        <v>124</v>
       </c>
       <c r="F3" t="n">
-        <v>52</v>
+        <v>75</v>
       </c>
     </row>
     <row r="4">
@@ -499,19 +499,19 @@
         </is>
       </c>
       <c r="B4" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="C4" t="n">
         <v>1</v>
       </c>
       <c r="D4" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="E4" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="F4" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
     </row>
     <row r="5">
@@ -524,16 +524,16 @@
         <v>2</v>
       </c>
       <c r="C5" t="n">
-        <v>3</v>
+        <v>0</v>
       </c>
       <c r="D5" t="n">
         <v>7</v>
       </c>
       <c r="E5" t="n">
-        <v>6</v>
+        <v>10</v>
       </c>
       <c r="F5" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
     </row>
     <row r="6">
@@ -546,10 +546,10 @@
         <v>0</v>
       </c>
       <c r="C6" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="D6" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="E6" t="n">
         <v>0</v>
@@ -568,16 +568,16 @@
         <v>0</v>
       </c>
       <c r="C7" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="D7" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="E7" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="F7" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
     </row>
     <row r="8">
@@ -587,19 +587,19 @@
         </is>
       </c>
       <c r="B8" t="n">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="C8" t="n">
-        <v>59</v>
+        <v>51</v>
       </c>
       <c r="D8" t="n">
-        <v>33</v>
+        <v>48</v>
       </c>
       <c r="E8" t="n">
-        <v>48</v>
+        <v>77</v>
       </c>
       <c r="F8" t="n">
-        <v>53</v>
+        <v>16</v>
       </c>
     </row>
     <row r="9">
@@ -609,19 +609,19 @@
         </is>
       </c>
       <c r="B9" t="n">
-        <v>234</v>
+        <v>137</v>
       </c>
       <c r="C9" t="n">
-        <v>45</v>
+        <v>31</v>
       </c>
       <c r="D9" t="n">
-        <v>127</v>
+        <v>99</v>
       </c>
       <c r="E9" t="n">
-        <v>55</v>
+        <v>123</v>
       </c>
       <c r="F9" t="n">
-        <v>59</v>
+        <v>130</v>
       </c>
     </row>
     <row r="10">
@@ -634,16 +634,16 @@
         <v>0</v>
       </c>
       <c r="C10" t="n">
-        <v>10</v>
+        <v>8</v>
       </c>
       <c r="D10" t="n">
-        <v>24</v>
+        <v>16</v>
       </c>
       <c r="E10" t="n">
-        <v>3</v>
+        <v>15</v>
       </c>
       <c r="F10" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
     </row>
     <row r="11">
@@ -653,19 +653,19 @@
         </is>
       </c>
       <c r="B11" t="n">
-        <v>2</v>
+        <v>5</v>
       </c>
       <c r="C11" t="n">
-        <v>70</v>
+        <v>44</v>
       </c>
       <c r="D11" t="n">
-        <v>104</v>
+        <v>97</v>
       </c>
       <c r="E11" t="n">
-        <v>29</v>
+        <v>81</v>
       </c>
       <c r="F11" t="n">
-        <v>30</v>
+        <v>8</v>
       </c>
     </row>
     <row r="12">
@@ -678,16 +678,16 @@
         <v>6</v>
       </c>
       <c r="C12" t="n">
-        <v>68</v>
+        <v>19</v>
       </c>
       <c r="D12" t="n">
-        <v>67</v>
+        <v>95</v>
       </c>
       <c r="E12" t="n">
-        <v>24</v>
+        <v>59</v>
       </c>
       <c r="F12" t="n">
-        <v>18</v>
+        <v>4</v>
       </c>
     </row>
     <row r="13">
@@ -697,19 +697,19 @@
         </is>
       </c>
       <c r="B13" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="C13" t="n">
-        <v>49</v>
+        <v>22</v>
       </c>
       <c r="D13" t="n">
-        <v>85</v>
+        <v>65</v>
       </c>
       <c r="E13" t="n">
-        <v>12</v>
+        <v>72</v>
       </c>
       <c r="F13" t="n">
-        <v>14</v>
+        <v>0</v>
       </c>
     </row>
     <row r="14">
@@ -719,19 +719,19 @@
         </is>
       </c>
       <c r="B14" t="n">
-        <v>4</v>
+        <v>2</v>
       </c>
       <c r="C14" t="n">
-        <v>47</v>
+        <v>26</v>
       </c>
       <c r="D14" t="n">
-        <v>97</v>
+        <v>95</v>
       </c>
       <c r="E14" t="n">
-        <v>34</v>
+        <v>71</v>
       </c>
       <c r="F14" t="n">
-        <v>20</v>
+        <v>8</v>
       </c>
     </row>
     <row r="15">
@@ -744,16 +744,16 @@
         <v>0</v>
       </c>
       <c r="C15" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="D15" t="n">
+        <v>1</v>
+      </c>
+      <c r="E15" t="n">
         <v>2</v>
       </c>
-      <c r="E15" t="n">
-        <v>1</v>
-      </c>
       <c r="F15" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
     </row>
     <row r="16">
@@ -763,19 +763,19 @@
         </is>
       </c>
       <c r="B16" t="n">
-        <v>1</v>
+        <v>4</v>
       </c>
       <c r="C16" t="n">
-        <v>69</v>
+        <v>15</v>
       </c>
       <c r="D16" t="n">
-        <v>97</v>
+        <v>82</v>
       </c>
       <c r="E16" t="n">
-        <v>34</v>
+        <v>109</v>
       </c>
       <c r="F16" t="n">
-        <v>9</v>
+        <v>0</v>
       </c>
     </row>
     <row r="17">
@@ -788,13 +788,13 @@
         <v>0</v>
       </c>
       <c r="C17" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="D17" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="E17" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="F17" t="n">
         <v>0</v>
@@ -807,19 +807,19 @@
         </is>
       </c>
       <c r="B18" t="n">
-        <v>120</v>
+        <v>83</v>
       </c>
       <c r="C18" t="n">
-        <v>40</v>
+        <v>35</v>
       </c>
       <c r="D18" t="n">
-        <v>58</v>
+        <v>46</v>
       </c>
       <c r="E18" t="n">
-        <v>17</v>
+        <v>47</v>
       </c>
       <c r="F18" t="n">
-        <v>18</v>
+        <v>42</v>
       </c>
     </row>
     <row r="19">
@@ -829,19 +829,19 @@
         </is>
       </c>
       <c r="B19" t="n">
-        <v>214</v>
+        <v>153</v>
       </c>
       <c r="C19" t="n">
-        <v>88</v>
+        <v>29</v>
       </c>
       <c r="D19" t="n">
-        <v>115</v>
+        <v>133</v>
       </c>
       <c r="E19" t="n">
-        <v>23</v>
+        <v>83</v>
       </c>
       <c r="F19" t="n">
-        <v>28</v>
+        <v>70</v>
       </c>
     </row>
     <row r="20">
@@ -857,13 +857,13 @@
         <v>8</v>
       </c>
       <c r="D20" t="n">
-        <v>16</v>
+        <v>8</v>
       </c>
       <c r="E20" t="n">
-        <v>4</v>
+        <v>14</v>
       </c>
       <c r="F20" t="n">
-        <v>3</v>
+        <v>1</v>
       </c>
     </row>
     <row r="21">
@@ -873,19 +873,19 @@
         </is>
       </c>
       <c r="B21" t="n">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="C21" t="n">
-        <v>3</v>
+        <v>0</v>
       </c>
       <c r="D21" t="n">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="E21" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="F21" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
     </row>
     <row r="22">
@@ -898,16 +898,16 @@
         <v>5</v>
       </c>
       <c r="C22" t="n">
-        <v>42</v>
+        <v>29</v>
       </c>
       <c r="D22" t="n">
-        <v>64</v>
+        <v>67</v>
       </c>
       <c r="E22" t="n">
-        <v>32</v>
+        <v>62</v>
       </c>
       <c r="F22" t="n">
-        <v>25</v>
+        <v>5</v>
       </c>
     </row>
     <row r="23">
@@ -920,10 +920,10 @@
         <v>0</v>
       </c>
       <c r="C23" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="D23" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="E23" t="n">
         <v>3</v>
@@ -939,16 +939,16 @@
         </is>
       </c>
       <c r="B24" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="C24" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="D24" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="E24" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="F24" t="n">
         <v>0</v>
@@ -964,16 +964,16 @@
         <v>0</v>
       </c>
       <c r="C25" t="n">
-        <v>18</v>
+        <v>5</v>
       </c>
       <c r="D25" t="n">
-        <v>14</v>
+        <v>28</v>
       </c>
       <c r="E25" t="n">
-        <v>10</v>
+        <v>15</v>
       </c>
       <c r="F25" t="n">
-        <v>10</v>
+        <v>4</v>
       </c>
     </row>
     <row r="26">
@@ -989,10 +989,10 @@
         <v>0</v>
       </c>
       <c r="D26" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="E26" t="n">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="F26" t="n">
         <v>1</v>
@@ -1005,19 +1005,19 @@
         </is>
       </c>
       <c r="B27" t="n">
-        <v>88</v>
+        <v>55</v>
       </c>
       <c r="C27" t="n">
-        <v>35</v>
+        <v>9</v>
       </c>
       <c r="D27" t="n">
-        <v>39</v>
+        <v>53</v>
       </c>
       <c r="E27" t="n">
-        <v>18</v>
+        <v>38</v>
       </c>
       <c r="F27" t="n">
-        <v>20</v>
+        <v>45</v>
       </c>
     </row>
     <row r="28">
@@ -1033,10 +1033,10 @@
         <v>2</v>
       </c>
       <c r="D28" t="n">
+        <v>3</v>
+      </c>
+      <c r="E28" t="n">
         <v>6</v>
-      </c>
-      <c r="E28" t="n">
-        <v>3</v>
       </c>
       <c r="F28" t="n">
         <v>0</v>
@@ -1049,19 +1049,19 @@
         </is>
       </c>
       <c r="B29" t="n">
-        <v>21</v>
+        <v>11</v>
       </c>
       <c r="C29" t="n">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="D29" t="n">
-        <v>12</v>
+        <v>11</v>
       </c>
       <c r="E29" t="n">
-        <v>2</v>
+        <v>5</v>
       </c>
       <c r="F29" t="n">
-        <v>4</v>
+        <v>11</v>
       </c>
     </row>
     <row r="30">
@@ -1074,16 +1074,16 @@
         <v>1</v>
       </c>
       <c r="C30" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="D30" t="n">
         <v>3</v>
       </c>
       <c r="E30" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="F30" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
     </row>
     <row r="31">
@@ -1096,16 +1096,16 @@
         <v>2</v>
       </c>
       <c r="C31" t="n">
-        <v>25</v>
+        <v>3</v>
       </c>
       <c r="D31" t="n">
-        <v>13</v>
+        <v>15</v>
       </c>
       <c r="E31" t="n">
-        <v>12</v>
+        <v>40</v>
       </c>
       <c r="F31" t="n">
-        <v>12</v>
+        <v>4</v>
       </c>
     </row>
     <row r="32">
@@ -1115,19 +1115,19 @@
         </is>
       </c>
       <c r="B32" t="n">
-        <v>101</v>
+        <v>70</v>
       </c>
       <c r="C32" t="n">
-        <v>33</v>
+        <v>24</v>
       </c>
       <c r="D32" t="n">
-        <v>50</v>
+        <v>47</v>
       </c>
       <c r="E32" t="n">
-        <v>32</v>
+        <v>56</v>
       </c>
       <c r="F32" t="n">
-        <v>23</v>
+        <v>42</v>
       </c>
     </row>
     <row r="33">
@@ -1137,19 +1137,19 @@
         </is>
       </c>
       <c r="B33" t="n">
-        <v>15</v>
+        <v>14</v>
       </c>
       <c r="C33" t="n">
-        <v>4</v>
+        <v>0</v>
       </c>
       <c r="D33" t="n">
-        <v>10</v>
+        <v>8</v>
       </c>
       <c r="E33" t="n">
-        <v>2</v>
+        <v>8</v>
       </c>
       <c r="F33" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
     </row>
   </sheetData>

--- a/data/output/topik_per_lokasi.xlsx
+++ b/data/output/topik_per_lokasi.xlsx
@@ -455,19 +455,19 @@
         </is>
       </c>
       <c r="B2" t="n">
-        <v>39</v>
+        <v>48</v>
       </c>
       <c r="C2" t="n">
-        <v>3</v>
+        <v>10</v>
       </c>
       <c r="D2" t="n">
-        <v>13</v>
+        <v>14</v>
       </c>
       <c r="E2" t="n">
-        <v>28</v>
+        <v>5</v>
       </c>
       <c r="F2" t="n">
-        <v>11</v>
+        <v>17</v>
       </c>
     </row>
     <row r="3">
@@ -477,19 +477,19 @@
         </is>
       </c>
       <c r="B3" t="n">
-        <v>135</v>
+        <v>203</v>
       </c>
       <c r="C3" t="n">
-        <v>32</v>
+        <v>74</v>
       </c>
       <c r="D3" t="n">
-        <v>131</v>
+        <v>122</v>
       </c>
       <c r="E3" t="n">
-        <v>124</v>
+        <v>33</v>
       </c>
       <c r="F3" t="n">
-        <v>75</v>
+        <v>65</v>
       </c>
     </row>
     <row r="4">
@@ -499,10 +499,10 @@
         </is>
       </c>
       <c r="B4" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="C4" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="D4" t="n">
         <v>0</v>
@@ -521,19 +521,19 @@
         </is>
       </c>
       <c r="B5" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="C5" t="n">
-        <v>0</v>
+        <v>4</v>
       </c>
       <c r="D5" t="n">
-        <v>7</v>
+        <v>3</v>
       </c>
       <c r="E5" t="n">
+        <v>4</v>
+      </c>
+      <c r="F5" t="n">
         <v>10</v>
-      </c>
-      <c r="F5" t="n">
-        <v>2</v>
       </c>
     </row>
     <row r="6">
@@ -546,7 +546,7 @@
         <v>0</v>
       </c>
       <c r="C6" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="D6" t="n">
         <v>0</v>
@@ -555,7 +555,7 @@
         <v>0</v>
       </c>
       <c r="F6" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
     </row>
     <row r="7">
@@ -568,16 +568,16 @@
         <v>0</v>
       </c>
       <c r="C7" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="D7" t="n">
         <v>1</v>
       </c>
       <c r="E7" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="F7" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
     </row>
     <row r="8">
@@ -587,19 +587,19 @@
         </is>
       </c>
       <c r="B8" t="n">
-        <v>5</v>
+        <v>3</v>
       </c>
       <c r="C8" t="n">
-        <v>51</v>
+        <v>57</v>
       </c>
       <c r="D8" t="n">
-        <v>48</v>
+        <v>24</v>
       </c>
       <c r="E8" t="n">
-        <v>77</v>
+        <v>39</v>
       </c>
       <c r="F8" t="n">
-        <v>16</v>
+        <v>74</v>
       </c>
     </row>
     <row r="9">
@@ -609,19 +609,19 @@
         </is>
       </c>
       <c r="B9" t="n">
-        <v>137</v>
+        <v>238</v>
       </c>
       <c r="C9" t="n">
-        <v>31</v>
+        <v>45</v>
       </c>
       <c r="D9" t="n">
-        <v>99</v>
+        <v>89</v>
       </c>
       <c r="E9" t="n">
-        <v>123</v>
+        <v>71</v>
       </c>
       <c r="F9" t="n">
-        <v>130</v>
+        <v>77</v>
       </c>
     </row>
     <row r="10">
@@ -634,16 +634,16 @@
         <v>0</v>
       </c>
       <c r="C10" t="n">
-        <v>8</v>
+        <v>4</v>
       </c>
       <c r="D10" t="n">
         <v>16</v>
       </c>
       <c r="E10" t="n">
-        <v>15</v>
+        <v>2</v>
       </c>
       <c r="F10" t="n">
-        <v>0</v>
+        <v>17</v>
       </c>
     </row>
     <row r="11">
@@ -653,19 +653,19 @@
         </is>
       </c>
       <c r="B11" t="n">
-        <v>5</v>
+        <v>2</v>
       </c>
       <c r="C11" t="n">
-        <v>44</v>
+        <v>18</v>
       </c>
       <c r="D11" t="n">
-        <v>97</v>
+        <v>79</v>
       </c>
       <c r="E11" t="n">
-        <v>81</v>
+        <v>12</v>
       </c>
       <c r="F11" t="n">
-        <v>8</v>
+        <v>124</v>
       </c>
     </row>
     <row r="12">
@@ -675,19 +675,19 @@
         </is>
       </c>
       <c r="B12" t="n">
-        <v>6</v>
+        <v>5</v>
       </c>
       <c r="C12" t="n">
-        <v>19</v>
+        <v>7</v>
       </c>
       <c r="D12" t="n">
-        <v>95</v>
+        <v>64</v>
       </c>
       <c r="E12" t="n">
-        <v>59</v>
+        <v>5</v>
       </c>
       <c r="F12" t="n">
-        <v>4</v>
+        <v>102</v>
       </c>
     </row>
     <row r="13">
@@ -697,19 +697,19 @@
         </is>
       </c>
       <c r="B13" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="C13" t="n">
-        <v>22</v>
+        <v>11</v>
       </c>
       <c r="D13" t="n">
-        <v>65</v>
+        <v>76</v>
       </c>
       <c r="E13" t="n">
-        <v>72</v>
+        <v>3</v>
       </c>
       <c r="F13" t="n">
-        <v>0</v>
+        <v>70</v>
       </c>
     </row>
     <row r="14">
@@ -719,19 +719,19 @@
         </is>
       </c>
       <c r="B14" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="C14" t="n">
+        <v>24</v>
+      </c>
+      <c r="D14" t="n">
+        <v>67</v>
+      </c>
+      <c r="E14" t="n">
         <v>26</v>
       </c>
-      <c r="D14" t="n">
-        <v>95</v>
-      </c>
-      <c r="E14" t="n">
-        <v>71</v>
-      </c>
       <c r="F14" t="n">
-        <v>8</v>
+        <v>84</v>
       </c>
     </row>
     <row r="15">
@@ -744,16 +744,16 @@
         <v>0</v>
       </c>
       <c r="C15" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="D15" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="E15" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="F15" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
     </row>
     <row r="16">
@@ -763,19 +763,19 @@
         </is>
       </c>
       <c r="B16" t="n">
-        <v>4</v>
+        <v>2</v>
       </c>
       <c r="C16" t="n">
-        <v>15</v>
+        <v>9</v>
       </c>
       <c r="D16" t="n">
-        <v>82</v>
+        <v>91</v>
       </c>
       <c r="E16" t="n">
-        <v>109</v>
+        <v>11</v>
       </c>
       <c r="F16" t="n">
-        <v>0</v>
+        <v>97</v>
       </c>
     </row>
     <row r="17">
@@ -794,10 +794,10 @@
         <v>1</v>
       </c>
       <c r="E17" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="F17" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
     </row>
     <row r="18">
@@ -807,19 +807,19 @@
         </is>
       </c>
       <c r="B18" t="n">
-        <v>83</v>
+        <v>119</v>
       </c>
       <c r="C18" t="n">
-        <v>35</v>
+        <v>17</v>
       </c>
       <c r="D18" t="n">
-        <v>46</v>
+        <v>36</v>
       </c>
       <c r="E18" t="n">
-        <v>47</v>
+        <v>7</v>
       </c>
       <c r="F18" t="n">
-        <v>42</v>
+        <v>74</v>
       </c>
     </row>
     <row r="19">
@@ -829,19 +829,19 @@
         </is>
       </c>
       <c r="B19" t="n">
-        <v>153</v>
+        <v>217</v>
       </c>
       <c r="C19" t="n">
-        <v>29</v>
+        <v>22</v>
       </c>
       <c r="D19" t="n">
-        <v>133</v>
+        <v>91</v>
       </c>
       <c r="E19" t="n">
-        <v>83</v>
+        <v>21</v>
       </c>
       <c r="F19" t="n">
-        <v>70</v>
+        <v>117</v>
       </c>
     </row>
     <row r="20">
@@ -854,16 +854,16 @@
         <v>0</v>
       </c>
       <c r="C20" t="n">
-        <v>8</v>
+        <v>2</v>
       </c>
       <c r="D20" t="n">
-        <v>8</v>
+        <v>5</v>
       </c>
       <c r="E20" t="n">
-        <v>14</v>
+        <v>6</v>
       </c>
       <c r="F20" t="n">
-        <v>1</v>
+        <v>18</v>
       </c>
     </row>
     <row r="21">
@@ -873,19 +873,19 @@
         </is>
       </c>
       <c r="B21" t="n">
+        <v>4</v>
+      </c>
+      <c r="C21" t="n">
+        <v>0</v>
+      </c>
+      <c r="D21" t="n">
         <v>3</v>
       </c>
-      <c r="C21" t="n">
-        <v>0</v>
-      </c>
-      <c r="D21" t="n">
-        <v>4</v>
-      </c>
       <c r="E21" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="F21" t="n">
-        <v>1</v>
+        <v>3</v>
       </c>
     </row>
     <row r="22">
@@ -895,19 +895,19 @@
         </is>
       </c>
       <c r="B22" t="n">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="C22" t="n">
+        <v>17</v>
+      </c>
+      <c r="D22" t="n">
+        <v>46</v>
+      </c>
+      <c r="E22" t="n">
         <v>29</v>
       </c>
-      <c r="D22" t="n">
-        <v>67</v>
-      </c>
-      <c r="E22" t="n">
-        <v>62</v>
-      </c>
       <c r="F22" t="n">
-        <v>5</v>
+        <v>72</v>
       </c>
     </row>
     <row r="23">
@@ -920,16 +920,16 @@
         <v>0</v>
       </c>
       <c r="C23" t="n">
+        <v>0</v>
+      </c>
+      <c r="D23" t="n">
+        <v>4</v>
+      </c>
+      <c r="E23" t="n">
+        <v>0</v>
+      </c>
+      <c r="F23" t="n">
         <v>2</v>
-      </c>
-      <c r="D23" t="n">
-        <v>1</v>
-      </c>
-      <c r="E23" t="n">
-        <v>3</v>
-      </c>
-      <c r="F23" t="n">
-        <v>0</v>
       </c>
     </row>
     <row r="24">
@@ -939,19 +939,19 @@
         </is>
       </c>
       <c r="B24" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="C24" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="D24" t="n">
         <v>0</v>
       </c>
       <c r="E24" t="n">
+        <v>0</v>
+      </c>
+      <c r="F24" t="n">
         <v>2</v>
-      </c>
-      <c r="F24" t="n">
-        <v>0</v>
       </c>
     </row>
     <row r="25">
@@ -964,16 +964,16 @@
         <v>0</v>
       </c>
       <c r="C25" t="n">
-        <v>5</v>
+        <v>3</v>
       </c>
       <c r="D25" t="n">
-        <v>28</v>
+        <v>15</v>
       </c>
       <c r="E25" t="n">
-        <v>15</v>
+        <v>10</v>
       </c>
       <c r="F25" t="n">
-        <v>4</v>
+        <v>24</v>
       </c>
     </row>
     <row r="26">
@@ -986,16 +986,16 @@
         <v>0</v>
       </c>
       <c r="C26" t="n">
-        <v>0</v>
+        <v>3</v>
       </c>
       <c r="D26" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="E26" t="n">
-        <v>5</v>
+        <v>0</v>
       </c>
       <c r="F26" t="n">
-        <v>1</v>
+        <v>4</v>
       </c>
     </row>
     <row r="27">
@@ -1005,19 +1005,19 @@
         </is>
       </c>
       <c r="B27" t="n">
-        <v>55</v>
+        <v>89</v>
       </c>
       <c r="C27" t="n">
-        <v>9</v>
+        <v>21</v>
       </c>
       <c r="D27" t="n">
-        <v>53</v>
+        <v>35</v>
       </c>
       <c r="E27" t="n">
-        <v>38</v>
+        <v>13</v>
       </c>
       <c r="F27" t="n">
-        <v>45</v>
+        <v>42</v>
       </c>
     </row>
     <row r="28">
@@ -1033,13 +1033,13 @@
         <v>2</v>
       </c>
       <c r="D28" t="n">
+        <v>6</v>
+      </c>
+      <c r="E28" t="n">
+        <v>0</v>
+      </c>
+      <c r="F28" t="n">
         <v>3</v>
-      </c>
-      <c r="E28" t="n">
-        <v>6</v>
-      </c>
-      <c r="F28" t="n">
-        <v>0</v>
       </c>
     </row>
     <row r="29">
@@ -1049,19 +1049,19 @@
         </is>
       </c>
       <c r="B29" t="n">
-        <v>11</v>
+        <v>22</v>
       </c>
       <c r="C29" t="n">
-        <v>5</v>
+        <v>3</v>
       </c>
       <c r="D29" t="n">
-        <v>11</v>
+        <v>7</v>
       </c>
       <c r="E29" t="n">
-        <v>5</v>
+        <v>3</v>
       </c>
       <c r="F29" t="n">
-        <v>11</v>
+        <v>8</v>
       </c>
     </row>
     <row r="30">
@@ -1071,19 +1071,19 @@
         </is>
       </c>
       <c r="B30" t="n">
-        <v>1</v>
+        <v>6</v>
       </c>
       <c r="C30" t="n">
         <v>1</v>
       </c>
       <c r="D30" t="n">
+        <v>1</v>
+      </c>
+      <c r="E30" t="n">
+        <v>1</v>
+      </c>
+      <c r="F30" t="n">
         <v>3</v>
-      </c>
-      <c r="E30" t="n">
-        <v>2</v>
-      </c>
-      <c r="F30" t="n">
-        <v>0</v>
       </c>
     </row>
     <row r="31">
@@ -1093,19 +1093,19 @@
         </is>
       </c>
       <c r="B31" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="C31" t="n">
-        <v>3</v>
+        <v>14</v>
       </c>
       <c r="D31" t="n">
-        <v>15</v>
+        <v>20</v>
       </c>
       <c r="E31" t="n">
-        <v>40</v>
+        <v>8</v>
       </c>
       <c r="F31" t="n">
-        <v>4</v>
+        <v>22</v>
       </c>
     </row>
     <row r="32">
@@ -1115,19 +1115,19 @@
         </is>
       </c>
       <c r="B32" t="n">
-        <v>70</v>
+        <v>102</v>
       </c>
       <c r="C32" t="n">
-        <v>24</v>
+        <v>16</v>
       </c>
       <c r="D32" t="n">
-        <v>47</v>
+        <v>40</v>
       </c>
       <c r="E32" t="n">
-        <v>56</v>
+        <v>18</v>
       </c>
       <c r="F32" t="n">
-        <v>42</v>
+        <v>63</v>
       </c>
     </row>
     <row r="33">
@@ -1137,19 +1137,19 @@
         </is>
       </c>
       <c r="B33" t="n">
-        <v>14</v>
+        <v>15</v>
       </c>
       <c r="C33" t="n">
         <v>0</v>
       </c>
       <c r="D33" t="n">
-        <v>8</v>
+        <v>4</v>
       </c>
       <c r="E33" t="n">
-        <v>8</v>
+        <v>2</v>
       </c>
       <c r="F33" t="n">
-        <v>1</v>
+        <v>10</v>
       </c>
     </row>
   </sheetData>

--- a/data/output/topik_per_lokasi.xlsx
+++ b/data/output/topik_per_lokasi.xlsx
@@ -455,19 +455,19 @@
         </is>
       </c>
       <c r="B2" t="n">
-        <v>48</v>
+        <v>47</v>
       </c>
       <c r="C2" t="n">
-        <v>10</v>
+        <v>0</v>
       </c>
       <c r="D2" t="n">
-        <v>14</v>
+        <v>3</v>
       </c>
       <c r="E2" t="n">
-        <v>5</v>
+        <v>43</v>
       </c>
       <c r="F2" t="n">
-        <v>17</v>
+        <v>1</v>
       </c>
     </row>
     <row r="3">
@@ -477,19 +477,19 @@
         </is>
       </c>
       <c r="B3" t="n">
-        <v>203</v>
+        <v>183</v>
       </c>
       <c r="C3" t="n">
-        <v>74</v>
+        <v>54</v>
       </c>
       <c r="D3" t="n">
-        <v>122</v>
+        <v>19</v>
       </c>
       <c r="E3" t="n">
-        <v>33</v>
+        <v>220</v>
       </c>
       <c r="F3" t="n">
-        <v>65</v>
+        <v>21</v>
       </c>
     </row>
     <row r="4">
@@ -502,7 +502,7 @@
         <v>1</v>
       </c>
       <c r="C4" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="D4" t="n">
         <v>0</v>
@@ -511,7 +511,7 @@
         <v>1</v>
       </c>
       <c r="F4" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
     </row>
     <row r="5">
@@ -524,16 +524,16 @@
         <v>0</v>
       </c>
       <c r="C5" t="n">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="D5" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="E5" t="n">
-        <v>4</v>
+        <v>13</v>
       </c>
       <c r="F5" t="n">
-        <v>10</v>
+        <v>1</v>
       </c>
     </row>
     <row r="6">
@@ -552,10 +552,10 @@
         <v>0</v>
       </c>
       <c r="E6" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="F6" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
     </row>
     <row r="7">
@@ -571,13 +571,13 @@
         <v>0</v>
       </c>
       <c r="D7" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="E7" t="n">
-        <v>0</v>
+        <v>3</v>
       </c>
       <c r="F7" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
     </row>
     <row r="8">
@@ -587,19 +587,19 @@
         </is>
       </c>
       <c r="B8" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="C8" t="n">
-        <v>57</v>
+        <v>55</v>
       </c>
       <c r="D8" t="n">
-        <v>24</v>
+        <v>30</v>
       </c>
       <c r="E8" t="n">
-        <v>39</v>
+        <v>103</v>
       </c>
       <c r="F8" t="n">
-        <v>74</v>
+        <v>7</v>
       </c>
     </row>
     <row r="9">
@@ -609,19 +609,19 @@
         </is>
       </c>
       <c r="B9" t="n">
-        <v>238</v>
+        <v>231</v>
       </c>
       <c r="C9" t="n">
-        <v>45</v>
+        <v>40</v>
       </c>
       <c r="D9" t="n">
-        <v>89</v>
+        <v>15</v>
       </c>
       <c r="E9" t="n">
-        <v>71</v>
+        <v>218</v>
       </c>
       <c r="F9" t="n">
-        <v>77</v>
+        <v>16</v>
       </c>
     </row>
     <row r="10">
@@ -634,16 +634,16 @@
         <v>0</v>
       </c>
       <c r="C10" t="n">
-        <v>4</v>
+        <v>2</v>
       </c>
       <c r="D10" t="n">
-        <v>16</v>
+        <v>1</v>
       </c>
       <c r="E10" t="n">
-        <v>2</v>
+        <v>36</v>
       </c>
       <c r="F10" t="n">
-        <v>17</v>
+        <v>0</v>
       </c>
     </row>
     <row r="11">
@@ -653,19 +653,19 @@
         </is>
       </c>
       <c r="B11" t="n">
-        <v>2</v>
+        <v>4</v>
       </c>
       <c r="C11" t="n">
-        <v>18</v>
+        <v>11</v>
       </c>
       <c r="D11" t="n">
-        <v>79</v>
+        <v>10</v>
       </c>
       <c r="E11" t="n">
-        <v>12</v>
+        <v>207</v>
       </c>
       <c r="F11" t="n">
-        <v>124</v>
+        <v>3</v>
       </c>
     </row>
     <row r="12">
@@ -675,19 +675,19 @@
         </is>
       </c>
       <c r="B12" t="n">
+        <v>144</v>
+      </c>
+      <c r="C12" t="n">
+        <v>10</v>
+      </c>
+      <c r="D12" t="n">
         <v>5</v>
       </c>
-      <c r="C12" t="n">
-        <v>7</v>
-      </c>
-      <c r="D12" t="n">
-        <v>64</v>
-      </c>
       <c r="E12" t="n">
-        <v>5</v>
+        <v>163</v>
       </c>
       <c r="F12" t="n">
-        <v>102</v>
+        <v>9</v>
       </c>
     </row>
     <row r="13">
@@ -700,16 +700,16 @@
         <v>0</v>
       </c>
       <c r="C13" t="n">
-        <v>11</v>
+        <v>6</v>
       </c>
       <c r="D13" t="n">
-        <v>76</v>
+        <v>1</v>
       </c>
       <c r="E13" t="n">
-        <v>3</v>
+        <v>152</v>
       </c>
       <c r="F13" t="n">
-        <v>70</v>
+        <v>1</v>
       </c>
     </row>
     <row r="14">
@@ -722,16 +722,16 @@
         <v>1</v>
       </c>
       <c r="C14" t="n">
-        <v>24</v>
+        <v>13</v>
       </c>
       <c r="D14" t="n">
-        <v>67</v>
+        <v>11</v>
       </c>
       <c r="E14" t="n">
-        <v>26</v>
+        <v>175</v>
       </c>
       <c r="F14" t="n">
-        <v>84</v>
+        <v>2</v>
       </c>
     </row>
     <row r="15">
@@ -744,16 +744,16 @@
         <v>0</v>
       </c>
       <c r="C15" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="D15" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="E15" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="F15" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
     </row>
     <row r="16">
@@ -763,19 +763,19 @@
         </is>
       </c>
       <c r="B16" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="C16" t="n">
         <v>9</v>
       </c>
       <c r="D16" t="n">
-        <v>91</v>
+        <v>4</v>
       </c>
       <c r="E16" t="n">
-        <v>11</v>
+        <v>196</v>
       </c>
       <c r="F16" t="n">
-        <v>97</v>
+        <v>1</v>
       </c>
     </row>
     <row r="17">
@@ -791,13 +791,13 @@
         <v>0</v>
       </c>
       <c r="D17" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="E17" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="F17" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
     </row>
     <row r="18">
@@ -807,19 +807,19 @@
         </is>
       </c>
       <c r="B18" t="n">
-        <v>119</v>
+        <v>117</v>
       </c>
       <c r="C18" t="n">
-        <v>17</v>
+        <v>12</v>
       </c>
       <c r="D18" t="n">
-        <v>36</v>
+        <v>5</v>
       </c>
       <c r="E18" t="n">
-        <v>7</v>
+        <v>111</v>
       </c>
       <c r="F18" t="n">
-        <v>74</v>
+        <v>8</v>
       </c>
     </row>
     <row r="19">
@@ -829,19 +829,19 @@
         </is>
       </c>
       <c r="B19" t="n">
-        <v>217</v>
+        <v>208</v>
       </c>
       <c r="C19" t="n">
-        <v>22</v>
+        <v>17</v>
       </c>
       <c r="D19" t="n">
-        <v>91</v>
+        <v>15</v>
       </c>
       <c r="E19" t="n">
-        <v>21</v>
+        <v>219</v>
       </c>
       <c r="F19" t="n">
-        <v>117</v>
+        <v>9</v>
       </c>
     </row>
     <row r="20">
@@ -857,13 +857,13 @@
         <v>2</v>
       </c>
       <c r="D20" t="n">
-        <v>5</v>
+        <v>1</v>
       </c>
       <c r="E20" t="n">
-        <v>6</v>
+        <v>28</v>
       </c>
       <c r="F20" t="n">
-        <v>18</v>
+        <v>0</v>
       </c>
     </row>
     <row r="21">
@@ -873,19 +873,19 @@
         </is>
       </c>
       <c r="B21" t="n">
+        <v>3</v>
+      </c>
+      <c r="C21" t="n">
+        <v>2</v>
+      </c>
+      <c r="D21" t="n">
+        <v>0</v>
+      </c>
+      <c r="E21" t="n">
         <v>4</v>
       </c>
-      <c r="C21" t="n">
-        <v>0</v>
-      </c>
-      <c r="D21" t="n">
-        <v>3</v>
-      </c>
-      <c r="E21" t="n">
-        <v>0</v>
-      </c>
       <c r="F21" t="n">
-        <v>3</v>
+        <v>1</v>
       </c>
     </row>
     <row r="22">
@@ -895,19 +895,19 @@
         </is>
       </c>
       <c r="B22" t="n">
-        <v>4</v>
+        <v>0</v>
       </c>
       <c r="C22" t="n">
-        <v>17</v>
+        <v>24</v>
       </c>
       <c r="D22" t="n">
-        <v>46</v>
+        <v>12</v>
       </c>
       <c r="E22" t="n">
-        <v>29</v>
+        <v>126</v>
       </c>
       <c r="F22" t="n">
-        <v>72</v>
+        <v>6</v>
       </c>
     </row>
     <row r="23">
@@ -920,16 +920,16 @@
         <v>0</v>
       </c>
       <c r="C23" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="D23" t="n">
+        <v>0</v>
+      </c>
+      <c r="E23" t="n">
         <v>4</v>
       </c>
-      <c r="E23" t="n">
-        <v>0</v>
-      </c>
       <c r="F23" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
     </row>
     <row r="24">
@@ -939,19 +939,19 @@
         </is>
       </c>
       <c r="B24" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="C24" t="n">
         <v>0</v>
       </c>
       <c r="D24" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="E24" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="F24" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
     </row>
     <row r="25">
@@ -967,13 +967,13 @@
         <v>3</v>
       </c>
       <c r="D25" t="n">
-        <v>15</v>
+        <v>1</v>
       </c>
       <c r="E25" t="n">
-        <v>10</v>
+        <v>45</v>
       </c>
       <c r="F25" t="n">
-        <v>24</v>
+        <v>3</v>
       </c>
     </row>
     <row r="26">
@@ -986,16 +986,16 @@
         <v>0</v>
       </c>
       <c r="C26" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="D26" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="E26" t="n">
-        <v>0</v>
+        <v>6</v>
       </c>
       <c r="F26" t="n">
-        <v>4</v>
+        <v>0</v>
       </c>
     </row>
     <row r="27">
@@ -1005,19 +1005,19 @@
         </is>
       </c>
       <c r="B27" t="n">
-        <v>89</v>
+        <v>91</v>
       </c>
       <c r="C27" t="n">
-        <v>21</v>
+        <v>9</v>
       </c>
       <c r="D27" t="n">
-        <v>35</v>
+        <v>5</v>
       </c>
       <c r="E27" t="n">
-        <v>13</v>
+        <v>88</v>
       </c>
       <c r="F27" t="n">
-        <v>42</v>
+        <v>7</v>
       </c>
     </row>
     <row r="28">
@@ -1030,16 +1030,16 @@
         <v>3</v>
       </c>
       <c r="C28" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="D28" t="n">
-        <v>6</v>
+        <v>0</v>
       </c>
       <c r="E28" t="n">
-        <v>0</v>
+        <v>11</v>
       </c>
       <c r="F28" t="n">
-        <v>3</v>
+        <v>0</v>
       </c>
     </row>
     <row r="29">
@@ -1049,19 +1049,19 @@
         </is>
       </c>
       <c r="B29" t="n">
-        <v>22</v>
+        <v>21</v>
       </c>
       <c r="C29" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="D29" t="n">
-        <v>7</v>
+        <v>0</v>
       </c>
       <c r="E29" t="n">
-        <v>3</v>
+        <v>18</v>
       </c>
       <c r="F29" t="n">
-        <v>8</v>
+        <v>2</v>
       </c>
     </row>
     <row r="30">
@@ -1071,19 +1071,19 @@
         </is>
       </c>
       <c r="B30" t="n">
+        <v>4</v>
+      </c>
+      <c r="C30" t="n">
+        <v>1</v>
+      </c>
+      <c r="D30" t="n">
+        <v>0</v>
+      </c>
+      <c r="E30" t="n">
         <v>6</v>
       </c>
-      <c r="C30" t="n">
-        <v>1</v>
-      </c>
-      <c r="D30" t="n">
-        <v>1</v>
-      </c>
-      <c r="E30" t="n">
-        <v>1</v>
-      </c>
       <c r="F30" t="n">
-        <v>3</v>
+        <v>1</v>
       </c>
     </row>
     <row r="31">
@@ -1093,19 +1093,19 @@
         </is>
       </c>
       <c r="B31" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="C31" t="n">
-        <v>14</v>
+        <v>6</v>
       </c>
       <c r="D31" t="n">
-        <v>20</v>
+        <v>5</v>
       </c>
       <c r="E31" t="n">
-        <v>8</v>
+        <v>49</v>
       </c>
       <c r="F31" t="n">
-        <v>22</v>
+        <v>3</v>
       </c>
     </row>
     <row r="32">
@@ -1115,19 +1115,19 @@
         </is>
       </c>
       <c r="B32" t="n">
-        <v>102</v>
+        <v>97</v>
       </c>
       <c r="C32" t="n">
         <v>16</v>
       </c>
       <c r="D32" t="n">
-        <v>40</v>
+        <v>5</v>
       </c>
       <c r="E32" t="n">
-        <v>18</v>
+        <v>110</v>
       </c>
       <c r="F32" t="n">
-        <v>63</v>
+        <v>11</v>
       </c>
     </row>
     <row r="33">
@@ -1137,19 +1137,19 @@
         </is>
       </c>
       <c r="B33" t="n">
-        <v>15</v>
+        <v>14</v>
       </c>
       <c r="C33" t="n">
         <v>0</v>
       </c>
       <c r="D33" t="n">
-        <v>4</v>
+        <v>1</v>
       </c>
       <c r="E33" t="n">
-        <v>2</v>
+        <v>16</v>
       </c>
       <c r="F33" t="n">
-        <v>10</v>
+        <v>0</v>
       </c>
     </row>
   </sheetData>

--- a/data/output/topik_per_lokasi.xlsx
+++ b/data/output/topik_per_lokasi.xlsx
@@ -455,19 +455,19 @@
         </is>
       </c>
       <c r="B2" t="n">
-        <v>47</v>
+        <v>43</v>
       </c>
       <c r="C2" t="n">
         <v>0</v>
       </c>
       <c r="D2" t="n">
-        <v>3</v>
+        <v>8</v>
       </c>
       <c r="E2" t="n">
-        <v>43</v>
+        <v>38</v>
       </c>
       <c r="F2" t="n">
-        <v>1</v>
+        <v>5</v>
       </c>
     </row>
     <row r="3">
@@ -477,19 +477,19 @@
         </is>
       </c>
       <c r="B3" t="n">
-        <v>183</v>
+        <v>193</v>
       </c>
       <c r="C3" t="n">
-        <v>54</v>
+        <v>16</v>
       </c>
       <c r="D3" t="n">
-        <v>19</v>
+        <v>131</v>
       </c>
       <c r="E3" t="n">
-        <v>220</v>
+        <v>142</v>
       </c>
       <c r="F3" t="n">
-        <v>21</v>
+        <v>15</v>
       </c>
     </row>
     <row r="4">
@@ -502,16 +502,16 @@
         <v>1</v>
       </c>
       <c r="C4" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="D4" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="E4" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="F4" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
     </row>
     <row r="5">
@@ -521,19 +521,19 @@
         </is>
       </c>
       <c r="B5" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="C5" t="n">
+        <v>1</v>
+      </c>
+      <c r="D5" t="n">
         <v>5</v>
       </c>
-      <c r="D5" t="n">
-        <v>2</v>
-      </c>
       <c r="E5" t="n">
-        <v>13</v>
+        <v>14</v>
       </c>
       <c r="F5" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
     </row>
     <row r="6">
@@ -552,10 +552,10 @@
         <v>0</v>
       </c>
       <c r="E6" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="F6" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
     </row>
     <row r="7">
@@ -571,10 +571,10 @@
         <v>0</v>
       </c>
       <c r="D7" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="E7" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="F7" t="n">
         <v>0</v>
@@ -587,19 +587,19 @@
         </is>
       </c>
       <c r="B8" t="n">
-        <v>2</v>
+        <v>5</v>
       </c>
       <c r="C8" t="n">
-        <v>55</v>
+        <v>9</v>
       </c>
       <c r="D8" t="n">
-        <v>30</v>
+        <v>75</v>
       </c>
       <c r="E8" t="n">
-        <v>103</v>
+        <v>95</v>
       </c>
       <c r="F8" t="n">
-        <v>7</v>
+        <v>13</v>
       </c>
     </row>
     <row r="9">
@@ -609,19 +609,19 @@
         </is>
       </c>
       <c r="B9" t="n">
-        <v>231</v>
+        <v>229</v>
       </c>
       <c r="C9" t="n">
-        <v>40</v>
+        <v>17</v>
       </c>
       <c r="D9" t="n">
-        <v>15</v>
+        <v>107</v>
       </c>
       <c r="E9" t="n">
-        <v>218</v>
+        <v>150</v>
       </c>
       <c r="F9" t="n">
-        <v>16</v>
+        <v>17</v>
       </c>
     </row>
     <row r="10">
@@ -634,13 +634,13 @@
         <v>0</v>
       </c>
       <c r="C10" t="n">
+        <v>0</v>
+      </c>
+      <c r="D10" t="n">
         <v>2</v>
       </c>
-      <c r="D10" t="n">
-        <v>1</v>
-      </c>
       <c r="E10" t="n">
-        <v>36</v>
+        <v>37</v>
       </c>
       <c r="F10" t="n">
         <v>0</v>
@@ -653,19 +653,19 @@
         </is>
       </c>
       <c r="B11" t="n">
-        <v>4</v>
+        <v>2</v>
       </c>
       <c r="C11" t="n">
-        <v>11</v>
+        <v>10</v>
       </c>
       <c r="D11" t="n">
-        <v>10</v>
+        <v>12</v>
       </c>
       <c r="E11" t="n">
-        <v>207</v>
+        <v>193</v>
       </c>
       <c r="F11" t="n">
-        <v>3</v>
+        <v>18</v>
       </c>
     </row>
     <row r="12">
@@ -675,19 +675,19 @@
         </is>
       </c>
       <c r="B12" t="n">
-        <v>144</v>
+        <v>138</v>
       </c>
       <c r="C12" t="n">
+        <v>7</v>
+      </c>
+      <c r="D12" t="n">
         <v>10</v>
       </c>
-      <c r="D12" t="n">
-        <v>5</v>
-      </c>
       <c r="E12" t="n">
-        <v>163</v>
+        <v>165</v>
       </c>
       <c r="F12" t="n">
-        <v>9</v>
+        <v>11</v>
       </c>
     </row>
     <row r="13">
@@ -700,16 +700,16 @@
         <v>0</v>
       </c>
       <c r="C13" t="n">
+        <v>0</v>
+      </c>
+      <c r="D13" t="n">
         <v>6</v>
       </c>
-      <c r="D13" t="n">
-        <v>1</v>
-      </c>
       <c r="E13" t="n">
-        <v>152</v>
+        <v>154</v>
       </c>
       <c r="F13" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
     </row>
     <row r="14">
@@ -719,19 +719,19 @@
         </is>
       </c>
       <c r="B14" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="C14" t="n">
-        <v>13</v>
+        <v>6</v>
       </c>
       <c r="D14" t="n">
-        <v>11</v>
+        <v>21</v>
       </c>
       <c r="E14" t="n">
-        <v>175</v>
+        <v>165</v>
       </c>
       <c r="F14" t="n">
-        <v>2</v>
+        <v>8</v>
       </c>
     </row>
     <row r="15">
@@ -741,19 +741,19 @@
         </is>
       </c>
       <c r="B15" t="n">
-        <v>0</v>
+        <v>3</v>
       </c>
       <c r="C15" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="D15" t="n">
         <v>0</v>
       </c>
       <c r="E15" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="F15" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
     </row>
     <row r="16">
@@ -766,16 +766,16 @@
         <v>0</v>
       </c>
       <c r="C16" t="n">
-        <v>9</v>
+        <v>1</v>
       </c>
       <c r="D16" t="n">
-        <v>4</v>
+        <v>13</v>
       </c>
       <c r="E16" t="n">
-        <v>196</v>
+        <v>193</v>
       </c>
       <c r="F16" t="n">
-        <v>1</v>
+        <v>3</v>
       </c>
     </row>
     <row r="17">
@@ -807,19 +807,19 @@
         </is>
       </c>
       <c r="B18" t="n">
-        <v>117</v>
+        <v>104</v>
       </c>
       <c r="C18" t="n">
-        <v>12</v>
+        <v>9</v>
       </c>
       <c r="D18" t="n">
-        <v>5</v>
+        <v>16</v>
       </c>
       <c r="E18" t="n">
-        <v>111</v>
+        <v>98</v>
       </c>
       <c r="F18" t="n">
-        <v>8</v>
+        <v>26</v>
       </c>
     </row>
     <row r="19">
@@ -829,19 +829,19 @@
         </is>
       </c>
       <c r="B19" t="n">
-        <v>208</v>
+        <v>200</v>
       </c>
       <c r="C19" t="n">
-        <v>17</v>
+        <v>7</v>
       </c>
       <c r="D19" t="n">
-        <v>15</v>
+        <v>29</v>
       </c>
       <c r="E19" t="n">
-        <v>219</v>
+        <v>212</v>
       </c>
       <c r="F19" t="n">
-        <v>9</v>
+        <v>20</v>
       </c>
     </row>
     <row r="20">
@@ -857,13 +857,13 @@
         <v>2</v>
       </c>
       <c r="D20" t="n">
-        <v>1</v>
+        <v>4</v>
       </c>
       <c r="E20" t="n">
-        <v>28</v>
+        <v>24</v>
       </c>
       <c r="F20" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
     </row>
     <row r="21">
@@ -873,19 +873,19 @@
         </is>
       </c>
       <c r="B21" t="n">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="C21" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="D21" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="E21" t="n">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="F21" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
     </row>
     <row r="22">
@@ -895,19 +895,19 @@
         </is>
       </c>
       <c r="B22" t="n">
-        <v>0</v>
+        <v>4</v>
       </c>
       <c r="C22" t="n">
-        <v>24</v>
+        <v>11</v>
       </c>
       <c r="D22" t="n">
-        <v>12</v>
+        <v>28</v>
       </c>
       <c r="E22" t="n">
-        <v>126</v>
+        <v>111</v>
       </c>
       <c r="F22" t="n">
-        <v>6</v>
+        <v>14</v>
       </c>
     </row>
     <row r="23">
@@ -920,16 +920,16 @@
         <v>0</v>
       </c>
       <c r="C23" t="n">
+        <v>0</v>
+      </c>
+      <c r="D23" t="n">
+        <v>1</v>
+      </c>
+      <c r="E23" t="n">
+        <v>3</v>
+      </c>
+      <c r="F23" t="n">
         <v>2</v>
-      </c>
-      <c r="D23" t="n">
-        <v>0</v>
-      </c>
-      <c r="E23" t="n">
-        <v>4</v>
-      </c>
-      <c r="F23" t="n">
-        <v>0</v>
       </c>
     </row>
     <row r="24">
@@ -939,19 +939,19 @@
         </is>
       </c>
       <c r="B24" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="C24" t="n">
         <v>0</v>
       </c>
       <c r="D24" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="E24" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="F24" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
     </row>
     <row r="25">
@@ -967,10 +967,10 @@
         <v>3</v>
       </c>
       <c r="D25" t="n">
-        <v>1</v>
+        <v>10</v>
       </c>
       <c r="E25" t="n">
-        <v>45</v>
+        <v>36</v>
       </c>
       <c r="F25" t="n">
         <v>3</v>
@@ -986,16 +986,16 @@
         <v>0</v>
       </c>
       <c r="C26" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="D26" t="n">
-        <v>0</v>
+        <v>3</v>
       </c>
       <c r="E26" t="n">
-        <v>6</v>
+        <v>4</v>
       </c>
       <c r="F26" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
     </row>
     <row r="27">
@@ -1005,19 +1005,19 @@
         </is>
       </c>
       <c r="B27" t="n">
-        <v>91</v>
+        <v>79</v>
       </c>
       <c r="C27" t="n">
-        <v>9</v>
+        <v>11</v>
       </c>
       <c r="D27" t="n">
-        <v>5</v>
+        <v>26</v>
       </c>
       <c r="E27" t="n">
-        <v>88</v>
+        <v>68</v>
       </c>
       <c r="F27" t="n">
-        <v>7</v>
+        <v>16</v>
       </c>
     </row>
     <row r="28">
@@ -1033,10 +1033,10 @@
         <v>0</v>
       </c>
       <c r="D28" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="E28" t="n">
-        <v>11</v>
+        <v>9</v>
       </c>
       <c r="F28" t="n">
         <v>0</v>
@@ -1049,19 +1049,19 @@
         </is>
       </c>
       <c r="B29" t="n">
-        <v>21</v>
+        <v>20</v>
       </c>
       <c r="C29" t="n">
+        <v>1</v>
+      </c>
+      <c r="D29" t="n">
         <v>2</v>
       </c>
-      <c r="D29" t="n">
-        <v>0</v>
-      </c>
       <c r="E29" t="n">
-        <v>18</v>
+        <v>17</v>
       </c>
       <c r="F29" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
     </row>
     <row r="30">
@@ -1074,16 +1074,16 @@
         <v>4</v>
       </c>
       <c r="C30" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="D30" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="E30" t="n">
-        <v>6</v>
+        <v>3</v>
       </c>
       <c r="F30" t="n">
-        <v>1</v>
+        <v>3</v>
       </c>
     </row>
     <row r="31">
@@ -1096,16 +1096,16 @@
         <v>1</v>
       </c>
       <c r="C31" t="n">
-        <v>6</v>
+        <v>2</v>
       </c>
       <c r="D31" t="n">
-        <v>5</v>
+        <v>18</v>
       </c>
       <c r="E31" t="n">
-        <v>49</v>
+        <v>39</v>
       </c>
       <c r="F31" t="n">
-        <v>3</v>
+        <v>4</v>
       </c>
     </row>
     <row r="32">
@@ -1115,19 +1115,19 @@
         </is>
       </c>
       <c r="B32" t="n">
-        <v>97</v>
+        <v>98</v>
       </c>
       <c r="C32" t="n">
-        <v>16</v>
+        <v>7</v>
       </c>
       <c r="D32" t="n">
-        <v>5</v>
+        <v>9</v>
       </c>
       <c r="E32" t="n">
-        <v>110</v>
+        <v>104</v>
       </c>
       <c r="F32" t="n">
-        <v>11</v>
+        <v>21</v>
       </c>
     </row>
     <row r="33">
@@ -1137,13 +1137,13 @@
         </is>
       </c>
       <c r="B33" t="n">
-        <v>14</v>
+        <v>15</v>
       </c>
       <c r="C33" t="n">
         <v>0</v>
       </c>
       <c r="D33" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="E33" t="n">
         <v>16</v>

--- a/data/output/topik_per_lokasi.xlsx
+++ b/data/output/topik_per_lokasi.xlsx
@@ -455,16 +455,16 @@
         </is>
       </c>
       <c r="B2" t="n">
-        <v>43</v>
+        <v>45</v>
       </c>
       <c r="C2" t="n">
-        <v>0</v>
+        <v>5</v>
       </c>
       <c r="D2" t="n">
-        <v>8</v>
+        <v>38</v>
       </c>
       <c r="E2" t="n">
-        <v>38</v>
+        <v>1</v>
       </c>
       <c r="F2" t="n">
         <v>5</v>
@@ -477,19 +477,19 @@
         </is>
       </c>
       <c r="B3" t="n">
-        <v>193</v>
+        <v>182</v>
       </c>
       <c r="C3" t="n">
-        <v>16</v>
+        <v>40</v>
       </c>
       <c r="D3" t="n">
-        <v>131</v>
+        <v>215</v>
       </c>
       <c r="E3" t="n">
-        <v>142</v>
+        <v>25</v>
       </c>
       <c r="F3" t="n">
-        <v>15</v>
+        <v>35</v>
       </c>
     </row>
     <row r="4">
@@ -502,7 +502,7 @@
         <v>1</v>
       </c>
       <c r="C4" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="D4" t="n">
         <v>1</v>
@@ -511,7 +511,7 @@
         <v>0</v>
       </c>
       <c r="F4" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
     </row>
     <row r="5">
@@ -524,13 +524,13 @@
         <v>1</v>
       </c>
       <c r="C5" t="n">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="D5" t="n">
-        <v>5</v>
+        <v>15</v>
       </c>
       <c r="E5" t="n">
-        <v>14</v>
+        <v>2</v>
       </c>
       <c r="F5" t="n">
         <v>0</v>
@@ -549,13 +549,13 @@
         <v>0</v>
       </c>
       <c r="D6" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="E6" t="n">
         <v>0</v>
       </c>
       <c r="F6" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
     </row>
     <row r="7">
@@ -568,13 +568,13 @@
         <v>0</v>
       </c>
       <c r="C7" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="D7" t="n">
         <v>1</v>
       </c>
       <c r="E7" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="F7" t="n">
         <v>0</v>
@@ -587,19 +587,19 @@
         </is>
       </c>
       <c r="B8" t="n">
-        <v>5</v>
+        <v>0</v>
       </c>
       <c r="C8" t="n">
-        <v>9</v>
+        <v>21</v>
       </c>
       <c r="D8" t="n">
-        <v>75</v>
+        <v>93</v>
       </c>
       <c r="E8" t="n">
-        <v>95</v>
+        <v>26</v>
       </c>
       <c r="F8" t="n">
-        <v>13</v>
+        <v>57</v>
       </c>
     </row>
     <row r="9">
@@ -609,19 +609,19 @@
         </is>
       </c>
       <c r="B9" t="n">
-        <v>229</v>
+        <v>225</v>
       </c>
       <c r="C9" t="n">
-        <v>17</v>
+        <v>23</v>
       </c>
       <c r="D9" t="n">
-        <v>107</v>
+        <v>196</v>
       </c>
       <c r="E9" t="n">
-        <v>150</v>
+        <v>48</v>
       </c>
       <c r="F9" t="n">
-        <v>17</v>
+        <v>28</v>
       </c>
     </row>
     <row r="10">
@@ -634,13 +634,13 @@
         <v>0</v>
       </c>
       <c r="C10" t="n">
-        <v>0</v>
+        <v>4</v>
       </c>
       <c r="D10" t="n">
+        <v>33</v>
+      </c>
+      <c r="E10" t="n">
         <v>2</v>
-      </c>
-      <c r="E10" t="n">
-        <v>37</v>
       </c>
       <c r="F10" t="n">
         <v>0</v>
@@ -656,16 +656,16 @@
         <v>2</v>
       </c>
       <c r="C11" t="n">
-        <v>10</v>
+        <v>21</v>
       </c>
       <c r="D11" t="n">
-        <v>12</v>
+        <v>199</v>
       </c>
       <c r="E11" t="n">
-        <v>193</v>
+        <v>8</v>
       </c>
       <c r="F11" t="n">
-        <v>18</v>
+        <v>5</v>
       </c>
     </row>
     <row r="12">
@@ -675,19 +675,19 @@
         </is>
       </c>
       <c r="B12" t="n">
-        <v>138</v>
+        <v>146</v>
       </c>
       <c r="C12" t="n">
-        <v>7</v>
+        <v>12</v>
       </c>
       <c r="D12" t="n">
-        <v>10</v>
+        <v>166</v>
       </c>
       <c r="E12" t="n">
-        <v>165</v>
+        <v>3</v>
       </c>
       <c r="F12" t="n">
-        <v>11</v>
+        <v>4</v>
       </c>
     </row>
     <row r="13">
@@ -700,16 +700,16 @@
         <v>0</v>
       </c>
       <c r="C13" t="n">
-        <v>0</v>
+        <v>5</v>
       </c>
       <c r="D13" t="n">
-        <v>6</v>
+        <v>153</v>
       </c>
       <c r="E13" t="n">
-        <v>154</v>
+        <v>1</v>
       </c>
       <c r="F13" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
     </row>
     <row r="14">
@@ -722,16 +722,16 @@
         <v>2</v>
       </c>
       <c r="C14" t="n">
+        <v>11</v>
+      </c>
+      <c r="D14" t="n">
+        <v>175</v>
+      </c>
+      <c r="E14" t="n">
+        <v>8</v>
+      </c>
+      <c r="F14" t="n">
         <v>6</v>
-      </c>
-      <c r="D14" t="n">
-        <v>21</v>
-      </c>
-      <c r="E14" t="n">
-        <v>165</v>
-      </c>
-      <c r="F14" t="n">
-        <v>8</v>
       </c>
     </row>
     <row r="15">
@@ -747,13 +747,13 @@
         <v>0</v>
       </c>
       <c r="D15" t="n">
-        <v>0</v>
+        <v>4</v>
       </c>
       <c r="E15" t="n">
-        <v>3</v>
+        <v>0</v>
       </c>
       <c r="F15" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
     </row>
     <row r="16">
@@ -763,16 +763,16 @@
         </is>
       </c>
       <c r="B16" t="n">
-        <v>0</v>
+        <v>5</v>
       </c>
       <c r="C16" t="n">
-        <v>1</v>
+        <v>8</v>
       </c>
       <c r="D16" t="n">
-        <v>13</v>
+        <v>194</v>
       </c>
       <c r="E16" t="n">
-        <v>193</v>
+        <v>5</v>
       </c>
       <c r="F16" t="n">
         <v>3</v>
@@ -791,10 +791,10 @@
         <v>0</v>
       </c>
       <c r="D17" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="E17" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="F17" t="n">
         <v>0</v>
@@ -807,19 +807,19 @@
         </is>
       </c>
       <c r="B18" t="n">
-        <v>104</v>
+        <v>115</v>
       </c>
       <c r="C18" t="n">
-        <v>9</v>
+        <v>11</v>
       </c>
       <c r="D18" t="n">
-        <v>16</v>
+        <v>113</v>
       </c>
       <c r="E18" t="n">
-        <v>98</v>
+        <v>3</v>
       </c>
       <c r="F18" t="n">
-        <v>26</v>
+        <v>11</v>
       </c>
     </row>
     <row r="19">
@@ -829,19 +829,19 @@
         </is>
       </c>
       <c r="B19" t="n">
-        <v>200</v>
+        <v>210</v>
       </c>
       <c r="C19" t="n">
+        <v>23</v>
+      </c>
+      <c r="D19" t="n">
+        <v>214</v>
+      </c>
+      <c r="E19" t="n">
         <v>7</v>
       </c>
-      <c r="D19" t="n">
-        <v>29</v>
-      </c>
-      <c r="E19" t="n">
-        <v>212</v>
-      </c>
       <c r="F19" t="n">
-        <v>20</v>
+        <v>14</v>
       </c>
     </row>
     <row r="20">
@@ -854,16 +854,16 @@
         <v>0</v>
       </c>
       <c r="C20" t="n">
+        <v>5</v>
+      </c>
+      <c r="D20" t="n">
+        <v>24</v>
+      </c>
+      <c r="E20" t="n">
         <v>2</v>
       </c>
-      <c r="D20" t="n">
-        <v>4</v>
-      </c>
-      <c r="E20" t="n">
-        <v>24</v>
-      </c>
       <c r="F20" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
     </row>
     <row r="21">
@@ -873,19 +873,19 @@
         </is>
       </c>
       <c r="B21" t="n">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="C21" t="n">
         <v>0</v>
       </c>
       <c r="D21" t="n">
-        <v>1</v>
+        <v>6</v>
       </c>
       <c r="E21" t="n">
-        <v>5</v>
+        <v>0</v>
       </c>
       <c r="F21" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
     </row>
     <row r="22">
@@ -895,19 +895,19 @@
         </is>
       </c>
       <c r="B22" t="n">
-        <v>4</v>
+        <v>0</v>
       </c>
       <c r="C22" t="n">
+        <v>23</v>
+      </c>
+      <c r="D22" t="n">
+        <v>126</v>
+      </c>
+      <c r="E22" t="n">
         <v>11</v>
       </c>
-      <c r="D22" t="n">
-        <v>28</v>
-      </c>
-      <c r="E22" t="n">
-        <v>111</v>
-      </c>
       <c r="F22" t="n">
-        <v>14</v>
+        <v>8</v>
       </c>
     </row>
     <row r="23">
@@ -923,13 +923,13 @@
         <v>0</v>
       </c>
       <c r="D23" t="n">
-        <v>1</v>
+        <v>5</v>
       </c>
       <c r="E23" t="n">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="F23" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
     </row>
     <row r="24">
@@ -939,19 +939,19 @@
         </is>
       </c>
       <c r="B24" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="C24" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="D24" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="E24" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="F24" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
     </row>
     <row r="25">
@@ -964,13 +964,13 @@
         <v>0</v>
       </c>
       <c r="C25" t="n">
-        <v>3</v>
+        <v>6</v>
       </c>
       <c r="D25" t="n">
-        <v>10</v>
+        <v>39</v>
       </c>
       <c r="E25" t="n">
-        <v>36</v>
+        <v>4</v>
       </c>
       <c r="F25" t="n">
         <v>3</v>
@@ -989,10 +989,10 @@
         <v>0</v>
       </c>
       <c r="D26" t="n">
-        <v>3</v>
+        <v>5</v>
       </c>
       <c r="E26" t="n">
-        <v>4</v>
+        <v>2</v>
       </c>
       <c r="F26" t="n">
         <v>1</v>
@@ -1005,19 +1005,19 @@
         </is>
       </c>
       <c r="B27" t="n">
+        <v>86</v>
+      </c>
+      <c r="C27" t="n">
+        <v>18</v>
+      </c>
+      <c r="D27" t="n">
         <v>79</v>
       </c>
-      <c r="C27" t="n">
-        <v>11</v>
-      </c>
-      <c r="D27" t="n">
-        <v>26</v>
-      </c>
       <c r="E27" t="n">
-        <v>68</v>
+        <v>10</v>
       </c>
       <c r="F27" t="n">
-        <v>16</v>
+        <v>7</v>
       </c>
     </row>
     <row r="28">
@@ -1033,10 +1033,10 @@
         <v>0</v>
       </c>
       <c r="D28" t="n">
-        <v>2</v>
+        <v>11</v>
       </c>
       <c r="E28" t="n">
-        <v>9</v>
+        <v>0</v>
       </c>
       <c r="F28" t="n">
         <v>0</v>
@@ -1052,16 +1052,16 @@
         <v>20</v>
       </c>
       <c r="C29" t="n">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="D29" t="n">
-        <v>2</v>
+        <v>18</v>
       </c>
       <c r="E29" t="n">
-        <v>17</v>
+        <v>1</v>
       </c>
       <c r="F29" t="n">
-        <v>3</v>
+        <v>1</v>
       </c>
     </row>
     <row r="30">
@@ -1074,16 +1074,16 @@
         <v>4</v>
       </c>
       <c r="C30" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="D30" t="n">
-        <v>2</v>
+        <v>6</v>
       </c>
       <c r="E30" t="n">
-        <v>3</v>
+        <v>0</v>
       </c>
       <c r="F30" t="n">
-        <v>3</v>
+        <v>1</v>
       </c>
     </row>
     <row r="31">
@@ -1096,16 +1096,16 @@
         <v>1</v>
       </c>
       <c r="C31" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="D31" t="n">
-        <v>18</v>
+        <v>50</v>
       </c>
       <c r="E31" t="n">
-        <v>39</v>
+        <v>5</v>
       </c>
       <c r="F31" t="n">
-        <v>4</v>
+        <v>5</v>
       </c>
     </row>
     <row r="32">
@@ -1115,19 +1115,19 @@
         </is>
       </c>
       <c r="B32" t="n">
-        <v>98</v>
+        <v>99</v>
       </c>
       <c r="C32" t="n">
-        <v>7</v>
+        <v>10</v>
       </c>
       <c r="D32" t="n">
+        <v>113</v>
+      </c>
+      <c r="E32" t="n">
         <v>9</v>
       </c>
-      <c r="E32" t="n">
-        <v>104</v>
-      </c>
       <c r="F32" t="n">
-        <v>21</v>
+        <v>8</v>
       </c>
     </row>
     <row r="33">
@@ -1137,19 +1137,19 @@
         </is>
       </c>
       <c r="B33" t="n">
-        <v>15</v>
+        <v>14</v>
       </c>
       <c r="C33" t="n">
         <v>0</v>
       </c>
       <c r="D33" t="n">
-        <v>0</v>
+        <v>16</v>
       </c>
       <c r="E33" t="n">
-        <v>16</v>
+        <v>0</v>
       </c>
       <c r="F33" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
     </row>
   </sheetData>

--- a/data/output/topik_per_lokasi.xlsx
+++ b/data/output/topik_per_lokasi.xlsx
@@ -455,19 +455,19 @@
         </is>
       </c>
       <c r="B2" t="n">
-        <v>45</v>
+        <v>33</v>
       </c>
       <c r="C2" t="n">
-        <v>5</v>
+        <v>14</v>
       </c>
       <c r="D2" t="n">
+        <v>6</v>
+      </c>
+      <c r="E2" t="n">
+        <v>3</v>
+      </c>
+      <c r="F2" t="n">
         <v>38</v>
-      </c>
-      <c r="E2" t="n">
-        <v>1</v>
-      </c>
-      <c r="F2" t="n">
-        <v>5</v>
       </c>
     </row>
     <row r="3">
@@ -477,19 +477,19 @@
         </is>
       </c>
       <c r="B3" t="n">
-        <v>182</v>
+        <v>151</v>
       </c>
       <c r="C3" t="n">
-        <v>40</v>
+        <v>41</v>
       </c>
       <c r="D3" t="n">
-        <v>215</v>
+        <v>28</v>
       </c>
       <c r="E3" t="n">
-        <v>25</v>
+        <v>24</v>
       </c>
       <c r="F3" t="n">
-        <v>35</v>
+        <v>254</v>
       </c>
     </row>
     <row r="4">
@@ -499,19 +499,19 @@
         </is>
       </c>
       <c r="B4" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="C4" t="n">
         <v>1</v>
       </c>
       <c r="D4" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="E4" t="n">
         <v>0</v>
       </c>
       <c r="F4" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
     </row>
     <row r="5">
@@ -524,16 +524,16 @@
         <v>1</v>
       </c>
       <c r="C5" t="n">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="D5" t="n">
+        <v>2</v>
+      </c>
+      <c r="E5" t="n">
+        <v>2</v>
+      </c>
+      <c r="F5" t="n">
         <v>15</v>
-      </c>
-      <c r="E5" t="n">
-        <v>2</v>
-      </c>
-      <c r="F5" t="n">
-        <v>0</v>
       </c>
     </row>
     <row r="6">
@@ -549,13 +549,13 @@
         <v>0</v>
       </c>
       <c r="D6" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="E6" t="n">
         <v>0</v>
       </c>
       <c r="F6" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
     </row>
     <row r="7">
@@ -568,16 +568,16 @@
         <v>0</v>
       </c>
       <c r="C7" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="D7" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="E7" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="F7" t="n">
-        <v>0</v>
+        <v>3</v>
       </c>
     </row>
     <row r="8">
@@ -587,19 +587,19 @@
         </is>
       </c>
       <c r="B8" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="C8" t="n">
-        <v>21</v>
+        <v>5</v>
       </c>
       <c r="D8" t="n">
-        <v>93</v>
+        <v>52</v>
       </c>
       <c r="E8" t="n">
-        <v>26</v>
+        <v>7</v>
       </c>
       <c r="F8" t="n">
-        <v>57</v>
+        <v>131</v>
       </c>
     </row>
     <row r="9">
@@ -609,19 +609,19 @@
         </is>
       </c>
       <c r="B9" t="n">
-        <v>225</v>
+        <v>165</v>
       </c>
       <c r="C9" t="n">
-        <v>23</v>
+        <v>76</v>
       </c>
       <c r="D9" t="n">
-        <v>196</v>
+        <v>55</v>
       </c>
       <c r="E9" t="n">
-        <v>48</v>
+        <v>14</v>
       </c>
       <c r="F9" t="n">
-        <v>28</v>
+        <v>210</v>
       </c>
     </row>
     <row r="10">
@@ -634,16 +634,16 @@
         <v>0</v>
       </c>
       <c r="C10" t="n">
-        <v>4</v>
+        <v>1</v>
       </c>
       <c r="D10" t="n">
-        <v>33</v>
+        <v>2</v>
       </c>
       <c r="E10" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="F10" t="n">
-        <v>0</v>
+        <v>36</v>
       </c>
     </row>
     <row r="11">
@@ -653,19 +653,19 @@
         </is>
       </c>
       <c r="B11" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="C11" t="n">
-        <v>21</v>
+        <v>9</v>
       </c>
       <c r="D11" t="n">
-        <v>199</v>
+        <v>15</v>
       </c>
       <c r="E11" t="n">
-        <v>8</v>
+        <v>2</v>
       </c>
       <c r="F11" t="n">
-        <v>5</v>
+        <v>209</v>
       </c>
     </row>
     <row r="12">
@@ -675,19 +675,19 @@
         </is>
       </c>
       <c r="B12" t="n">
-        <v>146</v>
+        <v>122</v>
       </c>
       <c r="C12" t="n">
-        <v>12</v>
+        <v>18</v>
       </c>
       <c r="D12" t="n">
-        <v>166</v>
+        <v>15</v>
       </c>
       <c r="E12" t="n">
-        <v>3</v>
+        <v>14</v>
       </c>
       <c r="F12" t="n">
-        <v>4</v>
+        <v>162</v>
       </c>
     </row>
     <row r="13">
@@ -700,16 +700,16 @@
         <v>0</v>
       </c>
       <c r="C13" t="n">
-        <v>5</v>
+        <v>0</v>
       </c>
       <c r="D13" t="n">
-        <v>153</v>
+        <v>12</v>
       </c>
       <c r="E13" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="F13" t="n">
-        <v>1</v>
+        <v>148</v>
       </c>
     </row>
     <row r="14">
@@ -719,19 +719,19 @@
         </is>
       </c>
       <c r="B14" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="C14" t="n">
-        <v>11</v>
+        <v>3</v>
       </c>
       <c r="D14" t="n">
-        <v>175</v>
+        <v>21</v>
       </c>
       <c r="E14" t="n">
-        <v>8</v>
+        <v>4</v>
       </c>
       <c r="F14" t="n">
-        <v>6</v>
+        <v>171</v>
       </c>
     </row>
     <row r="15">
@@ -741,19 +741,19 @@
         </is>
       </c>
       <c r="B15" t="n">
+        <v>2</v>
+      </c>
+      <c r="C15" t="n">
+        <v>0</v>
+      </c>
+      <c r="D15" t="n">
+        <v>1</v>
+      </c>
+      <c r="E15" t="n">
+        <v>1</v>
+      </c>
+      <c r="F15" t="n">
         <v>3</v>
-      </c>
-      <c r="C15" t="n">
-        <v>0</v>
-      </c>
-      <c r="D15" t="n">
-        <v>4</v>
-      </c>
-      <c r="E15" t="n">
-        <v>0</v>
-      </c>
-      <c r="F15" t="n">
-        <v>0</v>
       </c>
     </row>
     <row r="16">
@@ -763,19 +763,19 @@
         </is>
       </c>
       <c r="B16" t="n">
-        <v>5</v>
+        <v>3</v>
       </c>
       <c r="C16" t="n">
-        <v>8</v>
+        <v>2</v>
       </c>
       <c r="D16" t="n">
-        <v>194</v>
+        <v>16</v>
       </c>
       <c r="E16" t="n">
-        <v>5</v>
+        <v>1</v>
       </c>
       <c r="F16" t="n">
-        <v>3</v>
+        <v>193</v>
       </c>
     </row>
     <row r="17">
@@ -791,13 +791,13 @@
         <v>0</v>
       </c>
       <c r="D17" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="E17" t="n">
         <v>0</v>
       </c>
       <c r="F17" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
     </row>
     <row r="18">
@@ -807,19 +807,19 @@
         </is>
       </c>
       <c r="B18" t="n">
-        <v>115</v>
+        <v>87</v>
       </c>
       <c r="C18" t="n">
-        <v>11</v>
+        <v>28</v>
       </c>
       <c r="D18" t="n">
-        <v>113</v>
+        <v>14</v>
       </c>
       <c r="E18" t="n">
-        <v>3</v>
+        <v>10</v>
       </c>
       <c r="F18" t="n">
-        <v>11</v>
+        <v>114</v>
       </c>
     </row>
     <row r="19">
@@ -829,19 +829,19 @@
         </is>
       </c>
       <c r="B19" t="n">
-        <v>210</v>
+        <v>166</v>
       </c>
       <c r="C19" t="n">
-        <v>23</v>
+        <v>43</v>
       </c>
       <c r="D19" t="n">
-        <v>214</v>
+        <v>20</v>
       </c>
       <c r="E19" t="n">
-        <v>7</v>
+        <v>16</v>
       </c>
       <c r="F19" t="n">
-        <v>14</v>
+        <v>223</v>
       </c>
     </row>
     <row r="20">
@@ -854,16 +854,16 @@
         <v>0</v>
       </c>
       <c r="C20" t="n">
-        <v>5</v>
+        <v>0</v>
       </c>
       <c r="D20" t="n">
-        <v>24</v>
+        <v>2</v>
       </c>
       <c r="E20" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="F20" t="n">
-        <v>0</v>
+        <v>29</v>
       </c>
     </row>
     <row r="21">
@@ -873,19 +873,19 @@
         </is>
       </c>
       <c r="B21" t="n">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="C21" t="n">
         <v>0</v>
       </c>
       <c r="D21" t="n">
+        <v>0</v>
+      </c>
+      <c r="E21" t="n">
+        <v>0</v>
+      </c>
+      <c r="F21" t="n">
         <v>6</v>
-      </c>
-      <c r="E21" t="n">
-        <v>0</v>
-      </c>
-      <c r="F21" t="n">
-        <v>1</v>
       </c>
     </row>
     <row r="22">
@@ -895,19 +895,19 @@
         </is>
       </c>
       <c r="B22" t="n">
-        <v>0</v>
+        <v>3</v>
       </c>
       <c r="C22" t="n">
-        <v>23</v>
+        <v>3</v>
       </c>
       <c r="D22" t="n">
-        <v>126</v>
+        <v>25</v>
       </c>
       <c r="E22" t="n">
-        <v>11</v>
+        <v>6</v>
       </c>
       <c r="F22" t="n">
-        <v>8</v>
+        <v>131</v>
       </c>
     </row>
     <row r="23">
@@ -920,16 +920,16 @@
         <v>0</v>
       </c>
       <c r="C23" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="D23" t="n">
-        <v>5</v>
+        <v>2</v>
       </c>
       <c r="E23" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="F23" t="n">
-        <v>0</v>
+        <v>3</v>
       </c>
     </row>
     <row r="24">
@@ -942,7 +942,7 @@
         <v>0</v>
       </c>
       <c r="C24" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="D24" t="n">
         <v>2</v>
@@ -951,7 +951,7 @@
         <v>0</v>
       </c>
       <c r="F24" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
     </row>
     <row r="25">
@@ -964,16 +964,16 @@
         <v>0</v>
       </c>
       <c r="C25" t="n">
-        <v>6</v>
+        <v>2</v>
       </c>
       <c r="D25" t="n">
-        <v>39</v>
+        <v>5</v>
       </c>
       <c r="E25" t="n">
-        <v>4</v>
+        <v>2</v>
       </c>
       <c r="F25" t="n">
-        <v>3</v>
+        <v>43</v>
       </c>
     </row>
     <row r="26">
@@ -989,13 +989,13 @@
         <v>0</v>
       </c>
       <c r="D26" t="n">
-        <v>5</v>
+        <v>1</v>
       </c>
       <c r="E26" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="F26" t="n">
-        <v>1</v>
+        <v>7</v>
       </c>
     </row>
     <row r="27">
@@ -1005,19 +1005,19 @@
         </is>
       </c>
       <c r="B27" t="n">
-        <v>86</v>
+        <v>66</v>
       </c>
       <c r="C27" t="n">
-        <v>18</v>
+        <v>27</v>
       </c>
       <c r="D27" t="n">
-        <v>79</v>
+        <v>19</v>
       </c>
       <c r="E27" t="n">
-        <v>10</v>
+        <v>6</v>
       </c>
       <c r="F27" t="n">
-        <v>7</v>
+        <v>82</v>
       </c>
     </row>
     <row r="28">
@@ -1027,19 +1027,19 @@
         </is>
       </c>
       <c r="B28" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="C28" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="D28" t="n">
+        <v>0</v>
+      </c>
+      <c r="E28" t="n">
+        <v>0</v>
+      </c>
+      <c r="F28" t="n">
         <v>11</v>
-      </c>
-      <c r="E28" t="n">
-        <v>0</v>
-      </c>
-      <c r="F28" t="n">
-        <v>0</v>
       </c>
     </row>
     <row r="29">
@@ -1049,19 +1049,19 @@
         </is>
       </c>
       <c r="B29" t="n">
+        <v>17</v>
+      </c>
+      <c r="C29" t="n">
+        <v>5</v>
+      </c>
+      <c r="D29" t="n">
+        <v>0</v>
+      </c>
+      <c r="E29" t="n">
+        <v>1</v>
+      </c>
+      <c r="F29" t="n">
         <v>20</v>
-      </c>
-      <c r="C29" t="n">
-        <v>3</v>
-      </c>
-      <c r="D29" t="n">
-        <v>18</v>
-      </c>
-      <c r="E29" t="n">
-        <v>1</v>
-      </c>
-      <c r="F29" t="n">
-        <v>1</v>
       </c>
     </row>
     <row r="30">
@@ -1071,19 +1071,19 @@
         </is>
       </c>
       <c r="B30" t="n">
+        <v>2</v>
+      </c>
+      <c r="C30" t="n">
         <v>4</v>
       </c>
-      <c r="C30" t="n">
-        <v>1</v>
-      </c>
       <c r="D30" t="n">
-        <v>6</v>
+        <v>1</v>
       </c>
       <c r="E30" t="n">
         <v>0</v>
       </c>
       <c r="F30" t="n">
-        <v>1</v>
+        <v>5</v>
       </c>
     </row>
     <row r="31">
@@ -1093,19 +1093,19 @@
         </is>
       </c>
       <c r="B31" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="C31" t="n">
         <v>3</v>
       </c>
       <c r="D31" t="n">
+        <v>9</v>
+      </c>
+      <c r="E31" t="n">
+        <v>2</v>
+      </c>
+      <c r="F31" t="n">
         <v>50</v>
-      </c>
-      <c r="E31" t="n">
-        <v>5</v>
-      </c>
-      <c r="F31" t="n">
-        <v>5</v>
       </c>
     </row>
     <row r="32">
@@ -1115,19 +1115,19 @@
         </is>
       </c>
       <c r="B32" t="n">
-        <v>99</v>
+        <v>86</v>
       </c>
       <c r="C32" t="n">
-        <v>10</v>
+        <v>21</v>
       </c>
       <c r="D32" t="n">
-        <v>113</v>
+        <v>16</v>
       </c>
       <c r="E32" t="n">
-        <v>9</v>
+        <v>4</v>
       </c>
       <c r="F32" t="n">
-        <v>8</v>
+        <v>112</v>
       </c>
     </row>
     <row r="33">
@@ -1137,19 +1137,19 @@
         </is>
       </c>
       <c r="B33" t="n">
+        <v>13</v>
+      </c>
+      <c r="C33" t="n">
+        <v>1</v>
+      </c>
+      <c r="D33" t="n">
+        <v>2</v>
+      </c>
+      <c r="E33" t="n">
+        <v>1</v>
+      </c>
+      <c r="F33" t="n">
         <v>14</v>
-      </c>
-      <c r="C33" t="n">
-        <v>0</v>
-      </c>
-      <c r="D33" t="n">
-        <v>16</v>
-      </c>
-      <c r="E33" t="n">
-        <v>0</v>
-      </c>
-      <c r="F33" t="n">
-        <v>1</v>
       </c>
     </row>
   </sheetData>

--- a/data/output/topik_per_lokasi.xlsx
+++ b/data/output/topik_per_lokasi.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:F33"/>
+  <dimension ref="A1:F34"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -455,19 +455,19 @@
         </is>
       </c>
       <c r="B2" t="n">
-        <v>33</v>
+        <v>43</v>
       </c>
       <c r="C2" t="n">
-        <v>14</v>
+        <v>6</v>
       </c>
       <c r="D2" t="n">
-        <v>6</v>
+        <v>35</v>
       </c>
       <c r="E2" t="n">
-        <v>3</v>
+        <v>8</v>
       </c>
       <c r="F2" t="n">
-        <v>38</v>
+        <v>2</v>
       </c>
     </row>
     <row r="3">
@@ -477,19 +477,19 @@
         </is>
       </c>
       <c r="B3" t="n">
-        <v>151</v>
+        <v>190</v>
       </c>
       <c r="C3" t="n">
-        <v>41</v>
+        <v>42</v>
       </c>
       <c r="D3" t="n">
-        <v>28</v>
+        <v>220</v>
       </c>
       <c r="E3" t="n">
-        <v>24</v>
+        <v>38</v>
       </c>
       <c r="F3" t="n">
-        <v>254</v>
+        <v>8</v>
       </c>
     </row>
     <row r="4">
@@ -499,19 +499,19 @@
         </is>
       </c>
       <c r="B4" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="C4" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="D4" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="E4" t="n">
         <v>0</v>
       </c>
       <c r="F4" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
     </row>
     <row r="5">
@@ -521,19 +521,19 @@
         </is>
       </c>
       <c r="B5" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="C5" t="n">
         <v>1</v>
       </c>
       <c r="D5" t="n">
-        <v>2</v>
+        <v>14</v>
       </c>
       <c r="E5" t="n">
         <v>2</v>
       </c>
       <c r="F5" t="n">
-        <v>15</v>
+        <v>4</v>
       </c>
     </row>
     <row r="6">
@@ -568,16 +568,16 @@
         <v>0</v>
       </c>
       <c r="C7" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="D7" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="E7" t="n">
         <v>0</v>
       </c>
       <c r="F7" t="n">
-        <v>3</v>
+        <v>0</v>
       </c>
     </row>
     <row r="8">
@@ -587,19 +587,19 @@
         </is>
       </c>
       <c r="B8" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="C8" t="n">
-        <v>5</v>
+        <v>53</v>
       </c>
       <c r="D8" t="n">
-        <v>52</v>
+        <v>91</v>
       </c>
       <c r="E8" t="n">
-        <v>7</v>
+        <v>27</v>
       </c>
       <c r="F8" t="n">
-        <v>131</v>
+        <v>23</v>
       </c>
     </row>
     <row r="9">
@@ -609,19 +609,19 @@
         </is>
       </c>
       <c r="B9" t="n">
-        <v>165</v>
+        <v>227</v>
       </c>
       <c r="C9" t="n">
-        <v>76</v>
+        <v>49</v>
       </c>
       <c r="D9" t="n">
-        <v>55</v>
+        <v>170</v>
       </c>
       <c r="E9" t="n">
-        <v>14</v>
+        <v>61</v>
       </c>
       <c r="F9" t="n">
-        <v>210</v>
+        <v>13</v>
       </c>
     </row>
     <row r="10">
@@ -634,16 +634,16 @@
         <v>0</v>
       </c>
       <c r="C10" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="D10" t="n">
-        <v>2</v>
+        <v>34</v>
       </c>
       <c r="E10" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="F10" t="n">
-        <v>36</v>
+        <v>4</v>
       </c>
     </row>
     <row r="11">
@@ -656,16 +656,16 @@
         <v>0</v>
       </c>
       <c r="C11" t="n">
-        <v>9</v>
+        <v>8</v>
       </c>
       <c r="D11" t="n">
-        <v>15</v>
+        <v>194</v>
       </c>
       <c r="E11" t="n">
-        <v>2</v>
+        <v>13</v>
       </c>
       <c r="F11" t="n">
-        <v>209</v>
+        <v>20</v>
       </c>
     </row>
     <row r="12">
@@ -675,481 +675,503 @@
         </is>
       </c>
       <c r="B12" t="n">
-        <v>122</v>
+        <v>146</v>
       </c>
       <c r="C12" t="n">
-        <v>18</v>
+        <v>4</v>
       </c>
       <c r="D12" t="n">
-        <v>15</v>
+        <v>157</v>
       </c>
       <c r="E12" t="n">
-        <v>14</v>
+        <v>8</v>
       </c>
       <c r="F12" t="n">
-        <v>162</v>
+        <v>16</v>
       </c>
     </row>
     <row r="13">
       <c r="A13" t="inlineStr">
         <is>
-          <t>Pantai Citepus</t>
+          <t>Pantai Cipatuguran Palabuhanratu</t>
         </is>
       </c>
       <c r="B13" t="n">
-        <v>0</v>
+        <v>5</v>
       </c>
       <c r="C13" t="n">
         <v>0</v>
       </c>
       <c r="D13" t="n">
-        <v>12</v>
+        <v>0</v>
       </c>
       <c r="E13" t="n">
         <v>0</v>
       </c>
       <c r="F13" t="n">
-        <v>148</v>
+        <v>0</v>
       </c>
     </row>
     <row r="14">
       <c r="A14" t="inlineStr">
         <is>
-          <t>Pantai Citepus Sukabumi</t>
+          <t>Pantai Citepus</t>
         </is>
       </c>
       <c r="B14" t="n">
-        <v>3</v>
+        <v>0</v>
       </c>
       <c r="C14" t="n">
         <v>3</v>
       </c>
       <c r="D14" t="n">
-        <v>21</v>
+        <v>150</v>
       </c>
       <c r="E14" t="n">
+        <v>3</v>
+      </c>
+      <c r="F14" t="n">
         <v>4</v>
-      </c>
-      <c r="F14" t="n">
-        <v>171</v>
       </c>
     </row>
     <row r="15">
       <c r="A15" t="inlineStr">
         <is>
-          <t>Pantai Gopalo</t>
+          <t>Pantai Citepus Sukabumi</t>
         </is>
       </c>
       <c r="B15" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="C15" t="n">
-        <v>0</v>
+        <v>7</v>
       </c>
       <c r="D15" t="n">
-        <v>1</v>
+        <v>160</v>
       </c>
       <c r="E15" t="n">
-        <v>1</v>
+        <v>18</v>
       </c>
       <c r="F15" t="n">
-        <v>3</v>
+        <v>14</v>
       </c>
     </row>
     <row r="16">
       <c r="A16" t="inlineStr">
         <is>
-          <t>Pantai Istana Presiden Pelabuhanratu</t>
+          <t>Pantai Gopalo</t>
         </is>
       </c>
       <c r="B16" t="n">
         <v>3</v>
       </c>
       <c r="C16" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="D16" t="n">
-        <v>16</v>
+        <v>3</v>
       </c>
       <c r="E16" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="F16" t="n">
-        <v>193</v>
+        <v>0</v>
       </c>
     </row>
     <row r="17">
       <c r="A17" t="inlineStr">
         <is>
-          <t>Pantai Kandita</t>
+          <t>Pantai Istana Presiden Pelabuhanratu</t>
         </is>
       </c>
       <c r="B17" t="n">
-        <v>0</v>
+        <v>5</v>
       </c>
       <c r="C17" t="n">
-        <v>0</v>
+        <v>5</v>
       </c>
       <c r="D17" t="n">
-        <v>0</v>
+        <v>188</v>
       </c>
       <c r="E17" t="n">
-        <v>0</v>
+        <v>6</v>
       </c>
       <c r="F17" t="n">
-        <v>2</v>
+        <v>11</v>
       </c>
     </row>
     <row r="18">
       <c r="A18" t="inlineStr">
         <is>
-          <t>Pantai Karang Sari</t>
+          <t>Pantai Kandita</t>
         </is>
       </c>
       <c r="B18" t="n">
-        <v>87</v>
+        <v>0</v>
       </c>
       <c r="C18" t="n">
-        <v>28</v>
+        <v>0</v>
       </c>
       <c r="D18" t="n">
-        <v>14</v>
+        <v>2</v>
       </c>
       <c r="E18" t="n">
-        <v>10</v>
+        <v>0</v>
       </c>
       <c r="F18" t="n">
-        <v>114</v>
+        <v>0</v>
       </c>
     </row>
     <row r="19">
       <c r="A19" t="inlineStr">
         <is>
-          <t>Pantai Pelabuhan Ratu</t>
+          <t>Pantai Karang Sari</t>
         </is>
       </c>
       <c r="B19" t="n">
-        <v>166</v>
+        <v>115</v>
       </c>
       <c r="C19" t="n">
-        <v>43</v>
+        <v>7</v>
       </c>
       <c r="D19" t="n">
-        <v>20</v>
+        <v>96</v>
       </c>
       <c r="E19" t="n">
         <v>16</v>
       </c>
       <c r="F19" t="n">
-        <v>223</v>
+        <v>19</v>
       </c>
     </row>
     <row r="20">
       <c r="A20" t="inlineStr">
         <is>
-          <t>Pantai Twenty Cipatuguran</t>
+          <t>Pantai Pelabuhan Ratu</t>
         </is>
       </c>
       <c r="B20" t="n">
-        <v>0</v>
+        <v>208</v>
       </c>
       <c r="C20" t="n">
-        <v>0</v>
+        <v>15</v>
       </c>
       <c r="D20" t="n">
-        <v>2</v>
+        <v>213</v>
       </c>
       <c r="E20" t="n">
-        <v>0</v>
+        <v>16</v>
       </c>
       <c r="F20" t="n">
-        <v>29</v>
+        <v>16</v>
       </c>
     </row>
     <row r="21">
       <c r="A21" t="inlineStr">
         <is>
-          <t>Pantai buffalo</t>
+          <t>Pantai Twenty Cipatuguran</t>
         </is>
       </c>
       <c r="B21" t="n">
-        <v>4</v>
+        <v>0</v>
       </c>
       <c r="C21" t="n">
         <v>0</v>
       </c>
       <c r="D21" t="n">
-        <v>0</v>
+        <v>23</v>
       </c>
       <c r="E21" t="n">
-        <v>0</v>
+        <v>3</v>
       </c>
       <c r="F21" t="n">
-        <v>6</v>
+        <v>5</v>
       </c>
     </row>
     <row r="22">
       <c r="A22" t="inlineStr">
         <is>
-          <t>Pesanggrahan Tenjo Resmi Pelabuhan Ratu</t>
+          <t>Pantai buffalo</t>
         </is>
       </c>
       <c r="B22" t="n">
         <v>3</v>
       </c>
       <c r="C22" t="n">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="D22" t="n">
-        <v>25</v>
+        <v>5</v>
       </c>
       <c r="E22" t="n">
-        <v>6</v>
+        <v>0</v>
       </c>
       <c r="F22" t="n">
-        <v>131</v>
+        <v>1</v>
       </c>
     </row>
     <row r="23">
       <c r="A23" t="inlineStr">
         <is>
-          <t>Saung Bintang Katineung, wisata pantai, air dan kuliner</t>
+          <t>Pesanggrahan Tenjo Resmi Pelabuhan Ratu</t>
         </is>
       </c>
       <c r="B23" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="C23" t="n">
-        <v>1</v>
+        <v>7</v>
       </c>
       <c r="D23" t="n">
-        <v>2</v>
+        <v>131</v>
       </c>
       <c r="E23" t="n">
-        <v>0</v>
+        <v>15</v>
       </c>
       <c r="F23" t="n">
-        <v>3</v>
+        <v>13</v>
       </c>
     </row>
     <row r="24">
       <c r="A24" t="inlineStr">
         <is>
-          <t>Situ Rawa Kalong</t>
+          <t>Saung Bintang Katineung, wisata pantai, air dan kuliner</t>
         </is>
       </c>
       <c r="B24" t="n">
         <v>0</v>
       </c>
       <c r="C24" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="D24" t="n">
+        <v>3</v>
+      </c>
+      <c r="E24" t="n">
+        <v>0</v>
+      </c>
+      <c r="F24" t="n">
         <v>2</v>
-      </c>
-      <c r="E24" t="n">
-        <v>0</v>
-      </c>
-      <c r="F24" t="n">
-        <v>1</v>
       </c>
     </row>
     <row r="25">
       <c r="A25" t="inlineStr">
         <is>
-          <t>Smile hill Pelabuhan Ratu</t>
+          <t>Situ Rawa Kalong</t>
         </is>
       </c>
       <c r="B25" t="n">
         <v>0</v>
       </c>
       <c r="C25" t="n">
+        <v>0</v>
+      </c>
+      <c r="D25" t="n">
+        <v>1</v>
+      </c>
+      <c r="E25" t="n">
+        <v>0</v>
+      </c>
+      <c r="F25" t="n">
         <v>2</v>
-      </c>
-      <c r="D25" t="n">
-        <v>5</v>
-      </c>
-      <c r="E25" t="n">
-        <v>2</v>
-      </c>
-      <c r="F25" t="n">
-        <v>43</v>
       </c>
     </row>
     <row r="26">
       <c r="A26" t="inlineStr">
         <is>
-          <t>Taman Bappeda</t>
+          <t>Smile hill Pelabuhan Ratu</t>
         </is>
       </c>
       <c r="B26" t="n">
         <v>0</v>
       </c>
       <c r="C26" t="n">
-        <v>0</v>
+        <v>7</v>
       </c>
       <c r="D26" t="n">
-        <v>1</v>
+        <v>38</v>
       </c>
       <c r="E26" t="n">
-        <v>0</v>
+        <v>5</v>
       </c>
       <c r="F26" t="n">
-        <v>7</v>
+        <v>2</v>
       </c>
     </row>
     <row r="27">
       <c r="A27" t="inlineStr">
         <is>
-          <t>Taman Bunga Gunung Sumping</t>
+          <t>Taman Bappeda</t>
         </is>
       </c>
       <c r="B27" t="n">
-        <v>66</v>
+        <v>0</v>
       </c>
       <c r="C27" t="n">
-        <v>27</v>
+        <v>2</v>
       </c>
       <c r="D27" t="n">
-        <v>19</v>
+        <v>4</v>
       </c>
       <c r="E27" t="n">
-        <v>6</v>
+        <v>1</v>
       </c>
       <c r="F27" t="n">
-        <v>82</v>
+        <v>1</v>
       </c>
     </row>
     <row r="28">
       <c r="A28" t="inlineStr">
         <is>
-          <t>Taman Bunga Pelabuhan Ratu</t>
+          <t>Taman Bunga Gunung Sumping</t>
         </is>
       </c>
       <c r="B28" t="n">
-        <v>2</v>
+        <v>86</v>
       </c>
       <c r="C28" t="n">
-        <v>1</v>
+        <v>8</v>
       </c>
       <c r="D28" t="n">
-        <v>0</v>
+        <v>77</v>
       </c>
       <c r="E28" t="n">
-        <v>0</v>
+        <v>22</v>
       </c>
       <c r="F28" t="n">
-        <v>11</v>
+        <v>7</v>
       </c>
     </row>
     <row r="29">
       <c r="A29" t="inlineStr">
         <is>
-          <t>Taman Citepus (Ruang Terbuka Hijau) RTH</t>
+          <t>Taman Bunga Pelabuhan Ratu</t>
         </is>
       </c>
       <c r="B29" t="n">
-        <v>17</v>
+        <v>3</v>
       </c>
       <c r="C29" t="n">
-        <v>5</v>
+        <v>0</v>
       </c>
       <c r="D29" t="n">
-        <v>0</v>
+        <v>9</v>
       </c>
       <c r="E29" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="F29" t="n">
-        <v>20</v>
+        <v>0</v>
       </c>
     </row>
     <row r="30">
       <c r="A30" t="inlineStr">
         <is>
-          <t>Taman Kota Cangehgar Palabuhanratu</t>
+          <t>Taman Citepus (Ruang Terbuka Hijau) RTH</t>
         </is>
       </c>
       <c r="B30" t="n">
+        <v>23</v>
+      </c>
+      <c r="C30" t="n">
+        <v>0</v>
+      </c>
+      <c r="D30" t="n">
+        <v>17</v>
+      </c>
+      <c r="E30" t="n">
+        <v>1</v>
+      </c>
+      <c r="F30" t="n">
         <v>2</v>
-      </c>
-      <c r="C30" t="n">
-        <v>4</v>
-      </c>
-      <c r="D30" t="n">
-        <v>1</v>
-      </c>
-      <c r="E30" t="n">
-        <v>0</v>
-      </c>
-      <c r="F30" t="n">
-        <v>5</v>
       </c>
     </row>
     <row r="31">
       <c r="A31" t="inlineStr">
         <is>
-          <t>Waterpark Citepus Pelabuhanratu</t>
+          <t>Taman Kota Cangehgar Palabuhanratu</t>
         </is>
       </c>
       <c r="B31" t="n">
-        <v>0</v>
+        <v>4</v>
       </c>
       <c r="C31" t="n">
+        <v>1</v>
+      </c>
+      <c r="D31" t="n">
+        <v>4</v>
+      </c>
+      <c r="E31" t="n">
         <v>3</v>
       </c>
-      <c r="D31" t="n">
-        <v>9</v>
-      </c>
-      <c r="E31" t="n">
-        <v>2</v>
-      </c>
       <c r="F31" t="n">
-        <v>50</v>
+        <v>0</v>
       </c>
     </row>
     <row r="32">
       <c r="A32" t="inlineStr">
         <is>
-          <t>Wisata Alam Pantai Sukawayana</t>
+          <t>Waterpark Citepus Pelabuhanratu</t>
         </is>
       </c>
       <c r="B32" t="n">
-        <v>86</v>
+        <v>2</v>
       </c>
       <c r="C32" t="n">
-        <v>21</v>
+        <v>5</v>
       </c>
       <c r="D32" t="n">
-        <v>16</v>
+        <v>44</v>
       </c>
       <c r="E32" t="n">
-        <v>4</v>
+        <v>7</v>
       </c>
       <c r="F32" t="n">
-        <v>112</v>
+        <v>6</v>
       </c>
     </row>
     <row r="33">
       <c r="A33" t="inlineStr">
         <is>
+          <t>Wisata Alam Pantai Sukawayana</t>
+        </is>
+      </c>
+      <c r="B33" t="n">
+        <v>98</v>
+      </c>
+      <c r="C33" t="n">
+        <v>6</v>
+      </c>
+      <c r="D33" t="n">
+        <v>108</v>
+      </c>
+      <c r="E33" t="n">
+        <v>12</v>
+      </c>
+      <c r="F33" t="n">
+        <v>15</v>
+      </c>
+    </row>
+    <row r="34">
+      <c r="A34" t="inlineStr">
+        <is>
           <t>i-Pe Beach Pelabuhanratu</t>
         </is>
       </c>
-      <c r="B33" t="n">
-        <v>13</v>
-      </c>
-      <c r="C33" t="n">
-        <v>1</v>
-      </c>
-      <c r="D33" t="n">
-        <v>2</v>
-      </c>
-      <c r="E33" t="n">
-        <v>1</v>
-      </c>
-      <c r="F33" t="n">
-        <v>14</v>
+      <c r="B34" t="n">
+        <v>15</v>
+      </c>
+      <c r="C34" t="n">
+        <v>1</v>
+      </c>
+      <c r="D34" t="n">
+        <v>15</v>
+      </c>
+      <c r="E34" t="n">
+        <v>0</v>
+      </c>
+      <c r="F34" t="n">
+        <v>0</v>
       </c>
     </row>
   </sheetData>

--- a/data/output/topik_per_lokasi.xlsx
+++ b/data/output/topik_per_lokasi.xlsx
@@ -455,19 +455,19 @@
         </is>
       </c>
       <c r="B2" t="n">
-        <v>43</v>
+        <v>47</v>
       </c>
       <c r="C2" t="n">
-        <v>6</v>
+        <v>5</v>
       </c>
       <c r="D2" t="n">
-        <v>35</v>
+        <v>14</v>
       </c>
       <c r="E2" t="n">
-        <v>8</v>
+        <v>25</v>
       </c>
       <c r="F2" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
     </row>
     <row r="3">
@@ -477,19 +477,19 @@
         </is>
       </c>
       <c r="B3" t="n">
-        <v>190</v>
+        <v>185</v>
       </c>
       <c r="C3" t="n">
-        <v>42</v>
+        <v>27</v>
       </c>
       <c r="D3" t="n">
-        <v>220</v>
+        <v>120</v>
       </c>
       <c r="E3" t="n">
-        <v>38</v>
+        <v>130</v>
       </c>
       <c r="F3" t="n">
-        <v>8</v>
+        <v>36</v>
       </c>
     </row>
     <row r="4">
@@ -505,13 +505,13 @@
         <v>0</v>
       </c>
       <c r="D4" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="E4" t="n">
         <v>0</v>
       </c>
       <c r="F4" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
     </row>
     <row r="5">
@@ -521,19 +521,19 @@
         </is>
       </c>
       <c r="B5" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="C5" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="D5" t="n">
-        <v>14</v>
+        <v>7</v>
       </c>
       <c r="E5" t="n">
-        <v>2</v>
+        <v>9</v>
       </c>
       <c r="F5" t="n">
-        <v>4</v>
+        <v>2</v>
       </c>
     </row>
     <row r="6">
@@ -549,13 +549,13 @@
         <v>0</v>
       </c>
       <c r="D6" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="E6" t="n">
         <v>0</v>
       </c>
       <c r="F6" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
     </row>
     <row r="7">
@@ -568,10 +568,10 @@
         <v>0</v>
       </c>
       <c r="C7" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="D7" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="E7" t="n">
         <v>0</v>
@@ -587,16 +587,16 @@
         </is>
       </c>
       <c r="B8" t="n">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="C8" t="n">
-        <v>53</v>
+        <v>8</v>
       </c>
       <c r="D8" t="n">
-        <v>91</v>
+        <v>115</v>
       </c>
       <c r="E8" t="n">
-        <v>27</v>
+        <v>47</v>
       </c>
       <c r="F8" t="n">
         <v>23</v>
@@ -609,19 +609,19 @@
         </is>
       </c>
       <c r="B9" t="n">
-        <v>227</v>
+        <v>217</v>
       </c>
       <c r="C9" t="n">
-        <v>49</v>
+        <v>39</v>
       </c>
       <c r="D9" t="n">
-        <v>170</v>
+        <v>56</v>
       </c>
       <c r="E9" t="n">
-        <v>61</v>
+        <v>153</v>
       </c>
       <c r="F9" t="n">
-        <v>13</v>
+        <v>55</v>
       </c>
     </row>
     <row r="10">
@@ -634,16 +634,16 @@
         <v>0</v>
       </c>
       <c r="C10" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="D10" t="n">
-        <v>34</v>
+        <v>16</v>
       </c>
       <c r="E10" t="n">
-        <v>1</v>
+        <v>20</v>
       </c>
       <c r="F10" t="n">
-        <v>4</v>
+        <v>2</v>
       </c>
     </row>
     <row r="11">
@@ -653,19 +653,19 @@
         </is>
       </c>
       <c r="B11" t="n">
-        <v>0</v>
+        <v>3</v>
       </c>
       <c r="C11" t="n">
-        <v>8</v>
+        <v>4</v>
       </c>
       <c r="D11" t="n">
-        <v>194</v>
+        <v>103</v>
       </c>
       <c r="E11" t="n">
+        <v>112</v>
+      </c>
+      <c r="F11" t="n">
         <v>13</v>
-      </c>
-      <c r="F11" t="n">
-        <v>20</v>
       </c>
     </row>
     <row r="12">
@@ -675,19 +675,19 @@
         </is>
       </c>
       <c r="B12" t="n">
-        <v>146</v>
+        <v>145</v>
       </c>
       <c r="C12" t="n">
-        <v>4</v>
+        <v>8</v>
       </c>
       <c r="D12" t="n">
-        <v>157</v>
+        <v>80</v>
       </c>
       <c r="E12" t="n">
-        <v>8</v>
+        <v>92</v>
       </c>
       <c r="F12" t="n">
-        <v>16</v>
+        <v>6</v>
       </c>
     </row>
     <row r="13">
@@ -722,16 +722,16 @@
         <v>0</v>
       </c>
       <c r="C14" t="n">
-        <v>3</v>
+        <v>0</v>
       </c>
       <c r="D14" t="n">
-        <v>150</v>
+        <v>62</v>
       </c>
       <c r="E14" t="n">
-        <v>3</v>
+        <v>96</v>
       </c>
       <c r="F14" t="n">
-        <v>4</v>
+        <v>2</v>
       </c>
     </row>
     <row r="15">
@@ -741,19 +741,19 @@
         </is>
       </c>
       <c r="B15" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="C15" t="n">
-        <v>7</v>
+        <v>4</v>
       </c>
       <c r="D15" t="n">
-        <v>160</v>
+        <v>82</v>
       </c>
       <c r="E15" t="n">
-        <v>18</v>
+        <v>101</v>
       </c>
       <c r="F15" t="n">
-        <v>14</v>
+        <v>13</v>
       </c>
     </row>
     <row r="16">
@@ -763,16 +763,16 @@
         </is>
       </c>
       <c r="B16" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="C16" t="n">
         <v>1</v>
       </c>
       <c r="D16" t="n">
-        <v>3</v>
+        <v>0</v>
       </c>
       <c r="E16" t="n">
-        <v>0</v>
+        <v>4</v>
       </c>
       <c r="F16" t="n">
         <v>0</v>
@@ -788,16 +788,16 @@
         <v>5</v>
       </c>
       <c r="C17" t="n">
-        <v>5</v>
+        <v>2</v>
       </c>
       <c r="D17" t="n">
-        <v>188</v>
+        <v>87</v>
       </c>
       <c r="E17" t="n">
-        <v>6</v>
+        <v>118</v>
       </c>
       <c r="F17" t="n">
-        <v>11</v>
+        <v>3</v>
       </c>
     </row>
     <row r="18">
@@ -813,10 +813,10 @@
         <v>0</v>
       </c>
       <c r="D18" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="E18" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="F18" t="n">
         <v>0</v>
@@ -829,19 +829,19 @@
         </is>
       </c>
       <c r="B19" t="n">
-        <v>115</v>
+        <v>104</v>
       </c>
       <c r="C19" t="n">
-        <v>7</v>
+        <v>23</v>
       </c>
       <c r="D19" t="n">
-        <v>96</v>
+        <v>54</v>
       </c>
       <c r="E19" t="n">
-        <v>16</v>
+        <v>66</v>
       </c>
       <c r="F19" t="n">
-        <v>19</v>
+        <v>6</v>
       </c>
     </row>
     <row r="20">
@@ -851,19 +851,19 @@
         </is>
       </c>
       <c r="B20" t="n">
-        <v>208</v>
+        <v>205</v>
       </c>
       <c r="C20" t="n">
-        <v>15</v>
+        <v>14</v>
       </c>
       <c r="D20" t="n">
-        <v>213</v>
+        <v>107</v>
       </c>
       <c r="E20" t="n">
-        <v>16</v>
+        <v>132</v>
       </c>
       <c r="F20" t="n">
-        <v>16</v>
+        <v>10</v>
       </c>
     </row>
     <row r="21">
@@ -876,16 +876,16 @@
         <v>0</v>
       </c>
       <c r="C21" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="D21" t="n">
-        <v>23</v>
+        <v>14</v>
       </c>
       <c r="E21" t="n">
-        <v>3</v>
+        <v>13</v>
       </c>
       <c r="F21" t="n">
-        <v>5</v>
+        <v>2</v>
       </c>
     </row>
     <row r="22">
@@ -895,16 +895,16 @@
         </is>
       </c>
       <c r="B22" t="n">
+        <v>4</v>
+      </c>
+      <c r="C22" t="n">
+        <v>0</v>
+      </c>
+      <c r="D22" t="n">
+        <v>2</v>
+      </c>
+      <c r="E22" t="n">
         <v>3</v>
-      </c>
-      <c r="C22" t="n">
-        <v>1</v>
-      </c>
-      <c r="D22" t="n">
-        <v>5</v>
-      </c>
-      <c r="E22" t="n">
-        <v>0</v>
       </c>
       <c r="F22" t="n">
         <v>1</v>
@@ -920,16 +920,16 @@
         <v>2</v>
       </c>
       <c r="C23" t="n">
-        <v>7</v>
+        <v>6</v>
       </c>
       <c r="D23" t="n">
-        <v>131</v>
+        <v>72</v>
       </c>
       <c r="E23" t="n">
-        <v>15</v>
+        <v>74</v>
       </c>
       <c r="F23" t="n">
-        <v>13</v>
+        <v>14</v>
       </c>
     </row>
     <row r="24">
@@ -942,16 +942,16 @@
         <v>0</v>
       </c>
       <c r="C24" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="D24" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="E24" t="n">
-        <v>0</v>
+        <v>4</v>
       </c>
       <c r="F24" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
     </row>
     <row r="25">
@@ -961,7 +961,7 @@
         </is>
       </c>
       <c r="B25" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="C25" t="n">
         <v>0</v>
@@ -970,10 +970,10 @@
         <v>1</v>
       </c>
       <c r="E25" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="F25" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
     </row>
     <row r="26">
@@ -983,19 +983,19 @@
         </is>
       </c>
       <c r="B26" t="n">
-        <v>0</v>
+        <v>37</v>
       </c>
       <c r="C26" t="n">
         <v>7</v>
       </c>
       <c r="D26" t="n">
-        <v>38</v>
+        <v>32</v>
       </c>
       <c r="E26" t="n">
-        <v>5</v>
+        <v>15</v>
       </c>
       <c r="F26" t="n">
-        <v>2</v>
+        <v>6</v>
       </c>
     </row>
     <row r="27">
@@ -1008,16 +1008,16 @@
         <v>0</v>
       </c>
       <c r="C27" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="D27" t="n">
-        <v>4</v>
+        <v>2</v>
       </c>
       <c r="E27" t="n">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="F27" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
     </row>
     <row r="28">
@@ -1030,16 +1030,16 @@
         <v>86</v>
       </c>
       <c r="C28" t="n">
-        <v>8</v>
+        <v>16</v>
       </c>
       <c r="D28" t="n">
-        <v>77</v>
+        <v>33</v>
       </c>
       <c r="E28" t="n">
-        <v>22</v>
+        <v>52</v>
       </c>
       <c r="F28" t="n">
-        <v>7</v>
+        <v>13</v>
       </c>
     </row>
     <row r="29">
@@ -1055,10 +1055,10 @@
         <v>0</v>
       </c>
       <c r="D29" t="n">
+        <v>2</v>
+      </c>
+      <c r="E29" t="n">
         <v>9</v>
-      </c>
-      <c r="E29" t="n">
-        <v>2</v>
       </c>
       <c r="F29" t="n">
         <v>0</v>
@@ -1071,19 +1071,19 @@
         </is>
       </c>
       <c r="B30" t="n">
-        <v>23</v>
+        <v>21</v>
       </c>
       <c r="C30" t="n">
-        <v>0</v>
+        <v>4</v>
       </c>
       <c r="D30" t="n">
-        <v>17</v>
+        <v>5</v>
       </c>
       <c r="E30" t="n">
-        <v>1</v>
+        <v>12</v>
       </c>
       <c r="F30" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
     </row>
     <row r="31">
@@ -1096,13 +1096,13 @@
         <v>4</v>
       </c>
       <c r="C31" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="D31" t="n">
+        <v>2</v>
+      </c>
+      <c r="E31" t="n">
         <v>4</v>
-      </c>
-      <c r="E31" t="n">
-        <v>3</v>
       </c>
       <c r="F31" t="n">
         <v>0</v>
@@ -1115,19 +1115,19 @@
         </is>
       </c>
       <c r="B32" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="C32" t="n">
-        <v>5</v>
+        <v>7</v>
       </c>
       <c r="D32" t="n">
-        <v>44</v>
+        <v>20</v>
       </c>
       <c r="E32" t="n">
-        <v>7</v>
+        <v>33</v>
       </c>
       <c r="F32" t="n">
-        <v>6</v>
+        <v>4</v>
       </c>
     </row>
     <row r="33">
@@ -1137,19 +1137,19 @@
         </is>
       </c>
       <c r="B33" t="n">
-        <v>98</v>
+        <v>100</v>
       </c>
       <c r="C33" t="n">
-        <v>6</v>
+        <v>10</v>
       </c>
       <c r="D33" t="n">
-        <v>108</v>
+        <v>56</v>
       </c>
       <c r="E33" t="n">
-        <v>12</v>
+        <v>62</v>
       </c>
       <c r="F33" t="n">
-        <v>15</v>
+        <v>11</v>
       </c>
     </row>
     <row r="34">
@@ -1162,13 +1162,13 @@
         <v>15</v>
       </c>
       <c r="C34" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="D34" t="n">
-        <v>15</v>
+        <v>3</v>
       </c>
       <c r="E34" t="n">
-        <v>0</v>
+        <v>13</v>
       </c>
       <c r="F34" t="n">
         <v>0</v>

--- a/data/output/topik_per_lokasi.xlsx
+++ b/data/output/topik_per_lokasi.xlsx
@@ -455,19 +455,19 @@
         </is>
       </c>
       <c r="B2" t="n">
-        <v>47</v>
+        <v>48</v>
       </c>
       <c r="C2" t="n">
-        <v>5</v>
+        <v>2</v>
       </c>
       <c r="D2" t="n">
         <v>14</v>
       </c>
       <c r="E2" t="n">
-        <v>25</v>
+        <v>2</v>
       </c>
       <c r="F2" t="n">
-        <v>3</v>
+        <v>28</v>
       </c>
     </row>
     <row r="3">
@@ -477,19 +477,19 @@
         </is>
       </c>
       <c r="B3" t="n">
-        <v>185</v>
+        <v>173</v>
       </c>
       <c r="C3" t="n">
-        <v>27</v>
+        <v>24</v>
       </c>
       <c r="D3" t="n">
-        <v>120</v>
+        <v>84</v>
       </c>
       <c r="E3" t="n">
-        <v>130</v>
+        <v>33</v>
       </c>
       <c r="F3" t="n">
-        <v>36</v>
+        <v>184</v>
       </c>
     </row>
     <row r="4">
@@ -502,13 +502,13 @@
         <v>1</v>
       </c>
       <c r="C4" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="D4" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="E4" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="F4" t="n">
         <v>0</v>
@@ -521,19 +521,19 @@
         </is>
       </c>
       <c r="B5" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="C5" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="D5" t="n">
-        <v>7</v>
+        <v>2</v>
       </c>
       <c r="E5" t="n">
-        <v>9</v>
+        <v>1</v>
       </c>
       <c r="F5" t="n">
-        <v>2</v>
+        <v>13</v>
       </c>
     </row>
     <row r="6">
@@ -549,10 +549,10 @@
         <v>0</v>
       </c>
       <c r="D6" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="E6" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="F6" t="n">
         <v>0</v>
@@ -571,13 +571,13 @@
         <v>0</v>
       </c>
       <c r="D7" t="n">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="E7" t="n">
         <v>0</v>
       </c>
       <c r="F7" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
     </row>
     <row r="8">
@@ -587,19 +587,19 @@
         </is>
       </c>
       <c r="B8" t="n">
-        <v>4</v>
+        <v>2</v>
       </c>
       <c r="C8" t="n">
-        <v>8</v>
+        <v>30</v>
       </c>
       <c r="D8" t="n">
-        <v>115</v>
+        <v>90</v>
       </c>
       <c r="E8" t="n">
-        <v>47</v>
+        <v>15</v>
       </c>
       <c r="F8" t="n">
-        <v>23</v>
+        <v>60</v>
       </c>
     </row>
     <row r="9">
@@ -609,19 +609,19 @@
         </is>
       </c>
       <c r="B9" t="n">
-        <v>217</v>
+        <v>235</v>
       </c>
       <c r="C9" t="n">
-        <v>39</v>
+        <v>17</v>
       </c>
       <c r="D9" t="n">
-        <v>56</v>
+        <v>72</v>
       </c>
       <c r="E9" t="n">
-        <v>153</v>
+        <v>42</v>
       </c>
       <c r="F9" t="n">
-        <v>55</v>
+        <v>154</v>
       </c>
     </row>
     <row r="10">
@@ -634,16 +634,16 @@
         <v>0</v>
       </c>
       <c r="C10" t="n">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="D10" t="n">
-        <v>16</v>
+        <v>5</v>
       </c>
       <c r="E10" t="n">
-        <v>20</v>
+        <v>1</v>
       </c>
       <c r="F10" t="n">
-        <v>2</v>
+        <v>30</v>
       </c>
     </row>
     <row r="11">
@@ -653,19 +653,19 @@
         </is>
       </c>
       <c r="B11" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="C11" t="n">
-        <v>4</v>
+        <v>18</v>
       </c>
       <c r="D11" t="n">
-        <v>103</v>
+        <v>18</v>
       </c>
       <c r="E11" t="n">
-        <v>112</v>
+        <v>17</v>
       </c>
       <c r="F11" t="n">
-        <v>13</v>
+        <v>180</v>
       </c>
     </row>
     <row r="12">
@@ -675,19 +675,19 @@
         </is>
       </c>
       <c r="B12" t="n">
-        <v>145</v>
+        <v>143</v>
       </c>
       <c r="C12" t="n">
+        <v>6</v>
+      </c>
+      <c r="D12" t="n">
         <v>8</v>
       </c>
-      <c r="D12" t="n">
-        <v>80</v>
-      </c>
       <c r="E12" t="n">
-        <v>92</v>
+        <v>18</v>
       </c>
       <c r="F12" t="n">
-        <v>6</v>
+        <v>156</v>
       </c>
     </row>
     <row r="13">
@@ -722,16 +722,16 @@
         <v>0</v>
       </c>
       <c r="C14" t="n">
-        <v>0</v>
+        <v>5</v>
       </c>
       <c r="D14" t="n">
-        <v>62</v>
+        <v>8</v>
       </c>
       <c r="E14" t="n">
-        <v>96</v>
+        <v>3</v>
       </c>
       <c r="F14" t="n">
-        <v>2</v>
+        <v>144</v>
       </c>
     </row>
     <row r="15">
@@ -741,19 +741,19 @@
         </is>
       </c>
       <c r="B15" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="C15" t="n">
-        <v>4</v>
+        <v>14</v>
       </c>
       <c r="D15" t="n">
-        <v>82</v>
+        <v>24</v>
       </c>
       <c r="E15" t="n">
-        <v>101</v>
+        <v>9</v>
       </c>
       <c r="F15" t="n">
-        <v>13</v>
+        <v>154</v>
       </c>
     </row>
     <row r="16">
@@ -766,16 +766,16 @@
         <v>2</v>
       </c>
       <c r="C16" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="D16" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="E16" t="n">
-        <v>4</v>
+        <v>1</v>
       </c>
       <c r="F16" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
     </row>
     <row r="17">
@@ -785,19 +785,19 @@
         </is>
       </c>
       <c r="B17" t="n">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="C17" t="n">
-        <v>2</v>
+        <v>4</v>
       </c>
       <c r="D17" t="n">
-        <v>87</v>
+        <v>17</v>
       </c>
       <c r="E17" t="n">
-        <v>118</v>
+        <v>6</v>
       </c>
       <c r="F17" t="n">
-        <v>3</v>
+        <v>184</v>
       </c>
     </row>
     <row r="18">
@@ -813,13 +813,13 @@
         <v>0</v>
       </c>
       <c r="D18" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="E18" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="F18" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
     </row>
     <row r="19">
@@ -829,19 +829,19 @@
         </is>
       </c>
       <c r="B19" t="n">
-        <v>104</v>
+        <v>116</v>
       </c>
       <c r="C19" t="n">
-        <v>23</v>
+        <v>11</v>
       </c>
       <c r="D19" t="n">
-        <v>54</v>
+        <v>18</v>
       </c>
       <c r="E19" t="n">
-        <v>66</v>
+        <v>22</v>
       </c>
       <c r="F19" t="n">
-        <v>6</v>
+        <v>86</v>
       </c>
     </row>
     <row r="20">
@@ -851,19 +851,19 @@
         </is>
       </c>
       <c r="B20" t="n">
-        <v>205</v>
+        <v>210</v>
       </c>
       <c r="C20" t="n">
-        <v>14</v>
+        <v>18</v>
       </c>
       <c r="D20" t="n">
-        <v>107</v>
+        <v>19</v>
       </c>
       <c r="E20" t="n">
-        <v>132</v>
+        <v>15</v>
       </c>
       <c r="F20" t="n">
-        <v>10</v>
+        <v>206</v>
       </c>
     </row>
     <row r="21">
@@ -876,16 +876,16 @@
         <v>0</v>
       </c>
       <c r="C21" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="D21" t="n">
-        <v>14</v>
+        <v>2</v>
       </c>
       <c r="E21" t="n">
-        <v>13</v>
+        <v>4</v>
       </c>
       <c r="F21" t="n">
-        <v>2</v>
+        <v>25</v>
       </c>
     </row>
     <row r="22">
@@ -901,13 +901,13 @@
         <v>0</v>
       </c>
       <c r="D22" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="E22" t="n">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="F22" t="n">
-        <v>1</v>
+        <v>4</v>
       </c>
     </row>
     <row r="23">
@@ -917,19 +917,19 @@
         </is>
       </c>
       <c r="B23" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="C23" t="n">
-        <v>6</v>
+        <v>18</v>
       </c>
       <c r="D23" t="n">
-        <v>72</v>
+        <v>41</v>
       </c>
       <c r="E23" t="n">
-        <v>74</v>
+        <v>15</v>
       </c>
       <c r="F23" t="n">
-        <v>14</v>
+        <v>95</v>
       </c>
     </row>
     <row r="24">
@@ -942,16 +942,16 @@
         <v>0</v>
       </c>
       <c r="C24" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="D24" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="E24" t="n">
-        <v>4</v>
+        <v>1</v>
       </c>
       <c r="F24" t="n">
-        <v>0</v>
+        <v>3</v>
       </c>
     </row>
     <row r="25">
@@ -961,19 +961,19 @@
         </is>
       </c>
       <c r="B25" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="C25" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="D25" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="E25" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="F25" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
     </row>
     <row r="26">
@@ -986,16 +986,16 @@
         <v>37</v>
       </c>
       <c r="C26" t="n">
+        <v>11</v>
+      </c>
+      <c r="D26" t="n">
+        <v>14</v>
+      </c>
+      <c r="E26" t="n">
         <v>7</v>
       </c>
-      <c r="D26" t="n">
-        <v>32</v>
-      </c>
-      <c r="E26" t="n">
-        <v>15</v>
-      </c>
       <c r="F26" t="n">
-        <v>6</v>
+        <v>28</v>
       </c>
     </row>
     <row r="27">
@@ -1008,16 +1008,16 @@
         <v>0</v>
       </c>
       <c r="C27" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="D27" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="E27" t="n">
+        <v>0</v>
+      </c>
+      <c r="F27" t="n">
         <v>3</v>
-      </c>
-      <c r="F27" t="n">
-        <v>2</v>
       </c>
     </row>
     <row r="28">
@@ -1027,19 +1027,19 @@
         </is>
       </c>
       <c r="B28" t="n">
-        <v>86</v>
+        <v>91</v>
       </c>
       <c r="C28" t="n">
-        <v>16</v>
+        <v>13</v>
       </c>
       <c r="D28" t="n">
-        <v>33</v>
+        <v>24</v>
       </c>
       <c r="E28" t="n">
-        <v>52</v>
+        <v>9</v>
       </c>
       <c r="F28" t="n">
-        <v>13</v>
+        <v>63</v>
       </c>
     </row>
     <row r="29">
@@ -1058,10 +1058,10 @@
         <v>2</v>
       </c>
       <c r="E29" t="n">
+        <v>0</v>
+      </c>
+      <c r="F29" t="n">
         <v>9</v>
-      </c>
-      <c r="F29" t="n">
-        <v>0</v>
       </c>
     </row>
     <row r="30">
@@ -1074,16 +1074,16 @@
         <v>21</v>
       </c>
       <c r="C30" t="n">
-        <v>4</v>
+        <v>2</v>
       </c>
       <c r="D30" t="n">
-        <v>5</v>
+        <v>1</v>
       </c>
       <c r="E30" t="n">
-        <v>12</v>
+        <v>1</v>
       </c>
       <c r="F30" t="n">
-        <v>1</v>
+        <v>18</v>
       </c>
     </row>
     <row r="31">
@@ -1093,19 +1093,19 @@
         </is>
       </c>
       <c r="B31" t="n">
-        <v>4</v>
+        <v>6</v>
       </c>
       <c r="C31" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="D31" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="E31" t="n">
-        <v>4</v>
+        <v>1</v>
       </c>
       <c r="F31" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
     </row>
     <row r="32">
@@ -1115,19 +1115,19 @@
         </is>
       </c>
       <c r="B32" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="C32" t="n">
-        <v>7</v>
+        <v>4</v>
       </c>
       <c r="D32" t="n">
-        <v>20</v>
+        <v>5</v>
       </c>
       <c r="E32" t="n">
-        <v>33</v>
+        <v>6</v>
       </c>
       <c r="F32" t="n">
-        <v>4</v>
+        <v>47</v>
       </c>
     </row>
     <row r="33">
@@ -1137,19 +1137,19 @@
         </is>
       </c>
       <c r="B33" t="n">
-        <v>100</v>
+        <v>104</v>
       </c>
       <c r="C33" t="n">
         <v>10</v>
       </c>
       <c r="D33" t="n">
-        <v>56</v>
+        <v>21</v>
       </c>
       <c r="E33" t="n">
-        <v>62</v>
+        <v>12</v>
       </c>
       <c r="F33" t="n">
-        <v>11</v>
+        <v>92</v>
       </c>
     </row>
     <row r="34">
@@ -1165,13 +1165,13 @@
         <v>0</v>
       </c>
       <c r="D34" t="n">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="E34" t="n">
-        <v>13</v>
+        <v>0</v>
       </c>
       <c r="F34" t="n">
-        <v>0</v>
+        <v>15</v>
       </c>
     </row>
   </sheetData>

--- a/data/output/topik_per_lokasi.xlsx
+++ b/data/output/topik_per_lokasi.xlsx
@@ -455,19 +455,19 @@
         </is>
       </c>
       <c r="B2" t="n">
-        <v>48</v>
+        <v>43</v>
       </c>
       <c r="C2" t="n">
-        <v>2</v>
+        <v>10</v>
       </c>
       <c r="D2" t="n">
-        <v>14</v>
+        <v>3</v>
       </c>
       <c r="E2" t="n">
-        <v>2</v>
+        <v>6</v>
       </c>
       <c r="F2" t="n">
-        <v>28</v>
+        <v>32</v>
       </c>
     </row>
     <row r="3">
@@ -477,19 +477,19 @@
         </is>
       </c>
       <c r="B3" t="n">
-        <v>173</v>
+        <v>193</v>
       </c>
       <c r="C3" t="n">
-        <v>24</v>
+        <v>26</v>
       </c>
       <c r="D3" t="n">
-        <v>84</v>
+        <v>34</v>
       </c>
       <c r="E3" t="n">
         <v>33</v>
       </c>
       <c r="F3" t="n">
-        <v>184</v>
+        <v>212</v>
       </c>
     </row>
     <row r="4">
@@ -508,10 +508,10 @@
         <v>0</v>
       </c>
       <c r="E4" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="F4" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
     </row>
     <row r="5">
@@ -521,16 +521,16 @@
         </is>
       </c>
       <c r="B5" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="C5" t="n">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="D5" t="n">
         <v>2</v>
       </c>
       <c r="E5" t="n">
-        <v>1</v>
+        <v>4</v>
       </c>
       <c r="F5" t="n">
         <v>13</v>
@@ -552,10 +552,10 @@
         <v>0</v>
       </c>
       <c r="E6" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="F6" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
     </row>
     <row r="7">
@@ -587,19 +587,19 @@
         </is>
       </c>
       <c r="B8" t="n">
-        <v>2</v>
+        <v>4</v>
       </c>
       <c r="C8" t="n">
-        <v>30</v>
+        <v>21</v>
       </c>
       <c r="D8" t="n">
-        <v>90</v>
+        <v>33</v>
       </c>
       <c r="E8" t="n">
-        <v>15</v>
+        <v>39</v>
       </c>
       <c r="F8" t="n">
-        <v>60</v>
+        <v>100</v>
       </c>
     </row>
     <row r="9">
@@ -609,19 +609,19 @@
         </is>
       </c>
       <c r="B9" t="n">
-        <v>235</v>
+        <v>228</v>
       </c>
       <c r="C9" t="n">
-        <v>17</v>
+        <v>29</v>
       </c>
       <c r="D9" t="n">
-        <v>72</v>
+        <v>19</v>
       </c>
       <c r="E9" t="n">
-        <v>42</v>
+        <v>61</v>
       </c>
       <c r="F9" t="n">
-        <v>154</v>
+        <v>183</v>
       </c>
     </row>
     <row r="10">
@@ -631,19 +631,19 @@
         </is>
       </c>
       <c r="B10" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="C10" t="n">
+        <v>2</v>
+      </c>
+      <c r="D10" t="n">
+        <v>2</v>
+      </c>
+      <c r="E10" t="n">
         <v>3</v>
       </c>
-      <c r="D10" t="n">
-        <v>5</v>
-      </c>
-      <c r="E10" t="n">
-        <v>1</v>
-      </c>
       <c r="F10" t="n">
-        <v>30</v>
+        <v>31</v>
       </c>
     </row>
     <row r="11">
@@ -653,19 +653,19 @@
         </is>
       </c>
       <c r="B11" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="C11" t="n">
-        <v>18</v>
+        <v>10</v>
       </c>
       <c r="D11" t="n">
-        <v>18</v>
+        <v>12</v>
       </c>
       <c r="E11" t="n">
-        <v>17</v>
+        <v>15</v>
       </c>
       <c r="F11" t="n">
-        <v>180</v>
+        <v>198</v>
       </c>
     </row>
     <row r="12">
@@ -675,19 +675,19 @@
         </is>
       </c>
       <c r="B12" t="n">
-        <v>143</v>
+        <v>147</v>
       </c>
       <c r="C12" t="n">
-        <v>6</v>
+        <v>5</v>
       </c>
       <c r="D12" t="n">
+        <v>11</v>
+      </c>
+      <c r="E12" t="n">
         <v>8</v>
       </c>
-      <c r="E12" t="n">
-        <v>18</v>
-      </c>
       <c r="F12" t="n">
-        <v>156</v>
+        <v>160</v>
       </c>
     </row>
     <row r="13">
@@ -722,16 +722,16 @@
         <v>0</v>
       </c>
       <c r="C14" t="n">
-        <v>5</v>
+        <v>2</v>
       </c>
       <c r="D14" t="n">
-        <v>8</v>
+        <v>6</v>
       </c>
       <c r="E14" t="n">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="F14" t="n">
-        <v>144</v>
+        <v>148</v>
       </c>
     </row>
     <row r="15">
@@ -741,19 +741,19 @@
         </is>
       </c>
       <c r="B15" t="n">
-        <v>1</v>
+        <v>4</v>
       </c>
       <c r="C15" t="n">
-        <v>14</v>
+        <v>8</v>
       </c>
       <c r="D15" t="n">
+        <v>13</v>
+      </c>
+      <c r="E15" t="n">
         <v>24</v>
       </c>
-      <c r="E15" t="n">
-        <v>9</v>
-      </c>
       <c r="F15" t="n">
-        <v>154</v>
+        <v>153</v>
       </c>
     </row>
     <row r="16">
@@ -763,13 +763,13 @@
         </is>
       </c>
       <c r="B16" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="C16" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="D16" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="E16" t="n">
         <v>1</v>
@@ -785,16 +785,16 @@
         </is>
       </c>
       <c r="B17" t="n">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="C17" t="n">
-        <v>4</v>
+        <v>6</v>
       </c>
       <c r="D17" t="n">
-        <v>17</v>
+        <v>8</v>
       </c>
       <c r="E17" t="n">
-        <v>6</v>
+        <v>12</v>
       </c>
       <c r="F17" t="n">
         <v>184</v>
@@ -829,19 +829,19 @@
         </is>
       </c>
       <c r="B19" t="n">
-        <v>116</v>
+        <v>114</v>
       </c>
       <c r="C19" t="n">
-        <v>11</v>
+        <v>8</v>
       </c>
       <c r="D19" t="n">
-        <v>18</v>
+        <v>8</v>
       </c>
       <c r="E19" t="n">
-        <v>22</v>
+        <v>21</v>
       </c>
       <c r="F19" t="n">
-        <v>86</v>
+        <v>102</v>
       </c>
     </row>
     <row r="20">
@@ -854,16 +854,16 @@
         <v>210</v>
       </c>
       <c r="C20" t="n">
-        <v>18</v>
+        <v>13</v>
       </c>
       <c r="D20" t="n">
-        <v>19</v>
+        <v>12</v>
       </c>
       <c r="E20" t="n">
-        <v>15</v>
+        <v>16</v>
       </c>
       <c r="F20" t="n">
-        <v>206</v>
+        <v>217</v>
       </c>
     </row>
     <row r="21">
@@ -876,16 +876,16 @@
         <v>0</v>
       </c>
       <c r="C21" t="n">
-        <v>0</v>
+        <v>3</v>
       </c>
       <c r="D21" t="n">
         <v>2</v>
       </c>
       <c r="E21" t="n">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="F21" t="n">
-        <v>25</v>
+        <v>23</v>
       </c>
     </row>
     <row r="22">
@@ -898,13 +898,13 @@
         <v>4</v>
       </c>
       <c r="C22" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="D22" t="n">
         <v>1</v>
       </c>
       <c r="E22" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="F22" t="n">
         <v>4</v>
@@ -917,19 +917,19 @@
         </is>
       </c>
       <c r="B23" t="n">
-        <v>3</v>
+        <v>6</v>
       </c>
       <c r="C23" t="n">
-        <v>18</v>
+        <v>7</v>
       </c>
       <c r="D23" t="n">
-        <v>41</v>
+        <v>27</v>
       </c>
       <c r="E23" t="n">
-        <v>15</v>
+        <v>14</v>
       </c>
       <c r="F23" t="n">
-        <v>95</v>
+        <v>118</v>
       </c>
     </row>
     <row r="24">
@@ -945,13 +945,13 @@
         <v>1</v>
       </c>
       <c r="D24" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="E24" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="F24" t="n">
-        <v>3</v>
+        <v>5</v>
       </c>
     </row>
     <row r="25">
@@ -964,16 +964,16 @@
         <v>0</v>
       </c>
       <c r="C25" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="D25" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="E25" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="F25" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
     </row>
     <row r="26">
@@ -983,19 +983,19 @@
         </is>
       </c>
       <c r="B26" t="n">
-        <v>37</v>
+        <v>40</v>
       </c>
       <c r="C26" t="n">
-        <v>11</v>
+        <v>8</v>
       </c>
       <c r="D26" t="n">
-        <v>14</v>
+        <v>9</v>
       </c>
       <c r="E26" t="n">
-        <v>7</v>
+        <v>5</v>
       </c>
       <c r="F26" t="n">
-        <v>28</v>
+        <v>36</v>
       </c>
     </row>
     <row r="27">
@@ -1008,16 +1008,16 @@
         <v>0</v>
       </c>
       <c r="C27" t="n">
+        <v>0</v>
+      </c>
+      <c r="D27" t="n">
+        <v>1</v>
+      </c>
+      <c r="E27" t="n">
         <v>2</v>
       </c>
-      <c r="D27" t="n">
-        <v>3</v>
-      </c>
-      <c r="E27" t="n">
-        <v>0</v>
-      </c>
       <c r="F27" t="n">
-        <v>3</v>
+        <v>5</v>
       </c>
     </row>
     <row r="28">
@@ -1027,19 +1027,19 @@
         </is>
       </c>
       <c r="B28" t="n">
-        <v>91</v>
+        <v>89</v>
       </c>
       <c r="C28" t="n">
-        <v>13</v>
+        <v>10</v>
       </c>
       <c r="D28" t="n">
-        <v>24</v>
+        <v>11</v>
       </c>
       <c r="E28" t="n">
         <v>9</v>
       </c>
       <c r="F28" t="n">
-        <v>63</v>
+        <v>81</v>
       </c>
     </row>
     <row r="29">
@@ -1055,13 +1055,13 @@
         <v>0</v>
       </c>
       <c r="D29" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="E29" t="n">
         <v>0</v>
       </c>
       <c r="F29" t="n">
-        <v>9</v>
+        <v>10</v>
       </c>
     </row>
     <row r="30">
@@ -1071,7 +1071,7 @@
         </is>
       </c>
       <c r="B30" t="n">
-        <v>21</v>
+        <v>22</v>
       </c>
       <c r="C30" t="n">
         <v>2</v>
@@ -1080,10 +1080,10 @@
         <v>1</v>
       </c>
       <c r="E30" t="n">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="F30" t="n">
-        <v>18</v>
+        <v>15</v>
       </c>
     </row>
     <row r="31">
@@ -1093,19 +1093,19 @@
         </is>
       </c>
       <c r="B31" t="n">
-        <v>6</v>
+        <v>4</v>
       </c>
       <c r="C31" t="n">
         <v>1</v>
       </c>
       <c r="D31" t="n">
+        <v>0</v>
+      </c>
+      <c r="E31" t="n">
         <v>3</v>
       </c>
-      <c r="E31" t="n">
-        <v>1</v>
-      </c>
       <c r="F31" t="n">
-        <v>1</v>
+        <v>4</v>
       </c>
     </row>
     <row r="32">
@@ -1115,19 +1115,19 @@
         </is>
       </c>
       <c r="B32" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="C32" t="n">
         <v>4</v>
       </c>
       <c r="D32" t="n">
+        <v>8</v>
+      </c>
+      <c r="E32" t="n">
         <v>5</v>
       </c>
-      <c r="E32" t="n">
-        <v>6</v>
-      </c>
       <c r="F32" t="n">
-        <v>47</v>
+        <v>46</v>
       </c>
     </row>
     <row r="33">
@@ -1137,19 +1137,19 @@
         </is>
       </c>
       <c r="B33" t="n">
-        <v>104</v>
+        <v>100</v>
       </c>
       <c r="C33" t="n">
         <v>10</v>
       </c>
       <c r="D33" t="n">
-        <v>21</v>
+        <v>15</v>
       </c>
       <c r="E33" t="n">
         <v>12</v>
       </c>
       <c r="F33" t="n">
-        <v>92</v>
+        <v>102</v>
       </c>
     </row>
     <row r="34">
@@ -1165,10 +1165,10 @@
         <v>0</v>
       </c>
       <c r="D34" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="E34" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="F34" t="n">
         <v>15</v>

--- a/data/output/topik_per_lokasi.xlsx
+++ b/data/output/topik_per_lokasi.xlsx
@@ -455,19 +455,19 @@
         </is>
       </c>
       <c r="B2" t="n">
-        <v>43</v>
+        <v>35</v>
       </c>
       <c r="C2" t="n">
-        <v>10</v>
+        <v>9</v>
       </c>
       <c r="D2" t="n">
         <v>3</v>
       </c>
       <c r="E2" t="n">
-        <v>6</v>
+        <v>32</v>
       </c>
       <c r="F2" t="n">
-        <v>32</v>
+        <v>15</v>
       </c>
     </row>
     <row r="3">
@@ -477,19 +477,19 @@
         </is>
       </c>
       <c r="B3" t="n">
-        <v>193</v>
+        <v>153</v>
       </c>
       <c r="C3" t="n">
-        <v>26</v>
+        <v>66</v>
       </c>
       <c r="D3" t="n">
-        <v>34</v>
+        <v>24</v>
       </c>
       <c r="E3" t="n">
-        <v>33</v>
+        <v>194</v>
       </c>
       <c r="F3" t="n">
-        <v>212</v>
+        <v>61</v>
       </c>
     </row>
     <row r="4">
@@ -502,16 +502,16 @@
         <v>1</v>
       </c>
       <c r="C4" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="D4" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="E4" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="F4" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
     </row>
     <row r="5">
@@ -521,19 +521,19 @@
         </is>
       </c>
       <c r="B5" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="C5" t="n">
-        <v>1</v>
+        <v>7</v>
       </c>
       <c r="D5" t="n">
         <v>2</v>
       </c>
       <c r="E5" t="n">
-        <v>4</v>
+        <v>11</v>
       </c>
       <c r="F5" t="n">
-        <v>13</v>
+        <v>1</v>
       </c>
     </row>
     <row r="6">
@@ -552,10 +552,10 @@
         <v>0</v>
       </c>
       <c r="E6" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="F6" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
     </row>
     <row r="7">
@@ -568,16 +568,16 @@
         <v>0</v>
       </c>
       <c r="C7" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="D7" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="E7" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="F7" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
     </row>
     <row r="8">
@@ -587,19 +587,19 @@
         </is>
       </c>
       <c r="B8" t="n">
+        <v>3</v>
+      </c>
+      <c r="C8" t="n">
+        <v>74</v>
+      </c>
+      <c r="D8" t="n">
+        <v>37</v>
+      </c>
+      <c r="E8" t="n">
+        <v>79</v>
+      </c>
+      <c r="F8" t="n">
         <v>4</v>
-      </c>
-      <c r="C8" t="n">
-        <v>21</v>
-      </c>
-      <c r="D8" t="n">
-        <v>33</v>
-      </c>
-      <c r="E8" t="n">
-        <v>39</v>
-      </c>
-      <c r="F8" t="n">
-        <v>100</v>
       </c>
     </row>
     <row r="9">
@@ -609,19 +609,19 @@
         </is>
       </c>
       <c r="B9" t="n">
-        <v>228</v>
+        <v>134</v>
       </c>
       <c r="C9" t="n">
-        <v>29</v>
+        <v>81</v>
       </c>
       <c r="D9" t="n">
-        <v>19</v>
+        <v>20</v>
       </c>
       <c r="E9" t="n">
-        <v>61</v>
+        <v>173</v>
       </c>
       <c r="F9" t="n">
-        <v>183</v>
+        <v>112</v>
       </c>
     </row>
     <row r="10">
@@ -631,19 +631,19 @@
         </is>
       </c>
       <c r="B10" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="C10" t="n">
-        <v>2</v>
+        <v>12</v>
       </c>
       <c r="D10" t="n">
-        <v>2</v>
+        <v>5</v>
       </c>
       <c r="E10" t="n">
-        <v>3</v>
+        <v>22</v>
       </c>
       <c r="F10" t="n">
-        <v>31</v>
+        <v>0</v>
       </c>
     </row>
     <row r="11">
@@ -653,19 +653,19 @@
         </is>
       </c>
       <c r="B11" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="C11" t="n">
-        <v>10</v>
+        <v>77</v>
       </c>
       <c r="D11" t="n">
-        <v>12</v>
+        <v>15</v>
       </c>
       <c r="E11" t="n">
-        <v>15</v>
+        <v>135</v>
       </c>
       <c r="F11" t="n">
-        <v>198</v>
+        <v>7</v>
       </c>
     </row>
     <row r="12">
@@ -675,19 +675,19 @@
         </is>
       </c>
       <c r="B12" t="n">
-        <v>147</v>
+        <v>126</v>
       </c>
       <c r="C12" t="n">
-        <v>5</v>
+        <v>59</v>
       </c>
       <c r="D12" t="n">
-        <v>11</v>
+        <v>10</v>
       </c>
       <c r="E12" t="n">
-        <v>8</v>
+        <v>109</v>
       </c>
       <c r="F12" t="n">
-        <v>160</v>
+        <v>27</v>
       </c>
     </row>
     <row r="13">
@@ -697,7 +697,7 @@
         </is>
       </c>
       <c r="B13" t="n">
-        <v>5</v>
+        <v>3</v>
       </c>
       <c r="C13" t="n">
         <v>0</v>
@@ -709,7 +709,7 @@
         <v>0</v>
       </c>
       <c r="F13" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
     </row>
     <row r="14">
@@ -722,16 +722,16 @@
         <v>0</v>
       </c>
       <c r="C14" t="n">
-        <v>2</v>
+        <v>68</v>
       </c>
       <c r="D14" t="n">
-        <v>6</v>
+        <v>3</v>
       </c>
       <c r="E14" t="n">
-        <v>4</v>
+        <v>89</v>
       </c>
       <c r="F14" t="n">
-        <v>148</v>
+        <v>0</v>
       </c>
     </row>
     <row r="15">
@@ -744,16 +744,16 @@
         <v>4</v>
       </c>
       <c r="C15" t="n">
-        <v>8</v>
+        <v>72</v>
       </c>
       <c r="D15" t="n">
-        <v>13</v>
+        <v>18</v>
       </c>
       <c r="E15" t="n">
-        <v>24</v>
+        <v>107</v>
       </c>
       <c r="F15" t="n">
-        <v>153</v>
+        <v>5</v>
       </c>
     </row>
     <row r="16">
@@ -763,19 +763,19 @@
         </is>
       </c>
       <c r="B16" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="C16" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="D16" t="n">
         <v>0</v>
       </c>
       <c r="E16" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="F16" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
     </row>
     <row r="17">
@@ -785,19 +785,19 @@
         </is>
       </c>
       <c r="B17" t="n">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="C17" t="n">
-        <v>6</v>
+        <v>78</v>
       </c>
       <c r="D17" t="n">
-        <v>8</v>
+        <v>13</v>
       </c>
       <c r="E17" t="n">
-        <v>12</v>
+        <v>119</v>
       </c>
       <c r="F17" t="n">
-        <v>184</v>
+        <v>1</v>
       </c>
     </row>
     <row r="18">
@@ -810,16 +810,16 @@
         <v>0</v>
       </c>
       <c r="C18" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="D18" t="n">
         <v>0</v>
       </c>
       <c r="E18" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="F18" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
     </row>
     <row r="19">
@@ -829,19 +829,19 @@
         </is>
       </c>
       <c r="B19" t="n">
-        <v>114</v>
+        <v>96</v>
       </c>
       <c r="C19" t="n">
-        <v>8</v>
+        <v>46</v>
       </c>
       <c r="D19" t="n">
-        <v>8</v>
+        <v>13</v>
       </c>
       <c r="E19" t="n">
-        <v>21</v>
+        <v>72</v>
       </c>
       <c r="F19" t="n">
-        <v>102</v>
+        <v>26</v>
       </c>
     </row>
     <row r="20">
@@ -851,19 +851,19 @@
         </is>
       </c>
       <c r="B20" t="n">
-        <v>210</v>
+        <v>176</v>
       </c>
       <c r="C20" t="n">
-        <v>13</v>
+        <v>111</v>
       </c>
       <c r="D20" t="n">
-        <v>12</v>
+        <v>30</v>
       </c>
       <c r="E20" t="n">
-        <v>16</v>
+        <v>106</v>
       </c>
       <c r="F20" t="n">
-        <v>217</v>
+        <v>45</v>
       </c>
     </row>
     <row r="21">
@@ -876,16 +876,16 @@
         <v>0</v>
       </c>
       <c r="C21" t="n">
-        <v>3</v>
+        <v>13</v>
       </c>
       <c r="D21" t="n">
         <v>2</v>
       </c>
       <c r="E21" t="n">
-        <v>3</v>
+        <v>16</v>
       </c>
       <c r="F21" t="n">
-        <v>23</v>
+        <v>0</v>
       </c>
     </row>
     <row r="22">
@@ -895,19 +895,19 @@
         </is>
       </c>
       <c r="B22" t="n">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="C22" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="D22" t="n">
         <v>1</v>
       </c>
       <c r="E22" t="n">
-        <v>0</v>
+        <v>3</v>
       </c>
       <c r="F22" t="n">
-        <v>4</v>
+        <v>1</v>
       </c>
     </row>
     <row r="23">
@@ -917,19 +917,19 @@
         </is>
       </c>
       <c r="B23" t="n">
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="C23" t="n">
-        <v>7</v>
+        <v>51</v>
       </c>
       <c r="D23" t="n">
-        <v>27</v>
+        <v>32</v>
       </c>
       <c r="E23" t="n">
-        <v>14</v>
+        <v>78</v>
       </c>
       <c r="F23" t="n">
-        <v>118</v>
+        <v>4</v>
       </c>
     </row>
     <row r="24">
@@ -945,13 +945,13 @@
         <v>1</v>
       </c>
       <c r="D24" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="E24" t="n">
-        <v>0</v>
+        <v>3</v>
       </c>
       <c r="F24" t="n">
-        <v>5</v>
+        <v>0</v>
       </c>
     </row>
     <row r="25">
@@ -961,7 +961,7 @@
         </is>
       </c>
       <c r="B25" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="C25" t="n">
         <v>0</v>
@@ -973,7 +973,7 @@
         <v>1</v>
       </c>
       <c r="F25" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
     </row>
     <row r="26">
@@ -983,19 +983,19 @@
         </is>
       </c>
       <c r="B26" t="n">
-        <v>40</v>
+        <v>34</v>
       </c>
       <c r="C26" t="n">
-        <v>8</v>
+        <v>27</v>
       </c>
       <c r="D26" t="n">
-        <v>9</v>
+        <v>7</v>
       </c>
       <c r="E26" t="n">
-        <v>5</v>
+        <v>20</v>
       </c>
       <c r="F26" t="n">
-        <v>36</v>
+        <v>10</v>
       </c>
     </row>
     <row r="27">
@@ -1008,16 +1008,16 @@
         <v>0</v>
       </c>
       <c r="C27" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="D27" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="E27" t="n">
-        <v>2</v>
+        <v>7</v>
       </c>
       <c r="F27" t="n">
-        <v>5</v>
+        <v>0</v>
       </c>
     </row>
     <row r="28">
@@ -1027,19 +1027,19 @@
         </is>
       </c>
       <c r="B28" t="n">
-        <v>89</v>
+        <v>53</v>
       </c>
       <c r="C28" t="n">
-        <v>10</v>
+        <v>29</v>
       </c>
       <c r="D28" t="n">
-        <v>11</v>
+        <v>13</v>
       </c>
       <c r="E28" t="n">
-        <v>9</v>
+        <v>61</v>
       </c>
       <c r="F28" t="n">
-        <v>81</v>
+        <v>44</v>
       </c>
     </row>
     <row r="29">
@@ -1049,19 +1049,19 @@
         </is>
       </c>
       <c r="B29" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="C29" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="D29" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="E29" t="n">
-        <v>0</v>
+        <v>10</v>
       </c>
       <c r="F29" t="n">
-        <v>10</v>
+        <v>1</v>
       </c>
     </row>
     <row r="30">
@@ -1071,19 +1071,19 @@
         </is>
       </c>
       <c r="B30" t="n">
-        <v>22</v>
+        <v>15</v>
       </c>
       <c r="C30" t="n">
-        <v>2</v>
+        <v>6</v>
       </c>
       <c r="D30" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="E30" t="n">
-        <v>3</v>
+        <v>12</v>
       </c>
       <c r="F30" t="n">
-        <v>15</v>
+        <v>8</v>
       </c>
     </row>
     <row r="31">
@@ -1093,19 +1093,19 @@
         </is>
       </c>
       <c r="B31" t="n">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="C31" t="n">
         <v>1</v>
       </c>
       <c r="D31" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="E31" t="n">
-        <v>3</v>
+        <v>5</v>
       </c>
       <c r="F31" t="n">
-        <v>4</v>
+        <v>2</v>
       </c>
     </row>
     <row r="32">
@@ -1115,19 +1115,19 @@
         </is>
       </c>
       <c r="B32" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="C32" t="n">
-        <v>4</v>
+        <v>12</v>
       </c>
       <c r="D32" t="n">
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="E32" t="n">
-        <v>5</v>
+        <v>41</v>
       </c>
       <c r="F32" t="n">
-        <v>46</v>
+        <v>2</v>
       </c>
     </row>
     <row r="33">
@@ -1137,19 +1137,19 @@
         </is>
       </c>
       <c r="B33" t="n">
-        <v>100</v>
+        <v>79</v>
       </c>
       <c r="C33" t="n">
-        <v>10</v>
+        <v>38</v>
       </c>
       <c r="D33" t="n">
-        <v>15</v>
+        <v>12</v>
       </c>
       <c r="E33" t="n">
-        <v>12</v>
+        <v>84</v>
       </c>
       <c r="F33" t="n">
-        <v>102</v>
+        <v>26</v>
       </c>
     </row>
     <row r="34">
@@ -1159,19 +1159,19 @@
         </is>
       </c>
       <c r="B34" t="n">
-        <v>15</v>
+        <v>14</v>
       </c>
       <c r="C34" t="n">
-        <v>0</v>
+        <v>5</v>
       </c>
       <c r="D34" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="E34" t="n">
-        <v>1</v>
+        <v>10</v>
       </c>
       <c r="F34" t="n">
-        <v>15</v>
+        <v>1</v>
       </c>
     </row>
   </sheetData>

--- a/data/output/topik_per_lokasi.xlsx
+++ b/data/output/topik_per_lokasi.xlsx
@@ -455,19 +455,19 @@
         </is>
       </c>
       <c r="B2" t="n">
+        <v>46</v>
+      </c>
+      <c r="C2" t="n">
+        <v>1</v>
+      </c>
+      <c r="D2" t="n">
+        <v>2</v>
+      </c>
+      <c r="E2" t="n">
+        <v>10</v>
+      </c>
+      <c r="F2" t="n">
         <v>35</v>
-      </c>
-      <c r="C2" t="n">
-        <v>9</v>
-      </c>
-      <c r="D2" t="n">
-        <v>3</v>
-      </c>
-      <c r="E2" t="n">
-        <v>32</v>
-      </c>
-      <c r="F2" t="n">
-        <v>15</v>
       </c>
     </row>
     <row r="3">
@@ -477,19 +477,19 @@
         </is>
       </c>
       <c r="B3" t="n">
-        <v>153</v>
+        <v>178</v>
       </c>
       <c r="C3" t="n">
-        <v>66</v>
+        <v>39</v>
       </c>
       <c r="D3" t="n">
-        <v>24</v>
+        <v>36</v>
       </c>
       <c r="E3" t="n">
-        <v>194</v>
+        <v>76</v>
       </c>
       <c r="F3" t="n">
-        <v>61</v>
+        <v>169</v>
       </c>
     </row>
     <row r="4">
@@ -505,10 +505,10 @@
         <v>0</v>
       </c>
       <c r="D4" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="E4" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="F4" t="n">
         <v>0</v>
@@ -521,19 +521,19 @@
         </is>
       </c>
       <c r="B5" t="n">
-        <v>0</v>
+        <v>4</v>
       </c>
       <c r="C5" t="n">
-        <v>7</v>
+        <v>0</v>
       </c>
       <c r="D5" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="E5" t="n">
-        <v>11</v>
+        <v>8</v>
       </c>
       <c r="F5" t="n">
-        <v>1</v>
+        <v>9</v>
       </c>
     </row>
     <row r="6">
@@ -565,19 +565,19 @@
         </is>
       </c>
       <c r="B7" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="C7" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="D7" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="E7" t="n">
+        <v>0</v>
+      </c>
+      <c r="F7" t="n">
         <v>2</v>
-      </c>
-      <c r="F7" t="n">
-        <v>0</v>
       </c>
     </row>
     <row r="8">
@@ -587,19 +587,19 @@
         </is>
       </c>
       <c r="B8" t="n">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="C8" t="n">
-        <v>74</v>
+        <v>12</v>
       </c>
       <c r="D8" t="n">
-        <v>37</v>
+        <v>79</v>
       </c>
       <c r="E8" t="n">
-        <v>79</v>
+        <v>53</v>
       </c>
       <c r="F8" t="n">
-        <v>4</v>
+        <v>52</v>
       </c>
     </row>
     <row r="9">
@@ -609,19 +609,19 @@
         </is>
       </c>
       <c r="B9" t="n">
-        <v>134</v>
+        <v>216</v>
       </c>
       <c r="C9" t="n">
-        <v>81</v>
+        <v>47</v>
       </c>
       <c r="D9" t="n">
-        <v>20</v>
+        <v>47</v>
       </c>
       <c r="E9" t="n">
-        <v>173</v>
+        <v>71</v>
       </c>
       <c r="F9" t="n">
-        <v>112</v>
+        <v>139</v>
       </c>
     </row>
     <row r="10">
@@ -634,16 +634,16 @@
         <v>0</v>
       </c>
       <c r="C10" t="n">
-        <v>12</v>
+        <v>2</v>
       </c>
       <c r="D10" t="n">
-        <v>5</v>
+        <v>7</v>
       </c>
       <c r="E10" t="n">
-        <v>22</v>
+        <v>6</v>
       </c>
       <c r="F10" t="n">
-        <v>0</v>
+        <v>24</v>
       </c>
     </row>
     <row r="11">
@@ -653,19 +653,19 @@
         </is>
       </c>
       <c r="B11" t="n">
-        <v>1</v>
+        <v>4</v>
       </c>
       <c r="C11" t="n">
-        <v>77</v>
+        <v>4</v>
       </c>
       <c r="D11" t="n">
-        <v>15</v>
+        <v>22</v>
       </c>
       <c r="E11" t="n">
-        <v>135</v>
+        <v>40</v>
       </c>
       <c r="F11" t="n">
-        <v>7</v>
+        <v>165</v>
       </c>
     </row>
     <row r="12">
@@ -675,19 +675,19 @@
         </is>
       </c>
       <c r="B12" t="n">
-        <v>126</v>
+        <v>141</v>
       </c>
       <c r="C12" t="n">
-        <v>59</v>
+        <v>10</v>
       </c>
       <c r="D12" t="n">
-        <v>10</v>
+        <v>21</v>
       </c>
       <c r="E12" t="n">
-        <v>109</v>
+        <v>9</v>
       </c>
       <c r="F12" t="n">
-        <v>27</v>
+        <v>150</v>
       </c>
     </row>
     <row r="13">
@@ -697,7 +697,7 @@
         </is>
       </c>
       <c r="B13" t="n">
-        <v>3</v>
+        <v>5</v>
       </c>
       <c r="C13" t="n">
         <v>0</v>
@@ -709,7 +709,7 @@
         <v>0</v>
       </c>
       <c r="F13" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
     </row>
     <row r="14">
@@ -722,16 +722,16 @@
         <v>0</v>
       </c>
       <c r="C14" t="n">
-        <v>68</v>
+        <v>0</v>
       </c>
       <c r="D14" t="n">
-        <v>3</v>
+        <v>14</v>
       </c>
       <c r="E14" t="n">
-        <v>89</v>
+        <v>6</v>
       </c>
       <c r="F14" t="n">
-        <v>0</v>
+        <v>140</v>
       </c>
     </row>
     <row r="15">
@@ -741,19 +741,19 @@
         </is>
       </c>
       <c r="B15" t="n">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="C15" t="n">
-        <v>72</v>
+        <v>6</v>
       </c>
       <c r="D15" t="n">
-        <v>18</v>
+        <v>33</v>
       </c>
       <c r="E15" t="n">
-        <v>107</v>
+        <v>29</v>
       </c>
       <c r="F15" t="n">
-        <v>5</v>
+        <v>135</v>
       </c>
     </row>
     <row r="16">
@@ -763,19 +763,19 @@
         </is>
       </c>
       <c r="B16" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="C16" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="D16" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="E16" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="F16" t="n">
-        <v>1</v>
+        <v>3</v>
       </c>
     </row>
     <row r="17">
@@ -785,19 +785,19 @@
         </is>
       </c>
       <c r="B17" t="n">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="C17" t="n">
-        <v>78</v>
+        <v>3</v>
       </c>
       <c r="D17" t="n">
-        <v>13</v>
+        <v>17</v>
       </c>
       <c r="E17" t="n">
-        <v>119</v>
+        <v>7</v>
       </c>
       <c r="F17" t="n">
-        <v>1</v>
+        <v>183</v>
       </c>
     </row>
     <row r="18">
@@ -810,16 +810,16 @@
         <v>0</v>
       </c>
       <c r="C18" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="D18" t="n">
         <v>0</v>
       </c>
       <c r="E18" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="F18" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
     </row>
     <row r="19">
@@ -829,19 +829,19 @@
         </is>
       </c>
       <c r="B19" t="n">
-        <v>96</v>
+        <v>106</v>
       </c>
       <c r="C19" t="n">
-        <v>46</v>
+        <v>14</v>
       </c>
       <c r="D19" t="n">
-        <v>13</v>
+        <v>27</v>
       </c>
       <c r="E19" t="n">
-        <v>72</v>
+        <v>35</v>
       </c>
       <c r="F19" t="n">
-        <v>26</v>
+        <v>71</v>
       </c>
     </row>
     <row r="20">
@@ -851,19 +851,19 @@
         </is>
       </c>
       <c r="B20" t="n">
+        <v>210</v>
+      </c>
+      <c r="C20" t="n">
+        <v>21</v>
+      </c>
+      <c r="D20" t="n">
+        <v>39</v>
+      </c>
+      <c r="E20" t="n">
+        <v>28</v>
+      </c>
+      <c r="F20" t="n">
         <v>176</v>
-      </c>
-      <c r="C20" t="n">
-        <v>111</v>
-      </c>
-      <c r="D20" t="n">
-        <v>30</v>
-      </c>
-      <c r="E20" t="n">
-        <v>106</v>
-      </c>
-      <c r="F20" t="n">
-        <v>45</v>
       </c>
     </row>
     <row r="21">
@@ -876,16 +876,16 @@
         <v>0</v>
       </c>
       <c r="C21" t="n">
-        <v>13</v>
+        <v>1</v>
       </c>
       <c r="D21" t="n">
-        <v>2</v>
+        <v>7</v>
       </c>
       <c r="E21" t="n">
-        <v>16</v>
+        <v>4</v>
       </c>
       <c r="F21" t="n">
-        <v>0</v>
+        <v>19</v>
       </c>
     </row>
     <row r="22">
@@ -895,19 +895,19 @@
         </is>
       </c>
       <c r="B22" t="n">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="C22" t="n">
+        <v>0</v>
+      </c>
+      <c r="D22" t="n">
+        <v>1</v>
+      </c>
+      <c r="E22" t="n">
         <v>2</v>
       </c>
-      <c r="D22" t="n">
-        <v>1</v>
-      </c>
-      <c r="E22" t="n">
-        <v>3</v>
-      </c>
       <c r="F22" t="n">
-        <v>1</v>
+        <v>3</v>
       </c>
     </row>
     <row r="23">
@@ -917,19 +917,19 @@
         </is>
       </c>
       <c r="B23" t="n">
-        <v>7</v>
+        <v>5</v>
       </c>
       <c r="C23" t="n">
-        <v>51</v>
+        <v>4</v>
       </c>
       <c r="D23" t="n">
-        <v>32</v>
+        <v>35</v>
       </c>
       <c r="E23" t="n">
-        <v>78</v>
+        <v>53</v>
       </c>
       <c r="F23" t="n">
-        <v>4</v>
+        <v>75</v>
       </c>
     </row>
     <row r="24">
@@ -939,19 +939,19 @@
         </is>
       </c>
       <c r="B24" t="n">
-        <v>0</v>
+        <v>3</v>
       </c>
       <c r="C24" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="D24" t="n">
         <v>2</v>
       </c>
       <c r="E24" t="n">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="F24" t="n">
-        <v>0</v>
+        <v>3</v>
       </c>
     </row>
     <row r="25">
@@ -961,19 +961,19 @@
         </is>
       </c>
       <c r="B25" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="C25" t="n">
-        <v>0</v>
+        <v>3</v>
       </c>
       <c r="D25" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="E25" t="n">
         <v>1</v>
       </c>
       <c r="F25" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
     </row>
     <row r="26">
@@ -983,19 +983,19 @@
         </is>
       </c>
       <c r="B26" t="n">
-        <v>34</v>
+        <v>39</v>
       </c>
       <c r="C26" t="n">
-        <v>27</v>
+        <v>4</v>
       </c>
       <c r="D26" t="n">
-        <v>7</v>
+        <v>13</v>
       </c>
       <c r="E26" t="n">
-        <v>20</v>
+        <v>24</v>
       </c>
       <c r="F26" t="n">
-        <v>10</v>
+        <v>18</v>
       </c>
     </row>
     <row r="27">
@@ -1008,16 +1008,16 @@
         <v>0</v>
       </c>
       <c r="C27" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="D27" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="E27" t="n">
-        <v>7</v>
+        <v>3</v>
       </c>
       <c r="F27" t="n">
-        <v>0</v>
+        <v>4</v>
       </c>
     </row>
     <row r="28">
@@ -1027,19 +1027,19 @@
         </is>
       </c>
       <c r="B28" t="n">
-        <v>53</v>
+        <v>83</v>
       </c>
       <c r="C28" t="n">
-        <v>29</v>
+        <v>18</v>
       </c>
       <c r="D28" t="n">
-        <v>13</v>
+        <v>20</v>
       </c>
       <c r="E28" t="n">
-        <v>61</v>
+        <v>36</v>
       </c>
       <c r="F28" t="n">
-        <v>44</v>
+        <v>43</v>
       </c>
     </row>
     <row r="29">
@@ -1049,19 +1049,19 @@
         </is>
       </c>
       <c r="B29" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="C29" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="D29" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="E29" t="n">
+        <v>0</v>
+      </c>
+      <c r="F29" t="n">
         <v>10</v>
-      </c>
-      <c r="F29" t="n">
-        <v>1</v>
       </c>
     </row>
     <row r="30">
@@ -1071,19 +1071,19 @@
         </is>
       </c>
       <c r="B30" t="n">
-        <v>15</v>
+        <v>20</v>
       </c>
       <c r="C30" t="n">
-        <v>6</v>
+        <v>5</v>
       </c>
       <c r="D30" t="n">
         <v>2</v>
       </c>
       <c r="E30" t="n">
-        <v>12</v>
+        <v>3</v>
       </c>
       <c r="F30" t="n">
-        <v>8</v>
+        <v>13</v>
       </c>
     </row>
     <row r="31">
@@ -1093,16 +1093,16 @@
         </is>
       </c>
       <c r="B31" t="n">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="C31" t="n">
         <v>1</v>
       </c>
       <c r="D31" t="n">
-        <v>1</v>
+        <v>4</v>
       </c>
       <c r="E31" t="n">
-        <v>5</v>
+        <v>1</v>
       </c>
       <c r="F31" t="n">
         <v>2</v>
@@ -1115,19 +1115,19 @@
         </is>
       </c>
       <c r="B32" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="C32" t="n">
-        <v>12</v>
+        <v>3</v>
       </c>
       <c r="D32" t="n">
-        <v>9</v>
+        <v>17</v>
       </c>
       <c r="E32" t="n">
-        <v>41</v>
+        <v>11</v>
       </c>
       <c r="F32" t="n">
-        <v>2</v>
+        <v>32</v>
       </c>
     </row>
     <row r="33">
@@ -1137,19 +1137,19 @@
         </is>
       </c>
       <c r="B33" t="n">
-        <v>79</v>
+        <v>98</v>
       </c>
       <c r="C33" t="n">
-        <v>38</v>
+        <v>10</v>
       </c>
       <c r="D33" t="n">
-        <v>12</v>
+        <v>14</v>
       </c>
       <c r="E33" t="n">
-        <v>84</v>
+        <v>42</v>
       </c>
       <c r="F33" t="n">
-        <v>26</v>
+        <v>75</v>
       </c>
     </row>
     <row r="34">
@@ -1159,19 +1159,19 @@
         </is>
       </c>
       <c r="B34" t="n">
-        <v>14</v>
+        <v>15</v>
       </c>
       <c r="C34" t="n">
-        <v>5</v>
+        <v>1</v>
       </c>
       <c r="D34" t="n">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="E34" t="n">
-        <v>10</v>
+        <v>1</v>
       </c>
       <c r="F34" t="n">
-        <v>1</v>
+        <v>11</v>
       </c>
     </row>
   </sheetData>

--- a/data/output/topik_per_lokasi.xlsx
+++ b/data/output/topik_per_lokasi.xlsx
@@ -455,19 +455,19 @@
         </is>
       </c>
       <c r="B2" t="n">
-        <v>46</v>
+        <v>47</v>
       </c>
       <c r="C2" t="n">
-        <v>1</v>
+        <v>16</v>
       </c>
       <c r="D2" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="E2" t="n">
-        <v>10</v>
+        <v>19</v>
       </c>
       <c r="F2" t="n">
-        <v>35</v>
+        <v>11</v>
       </c>
     </row>
     <row r="3">
@@ -480,16 +480,16 @@
         <v>178</v>
       </c>
       <c r="C3" t="n">
-        <v>39</v>
+        <v>134</v>
       </c>
       <c r="D3" t="n">
-        <v>36</v>
+        <v>41</v>
       </c>
       <c r="E3" t="n">
-        <v>76</v>
+        <v>110</v>
       </c>
       <c r="F3" t="n">
-        <v>169</v>
+        <v>35</v>
       </c>
     </row>
     <row r="4">
@@ -502,16 +502,16 @@
         <v>1</v>
       </c>
       <c r="C4" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="D4" t="n">
         <v>0</v>
       </c>
       <c r="E4" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="F4" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
     </row>
     <row r="5">
@@ -521,19 +521,19 @@
         </is>
       </c>
       <c r="B5" t="n">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="C5" t="n">
-        <v>0</v>
+        <v>6</v>
       </c>
       <c r="D5" t="n">
         <v>3</v>
       </c>
       <c r="E5" t="n">
-        <v>8</v>
+        <v>6</v>
       </c>
       <c r="F5" t="n">
-        <v>9</v>
+        <v>6</v>
       </c>
     </row>
     <row r="6">
@@ -546,13 +546,13 @@
         <v>0</v>
       </c>
       <c r="C6" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="D6" t="n">
         <v>0</v>
       </c>
       <c r="E6" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="F6" t="n">
         <v>0</v>
@@ -565,7 +565,7 @@
         </is>
       </c>
       <c r="B7" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="C7" t="n">
         <v>0</v>
@@ -574,7 +574,7 @@
         <v>1</v>
       </c>
       <c r="E7" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="F7" t="n">
         <v>2</v>
@@ -587,19 +587,19 @@
         </is>
       </c>
       <c r="B8" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="C8" t="n">
-        <v>12</v>
+        <v>98</v>
       </c>
       <c r="D8" t="n">
-        <v>79</v>
+        <v>19</v>
       </c>
       <c r="E8" t="n">
-        <v>53</v>
+        <v>42</v>
       </c>
       <c r="F8" t="n">
-        <v>52</v>
+        <v>36</v>
       </c>
     </row>
     <row r="9">
@@ -609,19 +609,19 @@
         </is>
       </c>
       <c r="B9" t="n">
-        <v>216</v>
+        <v>198</v>
       </c>
       <c r="C9" t="n">
-        <v>47</v>
+        <v>93</v>
       </c>
       <c r="D9" t="n">
-        <v>47</v>
+        <v>50</v>
       </c>
       <c r="E9" t="n">
-        <v>71</v>
+        <v>134</v>
       </c>
       <c r="F9" t="n">
-        <v>139</v>
+        <v>45</v>
       </c>
     </row>
     <row r="10">
@@ -634,16 +634,16 @@
         <v>0</v>
       </c>
       <c r="C10" t="n">
-        <v>2</v>
+        <v>18</v>
       </c>
       <c r="D10" t="n">
-        <v>7</v>
+        <v>0</v>
       </c>
       <c r="E10" t="n">
-        <v>6</v>
+        <v>5</v>
       </c>
       <c r="F10" t="n">
-        <v>24</v>
+        <v>16</v>
       </c>
     </row>
     <row r="11">
@@ -653,19 +653,19 @@
         </is>
       </c>
       <c r="B11" t="n">
-        <v>4</v>
+        <v>0</v>
       </c>
       <c r="C11" t="n">
-        <v>4</v>
+        <v>75</v>
       </c>
       <c r="D11" t="n">
-        <v>22</v>
+        <v>9</v>
       </c>
       <c r="E11" t="n">
-        <v>40</v>
+        <v>85</v>
       </c>
       <c r="F11" t="n">
-        <v>165</v>
+        <v>66</v>
       </c>
     </row>
     <row r="12">
@@ -675,19 +675,19 @@
         </is>
       </c>
       <c r="B12" t="n">
-        <v>141</v>
+        <v>139</v>
       </c>
       <c r="C12" t="n">
-        <v>10</v>
+        <v>72</v>
       </c>
       <c r="D12" t="n">
-        <v>21</v>
+        <v>15</v>
       </c>
       <c r="E12" t="n">
-        <v>9</v>
+        <v>51</v>
       </c>
       <c r="F12" t="n">
-        <v>150</v>
+        <v>54</v>
       </c>
     </row>
     <row r="13">
@@ -719,19 +719,19 @@
         </is>
       </c>
       <c r="B14" t="n">
-        <v>0</v>
+        <v>5</v>
       </c>
       <c r="C14" t="n">
-        <v>0</v>
+        <v>82</v>
       </c>
       <c r="D14" t="n">
-        <v>14</v>
+        <v>0</v>
       </c>
       <c r="E14" t="n">
-        <v>6</v>
+        <v>43</v>
       </c>
       <c r="F14" t="n">
-        <v>140</v>
+        <v>35</v>
       </c>
     </row>
     <row r="15">
@@ -741,19 +741,19 @@
         </is>
       </c>
       <c r="B15" t="n">
-        <v>3</v>
+        <v>6</v>
       </c>
       <c r="C15" t="n">
-        <v>6</v>
+        <v>89</v>
       </c>
       <c r="D15" t="n">
-        <v>33</v>
+        <v>5</v>
       </c>
       <c r="E15" t="n">
-        <v>29</v>
+        <v>56</v>
       </c>
       <c r="F15" t="n">
-        <v>135</v>
+        <v>50</v>
       </c>
     </row>
     <row r="16">
@@ -763,10 +763,10 @@
         </is>
       </c>
       <c r="B16" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="C16" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="D16" t="n">
         <v>1</v>
@@ -775,7 +775,7 @@
         <v>0</v>
       </c>
       <c r="F16" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
     </row>
     <row r="17">
@@ -788,16 +788,16 @@
         <v>5</v>
       </c>
       <c r="C17" t="n">
-        <v>3</v>
+        <v>100</v>
       </c>
       <c r="D17" t="n">
-        <v>17</v>
+        <v>2</v>
       </c>
       <c r="E17" t="n">
-        <v>7</v>
+        <v>60</v>
       </c>
       <c r="F17" t="n">
-        <v>183</v>
+        <v>48</v>
       </c>
     </row>
     <row r="18">
@@ -810,7 +810,7 @@
         <v>0</v>
       </c>
       <c r="C18" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="D18" t="n">
         <v>0</v>
@@ -819,7 +819,7 @@
         <v>0</v>
       </c>
       <c r="F18" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
     </row>
     <row r="19">
@@ -829,19 +829,19 @@
         </is>
       </c>
       <c r="B19" t="n">
-        <v>106</v>
+        <v>109</v>
       </c>
       <c r="C19" t="n">
-        <v>14</v>
+        <v>47</v>
       </c>
       <c r="D19" t="n">
-        <v>27</v>
+        <v>15</v>
       </c>
       <c r="E19" t="n">
-        <v>35</v>
+        <v>28</v>
       </c>
       <c r="F19" t="n">
-        <v>71</v>
+        <v>54</v>
       </c>
     </row>
     <row r="20">
@@ -851,19 +851,19 @@
         </is>
       </c>
       <c r="B20" t="n">
-        <v>210</v>
+        <v>194</v>
       </c>
       <c r="C20" t="n">
-        <v>21</v>
+        <v>111</v>
       </c>
       <c r="D20" t="n">
-        <v>39</v>
+        <v>37</v>
       </c>
       <c r="E20" t="n">
-        <v>28</v>
+        <v>61</v>
       </c>
       <c r="F20" t="n">
-        <v>176</v>
+        <v>71</v>
       </c>
     </row>
     <row r="21">
@@ -873,19 +873,19 @@
         </is>
       </c>
       <c r="B21" t="n">
-        <v>0</v>
+        <v>5</v>
       </c>
       <c r="C21" t="n">
-        <v>1</v>
+        <v>11</v>
       </c>
       <c r="D21" t="n">
+        <v>1</v>
+      </c>
+      <c r="E21" t="n">
         <v>7</v>
       </c>
-      <c r="E21" t="n">
-        <v>4</v>
-      </c>
       <c r="F21" t="n">
-        <v>19</v>
+        <v>12</v>
       </c>
     </row>
     <row r="22">
@@ -898,13 +898,13 @@
         <v>4</v>
       </c>
       <c r="C22" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="D22" t="n">
         <v>1</v>
       </c>
       <c r="E22" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="F22" t="n">
         <v>3</v>
@@ -917,19 +917,19 @@
         </is>
       </c>
       <c r="B23" t="n">
-        <v>5</v>
+        <v>7</v>
       </c>
       <c r="C23" t="n">
-        <v>4</v>
+        <v>58</v>
       </c>
       <c r="D23" t="n">
-        <v>35</v>
+        <v>7</v>
       </c>
       <c r="E23" t="n">
-        <v>53</v>
+        <v>45</v>
       </c>
       <c r="F23" t="n">
-        <v>75</v>
+        <v>55</v>
       </c>
     </row>
     <row r="24">
@@ -942,16 +942,16 @@
         <v>3</v>
       </c>
       <c r="C24" t="n">
-        <v>0</v>
+        <v>5</v>
       </c>
       <c r="D24" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="E24" t="n">
         <v>1</v>
       </c>
       <c r="F24" t="n">
-        <v>3</v>
+        <v>0</v>
       </c>
     </row>
     <row r="25">
@@ -964,10 +964,10 @@
         <v>1</v>
       </c>
       <c r="C25" t="n">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="D25" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="E25" t="n">
         <v>1</v>
@@ -983,16 +983,16 @@
         </is>
       </c>
       <c r="B26" t="n">
-        <v>39</v>
+        <v>40</v>
       </c>
       <c r="C26" t="n">
-        <v>4</v>
+        <v>21</v>
       </c>
       <c r="D26" t="n">
-        <v>13</v>
+        <v>7</v>
       </c>
       <c r="E26" t="n">
-        <v>24</v>
+        <v>12</v>
       </c>
       <c r="F26" t="n">
         <v>18</v>
@@ -1008,16 +1008,16 @@
         <v>0</v>
       </c>
       <c r="C27" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="D27" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="E27" t="n">
-        <v>3</v>
+        <v>5</v>
       </c>
       <c r="F27" t="n">
-        <v>4</v>
+        <v>2</v>
       </c>
     </row>
     <row r="28">
@@ -1027,19 +1027,19 @@
         </is>
       </c>
       <c r="B28" t="n">
-        <v>83</v>
+        <v>77</v>
       </c>
       <c r="C28" t="n">
-        <v>18</v>
+        <v>37</v>
       </c>
       <c r="D28" t="n">
-        <v>20</v>
+        <v>25</v>
       </c>
       <c r="E28" t="n">
-        <v>36</v>
+        <v>34</v>
       </c>
       <c r="F28" t="n">
-        <v>43</v>
+        <v>28</v>
       </c>
     </row>
     <row r="29">
@@ -1052,16 +1052,16 @@
         <v>3</v>
       </c>
       <c r="C29" t="n">
-        <v>0</v>
+        <v>3</v>
       </c>
       <c r="D29" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="E29" t="n">
-        <v>0</v>
+        <v>6</v>
       </c>
       <c r="F29" t="n">
-        <v>10</v>
+        <v>2</v>
       </c>
     </row>
     <row r="30">
@@ -1071,19 +1071,19 @@
         </is>
       </c>
       <c r="B30" t="n">
-        <v>20</v>
+        <v>17</v>
       </c>
       <c r="C30" t="n">
+        <v>11</v>
+      </c>
+      <c r="D30" t="n">
         <v>5</v>
       </c>
-      <c r="D30" t="n">
+      <c r="E30" t="n">
         <v>2</v>
       </c>
-      <c r="E30" t="n">
-        <v>3</v>
-      </c>
       <c r="F30" t="n">
-        <v>13</v>
+        <v>8</v>
       </c>
     </row>
     <row r="31">
@@ -1096,16 +1096,16 @@
         <v>4</v>
       </c>
       <c r="C31" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="D31" t="n">
-        <v>4</v>
+        <v>2</v>
       </c>
       <c r="E31" t="n">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="F31" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
     </row>
     <row r="32">
@@ -1118,16 +1118,16 @@
         <v>1</v>
       </c>
       <c r="C32" t="n">
-        <v>3</v>
+        <v>16</v>
       </c>
       <c r="D32" t="n">
-        <v>17</v>
+        <v>5</v>
       </c>
       <c r="E32" t="n">
-        <v>11</v>
+        <v>27</v>
       </c>
       <c r="F32" t="n">
-        <v>32</v>
+        <v>15</v>
       </c>
     </row>
     <row r="33">
@@ -1137,19 +1137,19 @@
         </is>
       </c>
       <c r="B33" t="n">
-        <v>98</v>
+        <v>94</v>
       </c>
       <c r="C33" t="n">
-        <v>10</v>
+        <v>51</v>
       </c>
       <c r="D33" t="n">
-        <v>14</v>
+        <v>16</v>
       </c>
       <c r="E33" t="n">
-        <v>42</v>
+        <v>33</v>
       </c>
       <c r="F33" t="n">
-        <v>75</v>
+        <v>45</v>
       </c>
     </row>
     <row r="34">
@@ -1162,16 +1162,16 @@
         <v>15</v>
       </c>
       <c r="C34" t="n">
-        <v>1</v>
+        <v>5</v>
       </c>
       <c r="D34" t="n">
-        <v>3</v>
+        <v>0</v>
       </c>
       <c r="E34" t="n">
-        <v>1</v>
+        <v>7</v>
       </c>
       <c r="F34" t="n">
-        <v>11</v>
+        <v>4</v>
       </c>
     </row>
   </sheetData>

--- a/data/output/topik_per_lokasi.xlsx
+++ b/data/output/topik_per_lokasi.xlsx
@@ -458,16 +458,16 @@
         <v>47</v>
       </c>
       <c r="C2" t="n">
-        <v>16</v>
+        <v>3</v>
       </c>
       <c r="D2" t="n">
-        <v>1</v>
+        <v>12</v>
       </c>
       <c r="E2" t="n">
-        <v>19</v>
+        <v>30</v>
       </c>
       <c r="F2" t="n">
-        <v>11</v>
+        <v>2</v>
       </c>
     </row>
     <row r="3">
@@ -477,19 +477,19 @@
         </is>
       </c>
       <c r="B3" t="n">
-        <v>178</v>
+        <v>188</v>
       </c>
       <c r="C3" t="n">
-        <v>134</v>
+        <v>23</v>
       </c>
       <c r="D3" t="n">
-        <v>41</v>
+        <v>166</v>
       </c>
       <c r="E3" t="n">
-        <v>110</v>
+        <v>87</v>
       </c>
       <c r="F3" t="n">
-        <v>35</v>
+        <v>34</v>
       </c>
     </row>
     <row r="4">
@@ -502,16 +502,16 @@
         <v>1</v>
       </c>
       <c r="C4" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="D4" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="E4" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="F4" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
     </row>
     <row r="5">
@@ -524,16 +524,16 @@
         <v>3</v>
       </c>
       <c r="C5" t="n">
-        <v>6</v>
+        <v>1</v>
       </c>
       <c r="D5" t="n">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="E5" t="n">
-        <v>6</v>
+        <v>15</v>
       </c>
       <c r="F5" t="n">
-        <v>6</v>
+        <v>1</v>
       </c>
     </row>
     <row r="6">
@@ -546,10 +546,10 @@
         <v>0</v>
       </c>
       <c r="C6" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="D6" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="E6" t="n">
         <v>0</v>
@@ -568,16 +568,16 @@
         <v>0</v>
       </c>
       <c r="C7" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="D7" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="E7" t="n">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="F7" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
     </row>
     <row r="8">
@@ -587,19 +587,19 @@
         </is>
       </c>
       <c r="B8" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="C8" t="n">
-        <v>98</v>
+        <v>4</v>
       </c>
       <c r="D8" t="n">
-        <v>19</v>
+        <v>38</v>
       </c>
       <c r="E8" t="n">
-        <v>42</v>
+        <v>103</v>
       </c>
       <c r="F8" t="n">
-        <v>36</v>
+        <v>51</v>
       </c>
     </row>
     <row r="9">
@@ -609,19 +609,19 @@
         </is>
       </c>
       <c r="B9" t="n">
-        <v>198</v>
+        <v>219</v>
       </c>
       <c r="C9" t="n">
-        <v>93</v>
+        <v>30</v>
       </c>
       <c r="D9" t="n">
-        <v>50</v>
+        <v>147</v>
       </c>
       <c r="E9" t="n">
-        <v>134</v>
+        <v>109</v>
       </c>
       <c r="F9" t="n">
-        <v>45</v>
+        <v>15</v>
       </c>
     </row>
     <row r="10">
@@ -631,19 +631,19 @@
         </is>
       </c>
       <c r="B10" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="C10" t="n">
-        <v>18</v>
+        <v>1</v>
       </c>
       <c r="D10" t="n">
-        <v>0</v>
+        <v>12</v>
       </c>
       <c r="E10" t="n">
-        <v>5</v>
+        <v>23</v>
       </c>
       <c r="F10" t="n">
-        <v>16</v>
+        <v>4</v>
       </c>
     </row>
     <row r="11">
@@ -653,19 +653,19 @@
         </is>
       </c>
       <c r="B11" t="n">
-        <v>0</v>
+        <v>5</v>
       </c>
       <c r="C11" t="n">
-        <v>75</v>
+        <v>6</v>
       </c>
       <c r="D11" t="n">
-        <v>9</v>
+        <v>93</v>
       </c>
       <c r="E11" t="n">
-        <v>85</v>
+        <v>121</v>
       </c>
       <c r="F11" t="n">
-        <v>66</v>
+        <v>10</v>
       </c>
     </row>
     <row r="12">
@@ -675,19 +675,19 @@
         </is>
       </c>
       <c r="B12" t="n">
-        <v>139</v>
+        <v>147</v>
       </c>
       <c r="C12" t="n">
-        <v>72</v>
+        <v>6</v>
       </c>
       <c r="D12" t="n">
-        <v>15</v>
+        <v>52</v>
       </c>
       <c r="E12" t="n">
-        <v>51</v>
+        <v>115</v>
       </c>
       <c r="F12" t="n">
-        <v>54</v>
+        <v>11</v>
       </c>
     </row>
     <row r="13">
@@ -722,16 +722,16 @@
         <v>5</v>
       </c>
       <c r="C14" t="n">
-        <v>82</v>
+        <v>2</v>
       </c>
       <c r="D14" t="n">
-        <v>0</v>
+        <v>51</v>
       </c>
       <c r="E14" t="n">
-        <v>43</v>
+        <v>96</v>
       </c>
       <c r="F14" t="n">
-        <v>35</v>
+        <v>11</v>
       </c>
     </row>
     <row r="15">
@@ -741,19 +741,19 @@
         </is>
       </c>
       <c r="B15" t="n">
-        <v>6</v>
+        <v>5</v>
       </c>
       <c r="C15" t="n">
-        <v>89</v>
+        <v>9</v>
       </c>
       <c r="D15" t="n">
-        <v>5</v>
+        <v>75</v>
       </c>
       <c r="E15" t="n">
-        <v>56</v>
+        <v>108</v>
       </c>
       <c r="F15" t="n">
-        <v>50</v>
+        <v>9</v>
       </c>
     </row>
     <row r="16">
@@ -763,19 +763,19 @@
         </is>
       </c>
       <c r="B16" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="C16" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="D16" t="n">
         <v>1</v>
       </c>
       <c r="E16" t="n">
-        <v>0</v>
+        <v>3</v>
       </c>
       <c r="F16" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
     </row>
     <row r="17">
@@ -788,16 +788,16 @@
         <v>5</v>
       </c>
       <c r="C17" t="n">
-        <v>100</v>
+        <v>0</v>
       </c>
       <c r="D17" t="n">
-        <v>2</v>
+        <v>73</v>
       </c>
       <c r="E17" t="n">
-        <v>60</v>
+        <v>121</v>
       </c>
       <c r="F17" t="n">
-        <v>48</v>
+        <v>16</v>
       </c>
     </row>
     <row r="18">
@@ -810,16 +810,16 @@
         <v>0</v>
       </c>
       <c r="C18" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="D18" t="n">
         <v>0</v>
       </c>
       <c r="E18" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="F18" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
     </row>
     <row r="19">
@@ -829,19 +829,19 @@
         </is>
       </c>
       <c r="B19" t="n">
-        <v>109</v>
+        <v>117</v>
       </c>
       <c r="C19" t="n">
-        <v>47</v>
+        <v>9</v>
       </c>
       <c r="D19" t="n">
-        <v>15</v>
+        <v>38</v>
       </c>
       <c r="E19" t="n">
-        <v>28</v>
+        <v>84</v>
       </c>
       <c r="F19" t="n">
-        <v>54</v>
+        <v>5</v>
       </c>
     </row>
     <row r="20">
@@ -851,19 +851,19 @@
         </is>
       </c>
       <c r="B20" t="n">
-        <v>194</v>
+        <v>214</v>
       </c>
       <c r="C20" t="n">
-        <v>111</v>
+        <v>9</v>
       </c>
       <c r="D20" t="n">
-        <v>37</v>
+        <v>80</v>
       </c>
       <c r="E20" t="n">
-        <v>61</v>
+        <v>150</v>
       </c>
       <c r="F20" t="n">
-        <v>71</v>
+        <v>21</v>
       </c>
     </row>
     <row r="21">
@@ -876,16 +876,16 @@
         <v>5</v>
       </c>
       <c r="C21" t="n">
-        <v>11</v>
+        <v>0</v>
       </c>
       <c r="D21" t="n">
-        <v>1</v>
+        <v>6</v>
       </c>
       <c r="E21" t="n">
-        <v>7</v>
+        <v>23</v>
       </c>
       <c r="F21" t="n">
-        <v>12</v>
+        <v>2</v>
       </c>
     </row>
     <row r="22">
@@ -895,19 +895,19 @@
         </is>
       </c>
       <c r="B22" t="n">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="C22" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="D22" t="n">
-        <v>1</v>
+        <v>5</v>
       </c>
       <c r="E22" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="F22" t="n">
-        <v>3</v>
+        <v>0</v>
       </c>
     </row>
     <row r="23">
@@ -920,16 +920,16 @@
         <v>7</v>
       </c>
       <c r="C23" t="n">
-        <v>58</v>
+        <v>11</v>
       </c>
       <c r="D23" t="n">
-        <v>7</v>
+        <v>48</v>
       </c>
       <c r="E23" t="n">
-        <v>45</v>
+        <v>92</v>
       </c>
       <c r="F23" t="n">
-        <v>55</v>
+        <v>14</v>
       </c>
     </row>
     <row r="24">
@@ -942,10 +942,10 @@
         <v>3</v>
       </c>
       <c r="C24" t="n">
+        <v>0</v>
+      </c>
+      <c r="D24" t="n">
         <v>5</v>
-      </c>
-      <c r="D24" t="n">
-        <v>0</v>
       </c>
       <c r="E24" t="n">
         <v>1</v>
@@ -961,19 +961,19 @@
         </is>
       </c>
       <c r="B25" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="C25" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="D25" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="E25" t="n">
         <v>1</v>
       </c>
       <c r="F25" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
     </row>
     <row r="26">
@@ -986,16 +986,16 @@
         <v>40</v>
       </c>
       <c r="C26" t="n">
-        <v>21</v>
+        <v>3</v>
       </c>
       <c r="D26" t="n">
-        <v>7</v>
+        <v>19</v>
       </c>
       <c r="E26" t="n">
-        <v>12</v>
+        <v>26</v>
       </c>
       <c r="F26" t="n">
-        <v>18</v>
+        <v>10</v>
       </c>
     </row>
     <row r="27">
@@ -1008,16 +1008,16 @@
         <v>0</v>
       </c>
       <c r="C27" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="D27" t="n">
-        <v>0</v>
+        <v>4</v>
       </c>
       <c r="E27" t="n">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="F27" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
     </row>
     <row r="28">
@@ -1027,19 +1027,19 @@
         </is>
       </c>
       <c r="B28" t="n">
-        <v>77</v>
+        <v>94</v>
       </c>
       <c r="C28" t="n">
+        <v>8</v>
+      </c>
+      <c r="D28" t="n">
         <v>37</v>
       </c>
-      <c r="D28" t="n">
-        <v>25</v>
-      </c>
       <c r="E28" t="n">
-        <v>34</v>
+        <v>52</v>
       </c>
       <c r="F28" t="n">
-        <v>28</v>
+        <v>10</v>
       </c>
     </row>
     <row r="29">
@@ -1052,10 +1052,10 @@
         <v>3</v>
       </c>
       <c r="C29" t="n">
+        <v>0</v>
+      </c>
+      <c r="D29" t="n">
         <v>3</v>
-      </c>
-      <c r="D29" t="n">
-        <v>0</v>
       </c>
       <c r="E29" t="n">
         <v>6</v>
@@ -1071,19 +1071,19 @@
         </is>
       </c>
       <c r="B30" t="n">
-        <v>17</v>
+        <v>20</v>
       </c>
       <c r="C30" t="n">
-        <v>11</v>
+        <v>3</v>
       </c>
       <c r="D30" t="n">
-        <v>5</v>
+        <v>10</v>
       </c>
       <c r="E30" t="n">
-        <v>2</v>
+        <v>9</v>
       </c>
       <c r="F30" t="n">
-        <v>8</v>
+        <v>1</v>
       </c>
     </row>
     <row r="31">
@@ -1096,13 +1096,13 @@
         <v>4</v>
       </c>
       <c r="C31" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="D31" t="n">
         <v>2</v>
       </c>
       <c r="E31" t="n">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="F31" t="n">
         <v>1</v>
@@ -1115,19 +1115,19 @@
         </is>
       </c>
       <c r="B32" t="n">
-        <v>1</v>
+        <v>4</v>
       </c>
       <c r="C32" t="n">
-        <v>16</v>
+        <v>8</v>
       </c>
       <c r="D32" t="n">
-        <v>5</v>
+        <v>20</v>
       </c>
       <c r="E32" t="n">
-        <v>27</v>
+        <v>26</v>
       </c>
       <c r="F32" t="n">
-        <v>15</v>
+        <v>11</v>
       </c>
     </row>
     <row r="33">
@@ -1137,19 +1137,19 @@
         </is>
       </c>
       <c r="B33" t="n">
-        <v>94</v>
+        <v>99</v>
       </c>
       <c r="C33" t="n">
-        <v>51</v>
+        <v>9</v>
       </c>
       <c r="D33" t="n">
-        <v>16</v>
+        <v>50</v>
       </c>
       <c r="E33" t="n">
-        <v>33</v>
+        <v>71</v>
       </c>
       <c r="F33" t="n">
-        <v>45</v>
+        <v>10</v>
       </c>
     </row>
     <row r="34">
@@ -1162,16 +1162,16 @@
         <v>15</v>
       </c>
       <c r="C34" t="n">
-        <v>5</v>
+        <v>1</v>
       </c>
       <c r="D34" t="n">
-        <v>0</v>
+        <v>7</v>
       </c>
       <c r="E34" t="n">
         <v>7</v>
       </c>
       <c r="F34" t="n">
-        <v>4</v>
+        <v>1</v>
       </c>
     </row>
   </sheetData>

--- a/data/output/topik_per_lokasi.xlsx
+++ b/data/output/topik_per_lokasi.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:F34"/>
+  <dimension ref="A1:F35"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -455,19 +455,19 @@
         </is>
       </c>
       <c r="B2" t="n">
-        <v>47</v>
+        <v>45</v>
       </c>
       <c r="C2" t="n">
         <v>3</v>
       </c>
       <c r="D2" t="n">
-        <v>12</v>
+        <v>4</v>
       </c>
       <c r="E2" t="n">
-        <v>30</v>
+        <v>4</v>
       </c>
       <c r="F2" t="n">
-        <v>2</v>
+        <v>38</v>
       </c>
     </row>
     <row r="3">
@@ -477,19 +477,19 @@
         </is>
       </c>
       <c r="B3" t="n">
-        <v>188</v>
+        <v>189</v>
       </c>
       <c r="C3" t="n">
-        <v>23</v>
+        <v>20</v>
       </c>
       <c r="D3" t="n">
-        <v>166</v>
+        <v>24</v>
       </c>
       <c r="E3" t="n">
-        <v>87</v>
+        <v>26</v>
       </c>
       <c r="F3" t="n">
-        <v>34</v>
+        <v>239</v>
       </c>
     </row>
     <row r="4">
@@ -502,66 +502,66 @@
         <v>1</v>
       </c>
       <c r="C4" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="D4" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="E4" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="F4" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
     </row>
     <row r="5">
       <c r="A5" t="inlineStr">
         <is>
-          <t>Goa Karang Pamulang</t>
+          <t>Dermaga baru</t>
         </is>
       </c>
       <c r="B5" t="n">
-        <v>3</v>
+        <v>5</v>
       </c>
       <c r="C5" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="D5" t="n">
-        <v>4</v>
+        <v>0</v>
       </c>
       <c r="E5" t="n">
-        <v>15</v>
+        <v>0</v>
       </c>
       <c r="F5" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
     </row>
     <row r="6">
       <c r="A6" t="inlineStr">
         <is>
-          <t>Hidden Gems Pelabuhanratu</t>
+          <t>Goa Karang Pamulang</t>
         </is>
       </c>
       <c r="B6" t="n">
-        <v>0</v>
+        <v>3</v>
       </c>
       <c r="C6" t="n">
         <v>0</v>
       </c>
       <c r="D6" t="n">
-        <v>1</v>
+        <v>4</v>
       </c>
       <c r="E6" t="n">
-        <v>0</v>
+        <v>4</v>
       </c>
       <c r="F6" t="n">
-        <v>0</v>
+        <v>13</v>
       </c>
     </row>
     <row r="7">
       <c r="A7" t="inlineStr">
         <is>
-          <t>Ilove Palabuhanratu</t>
+          <t>Hidden Gems Pelabuhanratu</t>
         </is>
       </c>
       <c r="B7" t="n">
@@ -574,7 +574,7 @@
         <v>0</v>
       </c>
       <c r="E7" t="n">
-        <v>3</v>
+        <v>0</v>
       </c>
       <c r="F7" t="n">
         <v>0</v>
@@ -583,595 +583,617 @@
     <row r="8">
       <c r="A8" t="inlineStr">
         <is>
-          <t>Jangilus Monument</t>
+          <t>Ilove Palabuhanratu</t>
         </is>
       </c>
       <c r="B8" t="n">
         <v>1</v>
       </c>
       <c r="C8" t="n">
-        <v>4</v>
+        <v>1</v>
       </c>
       <c r="D8" t="n">
-        <v>38</v>
+        <v>0</v>
       </c>
       <c r="E8" t="n">
-        <v>103</v>
+        <v>0</v>
       </c>
       <c r="F8" t="n">
-        <v>51</v>
+        <v>2</v>
       </c>
     </row>
     <row r="9">
       <c r="A9" t="inlineStr">
         <is>
-          <t>Lapang Cangehgar Pelabuhanratu</t>
+          <t>Jangilus Monument</t>
         </is>
       </c>
       <c r="B9" t="n">
-        <v>219</v>
+        <v>3</v>
       </c>
       <c r="C9" t="n">
-        <v>30</v>
+        <v>19</v>
       </c>
       <c r="D9" t="n">
-        <v>147</v>
+        <v>28</v>
       </c>
       <c r="E9" t="n">
-        <v>109</v>
+        <v>79</v>
       </c>
       <c r="F9" t="n">
-        <v>15</v>
+        <v>68</v>
       </c>
     </row>
     <row r="10">
       <c r="A10" t="inlineStr">
         <is>
-          <t>Muara Citepus Palabuhanratu</t>
+          <t>Lapang Cangehgar Pelabuhanratu</t>
         </is>
       </c>
       <c r="B10" t="n">
-        <v>2</v>
+        <v>230</v>
       </c>
       <c r="C10" t="n">
-        <v>1</v>
+        <v>30</v>
       </c>
       <c r="D10" t="n">
-        <v>12</v>
+        <v>14</v>
       </c>
       <c r="E10" t="n">
-        <v>23</v>
+        <v>19</v>
       </c>
       <c r="F10" t="n">
-        <v>4</v>
+        <v>227</v>
       </c>
     </row>
     <row r="11">
       <c r="A11" t="inlineStr">
         <is>
-          <t>PANTAI CIBANGBAN</t>
+          <t>Muara Citepus Palabuhanratu</t>
         </is>
       </c>
       <c r="B11" t="n">
-        <v>5</v>
+        <v>3</v>
       </c>
       <c r="C11" t="n">
-        <v>6</v>
+        <v>1</v>
       </c>
       <c r="D11" t="n">
-        <v>93</v>
+        <v>4</v>
       </c>
       <c r="E11" t="n">
-        <v>121</v>
+        <v>3</v>
       </c>
       <c r="F11" t="n">
-        <v>10</v>
+        <v>31</v>
       </c>
     </row>
     <row r="12">
       <c r="A12" t="inlineStr">
         <is>
-          <t>Pantai Batu Bintang</t>
+          <t>PANTAI CIBANGBAN</t>
         </is>
       </c>
       <c r="B12" t="n">
-        <v>147</v>
+        <v>0</v>
       </c>
       <c r="C12" t="n">
-        <v>6</v>
+        <v>17</v>
       </c>
       <c r="D12" t="n">
-        <v>52</v>
+        <v>28</v>
       </c>
       <c r="E12" t="n">
-        <v>115</v>
+        <v>14</v>
       </c>
       <c r="F12" t="n">
-        <v>11</v>
+        <v>176</v>
       </c>
     </row>
     <row r="13">
       <c r="A13" t="inlineStr">
         <is>
-          <t>Pantai Cipatuguran Palabuhanratu</t>
+          <t>Pantai Batu Bintang</t>
         </is>
       </c>
       <c r="B13" t="n">
-        <v>5</v>
+        <v>147</v>
       </c>
       <c r="C13" t="n">
-        <v>0</v>
+        <v>4</v>
       </c>
       <c r="D13" t="n">
-        <v>0</v>
+        <v>14</v>
       </c>
       <c r="E13" t="n">
-        <v>0</v>
+        <v>11</v>
       </c>
       <c r="F13" t="n">
-        <v>0</v>
+        <v>155</v>
       </c>
     </row>
     <row r="14">
       <c r="A14" t="inlineStr">
         <is>
-          <t>Pantai Citepus</t>
+          <t>Pantai Cipatuguran Palabuhanratu</t>
         </is>
       </c>
       <c r="B14" t="n">
         <v>5</v>
       </c>
       <c r="C14" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="D14" t="n">
-        <v>51</v>
+        <v>0</v>
       </c>
       <c r="E14" t="n">
-        <v>96</v>
+        <v>0</v>
       </c>
       <c r="F14" t="n">
-        <v>11</v>
+        <v>0</v>
       </c>
     </row>
     <row r="15">
       <c r="A15" t="inlineStr">
         <is>
-          <t>Pantai Citepus Sukabumi</t>
+          <t>Pantai Citepus</t>
         </is>
       </c>
       <c r="B15" t="n">
         <v>5</v>
       </c>
       <c r="C15" t="n">
-        <v>9</v>
+        <v>0</v>
       </c>
       <c r="D15" t="n">
-        <v>75</v>
+        <v>10</v>
       </c>
       <c r="E15" t="n">
-        <v>108</v>
+        <v>10</v>
       </c>
       <c r="F15" t="n">
-        <v>9</v>
+        <v>140</v>
       </c>
     </row>
     <row r="16">
       <c r="A16" t="inlineStr">
         <is>
-          <t>Pantai Gopalo</t>
+          <t>Pantai Citepus Sukabumi</t>
         </is>
       </c>
       <c r="B16" t="n">
-        <v>3</v>
+        <v>5</v>
       </c>
       <c r="C16" t="n">
-        <v>0</v>
+        <v>8</v>
       </c>
       <c r="D16" t="n">
-        <v>1</v>
+        <v>28</v>
       </c>
       <c r="E16" t="n">
-        <v>3</v>
+        <v>16</v>
       </c>
       <c r="F16" t="n">
-        <v>0</v>
+        <v>149</v>
       </c>
     </row>
     <row r="17">
       <c r="A17" t="inlineStr">
         <is>
-          <t>Pantai Istana Presiden Pelabuhanratu</t>
+          <t>Pantai Gopalo</t>
         </is>
       </c>
       <c r="B17" t="n">
-        <v>5</v>
+        <v>2</v>
       </c>
       <c r="C17" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="D17" t="n">
-        <v>73</v>
+        <v>0</v>
       </c>
       <c r="E17" t="n">
-        <v>121</v>
+        <v>0</v>
       </c>
       <c r="F17" t="n">
-        <v>16</v>
+        <v>3</v>
       </c>
     </row>
     <row r="18">
       <c r="A18" t="inlineStr">
         <is>
-          <t>Pantai Kandita</t>
+          <t>Pantai Istana Presiden Pelabuhanratu</t>
         </is>
       </c>
       <c r="B18" t="n">
-        <v>0</v>
+        <v>5</v>
       </c>
       <c r="C18" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="D18" t="n">
-        <v>0</v>
+        <v>17</v>
       </c>
       <c r="E18" t="n">
-        <v>2</v>
+        <v>12</v>
       </c>
       <c r="F18" t="n">
-        <v>0</v>
+        <v>179</v>
       </c>
     </row>
     <row r="19">
       <c r="A19" t="inlineStr">
         <is>
-          <t>Pantai Karang Sari</t>
+          <t>Pantai Kandita</t>
         </is>
       </c>
       <c r="B19" t="n">
-        <v>117</v>
+        <v>2</v>
       </c>
       <c r="C19" t="n">
-        <v>9</v>
+        <v>0</v>
       </c>
       <c r="D19" t="n">
-        <v>38</v>
+        <v>0</v>
       </c>
       <c r="E19" t="n">
-        <v>84</v>
+        <v>0</v>
       </c>
       <c r="F19" t="n">
-        <v>5</v>
+        <v>2</v>
       </c>
     </row>
     <row r="20">
       <c r="A20" t="inlineStr">
         <is>
-          <t>Pantai Pelabuhan Ratu</t>
+          <t>Pantai Karang Sari</t>
         </is>
       </c>
       <c r="B20" t="n">
-        <v>214</v>
+        <v>115</v>
       </c>
       <c r="C20" t="n">
-        <v>9</v>
+        <v>19</v>
       </c>
       <c r="D20" t="n">
-        <v>80</v>
+        <v>27</v>
       </c>
       <c r="E20" t="n">
-        <v>150</v>
+        <v>11</v>
       </c>
       <c r="F20" t="n">
-        <v>21</v>
+        <v>81</v>
       </c>
     </row>
     <row r="21">
       <c r="A21" t="inlineStr">
         <is>
-          <t>Pantai Twenty Cipatuguran</t>
+          <t>Pantai Pelabuhan Ratu</t>
         </is>
       </c>
       <c r="B21" t="n">
-        <v>5</v>
+        <v>214</v>
       </c>
       <c r="C21" t="n">
-        <v>0</v>
+        <v>15</v>
       </c>
       <c r="D21" t="n">
-        <v>6</v>
+        <v>16</v>
       </c>
       <c r="E21" t="n">
-        <v>23</v>
+        <v>17</v>
       </c>
       <c r="F21" t="n">
-        <v>2</v>
+        <v>212</v>
       </c>
     </row>
     <row r="22">
       <c r="A22" t="inlineStr">
         <is>
-          <t>Pantai buffalo</t>
+          <t>Pantai Twenty Cipatuguran</t>
         </is>
       </c>
       <c r="B22" t="n">
+        <v>5</v>
+      </c>
+      <c r="C22" t="n">
+        <v>4</v>
+      </c>
+      <c r="D22" t="n">
         <v>3</v>
       </c>
-      <c r="C22" t="n">
-        <v>0</v>
-      </c>
-      <c r="D22" t="n">
+      <c r="E22" t="n">
         <v>5</v>
       </c>
-      <c r="E22" t="n">
-        <v>2</v>
-      </c>
       <c r="F22" t="n">
-        <v>0</v>
+        <v>19</v>
       </c>
     </row>
     <row r="23">
       <c r="A23" t="inlineStr">
         <is>
-          <t>Pesanggrahan Tenjo Resmi Pelabuhan Ratu</t>
+          <t>Pantai buffalo</t>
         </is>
       </c>
       <c r="B23" t="n">
-        <v>7</v>
+        <v>4</v>
       </c>
       <c r="C23" t="n">
-        <v>11</v>
+        <v>0</v>
       </c>
       <c r="D23" t="n">
-        <v>48</v>
+        <v>0</v>
       </c>
       <c r="E23" t="n">
-        <v>92</v>
+        <v>1</v>
       </c>
       <c r="F23" t="n">
-        <v>14</v>
+        <v>5</v>
       </c>
     </row>
     <row r="24">
       <c r="A24" t="inlineStr">
         <is>
-          <t>Saung Bintang Katineung, wisata pantai, air dan kuliner</t>
+          <t>Pesanggrahan Tenjo Resmi Pelabuhan Ratu</t>
         </is>
       </c>
       <c r="B24" t="n">
-        <v>3</v>
+        <v>6</v>
       </c>
       <c r="C24" t="n">
-        <v>0</v>
+        <v>13</v>
       </c>
       <c r="D24" t="n">
-        <v>5</v>
+        <v>34</v>
       </c>
       <c r="E24" t="n">
-        <v>1</v>
+        <v>17</v>
       </c>
       <c r="F24" t="n">
-        <v>0</v>
+        <v>102</v>
       </c>
     </row>
     <row r="25">
       <c r="A25" t="inlineStr">
         <is>
-          <t>Situ Rawa Kalong</t>
+          <t>Saung Bintang Katineung, wisata pantai, air dan kuliner</t>
         </is>
       </c>
       <c r="B25" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="C25" t="n">
         <v>2</v>
       </c>
       <c r="D25" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="E25" t="n">
         <v>1</v>
       </c>
       <c r="F25" t="n">
-        <v>0</v>
+        <v>3</v>
       </c>
     </row>
     <row r="26">
       <c r="A26" t="inlineStr">
         <is>
-          <t>Smile hill Pelabuhan Ratu</t>
+          <t>Situ Rawa Kalong</t>
         </is>
       </c>
       <c r="B26" t="n">
-        <v>40</v>
+        <v>4</v>
       </c>
       <c r="C26" t="n">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="D26" t="n">
-        <v>19</v>
+        <v>0</v>
       </c>
       <c r="E26" t="n">
-        <v>26</v>
+        <v>0</v>
       </c>
       <c r="F26" t="n">
-        <v>10</v>
+        <v>1</v>
       </c>
     </row>
     <row r="27">
       <c r="A27" t="inlineStr">
         <is>
-          <t>Taman Bappeda</t>
+          <t>Smile hill Pelabuhan Ratu</t>
         </is>
       </c>
       <c r="B27" t="n">
-        <v>0</v>
+        <v>41</v>
       </c>
       <c r="C27" t="n">
-        <v>0</v>
+        <v>4</v>
       </c>
       <c r="D27" t="n">
-        <v>4</v>
+        <v>14</v>
       </c>
       <c r="E27" t="n">
-        <v>4</v>
+        <v>12</v>
       </c>
       <c r="F27" t="n">
-        <v>0</v>
+        <v>27</v>
       </c>
     </row>
     <row r="28">
       <c r="A28" t="inlineStr">
         <is>
-          <t>Taman Bunga Gunung Sumping</t>
+          <t>Taman Bappeda</t>
         </is>
       </c>
       <c r="B28" t="n">
-        <v>94</v>
+        <v>0</v>
       </c>
       <c r="C28" t="n">
-        <v>8</v>
+        <v>0</v>
       </c>
       <c r="D28" t="n">
-        <v>37</v>
+        <v>0</v>
       </c>
       <c r="E28" t="n">
-        <v>52</v>
+        <v>1</v>
       </c>
       <c r="F28" t="n">
-        <v>10</v>
+        <v>7</v>
       </c>
     </row>
     <row r="29">
       <c r="A29" t="inlineStr">
         <is>
-          <t>Taman Bunga Pelabuhan Ratu</t>
+          <t>Taman Bunga Gunung Sumping</t>
         </is>
       </c>
       <c r="B29" t="n">
-        <v>3</v>
+        <v>91</v>
       </c>
       <c r="C29" t="n">
-        <v>0</v>
+        <v>13</v>
       </c>
       <c r="D29" t="n">
-        <v>3</v>
+        <v>12</v>
       </c>
       <c r="E29" t="n">
-        <v>6</v>
+        <v>9</v>
       </c>
       <c r="F29" t="n">
-        <v>2</v>
+        <v>76</v>
       </c>
     </row>
     <row r="30">
       <c r="A30" t="inlineStr">
         <is>
-          <t>Taman Citepus (Ruang Terbuka Hijau) RTH</t>
+          <t>Taman Bunga Pelabuhan Ratu</t>
         </is>
       </c>
       <c r="B30" t="n">
-        <v>20</v>
+        <v>3</v>
       </c>
       <c r="C30" t="n">
-        <v>3</v>
+        <v>0</v>
       </c>
       <c r="D30" t="n">
-        <v>10</v>
+        <v>0</v>
       </c>
       <c r="E30" t="n">
-        <v>9</v>
+        <v>0</v>
       </c>
       <c r="F30" t="n">
-        <v>1</v>
+        <v>11</v>
       </c>
     </row>
     <row r="31">
       <c r="A31" t="inlineStr">
         <is>
-          <t>Taman Kota Cangehgar Palabuhanratu</t>
+          <t>Taman Citepus (Ruang Terbuka Hijau) RTH</t>
         </is>
       </c>
       <c r="B31" t="n">
-        <v>4</v>
+        <v>22</v>
       </c>
       <c r="C31" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="D31" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="E31" t="n">
-        <v>4</v>
+        <v>0</v>
       </c>
       <c r="F31" t="n">
-        <v>1</v>
+        <v>18</v>
       </c>
     </row>
     <row r="32">
       <c r="A32" t="inlineStr">
         <is>
-          <t>Waterpark Citepus Pelabuhanratu</t>
+          <t>Taman Kota Cangehgar Palabuhanratu</t>
         </is>
       </c>
       <c r="B32" t="n">
         <v>4</v>
       </c>
       <c r="C32" t="n">
-        <v>8</v>
+        <v>3</v>
       </c>
       <c r="D32" t="n">
-        <v>20</v>
+        <v>1</v>
       </c>
       <c r="E32" t="n">
-        <v>26</v>
+        <v>0</v>
       </c>
       <c r="F32" t="n">
-        <v>11</v>
+        <v>4</v>
       </c>
     </row>
     <row r="33">
       <c r="A33" t="inlineStr">
         <is>
-          <t>Wisata Alam Pantai Sukawayana</t>
+          <t>Waterpark Citepus Pelabuhanratu</t>
         </is>
       </c>
       <c r="B33" t="n">
-        <v>99</v>
+        <v>6</v>
       </c>
       <c r="C33" t="n">
-        <v>9</v>
+        <v>4</v>
       </c>
       <c r="D33" t="n">
-        <v>50</v>
+        <v>12</v>
       </c>
       <c r="E33" t="n">
-        <v>71</v>
+        <v>7</v>
       </c>
       <c r="F33" t="n">
-        <v>10</v>
+        <v>40</v>
       </c>
     </row>
     <row r="34">
       <c r="A34" t="inlineStr">
         <is>
-          <t>i-Pe Beach Pelabuhanratu</t>
+          <t>Wisata Alam Pantai Sukawayana</t>
         </is>
       </c>
       <c r="B34" t="n">
-        <v>15</v>
+        <v>99</v>
       </c>
       <c r="C34" t="n">
-        <v>1</v>
+        <v>21</v>
       </c>
       <c r="D34" t="n">
-        <v>7</v>
+        <v>25</v>
       </c>
       <c r="E34" t="n">
         <v>7</v>
       </c>
       <c r="F34" t="n">
-        <v>1</v>
+        <v>87</v>
+      </c>
+    </row>
+    <row r="35">
+      <c r="A35" t="inlineStr">
+        <is>
+          <t>i-Pe Beach Pelabuhanratu</t>
+        </is>
+      </c>
+      <c r="B35" t="n">
+        <v>15</v>
+      </c>
+      <c r="C35" t="n">
+        <v>0</v>
+      </c>
+      <c r="D35" t="n">
+        <v>0</v>
+      </c>
+      <c r="E35" t="n">
+        <v>1</v>
+      </c>
+      <c r="F35" t="n">
+        <v>15</v>
       </c>
     </row>
   </sheetData>

--- a/data/output/topik_per_lokasi.xlsx
+++ b/data/output/topik_per_lokasi.xlsx
@@ -455,19 +455,19 @@
         </is>
       </c>
       <c r="B2" t="n">
-        <v>45</v>
+        <v>43</v>
       </c>
       <c r="C2" t="n">
         <v>3</v>
       </c>
       <c r="D2" t="n">
-        <v>4</v>
+        <v>1</v>
       </c>
       <c r="E2" t="n">
-        <v>4</v>
+        <v>7</v>
       </c>
       <c r="F2" t="n">
-        <v>38</v>
+        <v>40</v>
       </c>
     </row>
     <row r="3">
@@ -477,19 +477,19 @@
         </is>
       </c>
       <c r="B3" t="n">
-        <v>189</v>
+        <v>169</v>
       </c>
       <c r="C3" t="n">
-        <v>20</v>
+        <v>26</v>
       </c>
       <c r="D3" t="n">
-        <v>24</v>
+        <v>31</v>
       </c>
       <c r="E3" t="n">
-        <v>26</v>
+        <v>43</v>
       </c>
       <c r="F3" t="n">
-        <v>239</v>
+        <v>229</v>
       </c>
     </row>
     <row r="4">
@@ -502,13 +502,13 @@
         <v>1</v>
       </c>
       <c r="C4" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="D4" t="n">
         <v>0</v>
       </c>
       <c r="E4" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="F4" t="n">
         <v>1</v>
@@ -521,10 +521,10 @@
         </is>
       </c>
       <c r="B5" t="n">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="C5" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="D5" t="n">
         <v>0</v>
@@ -543,19 +543,19 @@
         </is>
       </c>
       <c r="B6" t="n">
+        <v>2</v>
+      </c>
+      <c r="C6" t="n">
         <v>3</v>
       </c>
-      <c r="C6" t="n">
-        <v>0</v>
-      </c>
       <c r="D6" t="n">
-        <v>4</v>
+        <v>6</v>
       </c>
       <c r="E6" t="n">
-        <v>4</v>
+        <v>1</v>
       </c>
       <c r="F6" t="n">
-        <v>13</v>
+        <v>12</v>
       </c>
     </row>
     <row r="7">
@@ -568,13 +568,13 @@
         <v>0</v>
       </c>
       <c r="C7" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="D7" t="n">
         <v>0</v>
       </c>
       <c r="E7" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="F7" t="n">
         <v>0</v>
@@ -587,19 +587,19 @@
         </is>
       </c>
       <c r="B8" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="C8" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="D8" t="n">
         <v>0</v>
       </c>
       <c r="E8" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="F8" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
     </row>
     <row r="9">
@@ -612,16 +612,16 @@
         <v>3</v>
       </c>
       <c r="C9" t="n">
-        <v>19</v>
+        <v>14</v>
       </c>
       <c r="D9" t="n">
         <v>28</v>
       </c>
       <c r="E9" t="n">
-        <v>79</v>
+        <v>68</v>
       </c>
       <c r="F9" t="n">
-        <v>68</v>
+        <v>84</v>
       </c>
     </row>
     <row r="10">
@@ -631,19 +631,19 @@
         </is>
       </c>
       <c r="B10" t="n">
-        <v>230</v>
+        <v>216</v>
       </c>
       <c r="C10" t="n">
-        <v>30</v>
+        <v>26</v>
       </c>
       <c r="D10" t="n">
-        <v>14</v>
+        <v>16</v>
       </c>
       <c r="E10" t="n">
-        <v>19</v>
+        <v>21</v>
       </c>
       <c r="F10" t="n">
-        <v>227</v>
+        <v>241</v>
       </c>
     </row>
     <row r="11">
@@ -653,19 +653,19 @@
         </is>
       </c>
       <c r="B11" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="C11" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="D11" t="n">
         <v>4</v>
       </c>
       <c r="E11" t="n">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="F11" t="n">
-        <v>31</v>
+        <v>35</v>
       </c>
     </row>
     <row r="12">
@@ -675,19 +675,19 @@
         </is>
       </c>
       <c r="B12" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="C12" t="n">
-        <v>17</v>
+        <v>9</v>
       </c>
       <c r="D12" t="n">
-        <v>28</v>
+        <v>10</v>
       </c>
       <c r="E12" t="n">
-        <v>14</v>
+        <v>20</v>
       </c>
       <c r="F12" t="n">
-        <v>176</v>
+        <v>195</v>
       </c>
     </row>
     <row r="13">
@@ -697,19 +697,19 @@
         </is>
       </c>
       <c r="B13" t="n">
-        <v>147</v>
+        <v>139</v>
       </c>
       <c r="C13" t="n">
-        <v>4</v>
+        <v>8</v>
       </c>
       <c r="D13" t="n">
-        <v>14</v>
+        <v>8</v>
       </c>
       <c r="E13" t="n">
-        <v>11</v>
+        <v>6</v>
       </c>
       <c r="F13" t="n">
-        <v>155</v>
+        <v>170</v>
       </c>
     </row>
     <row r="14">
@@ -741,19 +741,19 @@
         </is>
       </c>
       <c r="B15" t="n">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="C15" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="D15" t="n">
-        <v>10</v>
+        <v>2</v>
       </c>
       <c r="E15" t="n">
-        <v>10</v>
+        <v>1</v>
       </c>
       <c r="F15" t="n">
-        <v>140</v>
+        <v>156</v>
       </c>
     </row>
     <row r="16">
@@ -763,19 +763,19 @@
         </is>
       </c>
       <c r="B16" t="n">
-        <v>5</v>
+        <v>3</v>
       </c>
       <c r="C16" t="n">
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="D16" t="n">
-        <v>28</v>
+        <v>10</v>
       </c>
       <c r="E16" t="n">
-        <v>16</v>
+        <v>10</v>
       </c>
       <c r="F16" t="n">
-        <v>149</v>
+        <v>174</v>
       </c>
     </row>
     <row r="17">
@@ -788,7 +788,7 @@
         <v>2</v>
       </c>
       <c r="C17" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="D17" t="n">
         <v>0</v>
@@ -797,7 +797,7 @@
         <v>0</v>
       </c>
       <c r="F17" t="n">
-        <v>3</v>
+        <v>4</v>
       </c>
     </row>
     <row r="18">
@@ -813,13 +813,13 @@
         <v>2</v>
       </c>
       <c r="D18" t="n">
-        <v>17</v>
+        <v>2</v>
       </c>
       <c r="E18" t="n">
-        <v>12</v>
+        <v>9</v>
       </c>
       <c r="F18" t="n">
-        <v>179</v>
+        <v>197</v>
       </c>
     </row>
     <row r="19">
@@ -829,10 +829,10 @@
         </is>
       </c>
       <c r="B19" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="C19" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="D19" t="n">
         <v>0</v>
@@ -851,19 +851,19 @@
         </is>
       </c>
       <c r="B20" t="n">
-        <v>115</v>
+        <v>107</v>
       </c>
       <c r="C20" t="n">
-        <v>19</v>
+        <v>10</v>
       </c>
       <c r="D20" t="n">
-        <v>27</v>
+        <v>13</v>
       </c>
       <c r="E20" t="n">
-        <v>11</v>
+        <v>22</v>
       </c>
       <c r="F20" t="n">
-        <v>81</v>
+        <v>101</v>
       </c>
     </row>
     <row r="21">
@@ -873,19 +873,19 @@
         </is>
       </c>
       <c r="B21" t="n">
-        <v>214</v>
+        <v>199</v>
       </c>
       <c r="C21" t="n">
-        <v>15</v>
+        <v>16</v>
       </c>
       <c r="D21" t="n">
-        <v>16</v>
+        <v>17</v>
       </c>
       <c r="E21" t="n">
-        <v>17</v>
+        <v>27</v>
       </c>
       <c r="F21" t="n">
-        <v>212</v>
+        <v>215</v>
       </c>
     </row>
     <row r="22">
@@ -898,16 +898,16 @@
         <v>5</v>
       </c>
       <c r="C22" t="n">
-        <v>4</v>
+        <v>2</v>
       </c>
       <c r="D22" t="n">
         <v>3</v>
       </c>
       <c r="E22" t="n">
-        <v>5</v>
+        <v>3</v>
       </c>
       <c r="F22" t="n">
-        <v>19</v>
+        <v>23</v>
       </c>
     </row>
     <row r="23">
@@ -917,19 +917,19 @@
         </is>
       </c>
       <c r="B23" t="n">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="C23" t="n">
         <v>0</v>
       </c>
       <c r="D23" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="E23" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="F23" t="n">
-        <v>5</v>
+        <v>6</v>
       </c>
     </row>
     <row r="24">
@@ -939,19 +939,19 @@
         </is>
       </c>
       <c r="B24" t="n">
-        <v>6</v>
+        <v>4</v>
       </c>
       <c r="C24" t="n">
+        <v>10</v>
+      </c>
+      <c r="D24" t="n">
         <v>13</v>
-      </c>
-      <c r="D24" t="n">
-        <v>34</v>
       </c>
       <c r="E24" t="n">
         <v>17</v>
       </c>
       <c r="F24" t="n">
-        <v>102</v>
+        <v>128</v>
       </c>
     </row>
     <row r="25">
@@ -964,13 +964,13 @@
         <v>3</v>
       </c>
       <c r="C25" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="D25" t="n">
         <v>0</v>
       </c>
       <c r="E25" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="F25" t="n">
         <v>3</v>
@@ -983,16 +983,16 @@
         </is>
       </c>
       <c r="B26" t="n">
-        <v>4</v>
+        <v>2</v>
       </c>
       <c r="C26" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="D26" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="E26" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="F26" t="n">
         <v>1</v>
@@ -1005,19 +1005,19 @@
         </is>
       </c>
       <c r="B27" t="n">
-        <v>41</v>
+        <v>36</v>
       </c>
       <c r="C27" t="n">
-        <v>4</v>
+        <v>8</v>
       </c>
       <c r="D27" t="n">
-        <v>14</v>
+        <v>6</v>
       </c>
       <c r="E27" t="n">
-        <v>12</v>
+        <v>9</v>
       </c>
       <c r="F27" t="n">
-        <v>27</v>
+        <v>39</v>
       </c>
     </row>
     <row r="28">
@@ -1027,19 +1027,19 @@
         </is>
       </c>
       <c r="B28" t="n">
-        <v>0</v>
+        <v>4</v>
       </c>
       <c r="C28" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="D28" t="n">
         <v>0</v>
       </c>
       <c r="E28" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="F28" t="n">
-        <v>7</v>
+        <v>8</v>
       </c>
     </row>
     <row r="29">
@@ -1049,19 +1049,19 @@
         </is>
       </c>
       <c r="B29" t="n">
-        <v>91</v>
+        <v>81</v>
       </c>
       <c r="C29" t="n">
+        <v>9</v>
+      </c>
+      <c r="D29" t="n">
+        <v>11</v>
+      </c>
+      <c r="E29" t="n">
         <v>13</v>
       </c>
-      <c r="D29" t="n">
-        <v>12</v>
-      </c>
-      <c r="E29" t="n">
-        <v>9</v>
-      </c>
       <c r="F29" t="n">
-        <v>76</v>
+        <v>87</v>
       </c>
     </row>
     <row r="30">
@@ -1093,19 +1093,19 @@
         </is>
       </c>
       <c r="B31" t="n">
-        <v>22</v>
+        <v>17</v>
       </c>
       <c r="C31" t="n">
         <v>2</v>
       </c>
       <c r="D31" t="n">
-        <v>1</v>
+        <v>5</v>
       </c>
       <c r="E31" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="F31" t="n">
-        <v>18</v>
+        <v>17</v>
       </c>
     </row>
     <row r="32">
@@ -1118,13 +1118,13 @@
         <v>4</v>
       </c>
       <c r="C32" t="n">
+        <v>0</v>
+      </c>
+      <c r="D32" t="n">
+        <v>1</v>
+      </c>
+      <c r="E32" t="n">
         <v>3</v>
-      </c>
-      <c r="D32" t="n">
-        <v>1</v>
-      </c>
-      <c r="E32" t="n">
-        <v>0</v>
       </c>
       <c r="F32" t="n">
         <v>4</v>
@@ -1137,19 +1137,19 @@
         </is>
       </c>
       <c r="B33" t="n">
+        <v>5</v>
+      </c>
+      <c r="C33" t="n">
         <v>6</v>
       </c>
-      <c r="C33" t="n">
-        <v>4</v>
-      </c>
       <c r="D33" t="n">
-        <v>12</v>
+        <v>5</v>
       </c>
       <c r="E33" t="n">
-        <v>7</v>
+        <v>3</v>
       </c>
       <c r="F33" t="n">
-        <v>40</v>
+        <v>50</v>
       </c>
     </row>
     <row r="34">
@@ -1159,19 +1159,19 @@
         </is>
       </c>
       <c r="B34" t="n">
-        <v>99</v>
+        <v>92</v>
       </c>
       <c r="C34" t="n">
-        <v>21</v>
+        <v>14</v>
       </c>
       <c r="D34" t="n">
-        <v>25</v>
+        <v>17</v>
       </c>
       <c r="E34" t="n">
-        <v>7</v>
+        <v>13</v>
       </c>
       <c r="F34" t="n">
-        <v>87</v>
+        <v>103</v>
       </c>
     </row>
     <row r="35">
@@ -1190,10 +1190,10 @@
         <v>0</v>
       </c>
       <c r="E35" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="F35" t="n">
-        <v>15</v>
+        <v>16</v>
       </c>
     </row>
   </sheetData>

--- a/data/output/topik_per_lokasi.xlsx
+++ b/data/output/topik_per_lokasi.xlsx
@@ -455,19 +455,19 @@
         </is>
       </c>
       <c r="B2" t="n">
-        <v>43</v>
+        <v>45</v>
       </c>
       <c r="C2" t="n">
-        <v>3</v>
+        <v>13</v>
       </c>
       <c r="D2" t="n">
-        <v>1</v>
+        <v>6</v>
       </c>
       <c r="E2" t="n">
-        <v>7</v>
+        <v>27</v>
       </c>
       <c r="F2" t="n">
-        <v>40</v>
+        <v>3</v>
       </c>
     </row>
     <row r="3">
@@ -477,19 +477,19 @@
         </is>
       </c>
       <c r="B3" t="n">
-        <v>169</v>
+        <v>187</v>
       </c>
       <c r="C3" t="n">
-        <v>26</v>
+        <v>117</v>
       </c>
       <c r="D3" t="n">
-        <v>31</v>
+        <v>19</v>
       </c>
       <c r="E3" t="n">
-        <v>43</v>
+        <v>150</v>
       </c>
       <c r="F3" t="n">
-        <v>229</v>
+        <v>25</v>
       </c>
     </row>
     <row r="4">
@@ -505,10 +505,10 @@
         <v>0</v>
       </c>
       <c r="D4" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="E4" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="F4" t="n">
         <v>1</v>
@@ -521,10 +521,10 @@
         </is>
       </c>
       <c r="B5" t="n">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="C5" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="D5" t="n">
         <v>0</v>
@@ -543,19 +543,19 @@
         </is>
       </c>
       <c r="B6" t="n">
+        <v>3</v>
+      </c>
+      <c r="C6" t="n">
+        <v>7</v>
+      </c>
+      <c r="D6" t="n">
         <v>2</v>
       </c>
-      <c r="C6" t="n">
-        <v>3</v>
-      </c>
-      <c r="D6" t="n">
-        <v>6</v>
-      </c>
       <c r="E6" t="n">
-        <v>1</v>
+        <v>9</v>
       </c>
       <c r="F6" t="n">
-        <v>12</v>
+        <v>3</v>
       </c>
     </row>
     <row r="7">
@@ -571,10 +571,10 @@
         <v>0</v>
       </c>
       <c r="D7" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="E7" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="F7" t="n">
         <v>0</v>
@@ -587,19 +587,19 @@
         </is>
       </c>
       <c r="B8" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="C8" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="D8" t="n">
         <v>0</v>
       </c>
       <c r="E8" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="F8" t="n">
-        <v>3</v>
+        <v>0</v>
       </c>
     </row>
     <row r="9">
@@ -609,19 +609,19 @@
         </is>
       </c>
       <c r="B9" t="n">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="C9" t="n">
-        <v>14</v>
+        <v>67</v>
       </c>
       <c r="D9" t="n">
-        <v>28</v>
+        <v>24</v>
       </c>
       <c r="E9" t="n">
-        <v>68</v>
+        <v>61</v>
       </c>
       <c r="F9" t="n">
-        <v>84</v>
+        <v>45</v>
       </c>
     </row>
     <row r="10">
@@ -631,19 +631,19 @@
         </is>
       </c>
       <c r="B10" t="n">
-        <v>216</v>
+        <v>226</v>
       </c>
       <c r="C10" t="n">
-        <v>26</v>
+        <v>97</v>
       </c>
       <c r="D10" t="n">
-        <v>16</v>
+        <v>28</v>
       </c>
       <c r="E10" t="n">
-        <v>21</v>
+        <v>137</v>
       </c>
       <c r="F10" t="n">
-        <v>241</v>
+        <v>32</v>
       </c>
     </row>
     <row r="11">
@@ -653,19 +653,19 @@
         </is>
       </c>
       <c r="B11" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="C11" t="n">
-        <v>0</v>
+        <v>8</v>
       </c>
       <c r="D11" t="n">
-        <v>4</v>
+        <v>1</v>
       </c>
       <c r="E11" t="n">
-        <v>1</v>
+        <v>25</v>
       </c>
       <c r="F11" t="n">
-        <v>35</v>
+        <v>5</v>
       </c>
     </row>
     <row r="12">
@@ -675,19 +675,19 @@
         </is>
       </c>
       <c r="B12" t="n">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="C12" t="n">
-        <v>9</v>
+        <v>49</v>
       </c>
       <c r="D12" t="n">
-        <v>10</v>
+        <v>28</v>
       </c>
       <c r="E12" t="n">
-        <v>20</v>
+        <v>153</v>
       </c>
       <c r="F12" t="n">
-        <v>195</v>
+        <v>7</v>
       </c>
     </row>
     <row r="13">
@@ -697,19 +697,19 @@
         </is>
       </c>
       <c r="B13" t="n">
-        <v>139</v>
+        <v>144</v>
       </c>
       <c r="C13" t="n">
-        <v>8</v>
+        <v>33</v>
       </c>
       <c r="D13" t="n">
-        <v>8</v>
+        <v>5</v>
       </c>
       <c r="E13" t="n">
+        <v>143</v>
+      </c>
+      <c r="F13" t="n">
         <v>6</v>
-      </c>
-      <c r="F13" t="n">
-        <v>170</v>
       </c>
     </row>
     <row r="14">
@@ -741,19 +741,19 @@
         </is>
       </c>
       <c r="B15" t="n">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="C15" t="n">
-        <v>2</v>
+        <v>30</v>
       </c>
       <c r="D15" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="E15" t="n">
-        <v>1</v>
+        <v>127</v>
       </c>
       <c r="F15" t="n">
-        <v>156</v>
+        <v>0</v>
       </c>
     </row>
     <row r="16">
@@ -763,19 +763,19 @@
         </is>
       </c>
       <c r="B16" t="n">
-        <v>3</v>
+        <v>6</v>
       </c>
       <c r="C16" t="n">
-        <v>9</v>
+        <v>50</v>
       </c>
       <c r="D16" t="n">
-        <v>10</v>
+        <v>6</v>
       </c>
       <c r="E16" t="n">
-        <v>10</v>
+        <v>131</v>
       </c>
       <c r="F16" t="n">
-        <v>174</v>
+        <v>13</v>
       </c>
     </row>
     <row r="17">
@@ -785,7 +785,7 @@
         </is>
       </c>
       <c r="B17" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="C17" t="n">
         <v>1</v>
@@ -794,10 +794,10 @@
         <v>0</v>
       </c>
       <c r="E17" t="n">
-        <v>0</v>
+        <v>3</v>
       </c>
       <c r="F17" t="n">
-        <v>4</v>
+        <v>0</v>
       </c>
     </row>
     <row r="18">
@@ -810,16 +810,16 @@
         <v>5</v>
       </c>
       <c r="C18" t="n">
-        <v>2</v>
+        <v>43</v>
       </c>
       <c r="D18" t="n">
-        <v>2</v>
+        <v>7</v>
       </c>
       <c r="E18" t="n">
-        <v>9</v>
+        <v>154</v>
       </c>
       <c r="F18" t="n">
-        <v>197</v>
+        <v>6</v>
       </c>
     </row>
     <row r="19">
@@ -838,10 +838,10 @@
         <v>0</v>
       </c>
       <c r="E19" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="F19" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
     </row>
     <row r="20">
@@ -851,19 +851,19 @@
         </is>
       </c>
       <c r="B20" t="n">
-        <v>107</v>
+        <v>110</v>
       </c>
       <c r="C20" t="n">
-        <v>10</v>
+        <v>29</v>
       </c>
       <c r="D20" t="n">
-        <v>13</v>
+        <v>17</v>
       </c>
       <c r="E20" t="n">
-        <v>22</v>
+        <v>79</v>
       </c>
       <c r="F20" t="n">
-        <v>101</v>
+        <v>18</v>
       </c>
     </row>
     <row r="21">
@@ -873,19 +873,19 @@
         </is>
       </c>
       <c r="B21" t="n">
-        <v>199</v>
+        <v>209</v>
       </c>
       <c r="C21" t="n">
-        <v>16</v>
+        <v>73</v>
       </c>
       <c r="D21" t="n">
+        <v>23</v>
+      </c>
+      <c r="E21" t="n">
+        <v>152</v>
+      </c>
+      <c r="F21" t="n">
         <v>17</v>
-      </c>
-      <c r="E21" t="n">
-        <v>27</v>
-      </c>
-      <c r="F21" t="n">
-        <v>215</v>
       </c>
     </row>
     <row r="22">
@@ -898,16 +898,16 @@
         <v>5</v>
       </c>
       <c r="C22" t="n">
-        <v>2</v>
+        <v>8</v>
       </c>
       <c r="D22" t="n">
         <v>3</v>
       </c>
       <c r="E22" t="n">
-        <v>3</v>
+        <v>17</v>
       </c>
       <c r="F22" t="n">
-        <v>23</v>
+        <v>3</v>
       </c>
     </row>
     <row r="23">
@@ -917,19 +917,19 @@
         </is>
       </c>
       <c r="B23" t="n">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="C23" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="D23" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="E23" t="n">
-        <v>0</v>
+        <v>4</v>
       </c>
       <c r="F23" t="n">
-        <v>6</v>
+        <v>1</v>
       </c>
     </row>
     <row r="24">
@@ -939,19 +939,19 @@
         </is>
       </c>
       <c r="B24" t="n">
-        <v>4</v>
+        <v>7</v>
       </c>
       <c r="C24" t="n">
-        <v>10</v>
+        <v>51</v>
       </c>
       <c r="D24" t="n">
-        <v>13</v>
+        <v>16</v>
       </c>
       <c r="E24" t="n">
-        <v>17</v>
+        <v>87</v>
       </c>
       <c r="F24" t="n">
-        <v>128</v>
+        <v>11</v>
       </c>
     </row>
     <row r="25">
@@ -964,16 +964,16 @@
         <v>3</v>
       </c>
       <c r="C25" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="D25" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="E25" t="n">
-        <v>2</v>
+        <v>4</v>
       </c>
       <c r="F25" t="n">
-        <v>3</v>
+        <v>1</v>
       </c>
     </row>
     <row r="26">
@@ -983,19 +983,19 @@
         </is>
       </c>
       <c r="B26" t="n">
+        <v>3</v>
+      </c>
+      <c r="C26" t="n">
         <v>2</v>
       </c>
-      <c r="C26" t="n">
-        <v>0</v>
-      </c>
       <c r="D26" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="E26" t="n">
         <v>1</v>
       </c>
       <c r="F26" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
     </row>
     <row r="27">
@@ -1005,19 +1005,19 @@
         </is>
       </c>
       <c r="B27" t="n">
-        <v>36</v>
+        <v>39</v>
       </c>
       <c r="C27" t="n">
-        <v>8</v>
+        <v>26</v>
       </c>
       <c r="D27" t="n">
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="E27" t="n">
-        <v>9</v>
+        <v>19</v>
       </c>
       <c r="F27" t="n">
-        <v>39</v>
+        <v>7</v>
       </c>
     </row>
     <row r="28">
@@ -1027,19 +1027,19 @@
         </is>
       </c>
       <c r="B28" t="n">
+        <v>5</v>
+      </c>
+      <c r="C28" t="n">
         <v>4</v>
       </c>
-      <c r="C28" t="n">
-        <v>1</v>
-      </c>
       <c r="D28" t="n">
         <v>0</v>
       </c>
       <c r="E28" t="n">
-        <v>0</v>
+        <v>3</v>
       </c>
       <c r="F28" t="n">
-        <v>8</v>
+        <v>1</v>
       </c>
     </row>
     <row r="29">
@@ -1049,19 +1049,19 @@
         </is>
       </c>
       <c r="B29" t="n">
-        <v>81</v>
+        <v>85</v>
       </c>
       <c r="C29" t="n">
-        <v>9</v>
+        <v>42</v>
       </c>
       <c r="D29" t="n">
-        <v>11</v>
+        <v>18</v>
       </c>
       <c r="E29" t="n">
-        <v>13</v>
+        <v>51</v>
       </c>
       <c r="F29" t="n">
-        <v>87</v>
+        <v>5</v>
       </c>
     </row>
     <row r="30">
@@ -1074,16 +1074,16 @@
         <v>3</v>
       </c>
       <c r="C30" t="n">
-        <v>0</v>
+        <v>4</v>
       </c>
       <c r="D30" t="n">
         <v>0</v>
       </c>
       <c r="E30" t="n">
-        <v>0</v>
+        <v>7</v>
       </c>
       <c r="F30" t="n">
-        <v>11</v>
+        <v>0</v>
       </c>
     </row>
     <row r="31">
@@ -1093,19 +1093,19 @@
         </is>
       </c>
       <c r="B31" t="n">
-        <v>17</v>
+        <v>22</v>
       </c>
       <c r="C31" t="n">
-        <v>2</v>
+        <v>5</v>
       </c>
       <c r="D31" t="n">
-        <v>5</v>
+        <v>3</v>
       </c>
       <c r="E31" t="n">
-        <v>2</v>
+        <v>13</v>
       </c>
       <c r="F31" t="n">
-        <v>17</v>
+        <v>0</v>
       </c>
     </row>
     <row r="32">
@@ -1118,16 +1118,16 @@
         <v>4</v>
       </c>
       <c r="C32" t="n">
-        <v>0</v>
+        <v>3</v>
       </c>
       <c r="D32" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="E32" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="F32" t="n">
-        <v>4</v>
+        <v>1</v>
       </c>
     </row>
     <row r="33">
@@ -1137,19 +1137,19 @@
         </is>
       </c>
       <c r="B33" t="n">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="C33" t="n">
-        <v>6</v>
+        <v>16</v>
       </c>
       <c r="D33" t="n">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="E33" t="n">
-        <v>3</v>
+        <v>36</v>
       </c>
       <c r="F33" t="n">
-        <v>50</v>
+        <v>7</v>
       </c>
     </row>
     <row r="34">
@@ -1159,19 +1159,19 @@
         </is>
       </c>
       <c r="B34" t="n">
-        <v>92</v>
+        <v>97</v>
       </c>
       <c r="C34" t="n">
-        <v>14</v>
+        <v>32</v>
       </c>
       <c r="D34" t="n">
-        <v>17</v>
+        <v>22</v>
       </c>
       <c r="E34" t="n">
-        <v>13</v>
+        <v>80</v>
       </c>
       <c r="F34" t="n">
-        <v>103</v>
+        <v>8</v>
       </c>
     </row>
     <row r="35">
@@ -1184,16 +1184,16 @@
         <v>15</v>
       </c>
       <c r="C35" t="n">
-        <v>0</v>
+        <v>3</v>
       </c>
       <c r="D35" t="n">
         <v>0</v>
       </c>
       <c r="E35" t="n">
-        <v>0</v>
+        <v>12</v>
       </c>
       <c r="F35" t="n">
-        <v>16</v>
+        <v>1</v>
       </c>
     </row>
   </sheetData>

--- a/data/output/topik_per_lokasi.xlsx
+++ b/data/output/topik_per_lokasi.xlsx
@@ -455,19 +455,19 @@
         </is>
       </c>
       <c r="B2" t="n">
-        <v>45</v>
+        <v>44</v>
       </c>
       <c r="C2" t="n">
-        <v>13</v>
+        <v>6</v>
       </c>
       <c r="D2" t="n">
-        <v>6</v>
+        <v>5</v>
       </c>
       <c r="E2" t="n">
-        <v>27</v>
+        <v>37</v>
       </c>
       <c r="F2" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
     </row>
     <row r="3">
@@ -477,19 +477,19 @@
         </is>
       </c>
       <c r="B3" t="n">
-        <v>187</v>
+        <v>197</v>
       </c>
       <c r="C3" t="n">
-        <v>117</v>
+        <v>30</v>
       </c>
       <c r="D3" t="n">
-        <v>19</v>
+        <v>20</v>
       </c>
       <c r="E3" t="n">
-        <v>150</v>
+        <v>242</v>
       </c>
       <c r="F3" t="n">
-        <v>25</v>
+        <v>9</v>
       </c>
     </row>
     <row r="4">
@@ -502,10 +502,10 @@
         <v>1</v>
       </c>
       <c r="C4" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="D4" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="E4" t="n">
         <v>0</v>
@@ -521,13 +521,13 @@
         </is>
       </c>
       <c r="B5" t="n">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="C5" t="n">
         <v>0</v>
       </c>
       <c r="D5" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="E5" t="n">
         <v>0</v>
@@ -543,16 +543,16 @@
         </is>
       </c>
       <c r="B6" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="C6" t="n">
-        <v>7</v>
+        <v>2</v>
       </c>
       <c r="D6" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="E6" t="n">
-        <v>9</v>
+        <v>14</v>
       </c>
       <c r="F6" t="n">
         <v>3</v>
@@ -568,10 +568,10 @@
         <v>0</v>
       </c>
       <c r="C7" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="D7" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="E7" t="n">
         <v>0</v>
@@ -590,13 +590,13 @@
         <v>1</v>
       </c>
       <c r="C8" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="D8" t="n">
         <v>0</v>
       </c>
       <c r="E8" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="F8" t="n">
         <v>0</v>
@@ -609,19 +609,19 @@
         </is>
       </c>
       <c r="B9" t="n">
-        <v>4</v>
+        <v>124</v>
       </c>
       <c r="C9" t="n">
-        <v>67</v>
+        <v>56</v>
       </c>
       <c r="D9" t="n">
-        <v>24</v>
+        <v>35</v>
       </c>
       <c r="E9" t="n">
-        <v>61</v>
+        <v>118</v>
       </c>
       <c r="F9" t="n">
-        <v>45</v>
+        <v>26</v>
       </c>
     </row>
     <row r="10">
@@ -631,19 +631,19 @@
         </is>
       </c>
       <c r="B10" t="n">
-        <v>226</v>
+        <v>231</v>
       </c>
       <c r="C10" t="n">
-        <v>97</v>
+        <v>107</v>
       </c>
       <c r="D10" t="n">
         <v>28</v>
       </c>
       <c r="E10" t="n">
-        <v>137</v>
+        <v>146</v>
       </c>
       <c r="F10" t="n">
-        <v>32</v>
+        <v>8</v>
       </c>
     </row>
     <row r="11">
@@ -653,19 +653,19 @@
         </is>
       </c>
       <c r="B11" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="C11" t="n">
         <v>8</v>
       </c>
       <c r="D11" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="E11" t="n">
-        <v>25</v>
+        <v>29</v>
       </c>
       <c r="F11" t="n">
-        <v>5</v>
+        <v>1</v>
       </c>
     </row>
     <row r="12">
@@ -678,16 +678,16 @@
         <v>3</v>
       </c>
       <c r="C12" t="n">
-        <v>49</v>
+        <v>33</v>
       </c>
       <c r="D12" t="n">
-        <v>28</v>
+        <v>8</v>
       </c>
       <c r="E12" t="n">
-        <v>153</v>
+        <v>188</v>
       </c>
       <c r="F12" t="n">
-        <v>7</v>
+        <v>8</v>
       </c>
     </row>
     <row r="13">
@@ -697,19 +697,19 @@
         </is>
       </c>
       <c r="B13" t="n">
-        <v>144</v>
+        <v>145</v>
       </c>
       <c r="C13" t="n">
-        <v>33</v>
+        <v>16</v>
       </c>
       <c r="D13" t="n">
-        <v>5</v>
+        <v>9</v>
       </c>
       <c r="E13" t="n">
-        <v>143</v>
+        <v>158</v>
       </c>
       <c r="F13" t="n">
-        <v>6</v>
+        <v>3</v>
       </c>
     </row>
     <row r="14">
@@ -744,16 +744,16 @@
         <v>5</v>
       </c>
       <c r="C15" t="n">
-        <v>30</v>
+        <v>9</v>
       </c>
       <c r="D15" t="n">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="E15" t="n">
-        <v>127</v>
+        <v>148</v>
       </c>
       <c r="F15" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
     </row>
     <row r="16">
@@ -766,13 +766,13 @@
         <v>6</v>
       </c>
       <c r="C16" t="n">
-        <v>50</v>
+        <v>27</v>
       </c>
       <c r="D16" t="n">
-        <v>6</v>
+        <v>2</v>
       </c>
       <c r="E16" t="n">
-        <v>131</v>
+        <v>158</v>
       </c>
       <c r="F16" t="n">
         <v>13</v>
@@ -788,7 +788,7 @@
         <v>3</v>
       </c>
       <c r="C17" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="D17" t="n">
         <v>0</v>
@@ -797,7 +797,7 @@
         <v>3</v>
       </c>
       <c r="F17" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
     </row>
     <row r="18">
@@ -810,16 +810,16 @@
         <v>5</v>
       </c>
       <c r="C18" t="n">
-        <v>43</v>
+        <v>18</v>
       </c>
       <c r="D18" t="n">
-        <v>7</v>
+        <v>3</v>
       </c>
       <c r="E18" t="n">
-        <v>154</v>
+        <v>184</v>
       </c>
       <c r="F18" t="n">
-        <v>6</v>
+        <v>5</v>
       </c>
     </row>
     <row r="19">
@@ -829,19 +829,19 @@
         </is>
       </c>
       <c r="B19" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="C19" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="D19" t="n">
         <v>0</v>
       </c>
       <c r="E19" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="F19" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
     </row>
     <row r="20">
@@ -851,19 +851,19 @@
         </is>
       </c>
       <c r="B20" t="n">
-        <v>110</v>
+        <v>115</v>
       </c>
       <c r="C20" t="n">
-        <v>29</v>
+        <v>36</v>
       </c>
       <c r="D20" t="n">
-        <v>17</v>
+        <v>8</v>
       </c>
       <c r="E20" t="n">
-        <v>79</v>
+        <v>89</v>
       </c>
       <c r="F20" t="n">
-        <v>18</v>
+        <v>5</v>
       </c>
     </row>
     <row r="21">
@@ -873,19 +873,19 @@
         </is>
       </c>
       <c r="B21" t="n">
-        <v>209</v>
+        <v>212</v>
       </c>
       <c r="C21" t="n">
-        <v>73</v>
+        <v>31</v>
       </c>
       <c r="D21" t="n">
-        <v>23</v>
+        <v>14</v>
       </c>
       <c r="E21" t="n">
-        <v>152</v>
+        <v>203</v>
       </c>
       <c r="F21" t="n">
-        <v>17</v>
+        <v>14</v>
       </c>
     </row>
     <row r="22">
@@ -901,13 +901,13 @@
         <v>8</v>
       </c>
       <c r="D22" t="n">
-        <v>3</v>
+        <v>0</v>
       </c>
       <c r="E22" t="n">
-        <v>17</v>
+        <v>22</v>
       </c>
       <c r="F22" t="n">
-        <v>3</v>
+        <v>1</v>
       </c>
     </row>
     <row r="23">
@@ -917,10 +917,10 @@
         </is>
       </c>
       <c r="B23" t="n">
-        <v>4</v>
+        <v>8</v>
       </c>
       <c r="C23" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="D23" t="n">
         <v>0</v>
@@ -939,19 +939,19 @@
         </is>
       </c>
       <c r="B24" t="n">
-        <v>7</v>
+        <v>6</v>
       </c>
       <c r="C24" t="n">
-        <v>51</v>
+        <v>37</v>
       </c>
       <c r="D24" t="n">
-        <v>16</v>
+        <v>5</v>
       </c>
       <c r="E24" t="n">
-        <v>87</v>
+        <v>110</v>
       </c>
       <c r="F24" t="n">
-        <v>11</v>
+        <v>14</v>
       </c>
     </row>
     <row r="25">
@@ -964,16 +964,16 @@
         <v>3</v>
       </c>
       <c r="C25" t="n">
-        <v>0</v>
+        <v>3</v>
       </c>
       <c r="D25" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="E25" t="n">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="F25" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
     </row>
     <row r="26">
@@ -986,16 +986,16 @@
         <v>3</v>
       </c>
       <c r="C26" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="D26" t="n">
         <v>0</v>
       </c>
       <c r="E26" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="F26" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
     </row>
     <row r="27">
@@ -1005,19 +1005,19 @@
         </is>
       </c>
       <c r="B27" t="n">
-        <v>39</v>
+        <v>42</v>
       </c>
       <c r="C27" t="n">
-        <v>26</v>
+        <v>16</v>
       </c>
       <c r="D27" t="n">
-        <v>7</v>
+        <v>1</v>
       </c>
       <c r="E27" t="n">
-        <v>19</v>
+        <v>35</v>
       </c>
       <c r="F27" t="n">
-        <v>7</v>
+        <v>5</v>
       </c>
     </row>
     <row r="28">
@@ -1030,16 +1030,16 @@
         <v>5</v>
       </c>
       <c r="C28" t="n">
-        <v>4</v>
+        <v>1</v>
       </c>
       <c r="D28" t="n">
         <v>0</v>
       </c>
       <c r="E28" t="n">
-        <v>3</v>
+        <v>7</v>
       </c>
       <c r="F28" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
     </row>
     <row r="29">
@@ -1049,19 +1049,19 @@
         </is>
       </c>
       <c r="B29" t="n">
-        <v>85</v>
+        <v>86</v>
       </c>
       <c r="C29" t="n">
-        <v>42</v>
+        <v>27</v>
       </c>
       <c r="D29" t="n">
-        <v>18</v>
+        <v>14</v>
       </c>
       <c r="E29" t="n">
-        <v>51</v>
+        <v>70</v>
       </c>
       <c r="F29" t="n">
-        <v>5</v>
+        <v>4</v>
       </c>
     </row>
     <row r="30">
@@ -1074,13 +1074,13 @@
         <v>3</v>
       </c>
       <c r="C30" t="n">
-        <v>4</v>
+        <v>2</v>
       </c>
       <c r="D30" t="n">
         <v>0</v>
       </c>
       <c r="E30" t="n">
-        <v>7</v>
+        <v>9</v>
       </c>
       <c r="F30" t="n">
         <v>0</v>
@@ -1096,16 +1096,16 @@
         <v>22</v>
       </c>
       <c r="C31" t="n">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="D31" t="n">
-        <v>3</v>
+        <v>0</v>
       </c>
       <c r="E31" t="n">
         <v>13</v>
       </c>
       <c r="F31" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
     </row>
     <row r="32">
@@ -1124,10 +1124,10 @@
         <v>2</v>
       </c>
       <c r="E32" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="F32" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
     </row>
     <row r="33">
@@ -1137,19 +1137,19 @@
         </is>
       </c>
       <c r="B33" t="n">
+        <v>4</v>
+      </c>
+      <c r="C33" t="n">
         <v>6</v>
       </c>
-      <c r="C33" t="n">
-        <v>16</v>
-      </c>
       <c r="D33" t="n">
-        <v>4</v>
+        <v>7</v>
       </c>
       <c r="E33" t="n">
-        <v>36</v>
+        <v>46</v>
       </c>
       <c r="F33" t="n">
-        <v>7</v>
+        <v>6</v>
       </c>
     </row>
     <row r="34">
@@ -1159,19 +1159,19 @@
         </is>
       </c>
       <c r="B34" t="n">
-        <v>97</v>
+        <v>101</v>
       </c>
       <c r="C34" t="n">
-        <v>32</v>
+        <v>22</v>
       </c>
       <c r="D34" t="n">
-        <v>22</v>
+        <v>6</v>
       </c>
       <c r="E34" t="n">
-        <v>80</v>
+        <v>105</v>
       </c>
       <c r="F34" t="n">
-        <v>8</v>
+        <v>7</v>
       </c>
     </row>
     <row r="35">
@@ -1184,13 +1184,13 @@
         <v>15</v>
       </c>
       <c r="C35" t="n">
-        <v>3</v>
+        <v>0</v>
       </c>
       <c r="D35" t="n">
         <v>0</v>
       </c>
       <c r="E35" t="n">
-        <v>12</v>
+        <v>15</v>
       </c>
       <c r="F35" t="n">
         <v>1</v>

--- a/data/output/topik_per_lokasi.xlsx
+++ b/data/output/topik_per_lokasi.xlsx
@@ -458,13 +458,13 @@
         <v>44</v>
       </c>
       <c r="C2" t="n">
-        <v>6</v>
+        <v>5</v>
       </c>
       <c r="D2" t="n">
         <v>5</v>
       </c>
       <c r="E2" t="n">
-        <v>37</v>
+        <v>38</v>
       </c>
       <c r="F2" t="n">
         <v>2</v>
@@ -477,13 +477,13 @@
         </is>
       </c>
       <c r="B3" t="n">
-        <v>197</v>
+        <v>189</v>
       </c>
       <c r="C3" t="n">
         <v>30</v>
       </c>
       <c r="D3" t="n">
-        <v>20</v>
+        <v>28</v>
       </c>
       <c r="E3" t="n">
         <v>242</v>
@@ -618,10 +618,10 @@
         <v>35</v>
       </c>
       <c r="E9" t="n">
-        <v>118</v>
+        <v>117</v>
       </c>
       <c r="F9" t="n">
-        <v>26</v>
+        <v>27</v>
       </c>
     </row>
     <row r="10">
@@ -634,13 +634,13 @@
         <v>231</v>
       </c>
       <c r="C10" t="n">
-        <v>107</v>
+        <v>104</v>
       </c>
       <c r="D10" t="n">
         <v>28</v>
       </c>
       <c r="E10" t="n">
-        <v>146</v>
+        <v>149</v>
       </c>
       <c r="F10" t="n">
         <v>8</v>
@@ -678,16 +678,16 @@
         <v>3</v>
       </c>
       <c r="C12" t="n">
-        <v>33</v>
+        <v>31</v>
       </c>
       <c r="D12" t="n">
         <v>8</v>
       </c>
       <c r="E12" t="n">
-        <v>188</v>
+        <v>189</v>
       </c>
       <c r="F12" t="n">
-        <v>8</v>
+        <v>9</v>
       </c>
     </row>
     <row r="13">
@@ -700,13 +700,13 @@
         <v>145</v>
       </c>
       <c r="C13" t="n">
-        <v>16</v>
+        <v>15</v>
       </c>
       <c r="D13" t="n">
         <v>9</v>
       </c>
       <c r="E13" t="n">
-        <v>158</v>
+        <v>159</v>
       </c>
       <c r="F13" t="n">
         <v>3</v>
@@ -719,7 +719,7 @@
         </is>
       </c>
       <c r="B14" t="n">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="C14" t="n">
         <v>0</v>
@@ -744,13 +744,13 @@
         <v>5</v>
       </c>
       <c r="C15" t="n">
-        <v>9</v>
+        <v>7</v>
       </c>
       <c r="D15" t="n">
         <v>1</v>
       </c>
       <c r="E15" t="n">
-        <v>148</v>
+        <v>150</v>
       </c>
       <c r="F15" t="n">
         <v>2</v>
@@ -810,13 +810,13 @@
         <v>5</v>
       </c>
       <c r="C18" t="n">
-        <v>18</v>
+        <v>19</v>
       </c>
       <c r="D18" t="n">
         <v>3</v>
       </c>
       <c r="E18" t="n">
-        <v>184</v>
+        <v>183</v>
       </c>
       <c r="F18" t="n">
         <v>5</v>
@@ -854,13 +854,13 @@
         <v>115</v>
       </c>
       <c r="C20" t="n">
-        <v>36</v>
+        <v>35</v>
       </c>
       <c r="D20" t="n">
         <v>8</v>
       </c>
       <c r="E20" t="n">
-        <v>89</v>
+        <v>90</v>
       </c>
       <c r="F20" t="n">
         <v>5</v>
@@ -876,7 +876,7 @@
         <v>212</v>
       </c>
       <c r="C21" t="n">
-        <v>31</v>
+        <v>30</v>
       </c>
       <c r="D21" t="n">
         <v>14</v>
@@ -885,7 +885,7 @@
         <v>203</v>
       </c>
       <c r="F21" t="n">
-        <v>14</v>
+        <v>15</v>
       </c>
     </row>
     <row r="22">
@@ -923,13 +923,13 @@
         <v>2</v>
       </c>
       <c r="D23" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="E23" t="n">
         <v>4</v>
       </c>
       <c r="F23" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
     </row>
     <row r="24">
@@ -942,16 +942,16 @@
         <v>6</v>
       </c>
       <c r="C24" t="n">
-        <v>37</v>
+        <v>35</v>
       </c>
       <c r="D24" t="n">
         <v>5</v>
       </c>
       <c r="E24" t="n">
-        <v>110</v>
+        <v>111</v>
       </c>
       <c r="F24" t="n">
-        <v>14</v>
+        <v>15</v>
       </c>
     </row>
     <row r="25">
@@ -1008,7 +1008,7 @@
         <v>42</v>
       </c>
       <c r="C27" t="n">
-        <v>16</v>
+        <v>17</v>
       </c>
       <c r="D27" t="n">
         <v>1</v>
@@ -1017,7 +1017,7 @@
         <v>35</v>
       </c>
       <c r="F27" t="n">
-        <v>5</v>
+        <v>4</v>
       </c>
     </row>
     <row r="28">
@@ -1096,13 +1096,13 @@
         <v>22</v>
       </c>
       <c r="C31" t="n">
-        <v>6</v>
+        <v>5</v>
       </c>
       <c r="D31" t="n">
         <v>0</v>
       </c>
       <c r="E31" t="n">
-        <v>13</v>
+        <v>14</v>
       </c>
       <c r="F31" t="n">
         <v>2</v>
@@ -1140,13 +1140,13 @@
         <v>4</v>
       </c>
       <c r="C33" t="n">
-        <v>6</v>
+        <v>5</v>
       </c>
       <c r="D33" t="n">
         <v>7</v>
       </c>
       <c r="E33" t="n">
-        <v>46</v>
+        <v>47</v>
       </c>
       <c r="F33" t="n">
         <v>6</v>
@@ -1159,10 +1159,10 @@
         </is>
       </c>
       <c r="B34" t="n">
-        <v>101</v>
+        <v>100</v>
       </c>
       <c r="C34" t="n">
-        <v>22</v>
+        <v>23</v>
       </c>
       <c r="D34" t="n">
         <v>6</v>

--- a/data/output/topik_per_lokasi.xlsx
+++ b/data/output/topik_per_lokasi.xlsx
@@ -455,19 +455,19 @@
         </is>
       </c>
       <c r="B2" t="n">
-        <v>44</v>
+        <v>45</v>
       </c>
       <c r="C2" t="n">
-        <v>5</v>
+        <v>15</v>
       </c>
       <c r="D2" t="n">
-        <v>5</v>
+        <v>3</v>
       </c>
       <c r="E2" t="n">
-        <v>38</v>
+        <v>16</v>
       </c>
       <c r="F2" t="n">
-        <v>2</v>
+        <v>15</v>
       </c>
     </row>
     <row r="3">
@@ -477,19 +477,19 @@
         </is>
       </c>
       <c r="B3" t="n">
-        <v>189</v>
+        <v>182</v>
       </c>
       <c r="C3" t="n">
-        <v>30</v>
+        <v>41</v>
       </c>
       <c r="D3" t="n">
-        <v>28</v>
+        <v>35</v>
       </c>
       <c r="E3" t="n">
-        <v>242</v>
+        <v>126</v>
       </c>
       <c r="F3" t="n">
-        <v>9</v>
+        <v>114</v>
       </c>
     </row>
     <row r="4">
@@ -502,7 +502,7 @@
         <v>1</v>
       </c>
       <c r="C4" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="D4" t="n">
         <v>0</v>
@@ -511,7 +511,7 @@
         <v>0</v>
       </c>
       <c r="F4" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
     </row>
     <row r="5">
@@ -521,13 +521,13 @@
         </is>
       </c>
       <c r="B5" t="n">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="C5" t="n">
         <v>0</v>
       </c>
       <c r="D5" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="E5" t="n">
         <v>0</v>
@@ -543,19 +543,19 @@
         </is>
       </c>
       <c r="B6" t="n">
-        <v>2</v>
+        <v>4</v>
       </c>
       <c r="C6" t="n">
-        <v>2</v>
+        <v>8</v>
       </c>
       <c r="D6" t="n">
         <v>3</v>
       </c>
       <c r="E6" t="n">
-        <v>14</v>
+        <v>8</v>
       </c>
       <c r="F6" t="n">
-        <v>3</v>
+        <v>1</v>
       </c>
     </row>
     <row r="7">
@@ -590,13 +590,13 @@
         <v>1</v>
       </c>
       <c r="C8" t="n">
-        <v>0</v>
+        <v>3</v>
       </c>
       <c r="D8" t="n">
         <v>0</v>
       </c>
       <c r="E8" t="n">
-        <v>3</v>
+        <v>0</v>
       </c>
       <c r="F8" t="n">
         <v>0</v>
@@ -609,19 +609,19 @@
         </is>
       </c>
       <c r="B9" t="n">
-        <v>124</v>
+        <v>136</v>
       </c>
       <c r="C9" t="n">
-        <v>56</v>
+        <v>94</v>
       </c>
       <c r="D9" t="n">
-        <v>35</v>
+        <v>28</v>
       </c>
       <c r="E9" t="n">
-        <v>117</v>
+        <v>37</v>
       </c>
       <c r="F9" t="n">
-        <v>27</v>
+        <v>64</v>
       </c>
     </row>
     <row r="10">
@@ -634,16 +634,16 @@
         <v>231</v>
       </c>
       <c r="C10" t="n">
-        <v>104</v>
+        <v>53</v>
       </c>
       <c r="D10" t="n">
-        <v>28</v>
+        <v>25</v>
       </c>
       <c r="E10" t="n">
-        <v>149</v>
+        <v>160</v>
       </c>
       <c r="F10" t="n">
-        <v>8</v>
+        <v>51</v>
       </c>
     </row>
     <row r="11">
@@ -656,16 +656,16 @@
         <v>2</v>
       </c>
       <c r="C11" t="n">
-        <v>8</v>
+        <v>17</v>
       </c>
       <c r="D11" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="E11" t="n">
-        <v>29</v>
+        <v>5</v>
       </c>
       <c r="F11" t="n">
-        <v>1</v>
+        <v>15</v>
       </c>
     </row>
     <row r="12">
@@ -678,16 +678,16 @@
         <v>3</v>
       </c>
       <c r="C12" t="n">
-        <v>31</v>
+        <v>115</v>
       </c>
       <c r="D12" t="n">
         <v>8</v>
       </c>
       <c r="E12" t="n">
-        <v>189</v>
+        <v>44</v>
       </c>
       <c r="F12" t="n">
-        <v>9</v>
+        <v>70</v>
       </c>
     </row>
     <row r="13">
@@ -697,19 +697,19 @@
         </is>
       </c>
       <c r="B13" t="n">
-        <v>145</v>
+        <v>147</v>
       </c>
       <c r="C13" t="n">
-        <v>15</v>
+        <v>92</v>
       </c>
       <c r="D13" t="n">
-        <v>9</v>
+        <v>8</v>
       </c>
       <c r="E13" t="n">
-        <v>159</v>
+        <v>28</v>
       </c>
       <c r="F13" t="n">
-        <v>3</v>
+        <v>56</v>
       </c>
     </row>
     <row r="14">
@@ -744,16 +744,16 @@
         <v>5</v>
       </c>
       <c r="C15" t="n">
-        <v>7</v>
+        <v>42</v>
       </c>
       <c r="D15" t="n">
-        <v>1</v>
+        <v>4</v>
       </c>
       <c r="E15" t="n">
-        <v>150</v>
+        <v>29</v>
       </c>
       <c r="F15" t="n">
-        <v>2</v>
+        <v>85</v>
       </c>
     </row>
     <row r="16">
@@ -763,19 +763,19 @@
         </is>
       </c>
       <c r="B16" t="n">
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="C16" t="n">
-        <v>27</v>
+        <v>79</v>
       </c>
       <c r="D16" t="n">
-        <v>2</v>
+        <v>8</v>
       </c>
       <c r="E16" t="n">
-        <v>158</v>
+        <v>51</v>
       </c>
       <c r="F16" t="n">
-        <v>13</v>
+        <v>61</v>
       </c>
     </row>
     <row r="17">
@@ -788,13 +788,13 @@
         <v>3</v>
       </c>
       <c r="C17" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="D17" t="n">
         <v>0</v>
       </c>
       <c r="E17" t="n">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="F17" t="n">
         <v>1</v>
@@ -810,16 +810,16 @@
         <v>5</v>
       </c>
       <c r="C18" t="n">
-        <v>19</v>
+        <v>71</v>
       </c>
       <c r="D18" t="n">
         <v>3</v>
       </c>
       <c r="E18" t="n">
-        <v>183</v>
+        <v>46</v>
       </c>
       <c r="F18" t="n">
-        <v>5</v>
+        <v>90</v>
       </c>
     </row>
     <row r="19">
@@ -832,16 +832,16 @@
         <v>2</v>
       </c>
       <c r="C19" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="D19" t="n">
         <v>0</v>
       </c>
       <c r="E19" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="F19" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
     </row>
     <row r="20">
@@ -851,19 +851,19 @@
         </is>
       </c>
       <c r="B20" t="n">
-        <v>115</v>
+        <v>116</v>
       </c>
       <c r="C20" t="n">
-        <v>35</v>
+        <v>75</v>
       </c>
       <c r="D20" t="n">
-        <v>8</v>
+        <v>14</v>
       </c>
       <c r="E20" t="n">
-        <v>90</v>
+        <v>24</v>
       </c>
       <c r="F20" t="n">
-        <v>5</v>
+        <v>24</v>
       </c>
     </row>
     <row r="21">
@@ -873,19 +873,19 @@
         </is>
       </c>
       <c r="B21" t="n">
-        <v>212</v>
+        <v>210</v>
       </c>
       <c r="C21" t="n">
-        <v>30</v>
+        <v>108</v>
       </c>
       <c r="D21" t="n">
-        <v>14</v>
+        <v>17</v>
       </c>
       <c r="E21" t="n">
-        <v>203</v>
+        <v>58</v>
       </c>
       <c r="F21" t="n">
-        <v>15</v>
+        <v>81</v>
       </c>
     </row>
     <row r="22">
@@ -898,16 +898,16 @@
         <v>5</v>
       </c>
       <c r="C22" t="n">
-        <v>8</v>
+        <v>18</v>
       </c>
       <c r="D22" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="E22" t="n">
-        <v>22</v>
+        <v>5</v>
       </c>
       <c r="F22" t="n">
-        <v>1</v>
+        <v>7</v>
       </c>
     </row>
     <row r="23">
@@ -917,16 +917,16 @@
         </is>
       </c>
       <c r="B23" t="n">
-        <v>8</v>
+        <v>7</v>
       </c>
       <c r="C23" t="n">
-        <v>2</v>
+        <v>6</v>
       </c>
       <c r="D23" t="n">
         <v>1</v>
       </c>
       <c r="E23" t="n">
-        <v>4</v>
+        <v>1</v>
       </c>
       <c r="F23" t="n">
         <v>0</v>
@@ -942,16 +942,16 @@
         <v>6</v>
       </c>
       <c r="C24" t="n">
-        <v>35</v>
+        <v>75</v>
       </c>
       <c r="D24" t="n">
-        <v>5</v>
+        <v>15</v>
       </c>
       <c r="E24" t="n">
-        <v>111</v>
+        <v>47</v>
       </c>
       <c r="F24" t="n">
-        <v>15</v>
+        <v>29</v>
       </c>
     </row>
     <row r="25">
@@ -970,10 +970,10 @@
         <v>0</v>
       </c>
       <c r="E25" t="n">
+        <v>0</v>
+      </c>
+      <c r="F25" t="n">
         <v>3</v>
-      </c>
-      <c r="F25" t="n">
-        <v>0</v>
       </c>
     </row>
     <row r="26">
@@ -983,19 +983,19 @@
         </is>
       </c>
       <c r="B26" t="n">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="C26" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="D26" t="n">
         <v>0</v>
       </c>
       <c r="E26" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="F26" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
     </row>
     <row r="27">
@@ -1005,19 +1005,19 @@
         </is>
       </c>
       <c r="B27" t="n">
-        <v>42</v>
+        <v>44</v>
       </c>
       <c r="C27" t="n">
-        <v>17</v>
+        <v>28</v>
       </c>
       <c r="D27" t="n">
-        <v>1</v>
+        <v>7</v>
       </c>
       <c r="E27" t="n">
-        <v>35</v>
+        <v>13</v>
       </c>
       <c r="F27" t="n">
-        <v>4</v>
+        <v>7</v>
       </c>
     </row>
     <row r="28">
@@ -1036,10 +1036,10 @@
         <v>0</v>
       </c>
       <c r="E28" t="n">
-        <v>7</v>
+        <v>6</v>
       </c>
       <c r="F28" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
     </row>
     <row r="29">
@@ -1049,19 +1049,19 @@
         </is>
       </c>
       <c r="B29" t="n">
-        <v>86</v>
+        <v>91</v>
       </c>
       <c r="C29" t="n">
-        <v>27</v>
+        <v>40</v>
       </c>
       <c r="D29" t="n">
-        <v>14</v>
+        <v>11</v>
       </c>
       <c r="E29" t="n">
-        <v>70</v>
+        <v>48</v>
       </c>
       <c r="F29" t="n">
-        <v>4</v>
+        <v>11</v>
       </c>
     </row>
     <row r="30">
@@ -1071,19 +1071,19 @@
         </is>
       </c>
       <c r="B30" t="n">
+        <v>5</v>
+      </c>
+      <c r="C30" t="n">
+        <v>1</v>
+      </c>
+      <c r="D30" t="n">
+        <v>1</v>
+      </c>
+      <c r="E30" t="n">
+        <v>6</v>
+      </c>
+      <c r="F30" t="n">
         <v>3</v>
-      </c>
-      <c r="C30" t="n">
-        <v>2</v>
-      </c>
-      <c r="D30" t="n">
-        <v>0</v>
-      </c>
-      <c r="E30" t="n">
-        <v>9</v>
-      </c>
-      <c r="F30" t="n">
-        <v>0</v>
       </c>
     </row>
     <row r="31">
@@ -1099,13 +1099,13 @@
         <v>5</v>
       </c>
       <c r="D31" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="E31" t="n">
-        <v>14</v>
+        <v>5</v>
       </c>
       <c r="F31" t="n">
-        <v>2</v>
+        <v>10</v>
       </c>
     </row>
     <row r="32">
@@ -1118,16 +1118,16 @@
         <v>4</v>
       </c>
       <c r="C32" t="n">
+        <v>2</v>
+      </c>
+      <c r="D32" t="n">
         <v>3</v>
       </c>
-      <c r="D32" t="n">
+      <c r="E32" t="n">
         <v>2</v>
       </c>
-      <c r="E32" t="n">
-        <v>3</v>
-      </c>
       <c r="F32" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
     </row>
     <row r="33">
@@ -1137,19 +1137,19 @@
         </is>
       </c>
       <c r="B33" t="n">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="C33" t="n">
-        <v>5</v>
+        <v>16</v>
       </c>
       <c r="D33" t="n">
-        <v>7</v>
+        <v>3</v>
       </c>
       <c r="E33" t="n">
-        <v>47</v>
+        <v>13</v>
       </c>
       <c r="F33" t="n">
-        <v>6</v>
+        <v>32</v>
       </c>
     </row>
     <row r="34">
@@ -1159,19 +1159,19 @@
         </is>
       </c>
       <c r="B34" t="n">
-        <v>100</v>
+        <v>101</v>
       </c>
       <c r="C34" t="n">
-        <v>23</v>
+        <v>53</v>
       </c>
       <c r="D34" t="n">
-        <v>6</v>
+        <v>18</v>
       </c>
       <c r="E34" t="n">
-        <v>105</v>
+        <v>31</v>
       </c>
       <c r="F34" t="n">
-        <v>7</v>
+        <v>38</v>
       </c>
     </row>
     <row r="35">
@@ -1184,16 +1184,16 @@
         <v>15</v>
       </c>
       <c r="C35" t="n">
-        <v>0</v>
+        <v>4</v>
       </c>
       <c r="D35" t="n">
         <v>0</v>
       </c>
       <c r="E35" t="n">
-        <v>15</v>
+        <v>4</v>
       </c>
       <c r="F35" t="n">
-        <v>1</v>
+        <v>8</v>
       </c>
     </row>
   </sheetData>

--- a/data/output/topik_per_lokasi.xlsx
+++ b/data/output/topik_per_lokasi.xlsx
@@ -455,19 +455,19 @@
         </is>
       </c>
       <c r="B2" t="n">
-        <v>45</v>
+        <v>41</v>
       </c>
       <c r="C2" t="n">
-        <v>15</v>
+        <v>6</v>
       </c>
       <c r="D2" t="n">
-        <v>3</v>
+        <v>39</v>
       </c>
       <c r="E2" t="n">
-        <v>16</v>
+        <v>4</v>
       </c>
       <c r="F2" t="n">
-        <v>15</v>
+        <v>6</v>
       </c>
     </row>
     <row r="3">
@@ -477,19 +477,19 @@
         </is>
       </c>
       <c r="B3" t="n">
-        <v>182</v>
+        <v>179</v>
       </c>
       <c r="C3" t="n">
-        <v>41</v>
+        <v>17</v>
       </c>
       <c r="D3" t="n">
-        <v>35</v>
+        <v>230</v>
       </c>
       <c r="E3" t="n">
-        <v>126</v>
+        <v>17</v>
       </c>
       <c r="F3" t="n">
-        <v>114</v>
+        <v>55</v>
       </c>
     </row>
     <row r="4">
@@ -502,10 +502,10 @@
         <v>1</v>
       </c>
       <c r="C4" t="n">
+        <v>0</v>
+      </c>
+      <c r="D4" t="n">
         <v>2</v>
-      </c>
-      <c r="D4" t="n">
-        <v>0</v>
       </c>
       <c r="E4" t="n">
         <v>0</v>
@@ -543,16 +543,16 @@
         </is>
       </c>
       <c r="B6" t="n">
-        <v>4</v>
+        <v>19</v>
       </c>
       <c r="C6" t="n">
-        <v>8</v>
+        <v>5</v>
       </c>
       <c r="D6" t="n">
-        <v>3</v>
+        <v>14</v>
       </c>
       <c r="E6" t="n">
-        <v>8</v>
+        <v>6</v>
       </c>
       <c r="F6" t="n">
         <v>1</v>
@@ -568,10 +568,10 @@
         <v>0</v>
       </c>
       <c r="C7" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="D7" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="E7" t="n">
         <v>0</v>
@@ -587,16 +587,16 @@
         </is>
       </c>
       <c r="B8" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="C8" t="n">
+        <v>0</v>
+      </c>
+      <c r="D8" t="n">
         <v>3</v>
       </c>
-      <c r="D8" t="n">
-        <v>0</v>
-      </c>
       <c r="E8" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="F8" t="n">
         <v>0</v>
@@ -609,19 +609,19 @@
         </is>
       </c>
       <c r="B9" t="n">
-        <v>136</v>
+        <v>84</v>
       </c>
       <c r="C9" t="n">
-        <v>94</v>
+        <v>32</v>
       </c>
       <c r="D9" t="n">
-        <v>28</v>
+        <v>89</v>
       </c>
       <c r="E9" t="n">
-        <v>37</v>
+        <v>62</v>
       </c>
       <c r="F9" t="n">
-        <v>64</v>
+        <v>92</v>
       </c>
     </row>
     <row r="10">
@@ -631,19 +631,19 @@
         </is>
       </c>
       <c r="B10" t="n">
-        <v>231</v>
+        <v>218</v>
       </c>
       <c r="C10" t="n">
-        <v>53</v>
+        <v>23</v>
       </c>
       <c r="D10" t="n">
-        <v>25</v>
+        <v>216</v>
       </c>
       <c r="E10" t="n">
-        <v>160</v>
+        <v>20</v>
       </c>
       <c r="F10" t="n">
-        <v>51</v>
+        <v>43</v>
       </c>
     </row>
     <row r="11">
@@ -656,16 +656,16 @@
         <v>2</v>
       </c>
       <c r="C11" t="n">
-        <v>17</v>
+        <v>4</v>
       </c>
       <c r="D11" t="n">
+        <v>33</v>
+      </c>
+      <c r="E11" t="n">
+        <v>0</v>
+      </c>
+      <c r="F11" t="n">
         <v>3</v>
-      </c>
-      <c r="E11" t="n">
-        <v>5</v>
-      </c>
-      <c r="F11" t="n">
-        <v>15</v>
       </c>
     </row>
     <row r="12">
@@ -678,16 +678,16 @@
         <v>3</v>
       </c>
       <c r="C12" t="n">
-        <v>115</v>
+        <v>14</v>
       </c>
       <c r="D12" t="n">
-        <v>8</v>
+        <v>211</v>
       </c>
       <c r="E12" t="n">
-        <v>44</v>
+        <v>3</v>
       </c>
       <c r="F12" t="n">
-        <v>70</v>
+        <v>9</v>
       </c>
     </row>
     <row r="13">
@@ -697,19 +697,19 @@
         </is>
       </c>
       <c r="B13" t="n">
-        <v>147</v>
+        <v>142</v>
       </c>
       <c r="C13" t="n">
-        <v>92</v>
+        <v>5</v>
       </c>
       <c r="D13" t="n">
+        <v>165</v>
+      </c>
+      <c r="E13" t="n">
+        <v>11</v>
+      </c>
+      <c r="F13" t="n">
         <v>8</v>
-      </c>
-      <c r="E13" t="n">
-        <v>28</v>
-      </c>
-      <c r="F13" t="n">
-        <v>56</v>
       </c>
     </row>
     <row r="14">
@@ -719,16 +719,16 @@
         </is>
       </c>
       <c r="B14" t="n">
-        <v>6</v>
+        <v>9</v>
       </c>
       <c r="C14" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="D14" t="n">
         <v>0</v>
       </c>
       <c r="E14" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="F14" t="n">
         <v>0</v>
@@ -744,16 +744,16 @@
         <v>5</v>
       </c>
       <c r="C15" t="n">
-        <v>42</v>
+        <v>1</v>
       </c>
       <c r="D15" t="n">
-        <v>4</v>
+        <v>158</v>
       </c>
       <c r="E15" t="n">
-        <v>29</v>
+        <v>0</v>
       </c>
       <c r="F15" t="n">
-        <v>85</v>
+        <v>1</v>
       </c>
     </row>
     <row r="16">
@@ -763,19 +763,19 @@
         </is>
       </c>
       <c r="B16" t="n">
-        <v>7</v>
+        <v>5</v>
       </c>
       <c r="C16" t="n">
-        <v>79</v>
+        <v>10</v>
       </c>
       <c r="D16" t="n">
-        <v>8</v>
+        <v>177</v>
       </c>
       <c r="E16" t="n">
-        <v>51</v>
+        <v>4</v>
       </c>
       <c r="F16" t="n">
-        <v>61</v>
+        <v>10</v>
       </c>
     </row>
     <row r="17">
@@ -788,16 +788,16 @@
         <v>3</v>
       </c>
       <c r="C17" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="D17" t="n">
-        <v>0</v>
+        <v>4</v>
       </c>
       <c r="E17" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="F17" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
     </row>
     <row r="18">
@@ -810,16 +810,16 @@
         <v>5</v>
       </c>
       <c r="C18" t="n">
-        <v>71</v>
+        <v>2</v>
       </c>
       <c r="D18" t="n">
-        <v>3</v>
+        <v>201</v>
       </c>
       <c r="E18" t="n">
-        <v>46</v>
+        <v>1</v>
       </c>
       <c r="F18" t="n">
-        <v>90</v>
+        <v>6</v>
       </c>
     </row>
     <row r="19">
@@ -832,16 +832,16 @@
         <v>2</v>
       </c>
       <c r="C19" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="D19" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="E19" t="n">
         <v>0</v>
       </c>
       <c r="F19" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
     </row>
     <row r="20">
@@ -851,19 +851,19 @@
         </is>
       </c>
       <c r="B20" t="n">
-        <v>116</v>
+        <v>110</v>
       </c>
       <c r="C20" t="n">
-        <v>75</v>
+        <v>15</v>
       </c>
       <c r="D20" t="n">
-        <v>14</v>
+        <v>113</v>
       </c>
       <c r="E20" t="n">
-        <v>24</v>
+        <v>8</v>
       </c>
       <c r="F20" t="n">
-        <v>24</v>
+        <v>7</v>
       </c>
     </row>
     <row r="21">
@@ -873,19 +873,19 @@
         </is>
       </c>
       <c r="B21" t="n">
-        <v>210</v>
+        <v>199</v>
       </c>
       <c r="C21" t="n">
-        <v>108</v>
+        <v>19</v>
       </c>
       <c r="D21" t="n">
-        <v>17</v>
+        <v>226</v>
       </c>
       <c r="E21" t="n">
-        <v>58</v>
+        <v>18</v>
       </c>
       <c r="F21" t="n">
-        <v>81</v>
+        <v>12</v>
       </c>
     </row>
     <row r="22">
@@ -895,19 +895,19 @@
         </is>
       </c>
       <c r="B22" t="n">
-        <v>5</v>
+        <v>25</v>
       </c>
       <c r="C22" t="n">
-        <v>18</v>
+        <v>4</v>
       </c>
       <c r="D22" t="n">
-        <v>1</v>
+        <v>25</v>
       </c>
       <c r="E22" t="n">
-        <v>5</v>
+        <v>3</v>
       </c>
       <c r="F22" t="n">
-        <v>7</v>
+        <v>2</v>
       </c>
     </row>
     <row r="23">
@@ -917,16 +917,16 @@
         </is>
       </c>
       <c r="B23" t="n">
-        <v>7</v>
+        <v>6</v>
       </c>
       <c r="C23" t="n">
-        <v>6</v>
+        <v>1</v>
       </c>
       <c r="D23" t="n">
-        <v>1</v>
+        <v>5</v>
       </c>
       <c r="E23" t="n">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="F23" t="n">
         <v>0</v>
@@ -942,16 +942,16 @@
         <v>6</v>
       </c>
       <c r="C24" t="n">
-        <v>75</v>
+        <v>13</v>
       </c>
       <c r="D24" t="n">
-        <v>15</v>
+        <v>136</v>
       </c>
       <c r="E24" t="n">
-        <v>47</v>
+        <v>6</v>
       </c>
       <c r="F24" t="n">
-        <v>29</v>
+        <v>11</v>
       </c>
     </row>
     <row r="25">
@@ -964,16 +964,16 @@
         <v>3</v>
       </c>
       <c r="C25" t="n">
-        <v>3</v>
+        <v>0</v>
       </c>
       <c r="D25" t="n">
-        <v>0</v>
+        <v>5</v>
       </c>
       <c r="E25" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="F25" t="n">
-        <v>3</v>
+        <v>0</v>
       </c>
     </row>
     <row r="26">
@@ -983,16 +983,16 @@
         </is>
       </c>
       <c r="B26" t="n">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="C26" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="D26" t="n">
-        <v>0</v>
+        <v>3</v>
       </c>
       <c r="E26" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="F26" t="n">
         <v>0</v>
@@ -1005,19 +1005,19 @@
         </is>
       </c>
       <c r="B27" t="n">
-        <v>44</v>
+        <v>38</v>
       </c>
       <c r="C27" t="n">
-        <v>28</v>
+        <v>5</v>
       </c>
       <c r="D27" t="n">
-        <v>7</v>
+        <v>40</v>
       </c>
       <c r="E27" t="n">
-        <v>13</v>
+        <v>11</v>
       </c>
       <c r="F27" t="n">
-        <v>7</v>
+        <v>5</v>
       </c>
     </row>
     <row r="28">
@@ -1027,16 +1027,16 @@
         </is>
       </c>
       <c r="B28" t="n">
+        <v>4</v>
+      </c>
+      <c r="C28" t="n">
+        <v>1</v>
+      </c>
+      <c r="D28" t="n">
         <v>5</v>
       </c>
-      <c r="C28" t="n">
-        <v>1</v>
-      </c>
-      <c r="D28" t="n">
-        <v>0</v>
-      </c>
       <c r="E28" t="n">
-        <v>6</v>
+        <v>2</v>
       </c>
       <c r="F28" t="n">
         <v>1</v>
@@ -1049,19 +1049,19 @@
         </is>
       </c>
       <c r="B29" t="n">
-        <v>91</v>
+        <v>86</v>
       </c>
       <c r="C29" t="n">
-        <v>40</v>
+        <v>11</v>
       </c>
       <c r="D29" t="n">
-        <v>11</v>
+        <v>89</v>
       </c>
       <c r="E29" t="n">
-        <v>48</v>
+        <v>6</v>
       </c>
       <c r="F29" t="n">
-        <v>11</v>
+        <v>9</v>
       </c>
     </row>
     <row r="30">
@@ -1071,19 +1071,19 @@
         </is>
       </c>
       <c r="B30" t="n">
-        <v>5</v>
+        <v>11</v>
       </c>
       <c r="C30" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="D30" t="n">
-        <v>1</v>
+        <v>10</v>
       </c>
       <c r="E30" t="n">
-        <v>6</v>
+        <v>0</v>
       </c>
       <c r="F30" t="n">
-        <v>3</v>
+        <v>1</v>
       </c>
     </row>
     <row r="31">
@@ -1093,19 +1093,19 @@
         </is>
       </c>
       <c r="B31" t="n">
-        <v>22</v>
+        <v>21</v>
       </c>
       <c r="C31" t="n">
-        <v>5</v>
+        <v>1</v>
       </c>
       <c r="D31" t="n">
-        <v>1</v>
+        <v>19</v>
       </c>
       <c r="E31" t="n">
-        <v>5</v>
+        <v>1</v>
       </c>
       <c r="F31" t="n">
-        <v>10</v>
+        <v>1</v>
       </c>
     </row>
     <row r="32">
@@ -1118,16 +1118,16 @@
         <v>4</v>
       </c>
       <c r="C32" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="D32" t="n">
-        <v>3</v>
+        <v>5</v>
       </c>
       <c r="E32" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="F32" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
     </row>
     <row r="33">
@@ -1140,16 +1140,16 @@
         <v>5</v>
       </c>
       <c r="C33" t="n">
-        <v>16</v>
+        <v>7</v>
       </c>
       <c r="D33" t="n">
-        <v>3</v>
+        <v>51</v>
       </c>
       <c r="E33" t="n">
-        <v>13</v>
+        <v>2</v>
       </c>
       <c r="F33" t="n">
-        <v>32</v>
+        <v>4</v>
       </c>
     </row>
     <row r="34">
@@ -1159,19 +1159,19 @@
         </is>
       </c>
       <c r="B34" t="n">
-        <v>101</v>
+        <v>96</v>
       </c>
       <c r="C34" t="n">
-        <v>53</v>
+        <v>15</v>
       </c>
       <c r="D34" t="n">
-        <v>18</v>
+        <v>114</v>
       </c>
       <c r="E34" t="n">
-        <v>31</v>
+        <v>8</v>
       </c>
       <c r="F34" t="n">
-        <v>38</v>
+        <v>8</v>
       </c>
     </row>
     <row r="35">
@@ -1181,19 +1181,19 @@
         </is>
       </c>
       <c r="B35" t="n">
-        <v>15</v>
+        <v>14</v>
       </c>
       <c r="C35" t="n">
-        <v>4</v>
+        <v>0</v>
       </c>
       <c r="D35" t="n">
-        <v>0</v>
+        <v>16</v>
       </c>
       <c r="E35" t="n">
-        <v>4</v>
+        <v>1</v>
       </c>
       <c r="F35" t="n">
-        <v>8</v>
+        <v>0</v>
       </c>
     </row>
   </sheetData>

--- a/data/output/topik_per_lokasi.xlsx
+++ b/data/output/topik_per_lokasi.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:F35"/>
+  <dimension ref="A1:F36"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -455,19 +455,19 @@
         </is>
       </c>
       <c r="B2" t="n">
-        <v>41</v>
+        <v>46</v>
       </c>
       <c r="C2" t="n">
-        <v>6</v>
+        <v>11</v>
       </c>
       <c r="D2" t="n">
-        <v>39</v>
+        <v>28</v>
       </c>
       <c r="E2" t="n">
-        <v>4</v>
+        <v>10</v>
       </c>
       <c r="F2" t="n">
-        <v>6</v>
+        <v>1</v>
       </c>
     </row>
     <row r="3">
@@ -477,19 +477,19 @@
         </is>
       </c>
       <c r="B3" t="n">
-        <v>179</v>
+        <v>178</v>
       </c>
       <c r="C3" t="n">
-        <v>17</v>
+        <v>31</v>
       </c>
       <c r="D3" t="n">
-        <v>230</v>
+        <v>195</v>
       </c>
       <c r="E3" t="n">
-        <v>17</v>
+        <v>67</v>
       </c>
       <c r="F3" t="n">
-        <v>55</v>
+        <v>27</v>
       </c>
     </row>
     <row r="4">
@@ -505,13 +505,13 @@
         <v>0</v>
       </c>
       <c r="D4" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="E4" t="n">
         <v>0</v>
       </c>
       <c r="F4" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
     </row>
     <row r="5">
@@ -543,16 +543,16 @@
         </is>
       </c>
       <c r="B6" t="n">
-        <v>19</v>
+        <v>24</v>
       </c>
       <c r="C6" t="n">
-        <v>5</v>
+        <v>9</v>
       </c>
       <c r="D6" t="n">
-        <v>14</v>
+        <v>8</v>
       </c>
       <c r="E6" t="n">
-        <v>6</v>
+        <v>3</v>
       </c>
       <c r="F6" t="n">
         <v>1</v>
@@ -587,16 +587,16 @@
         </is>
       </c>
       <c r="B8" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="C8" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="D8" t="n">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="E8" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="F8" t="n">
         <v>0</v>
@@ -609,19 +609,19 @@
         </is>
       </c>
       <c r="B9" t="n">
-        <v>84</v>
+        <v>126</v>
       </c>
       <c r="C9" t="n">
-        <v>32</v>
+        <v>55</v>
       </c>
       <c r="D9" t="n">
-        <v>89</v>
+        <v>72</v>
       </c>
       <c r="E9" t="n">
-        <v>62</v>
+        <v>78</v>
       </c>
       <c r="F9" t="n">
-        <v>92</v>
+        <v>28</v>
       </c>
     </row>
     <row r="10">
@@ -631,16 +631,16 @@
         </is>
       </c>
       <c r="B10" t="n">
-        <v>218</v>
+        <v>220</v>
       </c>
       <c r="C10" t="n">
-        <v>23</v>
+        <v>34</v>
       </c>
       <c r="D10" t="n">
-        <v>216</v>
+        <v>182</v>
       </c>
       <c r="E10" t="n">
-        <v>20</v>
+        <v>41</v>
       </c>
       <c r="F10" t="n">
         <v>43</v>
@@ -653,19 +653,19 @@
         </is>
       </c>
       <c r="B11" t="n">
+        <v>3</v>
+      </c>
+      <c r="C11" t="n">
+        <v>7</v>
+      </c>
+      <c r="D11" t="n">
+        <v>25</v>
+      </c>
+      <c r="E11" t="n">
+        <v>5</v>
+      </c>
+      <c r="F11" t="n">
         <v>2</v>
-      </c>
-      <c r="C11" t="n">
-        <v>4</v>
-      </c>
-      <c r="D11" t="n">
-        <v>33</v>
-      </c>
-      <c r="E11" t="n">
-        <v>0</v>
-      </c>
-      <c r="F11" t="n">
-        <v>3</v>
       </c>
     </row>
     <row r="12">
@@ -675,19 +675,19 @@
         </is>
       </c>
       <c r="B12" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="C12" t="n">
+        <v>42</v>
+      </c>
+      <c r="D12" t="n">
+        <v>161</v>
+      </c>
+      <c r="E12" t="n">
+        <v>21</v>
+      </c>
+      <c r="F12" t="n">
         <v>14</v>
-      </c>
-      <c r="D12" t="n">
-        <v>211</v>
-      </c>
-      <c r="E12" t="n">
-        <v>3</v>
-      </c>
-      <c r="F12" t="n">
-        <v>9</v>
       </c>
     </row>
     <row r="13">
@@ -697,19 +697,19 @@
         </is>
       </c>
       <c r="B13" t="n">
-        <v>142</v>
+        <v>146</v>
       </c>
       <c r="C13" t="n">
-        <v>5</v>
+        <v>46</v>
       </c>
       <c r="D13" t="n">
-        <v>165</v>
+        <v>117</v>
       </c>
       <c r="E13" t="n">
-        <v>11</v>
+        <v>16</v>
       </c>
       <c r="F13" t="n">
-        <v>8</v>
+        <v>6</v>
       </c>
     </row>
     <row r="14">
@@ -719,16 +719,16 @@
         </is>
       </c>
       <c r="B14" t="n">
-        <v>9</v>
+        <v>11</v>
       </c>
       <c r="C14" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="D14" t="n">
         <v>0</v>
       </c>
       <c r="E14" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="F14" t="n">
         <v>0</v>
@@ -744,16 +744,16 @@
         <v>5</v>
       </c>
       <c r="C15" t="n">
-        <v>1</v>
+        <v>32</v>
       </c>
       <c r="D15" t="n">
-        <v>158</v>
+        <v>122</v>
       </c>
       <c r="E15" t="n">
-        <v>0</v>
+        <v>4</v>
       </c>
       <c r="F15" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
     </row>
     <row r="16">
@@ -763,19 +763,19 @@
         </is>
       </c>
       <c r="B16" t="n">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="C16" t="n">
-        <v>10</v>
+        <v>54</v>
       </c>
       <c r="D16" t="n">
-        <v>177</v>
+        <v>119</v>
       </c>
       <c r="E16" t="n">
-        <v>4</v>
+        <v>17</v>
       </c>
       <c r="F16" t="n">
-        <v>10</v>
+        <v>12</v>
       </c>
     </row>
     <row r="17">
@@ -788,16 +788,16 @@
         <v>3</v>
       </c>
       <c r="C17" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="D17" t="n">
-        <v>4</v>
+        <v>1</v>
       </c>
       <c r="E17" t="n">
         <v>0</v>
       </c>
       <c r="F17" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
     </row>
     <row r="18">
@@ -807,19 +807,19 @@
         </is>
       </c>
       <c r="B18" t="n">
-        <v>5</v>
+        <v>147</v>
       </c>
       <c r="C18" t="n">
-        <v>2</v>
+        <v>43</v>
       </c>
       <c r="D18" t="n">
-        <v>201</v>
+        <v>155</v>
       </c>
       <c r="E18" t="n">
-        <v>1</v>
+        <v>14</v>
       </c>
       <c r="F18" t="n">
-        <v>6</v>
+        <v>11</v>
       </c>
     </row>
     <row r="19">
@@ -832,10 +832,10 @@
         <v>2</v>
       </c>
       <c r="C19" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="D19" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="E19" t="n">
         <v>0</v>
@@ -851,19 +851,19 @@
         </is>
       </c>
       <c r="B20" t="n">
-        <v>110</v>
+        <v>115</v>
       </c>
       <c r="C20" t="n">
-        <v>15</v>
+        <v>50</v>
       </c>
       <c r="D20" t="n">
-        <v>113</v>
+        <v>70</v>
       </c>
       <c r="E20" t="n">
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="F20" t="n">
-        <v>7</v>
+        <v>9</v>
       </c>
     </row>
     <row r="21">
@@ -873,19 +873,19 @@
         </is>
       </c>
       <c r="B21" t="n">
-        <v>199</v>
+        <v>211</v>
       </c>
       <c r="C21" t="n">
-        <v>19</v>
+        <v>91</v>
       </c>
       <c r="D21" t="n">
-        <v>226</v>
+        <v>136</v>
       </c>
       <c r="E21" t="n">
-        <v>18</v>
+        <v>21</v>
       </c>
       <c r="F21" t="n">
-        <v>12</v>
+        <v>15</v>
       </c>
     </row>
     <row r="22">
@@ -895,19 +895,19 @@
         </is>
       </c>
       <c r="B22" t="n">
-        <v>25</v>
+        <v>27</v>
       </c>
       <c r="C22" t="n">
         <v>4</v>
       </c>
       <c r="D22" t="n">
-        <v>25</v>
+        <v>19</v>
       </c>
       <c r="E22" t="n">
-        <v>3</v>
+        <v>5</v>
       </c>
       <c r="F22" t="n">
-        <v>2</v>
+        <v>4</v>
       </c>
     </row>
     <row r="23">
@@ -917,16 +917,16 @@
         </is>
       </c>
       <c r="B23" t="n">
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="C23" t="n">
-        <v>1</v>
+        <v>4</v>
       </c>
       <c r="D23" t="n">
-        <v>5</v>
+        <v>2</v>
       </c>
       <c r="E23" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="F23" t="n">
         <v>0</v>
@@ -942,16 +942,16 @@
         <v>6</v>
       </c>
       <c r="C24" t="n">
-        <v>13</v>
+        <v>54</v>
       </c>
       <c r="D24" t="n">
-        <v>136</v>
+        <v>86</v>
       </c>
       <c r="E24" t="n">
-        <v>6</v>
+        <v>14</v>
       </c>
       <c r="F24" t="n">
-        <v>11</v>
+        <v>12</v>
       </c>
     </row>
     <row r="25">
@@ -964,10 +964,10 @@
         <v>3</v>
       </c>
       <c r="C25" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="D25" t="n">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="E25" t="n">
         <v>1</v>
@@ -989,13 +989,13 @@
         <v>0</v>
       </c>
       <c r="D26" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="E26" t="n">
         <v>0</v>
       </c>
       <c r="F26" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
     </row>
     <row r="27">
@@ -1005,16 +1005,16 @@
         </is>
       </c>
       <c r="B27" t="n">
-        <v>38</v>
+        <v>43</v>
       </c>
       <c r="C27" t="n">
+        <v>17</v>
+      </c>
+      <c r="D27" t="n">
+        <v>29</v>
+      </c>
+      <c r="E27" t="n">
         <v>5</v>
-      </c>
-      <c r="D27" t="n">
-        <v>40</v>
-      </c>
-      <c r="E27" t="n">
-        <v>11</v>
       </c>
       <c r="F27" t="n">
         <v>5</v>
@@ -1027,19 +1027,19 @@
         </is>
       </c>
       <c r="B28" t="n">
+        <v>5</v>
+      </c>
+      <c r="C28" t="n">
+        <v>2</v>
+      </c>
+      <c r="D28" t="n">
         <v>4</v>
-      </c>
-      <c r="C28" t="n">
-        <v>1</v>
-      </c>
-      <c r="D28" t="n">
-        <v>5</v>
       </c>
       <c r="E28" t="n">
         <v>2</v>
       </c>
       <c r="F28" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
     </row>
     <row r="29">
@@ -1049,19 +1049,19 @@
         </is>
       </c>
       <c r="B29" t="n">
-        <v>86</v>
+        <v>91</v>
       </c>
       <c r="C29" t="n">
+        <v>25</v>
+      </c>
+      <c r="D29" t="n">
+        <v>59</v>
+      </c>
+      <c r="E29" t="n">
+        <v>15</v>
+      </c>
+      <c r="F29" t="n">
         <v>11</v>
-      </c>
-      <c r="D29" t="n">
-        <v>89</v>
-      </c>
-      <c r="E29" t="n">
-        <v>6</v>
-      </c>
-      <c r="F29" t="n">
-        <v>9</v>
       </c>
     </row>
     <row r="30">
@@ -1074,16 +1074,16 @@
         <v>11</v>
       </c>
       <c r="C30" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="D30" t="n">
-        <v>10</v>
+        <v>9</v>
       </c>
       <c r="E30" t="n">
         <v>0</v>
       </c>
       <c r="F30" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
     </row>
     <row r="31">
@@ -1096,10 +1096,10 @@
         <v>21</v>
       </c>
       <c r="C31" t="n">
-        <v>1</v>
+        <v>6</v>
       </c>
       <c r="D31" t="n">
-        <v>19</v>
+        <v>14</v>
       </c>
       <c r="E31" t="n">
         <v>1</v>
@@ -1118,81 +1118,103 @@
         <v>4</v>
       </c>
       <c r="C32" t="n">
-        <v>3</v>
+        <v>0</v>
       </c>
       <c r="D32" t="n">
+        <v>2</v>
+      </c>
+      <c r="E32" t="n">
         <v>5</v>
       </c>
-      <c r="E32" t="n">
-        <v>0</v>
-      </c>
       <c r="F32" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
     </row>
     <row r="33">
       <c r="A33" t="inlineStr">
         <is>
-          <t>Waterpark Citepus Pelabuhanratu</t>
+          <t>Taman Tenjo Resmi</t>
         </is>
       </c>
       <c r="B33" t="n">
-        <v>5</v>
+        <v>1</v>
       </c>
       <c r="C33" t="n">
-        <v>7</v>
+        <v>1</v>
       </c>
       <c r="D33" t="n">
-        <v>51</v>
+        <v>0</v>
       </c>
       <c r="E33" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="F33" t="n">
-        <v>4</v>
+        <v>0</v>
       </c>
     </row>
     <row r="34">
       <c r="A34" t="inlineStr">
         <is>
-          <t>Wisata Alam Pantai Sukawayana</t>
+          <t>Waterpark Citepus Pelabuhanratu</t>
         </is>
       </c>
       <c r="B34" t="n">
-        <v>96</v>
+        <v>6</v>
       </c>
       <c r="C34" t="n">
-        <v>15</v>
+        <v>7</v>
       </c>
       <c r="D34" t="n">
-        <v>114</v>
+        <v>38</v>
       </c>
       <c r="E34" t="n">
-        <v>8</v>
+        <v>11</v>
       </c>
       <c r="F34" t="n">
-        <v>8</v>
+        <v>7</v>
       </c>
     </row>
     <row r="35">
       <c r="A35" t="inlineStr">
         <is>
+          <t>Wisata Alam Pantai Sukawayana</t>
+        </is>
+      </c>
+      <c r="B35" t="n">
+        <v>97</v>
+      </c>
+      <c r="C35" t="n">
+        <v>35</v>
+      </c>
+      <c r="D35" t="n">
+        <v>83</v>
+      </c>
+      <c r="E35" t="n">
+        <v>19</v>
+      </c>
+      <c r="F35" t="n">
+        <v>7</v>
+      </c>
+    </row>
+    <row r="36">
+      <c r="A36" t="inlineStr">
+        <is>
           <t>i-Pe Beach Pelabuhanratu</t>
         </is>
       </c>
-      <c r="B35" t="n">
-        <v>14</v>
-      </c>
-      <c r="C35" t="n">
-        <v>0</v>
-      </c>
-      <c r="D35" t="n">
-        <v>16</v>
-      </c>
-      <c r="E35" t="n">
-        <v>1</v>
-      </c>
-      <c r="F35" t="n">
+      <c r="B36" t="n">
+        <v>15</v>
+      </c>
+      <c r="C36" t="n">
+        <v>6</v>
+      </c>
+      <c r="D36" t="n">
+        <v>9</v>
+      </c>
+      <c r="E36" t="n">
+        <v>1</v>
+      </c>
+      <c r="F36" t="n">
         <v>0</v>
       </c>
     </row>

--- a/data/output/topik_per_lokasi.xlsx
+++ b/data/output/topik_per_lokasi.xlsx
@@ -455,19 +455,19 @@
         </is>
       </c>
       <c r="B2" t="n">
-        <v>46</v>
+        <v>39</v>
       </c>
       <c r="C2" t="n">
-        <v>11</v>
+        <v>12</v>
       </c>
       <c r="D2" t="n">
-        <v>28</v>
+        <v>12</v>
       </c>
       <c r="E2" t="n">
-        <v>10</v>
+        <v>1</v>
       </c>
       <c r="F2" t="n">
-        <v>1</v>
+        <v>32</v>
       </c>
     </row>
     <row r="3">
@@ -477,19 +477,19 @@
         </is>
       </c>
       <c r="B3" t="n">
-        <v>178</v>
+        <v>69</v>
       </c>
       <c r="C3" t="n">
-        <v>31</v>
+        <v>123</v>
       </c>
       <c r="D3" t="n">
-        <v>195</v>
+        <v>152</v>
       </c>
       <c r="E3" t="n">
-        <v>67</v>
+        <v>35</v>
       </c>
       <c r="F3" t="n">
-        <v>27</v>
+        <v>119</v>
       </c>
     </row>
     <row r="4">
@@ -499,16 +499,16 @@
         </is>
       </c>
       <c r="B4" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="C4" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="D4" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="E4" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="F4" t="n">
         <v>1</v>
@@ -521,10 +521,10 @@
         </is>
       </c>
       <c r="B5" t="n">
-        <v>5</v>
+        <v>3</v>
       </c>
       <c r="C5" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="D5" t="n">
         <v>0</v>
@@ -543,19 +543,19 @@
         </is>
       </c>
       <c r="B6" t="n">
-        <v>24</v>
+        <v>13</v>
       </c>
       <c r="C6" t="n">
-        <v>9</v>
+        <v>14</v>
       </c>
       <c r="D6" t="n">
-        <v>8</v>
+        <v>4</v>
       </c>
       <c r="E6" t="n">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="F6" t="n">
-        <v>1</v>
+        <v>13</v>
       </c>
     </row>
     <row r="7">
@@ -571,10 +571,10 @@
         <v>0</v>
       </c>
       <c r="D7" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="E7" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="F7" t="n">
         <v>0</v>
@@ -587,19 +587,19 @@
         </is>
       </c>
       <c r="B8" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="C8" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="D8" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="E8" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="F8" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
     </row>
     <row r="9">
@@ -609,19 +609,19 @@
         </is>
       </c>
       <c r="B9" t="n">
-        <v>126</v>
+        <v>49</v>
       </c>
       <c r="C9" t="n">
-        <v>55</v>
+        <v>114</v>
       </c>
       <c r="D9" t="n">
-        <v>72</v>
+        <v>56</v>
       </c>
       <c r="E9" t="n">
-        <v>78</v>
+        <v>20</v>
       </c>
       <c r="F9" t="n">
-        <v>28</v>
+        <v>120</v>
       </c>
     </row>
     <row r="10">
@@ -631,19 +631,19 @@
         </is>
       </c>
       <c r="B10" t="n">
-        <v>220</v>
+        <v>103</v>
       </c>
       <c r="C10" t="n">
-        <v>34</v>
+        <v>132</v>
       </c>
       <c r="D10" t="n">
-        <v>182</v>
+        <v>153</v>
       </c>
       <c r="E10" t="n">
-        <v>41</v>
+        <v>30</v>
       </c>
       <c r="F10" t="n">
-        <v>43</v>
+        <v>102</v>
       </c>
     </row>
     <row r="11">
@@ -653,19 +653,19 @@
         </is>
       </c>
       <c r="B11" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="C11" t="n">
-        <v>7</v>
+        <v>1</v>
       </c>
       <c r="D11" t="n">
-        <v>25</v>
+        <v>9</v>
       </c>
       <c r="E11" t="n">
-        <v>5</v>
+        <v>2</v>
       </c>
       <c r="F11" t="n">
-        <v>2</v>
+        <v>28</v>
       </c>
     </row>
     <row r="12">
@@ -675,19 +675,19 @@
         </is>
       </c>
       <c r="B12" t="n">
-        <v>2</v>
+        <v>133</v>
       </c>
       <c r="C12" t="n">
-        <v>42</v>
+        <v>72</v>
       </c>
       <c r="D12" t="n">
-        <v>161</v>
+        <v>40</v>
       </c>
       <c r="E12" t="n">
-        <v>21</v>
+        <v>23</v>
       </c>
       <c r="F12" t="n">
-        <v>14</v>
+        <v>170</v>
       </c>
     </row>
     <row r="13">
@@ -697,19 +697,19 @@
         </is>
       </c>
       <c r="B13" t="n">
-        <v>146</v>
+        <v>96</v>
       </c>
       <c r="C13" t="n">
-        <v>46</v>
+        <v>52</v>
       </c>
       <c r="D13" t="n">
-        <v>117</v>
+        <v>24</v>
       </c>
       <c r="E13" t="n">
-        <v>16</v>
+        <v>9</v>
       </c>
       <c r="F13" t="n">
-        <v>6</v>
+        <v>150</v>
       </c>
     </row>
     <row r="14">
@@ -719,19 +719,19 @@
         </is>
       </c>
       <c r="B14" t="n">
-        <v>11</v>
+        <v>9</v>
       </c>
       <c r="C14" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="D14" t="n">
         <v>0</v>
       </c>
       <c r="E14" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="F14" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
     </row>
     <row r="15">
@@ -741,19 +741,19 @@
         </is>
       </c>
       <c r="B15" t="n">
-        <v>5</v>
+        <v>2</v>
       </c>
       <c r="C15" t="n">
-        <v>32</v>
+        <v>3</v>
       </c>
       <c r="D15" t="n">
-        <v>122</v>
+        <v>27</v>
       </c>
       <c r="E15" t="n">
-        <v>4</v>
+        <v>2</v>
       </c>
       <c r="F15" t="n">
-        <v>2</v>
+        <v>131</v>
       </c>
     </row>
     <row r="16">
@@ -763,19 +763,19 @@
         </is>
       </c>
       <c r="B16" t="n">
-        <v>4</v>
+        <v>2</v>
       </c>
       <c r="C16" t="n">
-        <v>54</v>
+        <v>6</v>
       </c>
       <c r="D16" t="n">
-        <v>119</v>
+        <v>53</v>
       </c>
       <c r="E16" t="n">
-        <v>17</v>
+        <v>13</v>
       </c>
       <c r="F16" t="n">
-        <v>12</v>
+        <v>132</v>
       </c>
     </row>
     <row r="17">
@@ -785,19 +785,19 @@
         </is>
       </c>
       <c r="B17" t="n">
+        <v>2</v>
+      </c>
+      <c r="C17" t="n">
+        <v>1</v>
+      </c>
+      <c r="D17" t="n">
+        <v>1</v>
+      </c>
+      <c r="E17" t="n">
+        <v>0</v>
+      </c>
+      <c r="F17" t="n">
         <v>3</v>
-      </c>
-      <c r="C17" t="n">
-        <v>2</v>
-      </c>
-      <c r="D17" t="n">
-        <v>1</v>
-      </c>
-      <c r="E17" t="n">
-        <v>0</v>
-      </c>
-      <c r="F17" t="n">
-        <v>1</v>
       </c>
     </row>
     <row r="18">
@@ -807,19 +807,19 @@
         </is>
       </c>
       <c r="B18" t="n">
-        <v>147</v>
+        <v>92</v>
       </c>
       <c r="C18" t="n">
-        <v>43</v>
+        <v>56</v>
       </c>
       <c r="D18" t="n">
-        <v>155</v>
+        <v>30</v>
       </c>
       <c r="E18" t="n">
-        <v>14</v>
+        <v>18</v>
       </c>
       <c r="F18" t="n">
-        <v>11</v>
+        <v>174</v>
       </c>
     </row>
     <row r="19">
@@ -829,19 +829,19 @@
         </is>
       </c>
       <c r="B19" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="C19" t="n">
         <v>1</v>
       </c>
       <c r="D19" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="E19" t="n">
         <v>0</v>
       </c>
       <c r="F19" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
     </row>
     <row r="20">
@@ -851,19 +851,19 @@
         </is>
       </c>
       <c r="B20" t="n">
-        <v>115</v>
+        <v>71</v>
       </c>
       <c r="C20" t="n">
-        <v>50</v>
+        <v>53</v>
       </c>
       <c r="D20" t="n">
-        <v>70</v>
+        <v>16</v>
       </c>
       <c r="E20" t="n">
-        <v>9</v>
+        <v>21</v>
       </c>
       <c r="F20" t="n">
-        <v>9</v>
+        <v>92</v>
       </c>
     </row>
     <row r="21">
@@ -873,19 +873,19 @@
         </is>
       </c>
       <c r="B21" t="n">
-        <v>211</v>
+        <v>125</v>
       </c>
       <c r="C21" t="n">
-        <v>91</v>
+        <v>100</v>
       </c>
       <c r="D21" t="n">
-        <v>136</v>
+        <v>59</v>
       </c>
       <c r="E21" t="n">
-        <v>21</v>
+        <v>22</v>
       </c>
       <c r="F21" t="n">
-        <v>15</v>
+        <v>168</v>
       </c>
     </row>
     <row r="22">
@@ -895,19 +895,19 @@
         </is>
       </c>
       <c r="B22" t="n">
-        <v>27</v>
+        <v>18</v>
       </c>
       <c r="C22" t="n">
-        <v>4</v>
+        <v>9</v>
       </c>
       <c r="D22" t="n">
-        <v>19</v>
+        <v>7</v>
       </c>
       <c r="E22" t="n">
-        <v>5</v>
+        <v>3</v>
       </c>
       <c r="F22" t="n">
-        <v>4</v>
+        <v>22</v>
       </c>
     </row>
     <row r="23">
@@ -920,16 +920,16 @@
         <v>7</v>
       </c>
       <c r="C23" t="n">
-        <v>4</v>
+        <v>1</v>
       </c>
       <c r="D23" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="E23" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="F23" t="n">
-        <v>0</v>
+        <v>6</v>
       </c>
     </row>
     <row r="24">
@@ -939,19 +939,19 @@
         </is>
       </c>
       <c r="B24" t="n">
+        <v>2</v>
+      </c>
+      <c r="C24" t="n">
         <v>6</v>
       </c>
-      <c r="C24" t="n">
-        <v>54</v>
-      </c>
       <c r="D24" t="n">
-        <v>86</v>
+        <v>42</v>
       </c>
       <c r="E24" t="n">
         <v>14</v>
       </c>
       <c r="F24" t="n">
-        <v>12</v>
+        <v>108</v>
       </c>
     </row>
     <row r="25">
@@ -964,16 +964,16 @@
         <v>3</v>
       </c>
       <c r="C25" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="D25" t="n">
-        <v>4</v>
+        <v>2</v>
       </c>
       <c r="E25" t="n">
         <v>1</v>
       </c>
       <c r="F25" t="n">
-        <v>0</v>
+        <v>3</v>
       </c>
     </row>
     <row r="26">
@@ -983,16 +983,16 @@
         </is>
       </c>
       <c r="B26" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="C26" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="D26" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="E26" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="F26" t="n">
         <v>1</v>
@@ -1005,19 +1005,19 @@
         </is>
       </c>
       <c r="B27" t="n">
-        <v>43</v>
+        <v>21</v>
       </c>
       <c r="C27" t="n">
-        <v>17</v>
+        <v>26</v>
       </c>
       <c r="D27" t="n">
-        <v>29</v>
+        <v>4</v>
       </c>
       <c r="E27" t="n">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="F27" t="n">
-        <v>5</v>
+        <v>44</v>
       </c>
     </row>
     <row r="28">
@@ -1027,19 +1027,19 @@
         </is>
       </c>
       <c r="B28" t="n">
-        <v>5</v>
+        <v>1</v>
       </c>
       <c r="C28" t="n">
-        <v>2</v>
+        <v>4</v>
       </c>
       <c r="D28" t="n">
         <v>4</v>
       </c>
       <c r="E28" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="F28" t="n">
-        <v>0</v>
+        <v>4</v>
       </c>
     </row>
     <row r="29">
@@ -1049,19 +1049,19 @@
         </is>
       </c>
       <c r="B29" t="n">
-        <v>91</v>
+        <v>46</v>
       </c>
       <c r="C29" t="n">
-        <v>25</v>
+        <v>52</v>
       </c>
       <c r="D29" t="n">
-        <v>59</v>
+        <v>29</v>
       </c>
       <c r="E29" t="n">
-        <v>15</v>
+        <v>13</v>
       </c>
       <c r="F29" t="n">
-        <v>11</v>
+        <v>61</v>
       </c>
     </row>
     <row r="30">
@@ -1071,19 +1071,19 @@
         </is>
       </c>
       <c r="B30" t="n">
-        <v>11</v>
+        <v>4</v>
       </c>
       <c r="C30" t="n">
-        <v>2</v>
+        <v>7</v>
       </c>
       <c r="D30" t="n">
-        <v>9</v>
+        <v>5</v>
       </c>
       <c r="E30" t="n">
         <v>0</v>
       </c>
       <c r="F30" t="n">
-        <v>0</v>
+        <v>6</v>
       </c>
     </row>
     <row r="31">
@@ -1093,19 +1093,19 @@
         </is>
       </c>
       <c r="B31" t="n">
-        <v>21</v>
+        <v>11</v>
       </c>
       <c r="C31" t="n">
-        <v>6</v>
+        <v>10</v>
       </c>
       <c r="D31" t="n">
-        <v>14</v>
+        <v>11</v>
       </c>
       <c r="E31" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="F31" t="n">
-        <v>1</v>
+        <v>9</v>
       </c>
     </row>
     <row r="32">
@@ -1115,16 +1115,16 @@
         </is>
       </c>
       <c r="B32" t="n">
-        <v>4</v>
+        <v>1</v>
       </c>
       <c r="C32" t="n">
-        <v>0</v>
+        <v>5</v>
       </c>
       <c r="D32" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="E32" t="n">
-        <v>5</v>
+        <v>2</v>
       </c>
       <c r="F32" t="n">
         <v>1</v>
@@ -1137,7 +1137,7 @@
         </is>
       </c>
       <c r="B33" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="C33" t="n">
         <v>1</v>
@@ -1149,7 +1149,7 @@
         <v>0</v>
       </c>
       <c r="F33" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
     </row>
     <row r="34">
@@ -1159,19 +1159,19 @@
         </is>
       </c>
       <c r="B34" t="n">
+        <v>34</v>
+      </c>
+      <c r="C34" t="n">
+        <v>23</v>
+      </c>
+      <c r="D34" t="n">
+        <v>21</v>
+      </c>
+      <c r="E34" t="n">
         <v>6</v>
       </c>
-      <c r="C34" t="n">
-        <v>7</v>
-      </c>
-      <c r="D34" t="n">
+      <c r="F34" t="n">
         <v>38</v>
-      </c>
-      <c r="E34" t="n">
-        <v>11</v>
-      </c>
-      <c r="F34" t="n">
-        <v>7</v>
       </c>
     </row>
     <row r="35">
@@ -1181,19 +1181,19 @@
         </is>
       </c>
       <c r="B35" t="n">
-        <v>97</v>
+        <v>59</v>
       </c>
       <c r="C35" t="n">
-        <v>35</v>
+        <v>51</v>
       </c>
       <c r="D35" t="n">
-        <v>83</v>
+        <v>22</v>
       </c>
       <c r="E35" t="n">
-        <v>19</v>
+        <v>17</v>
       </c>
       <c r="F35" t="n">
-        <v>7</v>
+        <v>92</v>
       </c>
     </row>
     <row r="36">
@@ -1203,19 +1203,19 @@
         </is>
       </c>
       <c r="B36" t="n">
-        <v>15</v>
+        <v>12</v>
       </c>
       <c r="C36" t="n">
-        <v>6</v>
+        <v>3</v>
       </c>
       <c r="D36" t="n">
-        <v>9</v>
+        <v>3</v>
       </c>
       <c r="E36" t="n">
         <v>1</v>
       </c>
       <c r="F36" t="n">
-        <v>0</v>
+        <v>12</v>
       </c>
     </row>
   </sheetData>
